--- a/output_orderan.xlsx
+++ b/output_orderan.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="445" uniqueCount="228">
   <si>
     <t>DATE</t>
   </si>
@@ -46,155 +46,880 @@
     <t>PHONE</t>
   </si>
   <si>
+    <t>06 febuary 2026</t>
+  </si>
+  <si>
+    <t>7 / 3 / 2026</t>
+  </si>
+  <si>
+    <t>06 feb 2026</t>
+  </si>
+  <si>
+    <t>06 febuari 2026</t>
+  </si>
+  <si>
+    <t>07 febuari 2026</t>
+  </si>
+  <si>
+    <t>08 februari 2025</t>
+  </si>
+  <si>
+    <t>09 feb</t>
+  </si>
+  <si>
+    <t>9 februari 2026</t>
+  </si>
+  <si>
+    <t>10 / 02 / 2026</t>
+  </si>
+  <si>
+    <t>11 februari 2026</t>
+  </si>
+  <si>
     <t>12 februari 2026</t>
   </si>
   <si>
-    <t>12 / 2 / 2026</t>
-  </si>
-  <si>
-    <t>12 / 2 / 2026 ]</t>
-  </si>
-  <si>
-    <t>21 : 00 12 / 2 / 2026</t>
+    <t>12 / 02 / 2026</t>
+  </si>
+  <si>
+    <t>12 feb 26</t>
+  </si>
+  <si>
+    <t>3 maret 2026</t>
+  </si>
+  <si>
+    <t>03 : 00 04032026</t>
+  </si>
+  <si>
+    <t>03 maret 2026</t>
+  </si>
+  <si>
+    <t>04 maret 2026</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>5</t>
   </si>
   <si>
     <t>1</t>
   </si>
   <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>2</t>
+    <t>8</t>
+  </si>
+  <si>
+    <t>twb</t>
+  </si>
+  <si>
+    <t>wb</t>
   </si>
   <si>
     <t>cddl</t>
   </si>
   <si>
-    <t>twb</t>
+    <t>cddl cbm</t>
+  </si>
+  <si>
+    <t>tronton</t>
+  </si>
+  <si>
+    <t>twb cbm</t>
+  </si>
+  <si>
+    <t>argopantes</t>
+  </si>
+  <si>
+    <t>cikokol</t>
   </si>
   <si>
     <t>megahub</t>
   </si>
   <si>
-    <t>argopantes</t>
-  </si>
-  <si>
-    <t>cikokol</t>
-  </si>
-  <si>
-    <t>cgk jepara</t>
+    <t>argo pantes</t>
+  </si>
+  <si>
+    <t>jne sub</t>
+  </si>
+  <si>
+    <t>subcgk</t>
   </si>
   <si>
     <t>cgk sub</t>
   </si>
   <si>
-    <t>karyadi</t>
-  </si>
-  <si>
-    <t>m syaichoni</t>
-  </si>
-  <si>
-    <t>agus</t>
-  </si>
-  <si>
-    <t>ad 8517 ba</t>
-  </si>
-  <si>
-    <t>b 9999 rfy</t>
-  </si>
-  <si>
-    <t>n 8872 rk</t>
-  </si>
-  <si>
-    <t>w 1111 sip</t>
-  </si>
-  <si>
-    <t>d 9667 af</t>
-  </si>
-  <si>
-    <t>10 : 00</t>
+    <t>cgk mes</t>
+  </si>
+  <si>
+    <t>cgk pku</t>
+  </si>
+  <si>
+    <t>srg sub</t>
+  </si>
+  <si>
+    <t>jne srg</t>
+  </si>
+  <si>
+    <t>srgcgk</t>
+  </si>
+  <si>
+    <t>cgk dps</t>
+  </si>
+  <si>
+    <t>cgk</t>
+  </si>
+  <si>
+    <t>cikarang</t>
+  </si>
+  <si>
+    <t>ckrsubsux</t>
+  </si>
+  <si>
+    <t>cgkjbr</t>
+  </si>
+  <si>
+    <t>tronton cbm</t>
+  </si>
+  <si>
+    <t>mes ddriver</t>
+  </si>
+  <si>
+    <t>sub cgk</t>
+  </si>
+  <si>
+    <t>cgk jatim</t>
+  </si>
+  <si>
+    <t>cgk jateng tentatif</t>
+  </si>
+  <si>
+    <t>wahyudi</t>
+  </si>
+  <si>
+    <t>sofyan</t>
+  </si>
+  <si>
+    <t>akbar</t>
+  </si>
+  <si>
+    <t>chandra</t>
+  </si>
+  <si>
+    <t>sentot</t>
+  </si>
+  <si>
+    <t>purwanto</t>
+  </si>
+  <si>
+    <t>didik</t>
+  </si>
+  <si>
+    <t>haryono</t>
+  </si>
+  <si>
+    <t>hermanto</t>
+  </si>
+  <si>
+    <t>wijaya</t>
+  </si>
+  <si>
+    <t>darmawan</t>
+  </si>
+  <si>
+    <t>arif r</t>
+  </si>
+  <si>
+    <t>yuda</t>
+  </si>
+  <si>
+    <t>aldi</t>
+  </si>
+  <si>
+    <t>supriadi</t>
+  </si>
+  <si>
+    <t>syafrizal</t>
+  </si>
+  <si>
+    <t>nizar</t>
+  </si>
+  <si>
+    <t>samosir</t>
+  </si>
+  <si>
+    <t>joni</t>
+  </si>
+  <si>
+    <t>nasip k</t>
+  </si>
+  <si>
+    <t>ageng</t>
+  </si>
+  <si>
+    <t>ilham wahyudi</t>
+  </si>
+  <si>
+    <t>sri mardono</t>
+  </si>
+  <si>
+    <t>rosyit</t>
+  </si>
+  <si>
+    <t>m . ibnu</t>
+  </si>
+  <si>
+    <t>akiyat</t>
+  </si>
+  <si>
+    <t>ahmad wahyudi</t>
+  </si>
+  <si>
+    <t>ari purnama</t>
+  </si>
+  <si>
+    <t>dedeng</t>
+  </si>
+  <si>
+    <t>jupri</t>
+  </si>
+  <si>
+    <t>andi</t>
+  </si>
+  <si>
+    <t>n 9549 ua</t>
+  </si>
+  <si>
+    <t>b 9679 wt</t>
+  </si>
+  <si>
+    <t>l 8601 uh</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>b 9891 beu</t>
+  </si>
+  <si>
+    <t>b 9687 jm</t>
+  </si>
+  <si>
+    <t>b 8745 amr</t>
+  </si>
+  <si>
+    <t>s 8635 nj</t>
+  </si>
+  <si>
+    <t>h 9948 ra</t>
+  </si>
+  <si>
+    <t>ba 8829 bu</t>
+  </si>
+  <si>
+    <t>b 9787 xx</t>
+  </si>
+  <si>
+    <t>w 8973 uq</t>
+  </si>
+  <si>
+    <t>bm 8350 au</t>
+  </si>
+  <si>
+    <t>b 9586 txv</t>
+  </si>
+  <si>
+    <t>bm 8479 au</t>
+  </si>
+  <si>
+    <t>b 9172 scp</t>
+  </si>
+  <si>
+    <t>b 9727 uex</t>
+  </si>
+  <si>
+    <t>b 9169 uex</t>
+  </si>
+  <si>
+    <t>bh 8165 qi</t>
+  </si>
+  <si>
+    <t>b9654yu</t>
+  </si>
+  <si>
+    <t>f 9647 fh</t>
+  </si>
+  <si>
+    <t>bk 8678 ve</t>
+  </si>
+  <si>
+    <t>b 9654 yu</t>
+  </si>
+  <si>
+    <t>b 9563 teu</t>
+  </si>
+  <si>
+    <t>l 9511 al</t>
+  </si>
+  <si>
+    <t>l 9722 ue</t>
+  </si>
+  <si>
+    <t>w 8323 nv</t>
+  </si>
+  <si>
+    <t>b 9679wt</t>
+  </si>
+  <si>
+    <t>b 9383 txv</t>
+  </si>
+  <si>
+    <t>e 9426 aa</t>
+  </si>
+  <si>
+    <t>bm 9273 ro</t>
+  </si>
+  <si>
+    <t>be 8610 db</t>
   </si>
   <si>
     <t>segera</t>
   </si>
   <si>
-    <t>18 : 00</t>
-  </si>
-  <si>
-    <t>[08.10, 12/2/2026] Admin Rafay: REQUEST ORDER ONCALL 12 FEBRUARI 2026:
+    <t>07 : 00</t>
+  </si>
+  <si>
+    <t>02 : 00</t>
+  </si>
+  <si>
+    <t>03 : 00</t>
+  </si>
+  <si>
+    <t>[05.31, 7/3/2026] Akbar Rafay: Request Unit On Call Tgl 06 febuary 2026
+2 unit twb 50 CBM
+Lokasi : JNE SUB</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA 7/3/2026
+Rute/tujuan : SUB-CGK
+driver  : WAHYUDI
+Nopol  : N 9549 UA
+No hp  :085784422398</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA 7/3/2026
+Rute/tujuan : SUB-CGK
+driver  : SOFYAN
+Nopol  : B 9679 WT
+No hp  : 082231837381</t>
+  </si>
+  <si>
+    <t>[05.31, 7/3/2026] Akbar Rafay: REQUEST ORDER ULANG ONCALL
+06 FEB 2026
+6 UNIT WB/50 CBM
+Lokasi : ARGOPANTES</t>
+  </si>
+  <si>
+    <t>[05.31, 7/3/2026] REQUEST ORDER KHUSUS 07-02-2026</t>
+  </si>
+  <si>
+    <t>Waktu loading : 07:00
+Rute/tujuan : CGK - SUB
+driver  : Chandra
+Nopol  : L 8601 UH
+No hp  : +62 852-3168-1470</t>
+  </si>
+  <si>
+    <t>[05.31, 7/3/2026] Akbar Rafay: REQUEST ORDER ULANG ONCALL
+06 FEB 2026
+10 UNIT CDDL/24 CBM
+Lokasi : ARGOPANTES</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA 7/3/2026
+Rute/tujuan : CGK - JATIM TENTATIF
 RAFAY
-1 UNIT CDDL 24 CBM
-Lokasi : MEGAHUB</t>
-  </si>
-  <si>
-    <t>Waktu loading : 10:00 12/2/2026
-Rute/tujuan : CGK - JEPARA
-driver  : KARYADI
-Nopol  : AD 8517 BA
-No hp  : 085865762797</t>
-  </si>
-  <si>
-    <t>[08.45, 12/2/2026] Admin Rafay:
-Pak, revisi untuk unit jam 10:00 ya. Truknya mogok ganti unit lain.
-driver : KARYADI
-Nopol : B 9999 RFY</t>
-  </si>
-  <si>
-    <t>[09.05, 12/2/2026] Admin Rafay: REQUEST ORDER ULANG ONCALL
+3 unit TWB 50 Cbm
+Lokasi : ARGOPANTES
+Rute/ tuj : CGK - MES</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA 7/3/2026
+DRIVER 1 : SENTOT
+NOPOL    : B 9231 CEU
+NOHP      :+62 812-8714-7789</t>
+  </si>
+  <si>
+    <t>[05.31, 7/3/2026] Akbar Rafay: REQUEST ORDER ONCAL
+06 FEBUARI 2026
+5 unit TWB 50 Cbm
+Lokasi : ARGOPANTES
+Rute/ tuj : CGK - SUB</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA 7/3/2026
+RAFAY
+DRIVER 1 : PURWANTO
+NOPOL    : B 9891 BEU
+NOHP      :083142142113</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA 7/3/2026
+DRIVER : DIDIK
+NOPOL    : B 9687 JM
+NOHP      :085385220743</t>
+  </si>
+  <si>
+    <t>[05.31, 7/3/2026] Akbar Rafay: REQUEST ORDER ONCAL
+06 FEBUARI 2026
+Lokasi : ARGOPANTES
+Rute/ tuj : CGK - PKU</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA 7/3/2026
+DRIVER 1 : Haryono
+NOPOL    : B 8745 AMR
+NO HP      : 083166684195</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA 7/3/2026
+DRIVER : HERMANTO
+NOPOL : S 8635 NJ
+NOHP :085194592825</t>
+  </si>
+  <si>
+    <t>[05.31, 7/3/2026] Akbar Rafay: REQUEST ORDER ONCAL
+07 FEBUARI 2026
+RAFAY
+1 unit CDDL 24 Cbm
+Lokasi : SEMARANG
+Rute/ tuj : SRG - SUB</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA 7/3/2026
+DRIVER 1 :Agung
+DRIVER 2 :Wijaya
+NOPOL    :H 9948 RA
+NOHP      :0882016641381</t>
+  </si>
+  <si>
+    <t>[05.31, 7/3/2026] Akbar Rafay: REQUEST ORDER ONCALL 08 FEBRUARI 2025:
 3 UNIT TWB 50 CBM
 Lokasi : ARGOPANTES</t>
   </si>
   <si>
-    <t>Waktu loading : SEGERA 12/2/2026
+    <t>Waktu loading : SEGERA 7/3/2026
+Rute/tujuan : CGK - MES
+driver  : DARMAWAN
+Nopol  : BA 8829 BU
+No hp  :082363564665</t>
+  </si>
+  <si>
+    <t>[05.31, 7/3/2026] Akbar Rafay: Request Order Oncall Tgl 09 Feb
+1 UNIT CDDL 24 CBM
+Lokasi  : JNE SRG</t>
+  </si>
+  <si>
+    <t>Waktu loading : 22:00 7/3/2026
+Rute/tujuan : SRG-CGK
+Driver : Arif R
+Nopol :B 9787 XX
+No hp :089690885555</t>
+  </si>
+  <si>
+    <t>[05.31, 7/3/2026] Akbar Rafay: REQUEST ORDER  ONCALL 9 FEBRUARI 2026:
+2 unit TWB 50 Cbm
+Lokasi : cikokol</t>
+  </si>
+  <si>
+    <t>[05.31, 7/3/2026] REQUEST ORDER KHUSUS 10/02/2026</t>
+  </si>
+  <si>
+    <t>Waktu loading : 02:00
 Rute/tujuan : CGK - SUB
-driver :
-Nopol :
-No hp :</t>
-  </si>
-  <si>
-    <t>Waktu loading : 18:00 12/2/2026
-driver : M SYAICHONI
-Nopol : N 8872 RK
-No hp : 081231895971</t>
-  </si>
-  <si>
-    <t>Waktu loading : 21:00 12/2/2026
-driver :
-Nopol :
-No hp :</t>
-  </si>
-  <si>
-    <t>[09.30, 12/2/2026] Vendor Anggota:
-Update plat nomer yg jam 18:00 pak
-Nopol : W 1111 SIP
-No hp : 08111222333</t>
-  </si>
-  <si>
-    <t>[10.45, 12/2/2026] Admin Rafay: REQUEST TAMBAHAN ORDER
-2 UNIT TWB 50 CBM
-Lokasi : CIKOKOL</t>
-  </si>
-  <si>
-    <t>Waktu loading : SEGERA 12/2/2026
+NAMA : WAHYUDI
+NOPOL: N 9549 UA
+NO HP :085784422398</t>
+  </si>
+  <si>
+    <t>Waktu loading : 03:00
+NAMA : YUDA
+NOPOL: W 8973 UQ
+NO HP :089507296985</t>
+  </si>
+  <si>
+    <t>[05.31, 7/3/2026] Akbar Rafay: REQUEST ORDER  ONCALL 9 FEBRUARI 2026:
+2 unit  TWB 50 Cbm
+Lokasi : Cikokol</t>
+  </si>
+  <si>
+    <t>Waktu loading : 02:00
+Rute/tujuan : CGK - PKU
+NAMA : ALDI
+NOPOL: BM 8350 AU
+NO HP :0831-6761-0479</t>
+  </si>
+  <si>
+    <t>Waktu loading : 03:00
+NAMA :
+NOPOL:
+NO HP :</t>
+  </si>
+  <si>
+    <t>Waktu loading : 02:00 7/3/2026
+Rute/tujuan : SRG-CGK
+Driver : Supriadi
+Nopol : B 9586 TXV
+No hp :081350529712</t>
+  </si>
+  <si>
+    <t>Waktu loading : 02:00
+Rute/tujuan : CGK - PKU</t>
+  </si>
+  <si>
+    <t>Waktu loading : 03:00
+NAMA : SYAFRIZAL
+NOPOL: BM 8479 AU
+NO HP :082170733190</t>
+  </si>
+  <si>
+    <t>[05.31, 7/3/2026] Akbar Rafay: REQUEST ORDER  ONCALL 9 FEBRUARI 2026:
+RAFAY
+2 unit  TWB 50 Cbm
+Lokasi : Cikokol
+Rute/tujuan : CGK - PKU</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA 7/3/2026
+NAMA : SYAFRIZAL
+NOPOL: BM 8479 AU
+NO HP :082170733190</t>
+  </si>
+  <si>
+    <t>[05.31, 7/3/2026] Akbar Rafay: REQUEST ORDER ONCALL 11 FEBRUARI 2026:
+1 unit Cddl 24 Cbm
+Lokasi : Megahub</t>
+  </si>
+  <si>
+    <t>Waktu loading : 00:00 7/3/2026
+Rute/tujuan : CGK - DPS
+driver  :Nizar
+Nopol  :B 9172 SCP
+No hp  :081313444015</t>
+  </si>
+  <si>
+    <t>[05.31, 7/3/2026] Akbar Rafay: REQUEST ORDER ONCALL 11 FEBRUARI 2026:
+3 unit tronton 50 Cbm
+Lokasi : cikokol</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA 7/3/2026
+Rute/tujuan : CGK - MES</t>
+  </si>
+  <si>
+    <t>Waktu loading : 09:00 7/3/2026
+Driver : SAMOSIR
+Nopol : B 9727 UEX
+Hp :+62 822-7429-6236</t>
+  </si>
+  <si>
+    <t>Waktu loading : 12:00 7/3/2026
+Driver : JONI
+Nopol : B 9169 UEX
+Hp :+62 822-7638-5077</t>
+  </si>
+  <si>
+    <t>[05.31, 7/3/2026] Akbar Rafay: REQUEST ORDER TAMBAHAN ONCALL  12 FEBRUARI 2026:
+1 unit TRONTON 50 Cbm
+Lokasi : cikokol</t>
+  </si>
+  <si>
+    <t>[05.31, 7/3/2026] REQUEST ORDER KHUSUS 12/02/2026</t>
+  </si>
+  <si>
+    <t>Waktu loading : 02:00
+Rute/tujuan : CGK - PKU
+Nama 	: NASIP K
+Nopol		: BH 8165 QI
+No Tlp		:‪+6281272463920</t>
+  </si>
+  <si>
+    <t>[05.31, 7/3/2026] Akbar Rafay: Request Unit On Call Tgl 12 Feb 26
+1 Unit  TWB 50 Cbm
+Lokasi : Cikarang</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA 7/3/2026
+Rute/tujuan : CKR-SUB-SUX 
+Driver   : AGENG
+Nopol  : B9654YU
+No Hp  : +62 857-0738-0584</t>
+  </si>
+  <si>
+    <t>[05.31, 7/3/2026] Akbar Rafay: Request Unit On Call Tgl 12 Feb 26
+1 Unit  Cddl / 24 Cbm
+Lokasi : Cikokol + Cikarang</t>
+  </si>
+  <si>
+    <t>Waktu loading : 03:00 7/3/2026
+Rute/tujuan : CGK-JBR
+No pol.   : F 9647 FH
+Driver. 1 :  Jatmiyanta
+No hp :  : 082118558105
+Driver 2  : Ilham Wahyudi
+No hp.    : 089519041791</t>
+  </si>
+  <si>
+    <t>[05.31, 7/3/2026] Akbar Rafay: REQUEST ORDER ONCALL 12 FEBRUARI 2026:
+RAFAY
+3 unit tronton 50 Cbm
+Lokasi : cikokol</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA 7/3/2026
+Rute/tujuan : CGK - MES
+driver  : SRI MARDONO
+Nopol  : BK 8678 VE
+No hp  :085218843366</t>
+  </si>
+  <si>
+    <t>[05.31, 7/3/2026] Akbar Rafay: REQUEST ORDER ONCALL 12 FEBRUARI 2026:
+2 unit tronton 50 Cbm
+Lokasi : cikokol</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA 7/3/2026
 Rute/tujuan : CGK - SUB
-driver : AGUS
-Nopol : D 9667 AF
-No hp : 08817021866</t>
-  </si>
-  <si>
-    <t>085865762797</t>
-  </si>
-  <si>
-    <t>08</t>
-  </si>
-  <si>
-    <t>081231895971</t>
-  </si>
-  <si>
-    <t>08111222333</t>
-  </si>
-  <si>
-    <t>08817021866</t>
+driver  : AGENG
+Nopol  : B 9654 YU
+No hp  : +62 857-0738-0584</t>
+  </si>
+  <si>
+    <t>[05.31, 7/3/2026] Akbar Rafay: REQUEST ORDER ONCALL 12 FEBRUARI 2026:
+3 UNIT TWB 50 Cbm
+Lokasi : ARGOPANTES</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA 7/3/2026
+Rute/tujuan : CGK - SUB
+driver  : Rosyit
+Nopol  : B 9563 TEU
+No hp  : 082313572678</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA 7/3/2026
+Rute/tujuan : CGK - SUB
+driver  : M.ibnu
+Nopol  : L 9511 AL
+No hp  : 082191633212</t>
+  </si>
+  <si>
+    <t>Waktu loading : 03:00 7/3/2026
+Rute/tujuan : CGK - SUB
+driver  : Akiyat
+Nopol  : L 9722 UE
+No hp  :081281122738</t>
+  </si>
+  <si>
+    <t>Waktu loading : 03:00 7/3/2026
+Rute/tujuan : CGK - SUB
+Revisi
+driver  : Ahmad Wahyudi
+Nopol  : W 8323 NV
+No hp  : 085792725002
+Posisi sudah dilokasi muat</t>
+  </si>
+  <si>
+    <t>[05.31, 7/3/2026] REQUEST  ORDER  ONCALL  3 MARET 2026
+5 UNIT WB/50 CBM
+Lokasi : ARGOPANTES</t>
+  </si>
+  <si>
+    <t>Waktu loading : 23:00 3 MARET 2026
+Rute/tujuan : CGK - MES 
+ddriver  : Sri Mardono
+Nopol  : BK 8678 VE
+No hp  : 085218843366</t>
+  </si>
+  <si>
+    <t>Waktu loading : 03:00 04-03-2026
+Rute/tujuan : CGK - MES 
+driver  :
+Nopol  :
+No hp  :</t>
+  </si>
+  <si>
+    <t>[05.31, 7/3/2026] REQUEST  ORDER  ONCALL  3 MARET 2026
+6 UNIT WB/50 CBM
+Lokasi : ARGOPANTES</t>
+  </si>
+  <si>
+    <t>Waktu loading : 23:00 3 MARET 2026
+Rute/tujuan : CGK - SUB 
+driver  : Rosyit
+Nopol  : B 9562 TEU
+No hp  : 082313572678
+Driver : sofyan
+Nopol : B 9679WT
+No Hp : 082231837381</t>
+  </si>
+  <si>
+    <t>[05.31, 7/3/2026] REQUEST  ORDER  ONCALL  3 MARET 2026
+1 UNIT WB/50 CBM
+Lokasi : ARGOPANTES</t>
+  </si>
+  <si>
+    <t>Waktu loading : 23:00 3 MARET 2026
+Rute/tujuan : SUB - CGK
+driver  : Yuda
+Nopol  : W 8973 UQ
+No hp  : 089507296985</t>
+  </si>
+  <si>
+    <t>[05.31, 7/3/2026] REQUEST ORDER ONCALL 03 maret 2026:
+3 unit Cddl 24 Cbm
+Lokasi : Megahub</t>
+  </si>
+  <si>
+    <t>Waktu loading : 23:00 03 maret 2026
+Rute/tujuan : CGK - JATIM
+driver  : Ari purnama
+Nopol  : B 9383 TXV
+No hp : 082136689169
+Fyi pak  @Nomor tidak dikenal@Nomor tidak dikenal</t>
+  </si>
+  <si>
+    <t>[05.31, 7/3/2026] REQUEST ULANG ORDER ONCALL 04 MARET 2026:
+8 unit Cddl 24 Cbm
+Lokasi : *argo pantes *</t>
+  </si>
+  <si>
+    <t>[05.31, 7/3/2026] Waktu loading : SEGERA 04 MARET 2026
+Rute/tujuan : *CGK - Jateng tentatif
+Nama : Dedeng
+Nopol :E 9426 Aa
+No.hp : 0895393659401
+Request Unit On Call Tgl 04 Maret 2026
+5 UNIT TWB 50 CBM
+Lokasi : ARGOPANTES</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA 04 Maret 2026
+Rute/tujuan : CGK - PKU
+driver  : Jupri
+Nopol  : BM 9273 RO
+No Hp :082172471454</t>
+  </si>
+  <si>
+    <t>[05.31, 7/3/2026] REQUEST ORDER ONCALL
+04 MARET 2026:
+5 UNIT TWB 50 CBM
+Lokasi : ARGOPANTES</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA 04 Maret 2026
+Rute/tujuan : CGK - MES
+driver  : Andi
+Nopol  : BE 8610 DB
+No Hp :081374328877</t>
+  </si>
+  <si>
+    <t>085784422398</t>
+  </si>
+  <si>
+    <t>082231837381</t>
+  </si>
+  <si>
+    <t>07022026</t>
+  </si>
+  <si>
+    <t>0 85231681470</t>
+  </si>
+  <si>
+    <t>083142142113</t>
+  </si>
+  <si>
+    <t>085385220743</t>
+  </si>
+  <si>
+    <t>083166684195</t>
+  </si>
+  <si>
+    <t>085194592825</t>
+  </si>
+  <si>
+    <t>0882016641381</t>
+  </si>
+  <si>
+    <t>082363564665</t>
+  </si>
+  <si>
+    <t>089690885555</t>
+  </si>
+  <si>
+    <t>089507296985</t>
+  </si>
+  <si>
+    <t>083167610479</t>
+  </si>
+  <si>
+    <t>081350529712</t>
+  </si>
+  <si>
+    <t>082170733190</t>
+  </si>
+  <si>
+    <t>081313444015</t>
+  </si>
+  <si>
+    <t>0 82274296236</t>
+  </si>
+  <si>
+    <t>0 82276385077</t>
+  </si>
+  <si>
+    <t>081272463920</t>
+  </si>
+  <si>
+    <t>0 85707380584</t>
+  </si>
+  <si>
+    <t>089519041791</t>
+  </si>
+  <si>
+    <t>085218843366</t>
+  </si>
+  <si>
+    <t>082313572678</t>
+  </si>
+  <si>
+    <t>082191633212</t>
+  </si>
+  <si>
+    <t>081281122738</t>
+  </si>
+  <si>
+    <t>085792725002</t>
+  </si>
+  <si>
+    <t>082136689169</t>
+  </si>
+  <si>
+    <t>0895393659401</t>
+  </si>
+  <si>
+    <t>082172471454</t>
+  </si>
+  <si>
+    <t>081374328877</t>
   </si>
 </sst>
 </file>
@@ -552,7 +1277,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:J83"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:10">
@@ -592,16 +1317,16 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2" t="s">
-        <v>19</v>
+        <v>34</v>
+      </c>
+      <c r="E2" t="s">
+        <v>44</v>
       </c>
       <c r="I2" t="s">
-        <v>35</v>
+        <v>129</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -609,112 +1334,130 @@
         <v>11</v>
       </c>
       <c r="E3" t="s">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="F3" t="s">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="G3" t="s">
-        <v>27</v>
+        <v>93</v>
+      </c>
+      <c r="H3" t="s">
+        <v>125</v>
       </c>
       <c r="I3" t="s">
-        <v>36</v>
+        <v>130</v>
       </c>
       <c r="J3" t="s">
-        <v>45</v>
+        <v>198</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" t="s">
-        <v>24</v>
-      </c>
-      <c r="G4" t="s">
-        <v>28</v>
-      </c>
-      <c r="H4" t="s">
-        <v>32</v>
+        <v>10</v>
+      </c>
+      <c r="B4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E4" t="s">
+        <v>44</v>
       </c>
       <c r="I4" t="s">
-        <v>37</v>
-      </c>
-      <c r="J4" t="s">
-        <v>46</v>
+        <v>129</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
         <v>11</v>
       </c>
-      <c r="B5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" t="s">
-        <v>20</v>
+      <c r="E5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F5" t="s">
+        <v>63</v>
+      </c>
+      <c r="G5" t="s">
+        <v>94</v>
+      </c>
+      <c r="H5" t="s">
+        <v>125</v>
       </c>
       <c r="I5" t="s">
-        <v>38</v>
+        <v>131</v>
+      </c>
+      <c r="J5" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E6" t="s">
-        <v>23</v>
-      </c>
-      <c r="H6" t="s">
-        <v>33</v>
+        <v>12</v>
+      </c>
+      <c r="B6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D6" t="s">
+        <v>40</v>
+      </c>
+      <c r="F6" t="s">
+        <v>64</v>
       </c>
       <c r="I6" t="s">
-        <v>39</v>
+        <v>132</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
         <v>11</v>
       </c>
-      <c r="F7" t="s">
-        <v>25</v>
-      </c>
-      <c r="G7" t="s">
-        <v>29</v>
-      </c>
       <c r="I7" t="s">
-        <v>40</v>
+        <v>133</v>
       </c>
       <c r="J7" t="s">
-        <v>47</v>
+        <v>200</v>
       </c>
     </row>
     <row r="8" spans="1:10">
-      <c r="A8" t="s">
-        <v>13</v>
+      <c r="E8" t="s">
+        <v>46</v>
+      </c>
+      <c r="F8" t="s">
+        <v>65</v>
+      </c>
+      <c r="G8" t="s">
+        <v>95</v>
+      </c>
+      <c r="H8" t="s">
+        <v>126</v>
       </c>
       <c r="I8" t="s">
-        <v>41</v>
+        <v>134</v>
+      </c>
+      <c r="J8" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" t="s">
         <v>12</v>
       </c>
-      <c r="G9" t="s">
-        <v>30</v>
-      </c>
-      <c r="H9" t="s">
-        <v>34</v>
+      <c r="B9" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" t="s">
+        <v>36</v>
+      </c>
+      <c r="D9" t="s">
+        <v>40</v>
       </c>
       <c r="I9" t="s">
-        <v>42</v>
-      </c>
-      <c r="J9" t="s">
-        <v>48</v>
+        <v>135</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -722,39 +1465,1320 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C10" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="D10" t="s">
-        <v>21</v>
+        <v>40</v>
+      </c>
+      <c r="E10" t="s">
+        <v>47</v>
+      </c>
+      <c r="H10" t="s">
+        <v>125</v>
       </c>
       <c r="I10" t="s">
-        <v>43</v>
+        <v>136</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" t="s">
         <v>11</v>
       </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
+        <v>66</v>
+      </c>
+      <c r="G11" t="s">
+        <v>96</v>
+      </c>
+      <c r="H11" t="s">
+        <v>125</v>
+      </c>
+      <c r="I11" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12" t="s">
+        <v>34</v>
+      </c>
+      <c r="D12" t="s">
+        <v>40</v>
+      </c>
+      <c r="E12" t="s">
+        <v>46</v>
+      </c>
+      <c r="I12" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" t="s">
+        <v>11</v>
+      </c>
+      <c r="F13" t="s">
+        <v>67</v>
+      </c>
+      <c r="G13" t="s">
+        <v>97</v>
+      </c>
+      <c r="H13" t="s">
+        <v>125</v>
+      </c>
+      <c r="I13" t="s">
+        <v>139</v>
+      </c>
+      <c r="J13" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>31</v>
+      </c>
+      <c r="C14" t="s">
+        <v>34</v>
+      </c>
+      <c r="D14" t="s">
+        <v>40</v>
+      </c>
+      <c r="E14" t="s">
+        <v>46</v>
+      </c>
+      <c r="I14" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" t="s">
+        <v>11</v>
+      </c>
+      <c r="F15" t="s">
+        <v>68</v>
+      </c>
+      <c r="G15" t="s">
+        <v>98</v>
+      </c>
+      <c r="H15" t="s">
+        <v>125</v>
+      </c>
+      <c r="I15" t="s">
+        <v>140</v>
+      </c>
+      <c r="J15" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" t="s">
+        <v>13</v>
+      </c>
+      <c r="D16" t="s">
+        <v>40</v>
+      </c>
+      <c r="E16" t="s">
+        <v>48</v>
+      </c>
+      <c r="F16" t="s">
+        <v>64</v>
+      </c>
+      <c r="I16" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="A17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F17" t="s">
+        <v>69</v>
+      </c>
+      <c r="G17" t="s">
+        <v>99</v>
+      </c>
+      <c r="H17" t="s">
+        <v>125</v>
+      </c>
+      <c r="I17" t="s">
+        <v>142</v>
+      </c>
+      <c r="J17" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="A18" t="s">
+        <v>13</v>
+      </c>
+      <c r="B18" t="s">
+        <v>31</v>
+      </c>
+      <c r="C18" t="s">
+        <v>34</v>
+      </c>
+      <c r="D18" t="s">
+        <v>40</v>
+      </c>
+      <c r="E18" t="s">
+        <v>46</v>
+      </c>
+      <c r="I18" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
+      <c r="A19" t="s">
+        <v>11</v>
+      </c>
+      <c r="F19" t="s">
+        <v>70</v>
+      </c>
+      <c r="G19" t="s">
+        <v>100</v>
+      </c>
+      <c r="H19" t="s">
+        <v>125</v>
+      </c>
+      <c r="I19" t="s">
+        <v>143</v>
+      </c>
+      <c r="J19" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="A20" t="s">
+        <v>14</v>
+      </c>
+      <c r="B20" t="s">
+        <v>32</v>
+      </c>
+      <c r="C20" t="s">
+        <v>37</v>
+      </c>
+      <c r="E20" t="s">
+        <v>49</v>
+      </c>
+      <c r="I20" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="A21" t="s">
+        <v>11</v>
+      </c>
+      <c r="F21" t="s">
+        <v>71</v>
+      </c>
+      <c r="G21" t="s">
+        <v>101</v>
+      </c>
+      <c r="H21" t="s">
+        <v>125</v>
+      </c>
+      <c r="I21" t="s">
+        <v>145</v>
+      </c>
+      <c r="J21" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
+      <c r="A22" t="s">
+        <v>15</v>
+      </c>
+      <c r="B22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C22" t="s">
+        <v>34</v>
+      </c>
+      <c r="D22" t="s">
+        <v>40</v>
+      </c>
+      <c r="I22" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
+      <c r="A23" t="s">
+        <v>11</v>
+      </c>
+      <c r="E23" t="s">
+        <v>47</v>
+      </c>
+      <c r="F23" t="s">
+        <v>72</v>
+      </c>
+      <c r="G23" t="s">
+        <v>102</v>
+      </c>
+      <c r="H23" t="s">
+        <v>125</v>
+      </c>
+      <c r="I23" t="s">
+        <v>147</v>
+      </c>
+      <c r="J23" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
+      <c r="A24" t="s">
+        <v>16</v>
+      </c>
+      <c r="B24" t="s">
+        <v>32</v>
+      </c>
+      <c r="C24" t="s">
+        <v>37</v>
+      </c>
+      <c r="E24" t="s">
+        <v>50</v>
+      </c>
+      <c r="I24" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
+      <c r="A25" t="s">
+        <v>11</v>
+      </c>
+      <c r="E25" t="s">
+        <v>51</v>
+      </c>
+      <c r="F25" t="s">
+        <v>73</v>
+      </c>
+      <c r="G25" t="s">
+        <v>103</v>
+      </c>
+      <c r="I25" t="s">
+        <v>149</v>
+      </c>
+      <c r="J25" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
+      <c r="A26" t="s">
+        <v>17</v>
+      </c>
+      <c r="B26" t="s">
+        <v>27</v>
+      </c>
+      <c r="C26" t="s">
+        <v>34</v>
+      </c>
+      <c r="D26" t="s">
+        <v>41</v>
+      </c>
+      <c r="I26" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
+      <c r="A27" t="s">
+        <v>18</v>
+      </c>
+      <c r="I27" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10">
+      <c r="E28" t="s">
+        <v>46</v>
+      </c>
+      <c r="F28" t="s">
+        <v>62</v>
+      </c>
+      <c r="G28" t="s">
+        <v>93</v>
+      </c>
+      <c r="H28" t="s">
+        <v>127</v>
+      </c>
+      <c r="I28" t="s">
+        <v>152</v>
+      </c>
+      <c r="J28" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10">
+      <c r="A29" t="s">
+        <v>18</v>
+      </c>
+      <c r="I29" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
+      <c r="F30" t="s">
+        <v>74</v>
+      </c>
+      <c r="G30" t="s">
+        <v>104</v>
+      </c>
+      <c r="H30" t="s">
+        <v>128</v>
+      </c>
+      <c r="I30" t="s">
+        <v>153</v>
+      </c>
+      <c r="J30" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10">
+      <c r="A31" t="s">
+        <v>17</v>
+      </c>
+      <c r="B31" t="s">
+        <v>27</v>
+      </c>
+      <c r="C31" t="s">
+        <v>34</v>
+      </c>
+      <c r="D31" t="s">
+        <v>41</v>
+      </c>
+      <c r="I31" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10">
+      <c r="A32" t="s">
+        <v>18</v>
+      </c>
+      <c r="I32" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10">
+      <c r="E33" t="s">
+        <v>48</v>
+      </c>
+      <c r="F33" t="s">
+        <v>75</v>
+      </c>
+      <c r="G33" t="s">
+        <v>105</v>
+      </c>
+      <c r="H33" t="s">
+        <v>127</v>
+      </c>
+      <c r="I33" t="s">
+        <v>155</v>
+      </c>
+      <c r="J33" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10">
+      <c r="A34" t="s">
+        <v>18</v>
+      </c>
+      <c r="I34" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10">
+      <c r="H35" t="s">
+        <v>128</v>
+      </c>
+      <c r="I35" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10">
+      <c r="A36" t="s">
+        <v>16</v>
+      </c>
+      <c r="B36" t="s">
+        <v>32</v>
+      </c>
+      <c r="C36" t="s">
+        <v>37</v>
+      </c>
+      <c r="E36" t="s">
+        <v>50</v>
+      </c>
+      <c r="I36" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10">
+      <c r="A37" t="s">
+        <v>11</v>
+      </c>
+      <c r="E37" t="s">
+        <v>51</v>
+      </c>
+      <c r="F37" t="s">
+        <v>76</v>
+      </c>
+      <c r="G37" t="s">
+        <v>106</v>
+      </c>
+      <c r="I37" t="s">
+        <v>157</v>
+      </c>
+      <c r="J37" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10">
+      <c r="A38" t="s">
+        <v>17</v>
+      </c>
+      <c r="B38" t="s">
+        <v>27</v>
+      </c>
+      <c r="C38" t="s">
+        <v>34</v>
+      </c>
+      <c r="D38" t="s">
+        <v>41</v>
+      </c>
+      <c r="I38" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10">
+      <c r="A39" t="s">
+        <v>18</v>
+      </c>
+      <c r="I39" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10">
+      <c r="E40" t="s">
+        <v>48</v>
+      </c>
+      <c r="H40" t="s">
+        <v>127</v>
+      </c>
+      <c r="I40" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10">
+      <c r="A41" t="s">
+        <v>18</v>
+      </c>
+      <c r="I41" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10">
+      <c r="F42" t="s">
+        <v>77</v>
+      </c>
+      <c r="G42" t="s">
+        <v>107</v>
+      </c>
+      <c r="H42" t="s">
+        <v>128</v>
+      </c>
+      <c r="I42" t="s">
+        <v>159</v>
+      </c>
+      <c r="J42" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10">
+      <c r="A43" t="s">
+        <v>17</v>
+      </c>
+      <c r="B43" t="s">
+        <v>27</v>
+      </c>
+      <c r="C43" t="s">
+        <v>34</v>
+      </c>
+      <c r="E43" t="s">
+        <v>48</v>
+      </c>
+      <c r="I43" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10">
+      <c r="A44" t="s">
+        <v>11</v>
+      </c>
+      <c r="F44" t="s">
+        <v>77</v>
+      </c>
+      <c r="G44" t="s">
+        <v>107</v>
+      </c>
+      <c r="H44" t="s">
+        <v>125</v>
+      </c>
+      <c r="I44" t="s">
+        <v>161</v>
+      </c>
+      <c r="J44" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10">
+      <c r="A45" t="s">
+        <v>19</v>
+      </c>
+      <c r="B45" t="s">
+        <v>32</v>
+      </c>
+      <c r="C45" t="s">
+        <v>36</v>
+      </c>
+      <c r="D45" t="s">
+        <v>42</v>
+      </c>
+      <c r="I45" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10">
+      <c r="A46" t="s">
+        <v>11</v>
+      </c>
+      <c r="E46" t="s">
+        <v>52</v>
+      </c>
+      <c r="F46" t="s">
+        <v>78</v>
+      </c>
+      <c r="G46" t="s">
+        <v>108</v>
+      </c>
+      <c r="I46" t="s">
+        <v>163</v>
+      </c>
+      <c r="J46" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10">
+      <c r="A47" t="s">
+        <v>19</v>
+      </c>
+      <c r="B47" t="s">
+        <v>30</v>
+      </c>
+      <c r="C47" t="s">
+        <v>38</v>
+      </c>
+      <c r="D47" t="s">
+        <v>41</v>
+      </c>
+      <c r="I47" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10">
+      <c r="A48" t="s">
+        <v>11</v>
+      </c>
+      <c r="E48" t="s">
+        <v>53</v>
+      </c>
+      <c r="H48" t="s">
+        <v>125</v>
+      </c>
+      <c r="I48" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10">
+      <c r="A49" t="s">
+        <v>11</v>
+      </c>
+      <c r="F49" t="s">
+        <v>79</v>
+      </c>
+      <c r="G49" t="s">
+        <v>109</v>
+      </c>
+      <c r="I49" t="s">
+        <v>166</v>
+      </c>
+      <c r="J49" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10">
+      <c r="A50" t="s">
+        <v>11</v>
+      </c>
+      <c r="F50" t="s">
+        <v>80</v>
+      </c>
+      <c r="G50" t="s">
+        <v>110</v>
+      </c>
+      <c r="I50" t="s">
+        <v>167</v>
+      </c>
+      <c r="J50" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10">
+      <c r="A51" t="s">
+        <v>20</v>
+      </c>
+      <c r="B51" t="s">
+        <v>32</v>
+      </c>
+      <c r="C51" t="s">
+        <v>38</v>
+      </c>
+      <c r="D51" t="s">
+        <v>41</v>
+      </c>
+      <c r="I51" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10">
+      <c r="A52" t="s">
+        <v>21</v>
+      </c>
+      <c r="I52" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10">
+      <c r="E53" t="s">
+        <v>48</v>
+      </c>
+      <c r="F53" t="s">
+        <v>81</v>
+      </c>
+      <c r="G53" t="s">
+        <v>111</v>
+      </c>
+      <c r="H53" t="s">
+        <v>127</v>
+      </c>
+      <c r="I53" t="s">
+        <v>170</v>
+      </c>
+      <c r="J53" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10">
+      <c r="A54" t="s">
+        <v>22</v>
+      </c>
+      <c r="B54" t="s">
+        <v>32</v>
+      </c>
+      <c r="C54" t="s">
+        <v>34</v>
+      </c>
+      <c r="E54" t="s">
+        <v>54</v>
+      </c>
+      <c r="F54" t="s">
+        <v>64</v>
+      </c>
+      <c r="I54" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10">
+      <c r="A55" t="s">
+        <v>11</v>
+      </c>
+      <c r="E55" t="s">
+        <v>55</v>
+      </c>
+      <c r="F55" t="s">
+        <v>82</v>
+      </c>
+      <c r="G55" t="s">
+        <v>112</v>
+      </c>
+      <c r="H55" t="s">
+        <v>125</v>
+      </c>
+      <c r="I55" t="s">
+        <v>172</v>
+      </c>
+      <c r="J55" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10">
+      <c r="A56" t="s">
+        <v>22</v>
+      </c>
+      <c r="B56" t="s">
+        <v>32</v>
+      </c>
+      <c r="C56" t="s">
+        <v>36</v>
+      </c>
+      <c r="E56" t="s">
+        <v>54</v>
+      </c>
+      <c r="I56" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10">
+      <c r="A57" t="s">
+        <v>11</v>
+      </c>
+      <c r="E57" t="s">
+        <v>56</v>
+      </c>
+      <c r="F57" t="s">
+        <v>83</v>
+      </c>
+      <c r="G57" t="s">
+        <v>113</v>
+      </c>
+      <c r="I57" t="s">
+        <v>174</v>
+      </c>
+      <c r="J57" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10">
+      <c r="A58" t="s">
+        <v>20</v>
+      </c>
+      <c r="B58" t="s">
+        <v>30</v>
+      </c>
+      <c r="D58" t="s">
+        <v>41</v>
+      </c>
+      <c r="E58" t="s">
+        <v>57</v>
+      </c>
+      <c r="I58" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10">
+      <c r="A59" t="s">
+        <v>11</v>
+      </c>
+      <c r="E59" t="s">
+        <v>47</v>
+      </c>
+      <c r="F59" t="s">
+        <v>84</v>
+      </c>
+      <c r="G59" t="s">
+        <v>114</v>
+      </c>
+      <c r="H59" t="s">
+        <v>125</v>
+      </c>
+      <c r="I59" t="s">
+        <v>176</v>
+      </c>
+      <c r="J59" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10">
+      <c r="A60" t="s">
+        <v>20</v>
+      </c>
+      <c r="B60" t="s">
+        <v>27</v>
+      </c>
+      <c r="C60" t="s">
+        <v>38</v>
+      </c>
+      <c r="D60" t="s">
+        <v>41</v>
+      </c>
+      <c r="I60" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10">
+      <c r="A61" t="s">
+        <v>11</v>
+      </c>
+      <c r="E61" t="s">
+        <v>46</v>
+      </c>
+      <c r="F61" t="s">
+        <v>82</v>
+      </c>
+      <c r="G61" t="s">
+        <v>115</v>
+      </c>
+      <c r="H61" t="s">
+        <v>125</v>
+      </c>
+      <c r="I61" t="s">
+        <v>178</v>
+      </c>
+      <c r="J61" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10">
+      <c r="A62" t="s">
+        <v>20</v>
+      </c>
+      <c r="B62" t="s">
+        <v>30</v>
+      </c>
+      <c r="C62" t="s">
+        <v>34</v>
+      </c>
+      <c r="D62" t="s">
+        <v>40</v>
+      </c>
+      <c r="I62" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10">
+      <c r="A63" t="s">
+        <v>11</v>
+      </c>
+      <c r="E63" t="s">
+        <v>46</v>
+      </c>
+      <c r="F63" t="s">
+        <v>85</v>
+      </c>
+      <c r="G63" t="s">
+        <v>116</v>
+      </c>
+      <c r="H63" t="s">
+        <v>125</v>
+      </c>
+      <c r="I63" t="s">
+        <v>180</v>
+      </c>
+      <c r="J63" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10">
+      <c r="A64" t="s">
+        <v>11</v>
+      </c>
+      <c r="E64" t="s">
+        <v>46</v>
+      </c>
+      <c r="F64" t="s">
+        <v>86</v>
+      </c>
+      <c r="G64" t="s">
+        <v>117</v>
+      </c>
+      <c r="H64" t="s">
+        <v>125</v>
+      </c>
+      <c r="I64" t="s">
+        <v>181</v>
+      </c>
+      <c r="J64" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10">
+      <c r="A65" t="s">
+        <v>11</v>
+      </c>
+      <c r="E65" t="s">
+        <v>46</v>
+      </c>
+      <c r="F65" t="s">
+        <v>87</v>
+      </c>
+      <c r="G65" t="s">
+        <v>118</v>
+      </c>
+      <c r="I65" t="s">
+        <v>182</v>
+      </c>
+      <c r="J65" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10">
+      <c r="A66" t="s">
+        <v>20</v>
+      </c>
+      <c r="B66" t="s">
+        <v>30</v>
+      </c>
+      <c r="C66" t="s">
+        <v>34</v>
+      </c>
+      <c r="D66" t="s">
+        <v>40</v>
+      </c>
+      <c r="I66" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10">
+      <c r="A67" t="s">
+        <v>11</v>
+      </c>
+      <c r="E67" t="s">
+        <v>46</v>
+      </c>
+      <c r="F67" t="s">
+        <v>85</v>
+      </c>
+      <c r="G67" t="s">
+        <v>116</v>
+      </c>
+      <c r="H67" t="s">
+        <v>125</v>
+      </c>
+      <c r="I67" t="s">
+        <v>180</v>
+      </c>
+      <c r="J67" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10">
+      <c r="A68" t="s">
+        <v>11</v>
+      </c>
+      <c r="E68" t="s">
+        <v>46</v>
+      </c>
+      <c r="F68" t="s">
+        <v>86</v>
+      </c>
+      <c r="G68" t="s">
+        <v>117</v>
+      </c>
+      <c r="H68" t="s">
+        <v>125</v>
+      </c>
+      <c r="I68" t="s">
+        <v>181</v>
+      </c>
+      <c r="J68" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10">
+      <c r="A69" t="s">
+        <v>11</v>
+      </c>
+      <c r="E69" t="s">
+        <v>46</v>
+      </c>
+      <c r="F69" t="s">
+        <v>88</v>
+      </c>
+      <c r="G69" t="s">
+        <v>119</v>
+      </c>
+      <c r="I69" t="s">
+        <v>183</v>
+      </c>
+      <c r="J69" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10">
+      <c r="A70" t="s">
         <v>23</v>
       </c>
-      <c r="F11" t="s">
+      <c r="B70" t="s">
+        <v>31</v>
+      </c>
+      <c r="C70" t="s">
+        <v>35</v>
+      </c>
+      <c r="D70" t="s">
+        <v>40</v>
+      </c>
+      <c r="I70" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10">
+      <c r="A71" t="s">
+        <v>23</v>
+      </c>
+      <c r="E71" t="s">
+        <v>58</v>
+      </c>
+      <c r="F71" t="s">
+        <v>84</v>
+      </c>
+      <c r="G71" t="s">
+        <v>114</v>
+      </c>
+      <c r="I71" t="s">
+        <v>185</v>
+      </c>
+      <c r="J71" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10">
+      <c r="A72" t="s">
+        <v>24</v>
+      </c>
+      <c r="E72" t="s">
+        <v>47</v>
+      </c>
+      <c r="I72" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10">
+      <c r="A73" t="s">
+        <v>23</v>
+      </c>
+      <c r="B73" t="s">
+        <v>28</v>
+      </c>
+      <c r="C73" t="s">
+        <v>35</v>
+      </c>
+      <c r="D73" t="s">
+        <v>40</v>
+      </c>
+      <c r="I73" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10">
+      <c r="A74" t="s">
+        <v>23</v>
+      </c>
+      <c r="E74" t="s">
+        <v>46</v>
+      </c>
+      <c r="F74" t="s">
+        <v>63</v>
+      </c>
+      <c r="G74" t="s">
+        <v>120</v>
+      </c>
+      <c r="I74" t="s">
+        <v>188</v>
+      </c>
+      <c r="J74" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10">
+      <c r="A75" t="s">
+        <v>23</v>
+      </c>
+      <c r="B75" t="s">
+        <v>32</v>
+      </c>
+      <c r="C75" t="s">
+        <v>35</v>
+      </c>
+      <c r="D75" t="s">
+        <v>40</v>
+      </c>
+      <c r="I75" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10">
+      <c r="A76" t="s">
+        <v>23</v>
+      </c>
+      <c r="E76" t="s">
+        <v>59</v>
+      </c>
+      <c r="F76" t="s">
+        <v>74</v>
+      </c>
+      <c r="G76" t="s">
+        <v>104</v>
+      </c>
+      <c r="I76" t="s">
+        <v>190</v>
+      </c>
+      <c r="J76" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10">
+      <c r="A77" t="s">
+        <v>25</v>
+      </c>
+      <c r="B77" t="s">
+        <v>30</v>
+      </c>
+      <c r="C77" t="s">
+        <v>37</v>
+      </c>
+      <c r="D77" t="s">
+        <v>42</v>
+      </c>
+      <c r="I77" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10">
+      <c r="A78" t="s">
+        <v>25</v>
+      </c>
+      <c r="E78" t="s">
+        <v>60</v>
+      </c>
+      <c r="F78" t="s">
+        <v>89</v>
+      </c>
+      <c r="G78" t="s">
+        <v>121</v>
+      </c>
+      <c r="I78" t="s">
+        <v>192</v>
+      </c>
+      <c r="J78" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10">
+      <c r="A79" t="s">
         <v>26</v>
       </c>
-      <c r="G11" t="s">
+      <c r="B79" t="s">
+        <v>33</v>
+      </c>
+      <c r="C79" t="s">
+        <v>36</v>
+      </c>
+      <c r="D79" t="s">
+        <v>43</v>
+      </c>
+      <c r="I79" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10">
+      <c r="A80" t="s">
+        <v>26</v>
+      </c>
+      <c r="B80" t="s">
         <v>31</v>
       </c>
-      <c r="H11" t="s">
-        <v>33</v>
-      </c>
-      <c r="I11" t="s">
-        <v>44</v>
-      </c>
-      <c r="J11" t="s">
-        <v>49</v>
+      <c r="C80" t="s">
+        <v>39</v>
+      </c>
+      <c r="D80" t="s">
+        <v>40</v>
+      </c>
+      <c r="E80" t="s">
+        <v>61</v>
+      </c>
+      <c r="F80" t="s">
+        <v>90</v>
+      </c>
+      <c r="G80" t="s">
+        <v>122</v>
+      </c>
+      <c r="H80" t="s">
+        <v>125</v>
+      </c>
+      <c r="I80" t="s">
+        <v>194</v>
+      </c>
+      <c r="J80" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10">
+      <c r="A81" t="s">
+        <v>26</v>
+      </c>
+      <c r="E81" t="s">
+        <v>48</v>
+      </c>
+      <c r="F81" t="s">
+        <v>91</v>
+      </c>
+      <c r="G81" t="s">
+        <v>123</v>
+      </c>
+      <c r="H81" t="s">
+        <v>125</v>
+      </c>
+      <c r="I81" t="s">
+        <v>195</v>
+      </c>
+      <c r="J81" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10">
+      <c r="A82" t="s">
+        <v>26</v>
+      </c>
+      <c r="B82" t="s">
+        <v>31</v>
+      </c>
+      <c r="C82" t="s">
+        <v>34</v>
+      </c>
+      <c r="D82" t="s">
+        <v>40</v>
+      </c>
+      <c r="I82" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10">
+      <c r="A83" t="s">
+        <v>26</v>
+      </c>
+      <c r="E83" t="s">
+        <v>47</v>
+      </c>
+      <c r="F83" t="s">
+        <v>92</v>
+      </c>
+      <c r="G83" t="s">
+        <v>124</v>
+      </c>
+      <c r="H83" t="s">
+        <v>125</v>
+      </c>
+      <c r="I83" t="s">
+        <v>197</v>
+      </c>
+      <c r="J83" t="s">
+        <v>227</v>
       </c>
     </row>
   </sheetData>

--- a/output_orderan.xlsx
+++ b/output_orderan.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="172">
   <si>
     <t>DATE</t>
   </si>
@@ -37,82 +37,644 @@
     <t>PLATE</t>
   </si>
   <si>
+    <t>TIME</t>
+  </si>
+  <si>
     <t>Original_Text</t>
   </si>
   <si>
     <t>PHONE</t>
   </si>
   <si>
-    <t>3 maret 2026</t>
-  </si>
-  <si>
-    <t>18 maret 2026</t>
+    <t>06 febuary 2026</t>
+  </si>
+  <si>
+    <t>06 feb 2026</t>
+  </si>
+  <si>
+    <t>06 febuari 2026</t>
+  </si>
+  <si>
+    <t>07 febuari 2026</t>
+  </si>
+  <si>
+    <t>08 februari 2025</t>
+  </si>
+  <si>
+    <t>09 feb</t>
+  </si>
+  <si>
+    <t>9 februari 2026</t>
+  </si>
+  <si>
+    <t>10 / 02 / 2026</t>
+  </si>
+  <si>
+    <t>11 februari 2026</t>
+  </si>
+  <si>
+    <t>09 : 00 11 februari 2026</t>
+  </si>
+  <si>
+    <t>12 februari 2026</t>
+  </si>
+  <si>
+    <t>12 / 02 / 2026</t>
+  </si>
+  <si>
+    <t>12 feb 26</t>
+  </si>
+  <si>
+    <t>2</t>
   </si>
   <si>
     <t>6</t>
   </si>
   <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
     <t>1</t>
   </si>
   <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>twb</t>
+  </si>
+  <si>
     <t>wb</t>
   </si>
   <si>
-    <t>cbm</t>
+    <t>cddl</t>
+  </si>
+  <si>
+    <t>jne</t>
   </si>
   <si>
     <t>argopantes</t>
   </si>
   <si>
+    <t>cikokol</t>
+  </si>
+  <si>
+    <t>megahub</t>
+  </si>
+  <si>
+    <t>cikarang</t>
+  </si>
+  <si>
+    <t>subcgk</t>
+  </si>
+  <si>
     <t>cgk sub</t>
   </si>
   <si>
-    <t>sub cgk</t>
+    <t>cgk tentatif</t>
+  </si>
+  <si>
+    <t>cgk mes</t>
+  </si>
+  <si>
+    <t>cgk pku</t>
+  </si>
+  <si>
+    <t>srg sub</t>
+  </si>
+  <si>
+    <t>jne srg</t>
+  </si>
+  <si>
+    <t>srgcgk</t>
+  </si>
+  <si>
+    <t>cgk dps</t>
+  </si>
+  <si>
+    <t>cgk</t>
+  </si>
+  <si>
+    <t>ckrsubsux</t>
+  </si>
+  <si>
+    <t>cgkjbr</t>
+  </si>
+  <si>
+    <t>akbar</t>
+  </si>
+  <si>
+    <t>wahyudi</t>
   </si>
   <si>
     <t>sofyan</t>
   </si>
   <si>
+    <t>chandra</t>
+  </si>
+  <si>
+    <t>sentot</t>
+  </si>
+  <si>
+    <t>purwanto</t>
+  </si>
+  <si>
+    <t>didik</t>
+  </si>
+  <si>
+    <t>haryono</t>
+  </si>
+  <si>
+    <t>hermanto</t>
+  </si>
+  <si>
+    <t>wijaya</t>
+  </si>
+  <si>
+    <t>darmawan</t>
+  </si>
+  <si>
+    <t>arif r</t>
+  </si>
+  <si>
     <t>yuda</t>
   </si>
   <si>
-    <t>b 9679wt</t>
+    <t>aldi</t>
+  </si>
+  <si>
+    <t>supriadi</t>
+  </si>
+  <si>
+    <t>syafrizal</t>
+  </si>
+  <si>
+    <t>nizar</t>
+  </si>
+  <si>
+    <t>samosir</t>
+  </si>
+  <si>
+    <t>joni</t>
+  </si>
+  <si>
+    <t>nasip k</t>
+  </si>
+  <si>
+    <t>ageng</t>
+  </si>
+  <si>
+    <t>ilham wahyudi</t>
+  </si>
+  <si>
+    <t>sri mardono</t>
+  </si>
+  <si>
+    <t>n 9549 ua</t>
+  </si>
+  <si>
+    <t>b 9679 wt</t>
+  </si>
+  <si>
+    <t>l 8601 uh</t>
+  </si>
+  <si>
+    <t>b 9231 ceu</t>
+  </si>
+  <si>
+    <t>b 9891 beu</t>
+  </si>
+  <si>
+    <t>b 9687 jm</t>
+  </si>
+  <si>
+    <t>b 8745 amr</t>
+  </si>
+  <si>
+    <t>s 8635 nj</t>
+  </si>
+  <si>
+    <t>h 9948 ra</t>
+  </si>
+  <si>
+    <t>ba 8829 bu</t>
+  </si>
+  <si>
+    <t>b 9787 xx</t>
   </si>
   <si>
     <t>w 8973 uq</t>
   </si>
   <si>
-    <t>REQUEST  ORDER  ONCALL  3 MARET 2026
+    <t>bm 8350 au</t>
+  </si>
+  <si>
+    <t>b 9586 txv</t>
+  </si>
+  <si>
+    <t>bm 8479 au</t>
+  </si>
+  <si>
+    <t>b 9172 scp</t>
+  </si>
+  <si>
+    <t>b 9727 uex</t>
+  </si>
+  <si>
+    <t>b 9169 uex</t>
+  </si>
+  <si>
+    <t>bh 8165 qi</t>
+  </si>
+  <si>
+    <t>b9654yu</t>
+  </si>
+  <si>
+    <t>f 9647 fh</t>
+  </si>
+  <si>
+    <t>bk 8678 ve</t>
+  </si>
+  <si>
+    <t>segera</t>
+  </si>
+  <si>
+    <t>07 : 00</t>
+  </si>
+  <si>
+    <t>22 : 00</t>
+  </si>
+  <si>
+    <t>02 : 00</t>
+  </si>
+  <si>
+    <t>03 : 00</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: Request Unit On Call Tgl 06 febuary 2026
+2 unit twb 50 CBM
+Lokasi : JNE SUB</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA 06 febuary 2026
+Rute/tujuan : SUB-CGK
+driver  : WAHYUDI
+Nopol  : N 9549 UA
+No hp  :085784422398</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA 06 febuary 2026
+Rute/tujuan : SUB-CGK
+driver  : SOFYAN
+Nopol  : B 9679 WT
+No hp  : 082231837381</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: REQUEST ORDER ULANG ONCALL
+06 FEB 2026
 6 UNIT WB/50 CBM
 Lokasi : ARGOPANTES</t>
   </si>
   <si>
-    <t>Waktu loading : 23:00 3 MARET 2026
-Rute/tujuan : CGK - SUB 
-driver  : Rosyit
-Nopol  : B 9562 TEU
-No hp  : 082313572678
-Driver : sofyan
-Nopol : B 9679WT
-No Hp : 082231837381</t>
-  </si>
-  <si>
-    <t>REQUEST  ORDER  ONCALL  18 MARET 2026
-1 UNIT WB/50 CBM
+    <t>REQUEST ORDER KHUSUS 07-02-2026</t>
+  </si>
+  <si>
+    <t>Waktu loading : 07:00
+Rute/tujuan : CGK - SUB
+driver  : Chandra
+Nopol  : L 8601 UH
+No hp  : +62 852-3168-1470</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: REQUEST ORDER ULANG ONCALL
+06 FEB 2026
+10 UNIT CDDL/24 CBM
 Lokasi : ARGOPANTES</t>
   </si>
   <si>
-    <t>Waktu loading : 23:00 18 MARET 2026
-Rute/tujuan : SUB - CGK
-driver  : Yuda
-Nopol  : W 8973 UQ
-No hp  : 089507296985</t>
+    <t>Waktu loading : SEGERA
+Rute/tujuan : CGK - JATIM TENTATIF</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: REQUEST ORDER ONCAL
+06 FEBUARI 2026
+RAFAY
+3 unit TWB 50 Cbm
+Lokasi : ARGOPANTES
+Rute/ tuj : CGK - MES</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA
+DRIVER 1 : SENTOT
+NOPOL    : B 9231 CEU
+NOHP      :+62 812-8714-7789</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: REQUEST ORDER ONCAL
+06 FEBUARI 2026
+5 unit TWB 50 Cbm
+Lokasi : ARGOPANTES
+Rute/ tuj : CGK - SUB</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA
+RAFAY
+DRIVER 1 : PURWANTO
+NOPOL    : B 9891 BEU
+NOHP      :083142142113</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA
+DRIVER : DIDIK
+NOPOL    : B 9687 JM
+NOHP      :085385220743</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: REQUEST ORDER ONCAL
+06 FEBUARI 2026
+Lokasi : ARGOPANTES
+Rute/ tuj : CGK - PKU</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA
+DRIVER 1 : Haryono
+NOPOL    : B 8745 AMR
+NO HP      : 083166684195</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA
+DRIVER : HERMANTO
+NOPOL : S 8635 NJ
+NOHP :085194592825</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: REQUEST ORDER ONCAL
+07 FEBUARI 2026
+RAFAY
+1 unit CDDL 24 Cbm
+Lokasi : SEMARANG
+Rute/ tuj : SRG - SUB</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA
+DRIVER 1 :Agung
+DRIVER 2 :Wijaya
+NOPOL    :H 9948 RA
+NOHP      :0882016641381</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: REQUEST ORDER ONCALL 08 FEBRUARI 2025:
+3 UNIT TWB 50 CBM
+Lokasi : ARGOPANTES</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA 08 FEBRUARI 2025
+Rute/tujuan : CGK - MES
+driver  : DARMAWAN
+Nopol  : BA 8829 BU
+No hp  :082363564665</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: Request Order Oncall Tgl 09 Feb
+1 UNIT CDDL 24 CBM
+Lokasi  : JNE SRG</t>
+  </si>
+  <si>
+    <t>Waktu loading : 22:00
+Rute/tujuan : SRG-CGK
+Driver : Arif R
+Nopol :B 9787 XX
+No hp :089690885555</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: REQUEST ORDER  ONCALL 9 FEBRUARI 2026:
+2 unit TWB 50 Cbm
+Lokasi : cikokol</t>
+  </si>
+  <si>
+    <t>REQUEST ORDER KHUSUS 10/02/2026</t>
+  </si>
+  <si>
+    <t>Waktu loading : 02:00
+Rute/tujuan : CGK - SUB
+NAMA : WAHYUDI
+NOPOL: N 9549 UA
+NO HP :085784422398</t>
+  </si>
+  <si>
+    <t>Waktu loading : 03:00
+NAMA : YUDA
+NOPOL: W 8973 UQ
+NO HP :089507296985</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: REQUEST ORDER  ONCALL 9 FEBRUARI 2026:
+2 unit  TWB 50 Cbm
+Lokasi : Cikokol</t>
+  </si>
+  <si>
+    <t>Waktu loading : 02:00
+Rute/tujuan : CGK - PKU
+NAMA : ALDI
+NOPOL: BM 8350 AU
+NO HP :0831-6761-0479</t>
+  </si>
+  <si>
+    <t>Waktu loading : 03:00
+NAMA :
+NOPOL:
+NO HP :</t>
+  </si>
+  <si>
+    <t>Waktu loading : 02:00
+Rute/tujuan : SRG-CGK
+Driver : Supriadi
+Nopol : B 9586 TXV
+No hp :081350529712</t>
+  </si>
+  <si>
+    <t>Waktu loading : 02:00
+Rute/tujuan : CGK - PKU</t>
+  </si>
+  <si>
+    <t>Waktu loading : 03:00
+NAMA : SYAFRIZAL
+NOPOL: BM 8479 AU
+NO HP :082170733190</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: REQUEST ORDER  ONCALL 9 FEBRUARI 2026:
+RAFAY
+2 unit  TWB 50 Cbm
+Lokasi : Cikokol
+Rute/tujuan : CGK - PKU</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA 9 FEBRUARI 2026
+NAMA : SYAFRIZAL
+NOPOL: BM 8479 AU
+NO HP :082170733190</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: REQUEST ORDER ONCALL 11 FEBRUARI 2026:
+1 unit Cddl 24 Cbm
+Lokasi : Megahub</t>
+  </si>
+  <si>
+    <t>Waktu loading : 00:00 11 FEBRUARI 2026
+Rute/tujuan : CGK - DPS
+driver  :Nizar
+Nopol  :B 9172 SCP
+No hp  :081313444015</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: REQUEST ORDER ONCALL 11 FEBRUARI 2026:
+3 unit tronton 50 Cbm
+Lokasi : cikokol</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA 11 FEBRUARI 2026
+Rute/tujuan : CGK - MES</t>
+  </si>
+  <si>
+    <t>Waktu loading : 09:00 11 FEBRUARI 2026
+Driver : SAMOSIR
+Nopol : B 9727 UEX
+Hp :+62 822-7429-6236</t>
+  </si>
+  <si>
+    <t>Waktu loading : 12:00 11 FEBRUARI 2026
+Driver : JONI
+Nopol : B 9169 UEX
+Hp :+62 822-7638-5077</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: REQUEST ORDER TAMBAHAN ONCALL  12 FEBRUARI 2026:
+1 unit TRONTON 50 Cbm
+Lokasi : cikokol</t>
+  </si>
+  <si>
+    <t>REQUEST ORDER KHUSUS 12/02/2026</t>
+  </si>
+  <si>
+    <t>Waktu loading : 02:00
+Rute/tujuan : CGK - PKU
+Nama 	: NASIP K
+Nopol		: BH 8165 QI
+No Tlp		:‪+6281272463920</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: Request Unit On Call Tgl 12 Feb 26
+1 Unit  TWB 50 Cbm
+Lokasi : Cikarang</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA
+Rute/tujuan : CKR-SUB-SUX 
+Driver   : AGENG
+Nopol  : B9654YU
+No Hp  : +62 857-0738-0584</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: Request Unit On Call Tgl 12 Feb 26
+1 Unit  Cddl / 24 Cbm
+Lokasi : Cikokol + Cikarang</t>
+  </si>
+  <si>
+    <t>Waktu loading : 03:00
+Rute/tujuan : CGK-JBR
+No pol.   : F 9647 FH
+Driver. 1 :  Jatmiyanta
+No hp :  : 082118558105
+Driver 2  : Ilham Wahyudi
+No hp.    : 089519041791</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: REQUEST ORDER ONCALL 12 FEBRUARI 2026:
+RAFAY
+3 unit tronton 50 Cbm
+Lokasi : cikokol</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA 12 FEBRUARI 2026
+Rute/tujuan : CGK - MES
+driver  : SRI MARDONO
+Nopol  : BK 8678 VE
+No hp  :085218843366</t>
+  </si>
+  <si>
+    <t>085784422398</t>
   </si>
   <si>
     <t>082231837381</t>
   </si>
   <si>
+    <t>07022026</t>
+  </si>
+  <si>
+    <t>0 85231681470</t>
+  </si>
+  <si>
+    <t>0 81287147789</t>
+  </si>
+  <si>
+    <t>083142142113</t>
+  </si>
+  <si>
+    <t>085385220743</t>
+  </si>
+  <si>
+    <t>083166684195</t>
+  </si>
+  <si>
+    <t>085194592825</t>
+  </si>
+  <si>
+    <t>0882016641381</t>
+  </si>
+  <si>
+    <t>082363564665</t>
+  </si>
+  <si>
+    <t>089690885555</t>
+  </si>
+  <si>
     <t>089507296985</t>
+  </si>
+  <si>
+    <t>083167610479</t>
+  </si>
+  <si>
+    <t>081350529712</t>
+  </si>
+  <si>
+    <t>082170733190</t>
+  </si>
+  <si>
+    <t>081313444015</t>
+  </si>
+  <si>
+    <t>0 82274296236</t>
+  </si>
+  <si>
+    <t>0 82276385077</t>
+  </si>
+  <si>
+    <t>081272463920</t>
+  </si>
+  <si>
+    <t>0 85707380584</t>
+  </si>
+  <si>
+    <t>089519041791</t>
+  </si>
+  <si>
+    <t>085218843366</t>
   </si>
 </sst>
 </file>
@@ -470,10 +1032,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:J60"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -501,79 +1063,993 @@
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:9">
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="D2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9">
+        <v>33</v>
+      </c>
+      <c r="F2" t="s">
+        <v>50</v>
+      </c>
+      <c r="I2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E3" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="F3" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="G3" t="s">
-        <v>20</v>
-      </c>
-      <c r="H3" t="s">
-        <v>23</v>
+        <v>73</v>
       </c>
       <c r="I3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9">
+        <v>101</v>
+      </c>
+      <c r="J3" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
       <c r="A4" t="s">
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="D4" t="s">
-        <v>15</v>
-      </c>
-      <c r="H4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9">
+        <v>33</v>
+      </c>
+      <c r="F4" t="s">
+        <v>50</v>
+      </c>
+      <c r="I4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
       <c r="A5" t="s">
         <v>10</v>
       </c>
       <c r="E5" t="s">
+        <v>38</v>
+      </c>
+      <c r="F5" t="s">
+        <v>52</v>
+      </c>
+      <c r="G5" t="s">
+        <v>74</v>
+      </c>
+      <c r="H5" t="s">
+        <v>95</v>
+      </c>
+      <c r="I5" t="s">
+        <v>102</v>
+      </c>
+      <c r="J5" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" t="s">
+        <v>34</v>
+      </c>
+      <c r="I6" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="I7" t="s">
+        <v>104</v>
+      </c>
+      <c r="J7" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="E8" t="s">
+        <v>39</v>
+      </c>
+      <c r="F8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G8" t="s">
+        <v>75</v>
+      </c>
+      <c r="H8" t="s">
+        <v>96</v>
+      </c>
+      <c r="I8" t="s">
+        <v>105</v>
+      </c>
+      <c r="J8" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D9" t="s">
+        <v>34</v>
+      </c>
+      <c r="I9" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="E10" t="s">
+        <v>40</v>
+      </c>
+      <c r="H10" t="s">
+        <v>95</v>
+      </c>
+      <c r="I10" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" t="s">
+        <v>30</v>
+      </c>
+      <c r="D11" t="s">
+        <v>34</v>
+      </c>
+      <c r="E11" t="s">
+        <v>41</v>
+      </c>
+      <c r="I11" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="F12" t="s">
+        <v>54</v>
+      </c>
+      <c r="G12" t="s">
+        <v>76</v>
+      </c>
+      <c r="H12" t="s">
+        <v>95</v>
+      </c>
+      <c r="I12" t="s">
+        <v>109</v>
+      </c>
+      <c r="J12" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" t="s">
+        <v>30</v>
+      </c>
+      <c r="D13" t="s">
+        <v>34</v>
+      </c>
+      <c r="E13" t="s">
+        <v>39</v>
+      </c>
+      <c r="F13" t="s">
+        <v>50</v>
+      </c>
+      <c r="I13" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="F14" t="s">
+        <v>55</v>
+      </c>
+      <c r="G14" t="s">
+        <v>77</v>
+      </c>
+      <c r="H14" t="s">
+        <v>95</v>
+      </c>
+      <c r="I14" t="s">
+        <v>111</v>
+      </c>
+      <c r="J14" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" t="s">
+        <v>12</v>
+      </c>
+      <c r="B15" t="s">
+        <v>27</v>
+      </c>
+      <c r="C15" t="s">
+        <v>30</v>
+      </c>
+      <c r="D15" t="s">
+        <v>34</v>
+      </c>
+      <c r="E15" t="s">
+        <v>39</v>
+      </c>
+      <c r="F15" t="s">
+        <v>50</v>
+      </c>
+      <c r="I15" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="F16" t="s">
+        <v>56</v>
+      </c>
+      <c r="G16" t="s">
+        <v>78</v>
+      </c>
+      <c r="H16" t="s">
+        <v>95</v>
+      </c>
+      <c r="I16" t="s">
+        <v>112</v>
+      </c>
+      <c r="J16" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="A17" t="s">
+        <v>12</v>
+      </c>
+      <c r="D17" t="s">
+        <v>34</v>
+      </c>
+      <c r="E17" t="s">
+        <v>42</v>
+      </c>
+      <c r="F17" t="s">
+        <v>50</v>
+      </c>
+      <c r="I17" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="F18" t="s">
+        <v>57</v>
+      </c>
+      <c r="G18" t="s">
+        <v>79</v>
+      </c>
+      <c r="H18" t="s">
+        <v>95</v>
+      </c>
+      <c r="I18" t="s">
+        <v>114</v>
+      </c>
+      <c r="J18" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
+      <c r="A19" t="s">
+        <v>12</v>
+      </c>
+      <c r="B19" t="s">
+        <v>27</v>
+      </c>
+      <c r="C19" t="s">
+        <v>30</v>
+      </c>
+      <c r="D19" t="s">
+        <v>34</v>
+      </c>
+      <c r="E19" t="s">
+        <v>39</v>
+      </c>
+      <c r="F19" t="s">
+        <v>50</v>
+      </c>
+      <c r="I19" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="F20" t="s">
+        <v>58</v>
+      </c>
+      <c r="G20" t="s">
+        <v>80</v>
+      </c>
+      <c r="H20" t="s">
+        <v>95</v>
+      </c>
+      <c r="I20" t="s">
+        <v>115</v>
+      </c>
+      <c r="J20" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="A21" t="s">
+        <v>13</v>
+      </c>
+      <c r="B21" t="s">
+        <v>25</v>
+      </c>
+      <c r="C21" t="s">
+        <v>32</v>
+      </c>
+      <c r="E21" t="s">
+        <v>43</v>
+      </c>
+      <c r="I21" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
+      <c r="F22" t="s">
+        <v>59</v>
+      </c>
+      <c r="G22" t="s">
+        <v>81</v>
+      </c>
+      <c r="H22" t="s">
+        <v>95</v>
+      </c>
+      <c r="I22" t="s">
+        <v>117</v>
+      </c>
+      <c r="J22" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
+      <c r="A23" t="s">
+        <v>14</v>
+      </c>
+      <c r="B23" t="s">
+        <v>26</v>
+      </c>
+      <c r="C23" t="s">
+        <v>30</v>
+      </c>
+      <c r="D23" t="s">
+        <v>34</v>
+      </c>
+      <c r="I23" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
+      <c r="A24" t="s">
+        <v>14</v>
+      </c>
+      <c r="E24" t="s">
+        <v>41</v>
+      </c>
+      <c r="F24" t="s">
+        <v>60</v>
+      </c>
+      <c r="G24" t="s">
+        <v>82</v>
+      </c>
+      <c r="H24" t="s">
+        <v>95</v>
+      </c>
+      <c r="I24" t="s">
+        <v>119</v>
+      </c>
+      <c r="J24" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
+      <c r="A25" t="s">
+        <v>15</v>
+      </c>
+      <c r="B25" t="s">
+        <v>28</v>
+      </c>
+      <c r="C25" t="s">
+        <v>32</v>
+      </c>
+      <c r="E25" t="s">
+        <v>44</v>
+      </c>
+      <c r="I25" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
+      <c r="E26" t="s">
+        <v>45</v>
+      </c>
+      <c r="F26" t="s">
+        <v>61</v>
+      </c>
+      <c r="G26" t="s">
+        <v>83</v>
+      </c>
+      <c r="H26" t="s">
+        <v>97</v>
+      </c>
+      <c r="I26" t="s">
+        <v>121</v>
+      </c>
+      <c r="J26" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
+      <c r="A27" t="s">
+        <v>16</v>
+      </c>
+      <c r="B27" t="s">
+        <v>23</v>
+      </c>
+      <c r="C27" t="s">
+        <v>30</v>
+      </c>
+      <c r="D27" t="s">
+        <v>35</v>
+      </c>
+      <c r="I27" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10">
+      <c r="A28" t="s">
         <v>17</v>
       </c>
-      <c r="F5" t="s">
+      <c r="I28" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10">
+      <c r="E29" t="s">
+        <v>39</v>
+      </c>
+      <c r="F29" t="s">
+        <v>51</v>
+      </c>
+      <c r="G29" t="s">
+        <v>73</v>
+      </c>
+      <c r="H29" t="s">
+        <v>98</v>
+      </c>
+      <c r="I29" t="s">
+        <v>124</v>
+      </c>
+      <c r="J29" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
+      <c r="A30" t="s">
+        <v>17</v>
+      </c>
+      <c r="I30" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10">
+      <c r="F31" t="s">
+        <v>62</v>
+      </c>
+      <c r="G31" t="s">
+        <v>84</v>
+      </c>
+      <c r="H31" t="s">
+        <v>99</v>
+      </c>
+      <c r="I31" t="s">
+        <v>125</v>
+      </c>
+      <c r="J31" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10">
+      <c r="A32" t="s">
+        <v>16</v>
+      </c>
+      <c r="B32" t="s">
+        <v>23</v>
+      </c>
+      <c r="C32" t="s">
+        <v>30</v>
+      </c>
+      <c r="D32" t="s">
+        <v>35</v>
+      </c>
+      <c r="I32" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10">
+      <c r="A33" t="s">
+        <v>17</v>
+      </c>
+      <c r="I33" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10">
+      <c r="E34" t="s">
+        <v>42</v>
+      </c>
+      <c r="F34" t="s">
+        <v>63</v>
+      </c>
+      <c r="G34" t="s">
+        <v>85</v>
+      </c>
+      <c r="H34" t="s">
+        <v>98</v>
+      </c>
+      <c r="I34" t="s">
+        <v>127</v>
+      </c>
+      <c r="J34" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10">
+      <c r="A35" t="s">
+        <v>17</v>
+      </c>
+      <c r="I35" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10">
+      <c r="H36" t="s">
+        <v>99</v>
+      </c>
+      <c r="I36" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10">
+      <c r="A37" t="s">
+        <v>15</v>
+      </c>
+      <c r="B37" t="s">
+        <v>28</v>
+      </c>
+      <c r="C37" t="s">
+        <v>32</v>
+      </c>
+      <c r="E37" t="s">
+        <v>44</v>
+      </c>
+      <c r="I37" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10">
+      <c r="E38" t="s">
+        <v>45</v>
+      </c>
+      <c r="F38" t="s">
+        <v>64</v>
+      </c>
+      <c r="G38" t="s">
+        <v>86</v>
+      </c>
+      <c r="H38" t="s">
+        <v>98</v>
+      </c>
+      <c r="I38" t="s">
+        <v>129</v>
+      </c>
+      <c r="J38" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10">
+      <c r="A39" t="s">
+        <v>16</v>
+      </c>
+      <c r="B39" t="s">
+        <v>23</v>
+      </c>
+      <c r="C39" t="s">
+        <v>30</v>
+      </c>
+      <c r="D39" t="s">
+        <v>35</v>
+      </c>
+      <c r="I39" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10">
+      <c r="A40" t="s">
+        <v>17</v>
+      </c>
+      <c r="I40" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10">
+      <c r="E41" t="s">
+        <v>42</v>
+      </c>
+      <c r="H41" t="s">
+        <v>98</v>
+      </c>
+      <c r="I41" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10">
+      <c r="A42" t="s">
+        <v>17</v>
+      </c>
+      <c r="I42" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10">
+      <c r="F43" t="s">
+        <v>65</v>
+      </c>
+      <c r="G43" t="s">
+        <v>87</v>
+      </c>
+      <c r="H43" t="s">
+        <v>99</v>
+      </c>
+      <c r="I43" t="s">
+        <v>131</v>
+      </c>
+      <c r="J43" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10">
+      <c r="A44" t="s">
+        <v>16</v>
+      </c>
+      <c r="B44" t="s">
+        <v>23</v>
+      </c>
+      <c r="C44" t="s">
+        <v>30</v>
+      </c>
+      <c r="D44" t="s">
+        <v>35</v>
+      </c>
+      <c r="E44" t="s">
+        <v>42</v>
+      </c>
+      <c r="I44" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10">
+      <c r="A45" t="s">
+        <v>16</v>
+      </c>
+      <c r="F45" t="s">
+        <v>65</v>
+      </c>
+      <c r="G45" t="s">
+        <v>87</v>
+      </c>
+      <c r="H45" t="s">
+        <v>95</v>
+      </c>
+      <c r="I45" t="s">
+        <v>133</v>
+      </c>
+      <c r="J45" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10">
+      <c r="A46" t="s">
+        <v>18</v>
+      </c>
+      <c r="B46" t="s">
+        <v>28</v>
+      </c>
+      <c r="C46" t="s">
+        <v>32</v>
+      </c>
+      <c r="D46" t="s">
+        <v>36</v>
+      </c>
+      <c r="I46" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10">
+      <c r="A47" t="s">
+        <v>18</v>
+      </c>
+      <c r="E47" t="s">
+        <v>46</v>
+      </c>
+      <c r="F47" t="s">
+        <v>66</v>
+      </c>
+      <c r="G47" t="s">
+        <v>88</v>
+      </c>
+      <c r="I47" t="s">
+        <v>135</v>
+      </c>
+      <c r="J47" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10">
+      <c r="A48" t="s">
+        <v>18</v>
+      </c>
+      <c r="B48" t="s">
+        <v>29</v>
+      </c>
+      <c r="D48" t="s">
+        <v>35</v>
+      </c>
+      <c r="I48" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10">
+      <c r="A49" t="s">
+        <v>18</v>
+      </c>
+      <c r="E49" t="s">
+        <v>47</v>
+      </c>
+      <c r="H49" t="s">
+        <v>95</v>
+      </c>
+      <c r="I49" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10">
+      <c r="A50" t="s">
         <v>19</v>
       </c>
-      <c r="G5" t="s">
+      <c r="F50" t="s">
+        <v>67</v>
+      </c>
+      <c r="G50" t="s">
+        <v>89</v>
+      </c>
+      <c r="I50" t="s">
+        <v>138</v>
+      </c>
+      <c r="J50" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10">
+      <c r="A51" t="s">
+        <v>18</v>
+      </c>
+      <c r="F51" t="s">
+        <v>68</v>
+      </c>
+      <c r="G51" t="s">
+        <v>90</v>
+      </c>
+      <c r="I51" t="s">
+        <v>139</v>
+      </c>
+      <c r="J51" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10">
+      <c r="A52" t="s">
+        <v>20</v>
+      </c>
+      <c r="B52" t="s">
+        <v>29</v>
+      </c>
+      <c r="D52" t="s">
+        <v>35</v>
+      </c>
+      <c r="I52" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10">
+      <c r="A53" t="s">
         <v>21</v>
       </c>
-      <c r="H5" t="s">
-        <v>25</v>
-      </c>
-      <c r="I5" t="s">
-        <v>27</v>
+      <c r="I53" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10">
+      <c r="E54" t="s">
+        <v>42</v>
+      </c>
+      <c r="F54" t="s">
+        <v>69</v>
+      </c>
+      <c r="G54" t="s">
+        <v>91</v>
+      </c>
+      <c r="H54" t="s">
+        <v>98</v>
+      </c>
+      <c r="I54" t="s">
+        <v>142</v>
+      </c>
+      <c r="J54" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10">
+      <c r="A55" t="s">
+        <v>22</v>
+      </c>
+      <c r="B55" t="s">
+        <v>28</v>
+      </c>
+      <c r="C55" t="s">
+        <v>30</v>
+      </c>
+      <c r="D55" t="s">
+        <v>37</v>
+      </c>
+      <c r="F55" t="s">
+        <v>50</v>
+      </c>
+      <c r="I55" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10">
+      <c r="E56" t="s">
+        <v>48</v>
+      </c>
+      <c r="F56" t="s">
+        <v>70</v>
+      </c>
+      <c r="G56" t="s">
+        <v>92</v>
+      </c>
+      <c r="H56" t="s">
+        <v>95</v>
+      </c>
+      <c r="I56" t="s">
+        <v>144</v>
+      </c>
+      <c r="J56" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10">
+      <c r="A57" t="s">
+        <v>22</v>
+      </c>
+      <c r="B57" t="s">
+        <v>28</v>
+      </c>
+      <c r="C57" t="s">
+        <v>32</v>
+      </c>
+      <c r="E57" t="s">
+        <v>37</v>
+      </c>
+      <c r="F57" t="s">
+        <v>50</v>
+      </c>
+      <c r="I57" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10">
+      <c r="E58" t="s">
+        <v>49</v>
+      </c>
+      <c r="F58" t="s">
+        <v>71</v>
+      </c>
+      <c r="G58" t="s">
+        <v>93</v>
+      </c>
+      <c r="H58" t="s">
+        <v>99</v>
+      </c>
+      <c r="I58" t="s">
+        <v>146</v>
+      </c>
+      <c r="J58" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10">
+      <c r="A59" t="s">
+        <v>20</v>
+      </c>
+      <c r="B59" t="s">
+        <v>26</v>
+      </c>
+      <c r="D59" t="s">
+        <v>35</v>
+      </c>
+      <c r="I59" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10">
+      <c r="A60" t="s">
+        <v>20</v>
+      </c>
+      <c r="E60" t="s">
+        <v>41</v>
+      </c>
+      <c r="F60" t="s">
+        <v>72</v>
+      </c>
+      <c r="G60" t="s">
+        <v>94</v>
+      </c>
+      <c r="H60" t="s">
+        <v>95</v>
+      </c>
+      <c r="I60" t="s">
+        <v>148</v>
+      </c>
+      <c r="J60" t="s">
+        <v>171</v>
       </c>
     </row>
   </sheetData>

--- a/output_orderan.xlsx
+++ b/output_orderan.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="172">
   <si>
     <t>DATE</t>
   </si>
@@ -457,17 +457,14 @@
 Lokasi : cikokol</t>
   </si>
   <si>
-    <t>REQUEST ORDER KHUSUS 10/02/2026</t>
-  </si>
-  <si>
-    <t>Waktu loading : 02:00
+    <t>Waktu loading : 02:00 9 FEBRUARI 2026
 Rute/tujuan : CGK - SUB
 NAMA : WAHYUDI
 NOPOL: N 9549 UA
 NO HP :085784422398</t>
   </si>
   <si>
-    <t>Waktu loading : 03:00
+    <t>Waktu loading : 03:00 9 FEBRUARI 2026
 NAMA : YUDA
 NOPOL: W 8973 UQ
 NO HP :089507296985</t>
@@ -476,6 +473,9 @@
     <t>[WA_TS] Akbar Rafay: REQUEST ORDER  ONCALL 9 FEBRUARI 2026:
 2 unit  TWB 50 Cbm
 Lokasi : Cikokol</t>
+  </si>
+  <si>
+    <t>REQUEST ORDER KHUSUS 10/02/2026</t>
   </si>
   <si>
     <t>Waktu loading : 02:00
@@ -1032,7 +1032,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J60"/>
+  <dimension ref="A1:J58"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:10">
@@ -1544,72 +1544,84 @@
     </row>
     <row r="28" spans="1:10">
       <c r="A28" t="s">
-        <v>17</v>
+        <v>16</v>
+      </c>
+      <c r="E28" t="s">
+        <v>39</v>
+      </c>
+      <c r="F28" t="s">
+        <v>51</v>
+      </c>
+      <c r="G28" t="s">
+        <v>73</v>
       </c>
       <c r="I28" t="s">
         <v>123</v>
       </c>
+      <c r="J28" t="s">
+        <v>149</v>
+      </c>
     </row>
     <row r="29" spans="1:10">
-      <c r="E29" t="s">
-        <v>39</v>
+      <c r="A29" t="s">
+        <v>16</v>
       </c>
       <c r="F29" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="G29" t="s">
-        <v>73</v>
-      </c>
-      <c r="H29" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="I29" t="s">
         <v>124</v>
       </c>
       <c r="J29" t="s">
-        <v>149</v>
+        <v>161</v>
       </c>
     </row>
     <row r="30" spans="1:10">
       <c r="A30" t="s">
+        <v>16</v>
+      </c>
+      <c r="B30" t="s">
+        <v>23</v>
+      </c>
+      <c r="C30" t="s">
+        <v>30</v>
+      </c>
+      <c r="D30" t="s">
+        <v>35</v>
+      </c>
+      <c r="I30" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10">
+      <c r="A31" t="s">
         <v>17</v>
       </c>
-      <c r="I30" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10">
-      <c r="F31" t="s">
-        <v>62</v>
-      </c>
-      <c r="G31" t="s">
-        <v>84</v>
-      </c>
-      <c r="H31" t="s">
-        <v>99</v>
-      </c>
       <c r="I31" t="s">
-        <v>125</v>
-      </c>
-      <c r="J31" t="s">
-        <v>161</v>
+        <v>126</v>
       </c>
     </row>
     <row r="32" spans="1:10">
-      <c r="A32" t="s">
-        <v>16</v>
-      </c>
-      <c r="B32" t="s">
-        <v>23</v>
-      </c>
-      <c r="C32" t="s">
-        <v>30</v>
-      </c>
-      <c r="D32" t="s">
-        <v>35</v>
+      <c r="E32" t="s">
+        <v>42</v>
+      </c>
+      <c r="F32" t="s">
+        <v>63</v>
+      </c>
+      <c r="G32" t="s">
+        <v>85</v>
+      </c>
+      <c r="H32" t="s">
+        <v>98</v>
       </c>
       <c r="I32" t="s">
-        <v>126</v>
+        <v>127</v>
+      </c>
+      <c r="J32" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="33" spans="1:10">
@@ -1617,97 +1629,88 @@
         <v>17</v>
       </c>
       <c r="I33" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="34" spans="1:10">
-      <c r="E34" t="s">
-        <v>42</v>
-      </c>
-      <c r="F34" t="s">
-        <v>63</v>
-      </c>
-      <c r="G34" t="s">
-        <v>85</v>
-      </c>
       <c r="H34" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I34" t="s">
-        <v>127</v>
-      </c>
-      <c r="J34" t="s">
-        <v>162</v>
+        <v>128</v>
       </c>
     </row>
     <row r="35" spans="1:10">
       <c r="A35" t="s">
-        <v>17</v>
+        <v>15</v>
+      </c>
+      <c r="B35" t="s">
+        <v>28</v>
+      </c>
+      <c r="C35" t="s">
+        <v>32</v>
+      </c>
+      <c r="E35" t="s">
+        <v>44</v>
       </c>
       <c r="I35" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="36" spans="1:10">
+      <c r="E36" t="s">
+        <v>45</v>
+      </c>
+      <c r="F36" t="s">
+        <v>64</v>
+      </c>
+      <c r="G36" t="s">
+        <v>86</v>
+      </c>
       <c r="H36" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I36" t="s">
-        <v>128</v>
+        <v>129</v>
+      </c>
+      <c r="J36" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="37" spans="1:10">
       <c r="A37" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B37" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C37" t="s">
-        <v>32</v>
-      </c>
-      <c r="E37" t="s">
-        <v>44</v>
+        <v>30</v>
+      </c>
+      <c r="D37" t="s">
+        <v>35</v>
       </c>
       <c r="I37" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
     </row>
     <row r="38" spans="1:10">
-      <c r="E38" t="s">
-        <v>45</v>
-      </c>
-      <c r="F38" t="s">
-        <v>64</v>
-      </c>
-      <c r="G38" t="s">
-        <v>86</v>
-      </c>
-      <c r="H38" t="s">
+      <c r="A38" t="s">
+        <v>17</v>
+      </c>
+      <c r="I38" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10">
+      <c r="E39" t="s">
+        <v>42</v>
+      </c>
+      <c r="H39" t="s">
         <v>98</v>
       </c>
-      <c r="I38" t="s">
-        <v>129</v>
-      </c>
-      <c r="J38" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10">
-      <c r="A39" t="s">
-        <v>16</v>
-      </c>
-      <c r="B39" t="s">
-        <v>23</v>
-      </c>
-      <c r="C39" t="s">
-        <v>30</v>
-      </c>
-      <c r="D39" t="s">
-        <v>35</v>
-      </c>
       <c r="I39" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
     </row>
     <row r="40" spans="1:10">
@@ -1715,29 +1718,50 @@
         <v>17</v>
       </c>
       <c r="I40" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="41" spans="1:10">
-      <c r="E41" t="s">
-        <v>42</v>
+      <c r="F41" t="s">
+        <v>65</v>
+      </c>
+      <c r="G41" t="s">
+        <v>87</v>
       </c>
       <c r="H41" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I41" t="s">
-        <v>130</v>
+        <v>131</v>
+      </c>
+      <c r="J41" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="42" spans="1:10">
       <c r="A42" t="s">
-        <v>17</v>
+        <v>16</v>
+      </c>
+      <c r="B42" t="s">
+        <v>23</v>
+      </c>
+      <c r="C42" t="s">
+        <v>30</v>
+      </c>
+      <c r="D42" t="s">
+        <v>35</v>
+      </c>
+      <c r="E42" t="s">
+        <v>42</v>
       </c>
       <c r="I42" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
     </row>
     <row r="43" spans="1:10">
+      <c r="A43" t="s">
+        <v>16</v>
+      </c>
       <c r="F43" t="s">
         <v>65</v>
       </c>
@@ -1745,10 +1769,10 @@
         <v>87</v>
       </c>
       <c r="H43" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="I43" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="J43" t="s">
         <v>164</v>
@@ -1756,42 +1780,39 @@
     </row>
     <row r="44" spans="1:10">
       <c r="A44" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B44" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="C44" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D44" t="s">
-        <v>35</v>
-      </c>
-      <c r="E44" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="I44" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="45" spans="1:10">
       <c r="A45" t="s">
-        <v>16</v>
+        <v>18</v>
+      </c>
+      <c r="E45" t="s">
+        <v>46</v>
       </c>
       <c r="F45" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G45" t="s">
-        <v>87</v>
-      </c>
-      <c r="H45" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="I45" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J45" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="46" spans="1:10">
@@ -1799,16 +1820,13 @@
         <v>18</v>
       </c>
       <c r="B46" t="s">
-        <v>28</v>
-      </c>
-      <c r="C46" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D46" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I46" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="47" spans="1:10">
@@ -1816,123 +1834,129 @@
         <v>18</v>
       </c>
       <c r="E47" t="s">
-        <v>46</v>
-      </c>
-      <c r="F47" t="s">
-        <v>66</v>
-      </c>
-      <c r="G47" t="s">
-        <v>88</v>
+        <v>47</v>
+      </c>
+      <c r="H47" t="s">
+        <v>95</v>
       </c>
       <c r="I47" t="s">
-        <v>135</v>
-      </c>
-      <c r="J47" t="s">
-        <v>165</v>
+        <v>137</v>
       </c>
     </row>
     <row r="48" spans="1:10">
       <c r="A48" t="s">
-        <v>18</v>
-      </c>
-      <c r="B48" t="s">
-        <v>29</v>
-      </c>
-      <c r="D48" t="s">
-        <v>35</v>
+        <v>19</v>
+      </c>
+      <c r="F48" t="s">
+        <v>67</v>
+      </c>
+      <c r="G48" t="s">
+        <v>89</v>
       </c>
       <c r="I48" t="s">
-        <v>136</v>
+        <v>138</v>
+      </c>
+      <c r="J48" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="49" spans="1:10">
       <c r="A49" t="s">
         <v>18</v>
       </c>
-      <c r="E49" t="s">
-        <v>47</v>
-      </c>
-      <c r="H49" t="s">
-        <v>95</v>
+      <c r="F49" t="s">
+        <v>68</v>
+      </c>
+      <c r="G49" t="s">
+        <v>90</v>
       </c>
       <c r="I49" t="s">
-        <v>137</v>
+        <v>139</v>
+      </c>
+      <c r="J49" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="50" spans="1:10">
       <c r="A50" t="s">
-        <v>19</v>
-      </c>
-      <c r="F50" t="s">
-        <v>67</v>
-      </c>
-      <c r="G50" t="s">
-        <v>89</v>
+        <v>20</v>
+      </c>
+      <c r="B50" t="s">
+        <v>29</v>
+      </c>
+      <c r="D50" t="s">
+        <v>35</v>
       </c>
       <c r="I50" t="s">
-        <v>138</v>
-      </c>
-      <c r="J50" t="s">
-        <v>166</v>
+        <v>140</v>
       </c>
     </row>
     <row r="51" spans="1:10">
       <c r="A51" t="s">
-        <v>18</v>
-      </c>
-      <c r="F51" t="s">
-        <v>68</v>
-      </c>
-      <c r="G51" t="s">
-        <v>90</v>
+        <v>21</v>
       </c>
       <c r="I51" t="s">
-        <v>139</v>
-      </c>
-      <c r="J51" t="s">
-        <v>167</v>
+        <v>141</v>
       </c>
     </row>
     <row r="52" spans="1:10">
-      <c r="A52" t="s">
-        <v>20</v>
-      </c>
-      <c r="B52" t="s">
-        <v>29</v>
-      </c>
-      <c r="D52" t="s">
-        <v>35</v>
+      <c r="E52" t="s">
+        <v>42</v>
+      </c>
+      <c r="F52" t="s">
+        <v>69</v>
+      </c>
+      <c r="G52" t="s">
+        <v>91</v>
+      </c>
+      <c r="H52" t="s">
+        <v>98</v>
       </c>
       <c r="I52" t="s">
-        <v>140</v>
+        <v>142</v>
+      </c>
+      <c r="J52" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="53" spans="1:10">
       <c r="A53" t="s">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="B53" t="s">
+        <v>28</v>
+      </c>
+      <c r="C53" t="s">
+        <v>30</v>
+      </c>
+      <c r="D53" t="s">
+        <v>37</v>
+      </c>
+      <c r="F53" t="s">
+        <v>50</v>
       </c>
       <c r="I53" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="54" spans="1:10">
       <c r="E54" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="F54" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G54" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H54" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="I54" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="J54" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="55" spans="1:10">
@@ -1943,112 +1967,72 @@
         <v>28</v>
       </c>
       <c r="C55" t="s">
-        <v>30</v>
-      </c>
-      <c r="D55" t="s">
+        <v>32</v>
+      </c>
+      <c r="E55" t="s">
         <v>37</v>
       </c>
       <c r="F55" t="s">
         <v>50</v>
       </c>
       <c r="I55" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="56" spans="1:10">
       <c r="E56" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F56" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G56" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H56" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="I56" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="J56" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="57" spans="1:10">
       <c r="A57" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B57" t="s">
-        <v>28</v>
-      </c>
-      <c r="C57" t="s">
-        <v>32</v>
-      </c>
-      <c r="E57" t="s">
-        <v>37</v>
-      </c>
-      <c r="F57" t="s">
-        <v>50</v>
+        <v>26</v>
+      </c>
+      <c r="D57" t="s">
+        <v>35</v>
       </c>
       <c r="I57" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="58" spans="1:10">
+      <c r="A58" t="s">
+        <v>20</v>
+      </c>
       <c r="E58" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="F58" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G58" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H58" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="I58" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="J58" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="59" spans="1:10">
-      <c r="A59" t="s">
-        <v>20</v>
-      </c>
-      <c r="B59" t="s">
-        <v>26</v>
-      </c>
-      <c r="D59" t="s">
-        <v>35</v>
-      </c>
-      <c r="I59" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="60" spans="1:10">
-      <c r="A60" t="s">
-        <v>20</v>
-      </c>
-      <c r="E60" t="s">
-        <v>41</v>
-      </c>
-      <c r="F60" t="s">
-        <v>72</v>
-      </c>
-      <c r="G60" t="s">
-        <v>94</v>
-      </c>
-      <c r="H60" t="s">
-        <v>95</v>
-      </c>
-      <c r="I60" t="s">
-        <v>148</v>
-      </c>
-      <c r="J60" t="s">
         <v>171</v>
       </c>
     </row>

--- a/output_orderan.xlsx
+++ b/output_orderan.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="547" uniqueCount="273">
   <si>
     <t>DATE</t>
   </si>
@@ -85,21 +85,48 @@
     <t>12 feb 26</t>
   </si>
   <si>
+    <t>03 : 00 12 februari 2026</t>
+  </si>
+  <si>
+    <t>3 maret 2026</t>
+  </si>
+  <si>
+    <t>03 : 00 04032026</t>
+  </si>
+  <si>
+    <t>03 maret 2026</t>
+  </si>
+  <si>
+    <t>04 maret 2026</t>
+  </si>
+  <si>
+    <t>04 mar 2026</t>
+  </si>
+  <si>
+    <t>05 mar 26</t>
+  </si>
+  <si>
+    <t>05 maret 2026</t>
+  </si>
+  <si>
+    <t>06 maret 2026</t>
+  </si>
+  <si>
     <t>2</t>
   </si>
   <si>
     <t>6</t>
   </si>
   <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
     <t>24</t>
   </si>
   <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
     <t>1</t>
   </si>
   <si>
@@ -115,6 +142,9 @@
     <t>cddl</t>
   </si>
   <si>
+    <t>tronton</t>
+  </si>
+  <si>
     <t>jne</t>
   </si>
   <si>
@@ -130,15 +160,18 @@
     <t>cikarang</t>
   </si>
   <si>
+    <t>cgk sub</t>
+  </si>
+  <si>
+    <t>argo pantes</t>
+  </si>
+  <si>
+    <t>cgk jatim</t>
+  </si>
+  <si>
     <t>subcgk</t>
   </si>
   <si>
-    <t>cgk sub</t>
-  </si>
-  <si>
-    <t>cgk tentatif</t>
-  </si>
-  <si>
     <t>cgk mes</t>
   </si>
   <si>
@@ -166,6 +199,27 @@
     <t>cgkjbr</t>
   </si>
   <si>
+    <t>mes ddriver</t>
+  </si>
+  <si>
+    <t>sub cgk</t>
+  </si>
+  <si>
+    <t>suxcgk</t>
+  </si>
+  <si>
+    <t>cgkpsr</t>
+  </si>
+  <si>
+    <t>jatim tentatif</t>
+  </si>
+  <si>
+    <t>cgksub</t>
+  </si>
+  <si>
+    <t>pku</t>
+  </si>
+  <si>
     <t>akbar</t>
   </si>
   <si>
@@ -235,6 +289,54 @@
     <t>sri mardono</t>
   </si>
   <si>
+    <t>rosyit</t>
+  </si>
+  <si>
+    <t>m . ibnu</t>
+  </si>
+  <si>
+    <t>akiyat</t>
+  </si>
+  <si>
+    <t>ahmad wahyudi</t>
+  </si>
+  <si>
+    <t>ari purnama</t>
+  </si>
+  <si>
+    <t>dedeng</t>
+  </si>
+  <si>
+    <t>jupri</t>
+  </si>
+  <si>
+    <t>andi</t>
+  </si>
+  <si>
+    <t>misno</t>
+  </si>
+  <si>
+    <t>usman afandi</t>
+  </si>
+  <si>
+    <t>miyanta</t>
+  </si>
+  <si>
+    <t>davit</t>
+  </si>
+  <si>
+    <t>iwan hariono</t>
+  </si>
+  <si>
+    <t>suryadi</t>
+  </si>
+  <si>
+    <t>sobar</t>
+  </si>
+  <si>
+    <t>nasip</t>
+  </si>
+  <si>
     <t>n 9549 ua</t>
   </si>
   <si>
@@ -301,6 +403,54 @@
     <t>bk 8678 ve</t>
   </si>
   <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>b 9563 teu</t>
+  </si>
+  <si>
+    <t>l 9511 al</t>
+  </si>
+  <si>
+    <t>l 9722 ue</t>
+  </si>
+  <si>
+    <t>w 8323 nv</t>
+  </si>
+  <si>
+    <t>b 9679wt</t>
+  </si>
+  <si>
+    <t>b 9383 txv</t>
+  </si>
+  <si>
+    <t>e 9426 aa</t>
+  </si>
+  <si>
+    <t>bm 9273 ro</t>
+  </si>
+  <si>
+    <t>be 8610 db</t>
+  </si>
+  <si>
+    <t>bn 8038 rp</t>
+  </si>
+  <si>
+    <t>be 8456 fn</t>
+  </si>
+  <si>
+    <t>b 9726 sxw</t>
+  </si>
+  <si>
+    <t>bl 8188 jp</t>
+  </si>
+  <si>
+    <t>l 8183uv</t>
+  </si>
+  <si>
+    <t>bk 8330 vy</t>
+  </si>
+  <si>
     <t>segera</t>
   </si>
   <si>
@@ -314,6 +464,9 @@
   </si>
   <si>
     <t>03 : 00</t>
+  </si>
+  <si>
+    <t>06 : 00</t>
   </si>
   <si>
     <t>[WA_TS] Akbar Rafay: Request Unit On Call Tgl 06 febuary 2026
@@ -349,16 +502,6 @@
 driver  : Chandra
 Nopol  : L 8601 UH
 No hp  : +62 852-3168-1470</t>
-  </si>
-  <si>
-    <t>[WA_TS] Akbar Rafay: REQUEST ORDER ULANG ONCALL
-06 FEB 2026
-10 UNIT CDDL/24 CBM
-Lokasi : ARGOPANTES</t>
-  </si>
-  <si>
-    <t>Waktu loading : SEGERA
-Rute/tujuan : CGK - JATIM TENTATIF</t>
   </si>
   <si>
     <t>[WA_TS] Akbar Rafay: REQUEST ORDER ONCAL
@@ -608,6 +751,299 @@
 No hp  :085218843366</t>
   </si>
   <si>
+    <t>[WA_TS] Akbar Rafay: REQUEST ORDER ONCALL 12 FEBRUARI 2026:
+2 unit tronton 50 Cbm
+Lokasi : cikokol</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA 12 FEBRUARI 2026
+Rute/tujuan : CGK - SUB
+driver  : AGENG
+Nopol  : B 9654 YU
+No hp  : +62 857-0738-0584</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: REQUEST ORDER ONCALL 12 FEBRUARI 2026:
+3 UNIT TWB 50 Cbm
+Lokasi : ARGOPANTES</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA 12 FEBRUARI 2026
+Rute/tujuan : CGK - SUB
+driver  : Rosyit
+Nopol  : B 9563 TEU
+No hp  : 082313572678</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA 12 FEBRUARI 2026
+Rute/tujuan : CGK - SUB
+driver  : M.ibnu
+Nopol  : L 9511 AL
+No hp  : 082191633212</t>
+  </si>
+  <si>
+    <t>Waktu loading : 03:00 12 FEBRUARI 2026
+Rute/tujuan : CGK - SUB
+driver  : Akiyat
+Nopol  : L 9722 UE
+No hp  :081281122738
+Akbar Rafay: REQUEST ORDER ONCALL 12 FEBRUARI 2026:
+3 UNIT TWB 50 Cbm
+Lokasi : ARGOPANTES</t>
+  </si>
+  <si>
+    <t>Waktu loading : 03:00 12 FEBRUARI 2026
+Rute/tujuan : CGK - SUB
+Revisi
+driver  : Ahmad Wahyudi
+Nopol  : W 8323 NV
+No hp  : 085792725002
+Posisi sudah dilokasi muat</t>
+  </si>
+  <si>
+    <t>REQUEST  ORDER  ONCALL  3 MARET 2026
+5 UNIT WB/50 CBM
+Lokasi : ARGOPANTES</t>
+  </si>
+  <si>
+    <t>Waktu loading : 23:00 3 MARET 2026
+Rute/tujuan : CGK - MES 
+ddriver  : Sri Mardono
+Nopol  : BK 8678 VE
+No hp  : 085218843366</t>
+  </si>
+  <si>
+    <t>Waktu loading : 03:00 04-03-2026
+Rute/tujuan : CGK - MES 
+driver  :
+Nopol  :
+No hp  :</t>
+  </si>
+  <si>
+    <t>REQUEST  ORDER  ONCALL  3 MARET 2026
+6 UNIT WB/50 CBM
+Lokasi : ARGOPANTES</t>
+  </si>
+  <si>
+    <t>Waktu loading : 23:00 3 MARET 2026
+Rute/tujuan : CGK - SUB 
+driver  : Rosyit
+Nopol  : B 9562 TEU
+No hp  : 082313572678
+Driver : sofyan
+Nopol : B 9679WT
+No Hp : 082231837381</t>
+  </si>
+  <si>
+    <t>REQUEST  ORDER  ONCALL  3 MARET 2026
+1 UNIT WB/50 CBM
+Lokasi : ARGOPANTES</t>
+  </si>
+  <si>
+    <t>Waktu loading : 23:00 3 MARET 2026
+Rute/tujuan : SUB - CGK
+driver  : Yuda
+Nopol  : W 8973 UQ
+No hp  : 089507296985</t>
+  </si>
+  <si>
+    <t>REQUEST ORDER ONCALL 03 maret 2026:
+3 unit Cddl 24 Cbm
+Lokasi : Megahub</t>
+  </si>
+  <si>
+    <t>Waktu loading : 23:00 03 maret 2026
+Rute/tujuan : CGK - JATIM
+driver  : Ari purnama
+Nopol  : B 9383 TXV
+No hp : 082136689169
+Fyi pak  @Nomor tidak dikenal@Nomor tidak dikenal</t>
+  </si>
+  <si>
+    <t>REQUEST ULANG ORDER ONCALL 04 MARET 2026:
+8 unit Cddl 24 Cbm
+Lokasi : *argo pantes *</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA 04 MARET 2026
+Rute/tujuan : *CGK - Jateng tentatif
+Nama : Dedeng
+Nopol :E 9426 Aa
+No.hp : 0895393659401
+Request Unit On Call Tgl 04 Maret 2026
+5 UNIT TWB 50 CBM
+Lokasi : ARGOPANTES</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA 04 Maret 2026
+Rute/tujuan : CGK - PKU
+driver  : Jupri
+Nopol  : BM 9273 RO
+No Hp :082172471454</t>
+  </si>
+  <si>
+    <t>REQUEST ORDER ONCALL
+04 MARET 2026:
+5 UNIT TWB 50 CBM
+Lokasi : ARGOPANTES</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA
+Rute/tujuan : CGK - MES
+driver  : Andi
+Nopol  : BE 8610 DB
+No Hp :081374328877</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA
+Rute/tujuan : CGK - MES
+driver  : Misno
+Nopol  : BN 8038 RP
+No Hp :082211762649</t>
+  </si>
+  <si>
+    <t>REQUEST ORDER ONCALL
+04 MARET 2026:
+REVISI NOPOL BE 8610 DB
+5 UNIT TWB 50 CBM
+Lokasi : ARGOPANTES</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA
+Rute/tujuan : CGK - MES
+driver  : Usman Afandi
+Nopol  : BE 8456 FN
+No Hp : +62 853-7337-2594
+Request Order Oncall  04 Mar 2026
+2 UNIT TWB 50 CBM
+Lokasi : JNE SURABAYA
+Rute/ Tujuan   : SUX-CGK</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA 04 Mar 2026
+NAMA   : Wahyudi
+NOPOL : N 9549 UA
+NO HP : 085784422398
+Request Unit On Call Tgl 05 Mar 26
+1 Unit  Cddl / 24 Cbm
+Lokasi : Cikarang</t>
+  </si>
+  <si>
+    <t>Waktu loading : 06:00
+Rute/tujuan : CKR-JBR
+Driver   : miyanta
+Nopol  : F 9647 FH
+No Hp  :08118558105
+Request Unit On Call Tgl 05 Mar 26
+RAFAY
+1 Unit  Cddl / 24 Cbm
+Lokasi : Cikokol + Cikarang</t>
+  </si>
+  <si>
+    <t>Waktu loading : 03:00
+Rute/tujuan : CGK-PSR
+Driver   : Davit
+Nopol  : B 9726 SXW
+No Hp  :082117275166</t>
+  </si>
+  <si>
+    <t>REQUEST ORDER ONCALL
+05 MARET 2026:
+5 UNIT TWB 50 CBM
+Lokasi : ARGOPANTES</t>
+  </si>
+  <si>
+    <t>Waktu loading : 17:00 05-03-2026
+Rute/tujuan : CGK - SUB
+driver  : Iwan Hariono
+Nopol  : BL 8188 JP
+No Hp :081389976421
+Request Order Oncall  05 Maret  2026</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: REQUEST ORDER ULANG ONCALL
+06 FEB 2026
+10 UNIT CDDL/24 CBM
+Lokasi : ARGOPANTES</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA
+Rute/tujuan : CGK - JATIM TENTATIF
+2 UNIT TWB 50 CBM
+Lokasi : JNE SURABAYA
+Rute/ Tujuan   : SUX-CGK</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA
+Driver : Akiyat
+Nopol : L 9722 UE
+No HP :081281122738
+REQUER ORDER ULANG DAN TAMBAHAN ON CALL
+06 MARET 2026
+3 UNIT TWB 50 CBM
+ Lokasi : ARGOPANTES
+Rute / tujuan : *JATim TENTATIF</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA
+Nama 	: M. Ibnu
+Nopol		: L 9511 AL
+No Tlp	:082191633212
+Nama : Jamaadi
+Nopol : L 8786 BN
+No Hp :082229973792
+Nama : Suryadi 
+Nopol : L 8183UV
+No hp :085729113217
+REQUER ORDER ULANG DAN TAMBAHAN ON CALL
+06 MARET 2026
+3 UNIT TWB 50 CBM
+ Lokasi : ARGOPANTES
+Rute / tujuan : CGK-SUB</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA
+Nama 	: Yuda
+Nopol		: W 8973 UQ
+No Tlp	:089507296985
+REQUER ORDER ULANG DAN TAMBAHAN ON CALL
+06 MARET 2026
+DATA SUMATERA
+2 UNIT TWB 50 CBM
+ Lokasi : ARGOPANTES
+Rute / tujuan : PKU</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA
+Nama 	: Ridwan
+Nopol		: BK 8330 VY
+No Tlp	: 082382200400
+Fyi pak Sobar data tambahan nya
+REQUER ORDER ULANG DAN TAMBAHAN ON CALL
+06 MARET 2026
+DATA SUMATERA
+2 UNIT TWB 50 CBM
+ Lokasi : ARGOPANTES
+Rute / tujuan : PKU</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA
+Nama 	: Nasip
+Nopol		: BH 8165 QI
+No Tlp	:+6281272463920
+REQUER ORDER ULANG DAN TAMBAHAN ON CALL
+06 MARET 2026
+3 UNIT TWB 50 CBM
+Lokasi : ARGOPANTES
+Rute / tujuan : CGK-SUB</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA
+Nama 	: Wahyudi
+Nopol	: N 9549 UA
+No Tlp	:085784422398</t>
+  </si>
+  <si>
     <t>085784422398</t>
   </si>
   <si>
@@ -675,6 +1111,51 @@
   </si>
   <si>
     <t>085218843366</t>
+  </si>
+  <si>
+    <t>082313572678</t>
+  </si>
+  <si>
+    <t>082191633212</t>
+  </si>
+  <si>
+    <t>081281122738</t>
+  </si>
+  <si>
+    <t>085792725002</t>
+  </si>
+  <si>
+    <t>082136689169</t>
+  </si>
+  <si>
+    <t>0895393659401</t>
+  </si>
+  <si>
+    <t>082172471454</t>
+  </si>
+  <si>
+    <t>081374328877</t>
+  </si>
+  <si>
+    <t>082211762649</t>
+  </si>
+  <si>
+    <t>0 85373372594</t>
+  </si>
+  <si>
+    <t>08118558105</t>
+  </si>
+  <si>
+    <t>082117275166</t>
+  </si>
+  <si>
+    <t>081389976421</t>
+  </si>
+  <si>
+    <t>085729113217</t>
+  </si>
+  <si>
+    <t>082382200400</t>
   </si>
 </sst>
 </file>
@@ -1032,7 +1513,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J58"/>
+  <dimension ref="A1:J95"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:10">
@@ -1072,19 +1553,19 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="C2" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="D2" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="F2" t="s">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="I2" t="s">
-        <v>100</v>
+        <v>151</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -1092,19 +1573,19 @@
         <v>10</v>
       </c>
       <c r="E3" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="F3" t="s">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="G3" t="s">
-        <v>73</v>
+        <v>107</v>
       </c>
       <c r="I3" t="s">
-        <v>101</v>
+        <v>152</v>
       </c>
       <c r="J3" t="s">
-        <v>149</v>
+        <v>235</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -1112,19 +1593,19 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="C4" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="D4" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="F4" t="s">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="I4" t="s">
-        <v>100</v>
+        <v>151</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -1132,22 +1613,22 @@
         <v>10</v>
       </c>
       <c r="E5" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="F5" t="s">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="G5" t="s">
-        <v>74</v>
+        <v>108</v>
       </c>
       <c r="H5" t="s">
-        <v>95</v>
+        <v>145</v>
       </c>
       <c r="I5" t="s">
-        <v>102</v>
+        <v>153</v>
       </c>
       <c r="J5" t="s">
-        <v>150</v>
+        <v>236</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -1155,72 +1636,81 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C6" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="D6" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="I6" t="s">
-        <v>103</v>
+        <v>154</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="I7" t="s">
-        <v>104</v>
+        <v>155</v>
       </c>
       <c r="J7" t="s">
-        <v>151</v>
+        <v>237</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="E8" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="F8" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="G8" t="s">
-        <v>75</v>
+        <v>109</v>
       </c>
       <c r="H8" t="s">
-        <v>96</v>
+        <v>146</v>
       </c>
       <c r="I8" t="s">
-        <v>105</v>
+        <v>156</v>
       </c>
       <c r="J8" t="s">
-        <v>152</v>
+        <v>238</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B9" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="C9" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="D9" t="s">
-        <v>34</v>
+        <v>44</v>
+      </c>
+      <c r="E9" t="s">
+        <v>52</v>
       </c>
       <c r="I9" t="s">
-        <v>106</v>
+        <v>157</v>
       </c>
     </row>
     <row r="10" spans="1:10">
-      <c r="E10" t="s">
-        <v>40</v>
+      <c r="F10" t="s">
+        <v>72</v>
+      </c>
+      <c r="G10" t="s">
+        <v>110</v>
       </c>
       <c r="H10" t="s">
-        <v>95</v>
+        <v>145</v>
       </c>
       <c r="I10" t="s">
-        <v>107</v>
+        <v>158</v>
+      </c>
+      <c r="J10" t="s">
+        <v>239</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -1228,36 +1718,39 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="C11" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="D11" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="E11" t="s">
-        <v>41</v>
+        <v>48</v>
+      </c>
+      <c r="F11" t="s">
+        <v>68</v>
       </c>
       <c r="I11" t="s">
-        <v>108</v>
+        <v>159</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="F12" t="s">
-        <v>54</v>
+        <v>73</v>
       </c>
       <c r="G12" t="s">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="H12" t="s">
-        <v>95</v>
+        <v>145</v>
       </c>
       <c r="I12" t="s">
-        <v>109</v>
+        <v>160</v>
       </c>
       <c r="J12" t="s">
-        <v>153</v>
+        <v>240</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -1265,335 +1758,323 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="C13" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="D13" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="E13" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="F13" t="s">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="I13" t="s">
-        <v>110</v>
+        <v>159</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="F14" t="s">
-        <v>55</v>
+        <v>74</v>
       </c>
       <c r="G14" t="s">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="H14" t="s">
-        <v>95</v>
+        <v>145</v>
       </c>
       <c r="I14" t="s">
-        <v>111</v>
+        <v>161</v>
       </c>
       <c r="J14" t="s">
-        <v>154</v>
+        <v>241</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" t="s">
         <v>12</v>
       </c>
-      <c r="B15" t="s">
-        <v>27</v>
-      </c>
-      <c r="C15" t="s">
-        <v>30</v>
-      </c>
       <c r="D15" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="E15" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="F15" t="s">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="I15" t="s">
-        <v>110</v>
+        <v>162</v>
       </c>
     </row>
     <row r="16" spans="1:10">
       <c r="F16" t="s">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="G16" t="s">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="H16" t="s">
-        <v>95</v>
+        <v>145</v>
       </c>
       <c r="I16" t="s">
-        <v>112</v>
+        <v>163</v>
       </c>
       <c r="J16" t="s">
-        <v>155</v>
+        <v>242</v>
       </c>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" t="s">
         <v>12</v>
       </c>
+      <c r="B17" t="s">
+        <v>35</v>
+      </c>
+      <c r="C17" t="s">
+        <v>39</v>
+      </c>
       <c r="D17" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="E17" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="F17" t="s">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="I17" t="s">
-        <v>113</v>
+        <v>159</v>
       </c>
     </row>
     <row r="18" spans="1:10">
       <c r="F18" t="s">
-        <v>57</v>
+        <v>76</v>
       </c>
       <c r="G18" t="s">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="H18" t="s">
-        <v>95</v>
+        <v>145</v>
       </c>
       <c r="I18" t="s">
-        <v>114</v>
+        <v>164</v>
       </c>
       <c r="J18" t="s">
-        <v>156</v>
+        <v>243</v>
       </c>
     </row>
     <row r="19" spans="1:10">
       <c r="A19" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B19" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C19" t="s">
-        <v>30</v>
-      </c>
-      <c r="D19" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="E19" t="s">
-        <v>39</v>
-      </c>
-      <c r="F19" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="I19" t="s">
-        <v>110</v>
+        <v>165</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="F20" t="s">
-        <v>58</v>
+        <v>77</v>
       </c>
       <c r="G20" t="s">
-        <v>80</v>
+        <v>115</v>
       </c>
       <c r="H20" t="s">
-        <v>95</v>
+        <v>145</v>
       </c>
       <c r="I20" t="s">
-        <v>115</v>
+        <v>166</v>
       </c>
       <c r="J20" t="s">
-        <v>157</v>
+        <v>244</v>
       </c>
     </row>
     <row r="21" spans="1:10">
       <c r="A21" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="C21" t="s">
-        <v>32</v>
-      </c>
-      <c r="E21" t="s">
-        <v>43</v>
+        <v>39</v>
+      </c>
+      <c r="D21" t="s">
+        <v>44</v>
       </c>
       <c r="I21" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
+      <c r="A22" t="s">
+        <v>14</v>
+      </c>
+      <c r="E22" t="s">
+        <v>52</v>
+      </c>
+      <c r="F22" t="s">
+        <v>78</v>
+      </c>
+      <c r="G22" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="22" spans="1:10">
-      <c r="F22" t="s">
-        <v>59</v>
-      </c>
-      <c r="G22" t="s">
-        <v>81</v>
-      </c>
       <c r="H22" t="s">
-        <v>95</v>
+        <v>145</v>
       </c>
       <c r="I22" t="s">
-        <v>117</v>
+        <v>168</v>
       </c>
       <c r="J22" t="s">
-        <v>158</v>
+        <v>245</v>
       </c>
     </row>
     <row r="23" spans="1:10">
       <c r="A23" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B23" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="C23" t="s">
-        <v>30</v>
-      </c>
-      <c r="D23" t="s">
-        <v>34</v>
+        <v>41</v>
+      </c>
+      <c r="E23" t="s">
+        <v>55</v>
       </c>
       <c r="I23" t="s">
-        <v>118</v>
+        <v>169</v>
       </c>
     </row>
     <row r="24" spans="1:10">
-      <c r="A24" t="s">
-        <v>14</v>
-      </c>
       <c r="E24" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="F24" t="s">
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="G24" t="s">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="H24" t="s">
-        <v>95</v>
+        <v>147</v>
       </c>
       <c r="I24" t="s">
-        <v>119</v>
+        <v>170</v>
       </c>
       <c r="J24" t="s">
-        <v>159</v>
+        <v>246</v>
       </c>
     </row>
     <row r="25" spans="1:10">
       <c r="A25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B25" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C25" t="s">
-        <v>32</v>
-      </c>
-      <c r="E25" t="s">
-        <v>44</v>
+        <v>39</v>
+      </c>
+      <c r="D25" t="s">
+        <v>45</v>
       </c>
       <c r="I25" t="s">
-        <v>120</v>
+        <v>171</v>
       </c>
     </row>
     <row r="26" spans="1:10">
+      <c r="A26" t="s">
+        <v>16</v>
+      </c>
       <c r="E26" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="F26" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="G26" t="s">
-        <v>83</v>
-      </c>
-      <c r="H26" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="I26" t="s">
-        <v>121</v>
+        <v>172</v>
       </c>
       <c r="J26" t="s">
-        <v>160</v>
+        <v>235</v>
       </c>
     </row>
     <row r="27" spans="1:10">
       <c r="A27" t="s">
         <v>16</v>
       </c>
-      <c r="B27" t="s">
-        <v>23</v>
-      </c>
-      <c r="C27" t="s">
-        <v>30</v>
-      </c>
-      <c r="D27" t="s">
-        <v>35</v>
+      <c r="F27" t="s">
+        <v>80</v>
+      </c>
+      <c r="G27" t="s">
+        <v>118</v>
       </c>
       <c r="I27" t="s">
-        <v>122</v>
+        <v>173</v>
+      </c>
+      <c r="J27" t="s">
+        <v>247</v>
       </c>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" t="s">
         <v>16</v>
       </c>
-      <c r="E28" t="s">
+      <c r="B28" t="s">
+        <v>32</v>
+      </c>
+      <c r="C28" t="s">
         <v>39</v>
       </c>
-      <c r="F28" t="s">
-        <v>51</v>
-      </c>
-      <c r="G28" t="s">
-        <v>73</v>
+      <c r="D28" t="s">
+        <v>45</v>
       </c>
       <c r="I28" t="s">
-        <v>123</v>
-      </c>
-      <c r="J28" t="s">
-        <v>149</v>
+        <v>174</v>
       </c>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" t="s">
-        <v>16</v>
-      </c>
-      <c r="F29" t="s">
-        <v>62</v>
-      </c>
-      <c r="G29" t="s">
-        <v>84</v>
+        <v>17</v>
       </c>
       <c r="I29" t="s">
-        <v>124</v>
-      </c>
-      <c r="J29" t="s">
-        <v>161</v>
+        <v>175</v>
       </c>
     </row>
     <row r="30" spans="1:10">
-      <c r="A30" t="s">
-        <v>16</v>
-      </c>
-      <c r="B30" t="s">
-        <v>23</v>
-      </c>
-      <c r="C30" t="s">
-        <v>30</v>
-      </c>
-      <c r="D30" t="s">
-        <v>35</v>
+      <c r="E30" t="s">
+        <v>53</v>
+      </c>
+      <c r="F30" t="s">
+        <v>81</v>
+      </c>
+      <c r="G30" t="s">
+        <v>119</v>
+      </c>
+      <c r="H30" t="s">
+        <v>148</v>
       </c>
       <c r="I30" t="s">
-        <v>125</v>
+        <v>176</v>
+      </c>
+      <c r="J30" t="s">
+        <v>248</v>
       </c>
     </row>
     <row r="31" spans="1:10">
@@ -1601,97 +2082,88 @@
         <v>17</v>
       </c>
       <c r="I31" t="s">
-        <v>126</v>
+        <v>175</v>
       </c>
     </row>
     <row r="32" spans="1:10">
-      <c r="E32" t="s">
-        <v>42</v>
-      </c>
-      <c r="F32" t="s">
-        <v>63</v>
-      </c>
-      <c r="G32" t="s">
-        <v>85</v>
-      </c>
       <c r="H32" t="s">
-        <v>98</v>
+        <v>149</v>
       </c>
       <c r="I32" t="s">
-        <v>127</v>
-      </c>
-      <c r="J32" t="s">
-        <v>162</v>
+        <v>177</v>
       </c>
     </row>
     <row r="33" spans="1:10">
       <c r="A33" t="s">
-        <v>17</v>
+        <v>15</v>
+      </c>
+      <c r="B33" t="s">
+        <v>37</v>
+      </c>
+      <c r="C33" t="s">
+        <v>41</v>
+      </c>
+      <c r="E33" t="s">
+        <v>55</v>
       </c>
       <c r="I33" t="s">
-        <v>126</v>
+        <v>169</v>
       </c>
     </row>
     <row r="34" spans="1:10">
+      <c r="E34" t="s">
+        <v>56</v>
+      </c>
+      <c r="F34" t="s">
+        <v>82</v>
+      </c>
+      <c r="G34" t="s">
+        <v>120</v>
+      </c>
       <c r="H34" t="s">
-        <v>99</v>
+        <v>148</v>
       </c>
       <c r="I34" t="s">
-        <v>128</v>
+        <v>178</v>
+      </c>
+      <c r="J34" t="s">
+        <v>249</v>
       </c>
     </row>
     <row r="35" spans="1:10">
       <c r="A35" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B35" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C35" t="s">
-        <v>32</v>
-      </c>
-      <c r="E35" t="s">
-        <v>44</v>
+        <v>39</v>
+      </c>
+      <c r="D35" t="s">
+        <v>45</v>
       </c>
       <c r="I35" t="s">
-        <v>120</v>
+        <v>174</v>
       </c>
     </row>
     <row r="36" spans="1:10">
-      <c r="E36" t="s">
-        <v>45</v>
-      </c>
-      <c r="F36" t="s">
-        <v>64</v>
-      </c>
-      <c r="G36" t="s">
-        <v>86</v>
-      </c>
-      <c r="H36" t="s">
-        <v>98</v>
+      <c r="A36" t="s">
+        <v>17</v>
       </c>
       <c r="I36" t="s">
-        <v>129</v>
-      </c>
-      <c r="J36" t="s">
-        <v>163</v>
+        <v>175</v>
       </c>
     </row>
     <row r="37" spans="1:10">
-      <c r="A37" t="s">
-        <v>16</v>
-      </c>
-      <c r="B37" t="s">
-        <v>23</v>
-      </c>
-      <c r="C37" t="s">
-        <v>30</v>
-      </c>
-      <c r="D37" t="s">
-        <v>35</v>
+      <c r="E37" t="s">
+        <v>53</v>
+      </c>
+      <c r="H37" t="s">
+        <v>148</v>
       </c>
       <c r="I37" t="s">
-        <v>125</v>
+        <v>179</v>
       </c>
     </row>
     <row r="38" spans="1:10">
@@ -1699,83 +2171,101 @@
         <v>17</v>
       </c>
       <c r="I38" t="s">
-        <v>126</v>
+        <v>175</v>
       </c>
     </row>
     <row r="39" spans="1:10">
-      <c r="E39" t="s">
-        <v>42</v>
+      <c r="F39" t="s">
+        <v>83</v>
+      </c>
+      <c r="G39" t="s">
+        <v>121</v>
       </c>
       <c r="H39" t="s">
-        <v>98</v>
+        <v>149</v>
       </c>
       <c r="I39" t="s">
-        <v>130</v>
+        <v>180</v>
+      </c>
+      <c r="J39" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="40" spans="1:10">
       <c r="A40" t="s">
-        <v>17</v>
+        <v>16</v>
+      </c>
+      <c r="B40" t="s">
+        <v>32</v>
+      </c>
+      <c r="C40" t="s">
+        <v>39</v>
+      </c>
+      <c r="D40" t="s">
+        <v>45</v>
+      </c>
+      <c r="E40" t="s">
+        <v>53</v>
       </c>
       <c r="I40" t="s">
-        <v>126</v>
+        <v>181</v>
       </c>
     </row>
     <row r="41" spans="1:10">
+      <c r="A41" t="s">
+        <v>16</v>
+      </c>
       <c r="F41" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="G41" t="s">
-        <v>87</v>
+        <v>121</v>
       </c>
       <c r="H41" t="s">
-        <v>99</v>
+        <v>145</v>
       </c>
       <c r="I41" t="s">
-        <v>131</v>
+        <v>182</v>
       </c>
       <c r="J41" t="s">
-        <v>164</v>
+        <v>250</v>
       </c>
     </row>
     <row r="42" spans="1:10">
       <c r="A42" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B42" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="C42" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="D42" t="s">
-        <v>35</v>
-      </c>
-      <c r="E42" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="I42" t="s">
-        <v>132</v>
+        <v>183</v>
       </c>
     </row>
     <row r="43" spans="1:10">
       <c r="A43" t="s">
-        <v>16</v>
+        <v>18</v>
+      </c>
+      <c r="E43" t="s">
+        <v>57</v>
       </c>
       <c r="F43" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="G43" t="s">
-        <v>87</v>
-      </c>
-      <c r="H43" t="s">
-        <v>95</v>
+        <v>122</v>
       </c>
       <c r="I43" t="s">
-        <v>133</v>
+        <v>184</v>
       </c>
       <c r="J43" t="s">
-        <v>164</v>
+        <v>251</v>
       </c>
     </row>
     <row r="44" spans="1:10">
@@ -1783,16 +2273,13 @@
         <v>18</v>
       </c>
       <c r="B44" t="s">
-        <v>28</v>
-      </c>
-      <c r="C44" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D44" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="I44" t="s">
-        <v>134</v>
+        <v>185</v>
       </c>
     </row>
     <row r="45" spans="1:10">
@@ -1800,123 +2287,129 @@
         <v>18</v>
       </c>
       <c r="E45" t="s">
-        <v>46</v>
-      </c>
-      <c r="F45" t="s">
-        <v>66</v>
-      </c>
-      <c r="G45" t="s">
-        <v>88</v>
+        <v>58</v>
+      </c>
+      <c r="H45" t="s">
+        <v>145</v>
       </c>
       <c r="I45" t="s">
-        <v>135</v>
-      </c>
-      <c r="J45" t="s">
-        <v>165</v>
+        <v>186</v>
       </c>
     </row>
     <row r="46" spans="1:10">
       <c r="A46" t="s">
-        <v>18</v>
-      </c>
-      <c r="B46" t="s">
-        <v>29</v>
-      </c>
-      <c r="D46" t="s">
-        <v>35</v>
+        <v>19</v>
+      </c>
+      <c r="F46" t="s">
+        <v>85</v>
+      </c>
+      <c r="G46" t="s">
+        <v>123</v>
       </c>
       <c r="I46" t="s">
-        <v>136</v>
+        <v>187</v>
+      </c>
+      <c r="J46" t="s">
+        <v>252</v>
       </c>
     </row>
     <row r="47" spans="1:10">
       <c r="A47" t="s">
         <v>18</v>
       </c>
-      <c r="E47" t="s">
-        <v>47</v>
-      </c>
-      <c r="H47" t="s">
-        <v>95</v>
+      <c r="F47" t="s">
+        <v>86</v>
+      </c>
+      <c r="G47" t="s">
+        <v>124</v>
       </c>
       <c r="I47" t="s">
-        <v>137</v>
+        <v>188</v>
+      </c>
+      <c r="J47" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="48" spans="1:10">
       <c r="A48" t="s">
-        <v>19</v>
-      </c>
-      <c r="F48" t="s">
-        <v>67</v>
-      </c>
-      <c r="G48" t="s">
-        <v>89</v>
+        <v>20</v>
+      </c>
+      <c r="B48" t="s">
+        <v>38</v>
+      </c>
+      <c r="D48" t="s">
+        <v>45</v>
       </c>
       <c r="I48" t="s">
-        <v>138</v>
-      </c>
-      <c r="J48" t="s">
-        <v>166</v>
+        <v>189</v>
       </c>
     </row>
     <row r="49" spans="1:10">
       <c r="A49" t="s">
-        <v>18</v>
-      </c>
-      <c r="F49" t="s">
-        <v>68</v>
-      </c>
-      <c r="G49" t="s">
-        <v>90</v>
+        <v>21</v>
       </c>
       <c r="I49" t="s">
-        <v>139</v>
-      </c>
-      <c r="J49" t="s">
-        <v>167</v>
+        <v>190</v>
       </c>
     </row>
     <row r="50" spans="1:10">
-      <c r="A50" t="s">
-        <v>20</v>
-      </c>
-      <c r="B50" t="s">
-        <v>29</v>
-      </c>
-      <c r="D50" t="s">
-        <v>35</v>
+      <c r="E50" t="s">
+        <v>53</v>
+      </c>
+      <c r="F50" t="s">
+        <v>87</v>
+      </c>
+      <c r="G50" t="s">
+        <v>125</v>
+      </c>
+      <c r="H50" t="s">
+        <v>148</v>
       </c>
       <c r="I50" t="s">
-        <v>140</v>
+        <v>191</v>
+      </c>
+      <c r="J50" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="51" spans="1:10">
       <c r="A51" t="s">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="B51" t="s">
+        <v>37</v>
+      </c>
+      <c r="C51" t="s">
+        <v>39</v>
+      </c>
+      <c r="D51" t="s">
+        <v>47</v>
+      </c>
+      <c r="F51" t="s">
+        <v>68</v>
       </c>
       <c r="I51" t="s">
-        <v>141</v>
+        <v>192</v>
       </c>
     </row>
     <row r="52" spans="1:10">
       <c r="E52" t="s">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="F52" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="G52" t="s">
-        <v>91</v>
+        <v>126</v>
       </c>
       <c r="H52" t="s">
-        <v>98</v>
+        <v>145</v>
       </c>
       <c r="I52" t="s">
-        <v>142</v>
+        <v>193</v>
       </c>
       <c r="J52" t="s">
-        <v>168</v>
+        <v>255</v>
       </c>
     </row>
     <row r="53" spans="1:10">
@@ -1924,79 +2417,76 @@
         <v>22</v>
       </c>
       <c r="B53" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="C53" t="s">
-        <v>30</v>
-      </c>
-      <c r="D53" t="s">
-        <v>37</v>
+        <v>41</v>
+      </c>
+      <c r="E53" t="s">
+        <v>47</v>
       </c>
       <c r="F53" t="s">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="I53" t="s">
-        <v>143</v>
+        <v>194</v>
       </c>
     </row>
     <row r="54" spans="1:10">
       <c r="E54" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="F54" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="G54" t="s">
-        <v>92</v>
+        <v>127</v>
       </c>
       <c r="H54" t="s">
-        <v>95</v>
+        <v>149</v>
       </c>
       <c r="I54" t="s">
-        <v>144</v>
+        <v>195</v>
       </c>
       <c r="J54" t="s">
-        <v>169</v>
+        <v>256</v>
       </c>
     </row>
     <row r="55" spans="1:10">
       <c r="A55" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B55" t="s">
-        <v>28</v>
-      </c>
-      <c r="C55" t="s">
-        <v>32</v>
-      </c>
-      <c r="E55" t="s">
-        <v>37</v>
-      </c>
-      <c r="F55" t="s">
-        <v>50</v>
+        <v>34</v>
+      </c>
+      <c r="D55" t="s">
+        <v>45</v>
       </c>
       <c r="I55" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10">
+      <c r="A56" t="s">
+        <v>20</v>
+      </c>
+      <c r="E56" t="s">
+        <v>52</v>
+      </c>
+      <c r="F56" t="s">
+        <v>90</v>
+      </c>
+      <c r="G56" t="s">
+        <v>128</v>
+      </c>
+      <c r="H56" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="56" spans="1:10">
-      <c r="E56" t="s">
-        <v>49</v>
-      </c>
-      <c r="F56" t="s">
-        <v>71</v>
-      </c>
-      <c r="G56" t="s">
-        <v>93</v>
-      </c>
-      <c r="H56" t="s">
-        <v>99</v>
-      </c>
       <c r="I56" t="s">
-        <v>146</v>
+        <v>197</v>
       </c>
       <c r="J56" t="s">
-        <v>170</v>
+        <v>257</v>
       </c>
     </row>
     <row r="57" spans="1:10">
@@ -2004,13 +2494,16 @@
         <v>20</v>
       </c>
       <c r="B57" t="s">
-        <v>26</v>
+        <v>38</v>
+      </c>
+      <c r="C57" t="s">
+        <v>42</v>
       </c>
       <c r="D57" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="I57" t="s">
-        <v>147</v>
+        <v>198</v>
       </c>
     </row>
     <row r="58" spans="1:10">
@@ -2018,22 +2511,840 @@
         <v>20</v>
       </c>
       <c r="E58" t="s">
+        <v>48</v>
+      </c>
+      <c r="F58" t="s">
+        <v>88</v>
+      </c>
+      <c r="G58" t="s">
+        <v>129</v>
+      </c>
+      <c r="H58" t="s">
+        <v>145</v>
+      </c>
+      <c r="I58" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10">
+      <c r="A59" t="s">
+        <v>20</v>
+      </c>
+      <c r="B59" t="s">
+        <v>34</v>
+      </c>
+      <c r="C59" t="s">
+        <v>39</v>
+      </c>
+      <c r="D59" t="s">
+        <v>44</v>
+      </c>
+      <c r="I59" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10">
+      <c r="A60" t="s">
+        <v>20</v>
+      </c>
+      <c r="E60" t="s">
+        <v>48</v>
+      </c>
+      <c r="F60" t="s">
+        <v>91</v>
+      </c>
+      <c r="G60" t="s">
+        <v>130</v>
+      </c>
+      <c r="H60" t="s">
+        <v>145</v>
+      </c>
+      <c r="I60" t="s">
+        <v>201</v>
+      </c>
+      <c r="J60" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10">
+      <c r="A61" t="s">
+        <v>20</v>
+      </c>
+      <c r="E61" t="s">
+        <v>48</v>
+      </c>
+      <c r="F61" t="s">
+        <v>92</v>
+      </c>
+      <c r="G61" t="s">
+        <v>131</v>
+      </c>
+      <c r="H61" t="s">
+        <v>145</v>
+      </c>
+      <c r="I61" t="s">
+        <v>202</v>
+      </c>
+      <c r="J61" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10">
+      <c r="A62" t="s">
+        <v>20</v>
+      </c>
+      <c r="B62" t="s">
+        <v>34</v>
+      </c>
+      <c r="C62" t="s">
+        <v>39</v>
+      </c>
+      <c r="D62" t="s">
+        <v>44</v>
+      </c>
+      <c r="F62" t="s">
+        <v>93</v>
+      </c>
+      <c r="G62" t="s">
+        <v>132</v>
+      </c>
+      <c r="I62" t="s">
+        <v>203</v>
+      </c>
+      <c r="J62" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10">
+      <c r="A63" t="s">
+        <v>20</v>
+      </c>
+      <c r="E63" t="s">
+        <v>48</v>
+      </c>
+      <c r="F63" t="s">
+        <v>91</v>
+      </c>
+      <c r="G63" t="s">
+        <v>130</v>
+      </c>
+      <c r="H63" t="s">
+        <v>145</v>
+      </c>
+      <c r="I63" t="s">
+        <v>201</v>
+      </c>
+      <c r="J63" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10">
+      <c r="A64" t="s">
+        <v>20</v>
+      </c>
+      <c r="E64" t="s">
+        <v>48</v>
+      </c>
+      <c r="F64" t="s">
+        <v>92</v>
+      </c>
+      <c r="G64" t="s">
+        <v>131</v>
+      </c>
+      <c r="H64" t="s">
+        <v>145</v>
+      </c>
+      <c r="I64" t="s">
+        <v>202</v>
+      </c>
+      <c r="J64" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10">
+      <c r="A65" t="s">
+        <v>23</v>
+      </c>
+      <c r="D65" t="s">
+        <v>48</v>
+      </c>
+      <c r="F65" t="s">
+        <v>94</v>
+      </c>
+      <c r="G65" t="s">
+        <v>133</v>
+      </c>
+      <c r="I65" t="s">
+        <v>204</v>
+      </c>
+      <c r="J65" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10">
+      <c r="A66" t="s">
+        <v>24</v>
+      </c>
+      <c r="B66" t="s">
+        <v>35</v>
+      </c>
+      <c r="C66" t="s">
+        <v>40</v>
+      </c>
+      <c r="D66" t="s">
+        <v>44</v>
+      </c>
+      <c r="I66" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10">
+      <c r="A67" t="s">
+        <v>24</v>
+      </c>
+      <c r="E67" t="s">
+        <v>61</v>
+      </c>
+      <c r="F67" t="s">
+        <v>90</v>
+      </c>
+      <c r="G67" t="s">
+        <v>128</v>
+      </c>
+      <c r="I67" t="s">
+        <v>206</v>
+      </c>
+      <c r="J67" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10">
+      <c r="A68" t="s">
+        <v>25</v>
+      </c>
+      <c r="E68" t="s">
+        <v>52</v>
+      </c>
+      <c r="I68" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10">
+      <c r="A69" t="s">
+        <v>24</v>
+      </c>
+      <c r="B69" t="s">
+        <v>33</v>
+      </c>
+      <c r="C69" t="s">
+        <v>40</v>
+      </c>
+      <c r="D69" t="s">
+        <v>44</v>
+      </c>
+      <c r="I69" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10">
+      <c r="A70" t="s">
+        <v>24</v>
+      </c>
+      <c r="E70" t="s">
+        <v>48</v>
+      </c>
+      <c r="F70" t="s">
+        <v>70</v>
+      </c>
+      <c r="G70" t="s">
+        <v>134</v>
+      </c>
+      <c r="I70" t="s">
+        <v>209</v>
+      </c>
+      <c r="J70" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10">
+      <c r="A71" t="s">
+        <v>24</v>
+      </c>
+      <c r="B71" t="s">
+        <v>37</v>
+      </c>
+      <c r="C71" t="s">
+        <v>40</v>
+      </c>
+      <c r="D71" t="s">
+        <v>44</v>
+      </c>
+      <c r="I71" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10">
+      <c r="A72" t="s">
+        <v>24</v>
+      </c>
+      <c r="E72" t="s">
+        <v>62</v>
+      </c>
+      <c r="F72" t="s">
+        <v>80</v>
+      </c>
+      <c r="G72" t="s">
+        <v>118</v>
+      </c>
+      <c r="I72" t="s">
+        <v>211</v>
+      </c>
+      <c r="J72" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10">
+      <c r="A73" t="s">
+        <v>26</v>
+      </c>
+      <c r="B73" t="s">
+        <v>36</v>
+      </c>
+      <c r="C73" t="s">
         <v>41</v>
       </c>
-      <c r="F58" t="s">
-        <v>72</v>
-      </c>
-      <c r="G58" t="s">
-        <v>94</v>
-      </c>
-      <c r="H58" t="s">
+      <c r="D73" t="s">
+        <v>46</v>
+      </c>
+      <c r="I73" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10">
+      <c r="A74" t="s">
+        <v>26</v>
+      </c>
+      <c r="E74" t="s">
+        <v>50</v>
+      </c>
+      <c r="F74" t="s">
         <v>95</v>
       </c>
-      <c r="I58" t="s">
-        <v>148</v>
-      </c>
-      <c r="J58" t="s">
-        <v>171</v>
+      <c r="G74" t="s">
+        <v>135</v>
+      </c>
+      <c r="I74" t="s">
+        <v>213</v>
+      </c>
+      <c r="J74" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10">
+      <c r="A75" t="s">
+        <v>27</v>
+      </c>
+      <c r="B75" t="s">
+        <v>36</v>
+      </c>
+      <c r="C75" t="s">
+        <v>41</v>
+      </c>
+      <c r="D75" t="s">
+        <v>49</v>
+      </c>
+      <c r="I75" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10">
+      <c r="A76" t="s">
+        <v>27</v>
+      </c>
+      <c r="B76" t="s">
+        <v>35</v>
+      </c>
+      <c r="C76" t="s">
+        <v>39</v>
+      </c>
+      <c r="D76" t="s">
+        <v>44</v>
+      </c>
+      <c r="F76" t="s">
+        <v>96</v>
+      </c>
+      <c r="G76" t="s">
+        <v>136</v>
+      </c>
+      <c r="H76" t="s">
+        <v>145</v>
+      </c>
+      <c r="I76" t="s">
+        <v>215</v>
+      </c>
+      <c r="J76" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10">
+      <c r="A77" t="s">
+        <v>27</v>
+      </c>
+      <c r="E77" t="s">
+        <v>53</v>
+      </c>
+      <c r="F77" t="s">
+        <v>97</v>
+      </c>
+      <c r="G77" t="s">
+        <v>137</v>
+      </c>
+      <c r="H77" t="s">
+        <v>145</v>
+      </c>
+      <c r="I77" t="s">
+        <v>216</v>
+      </c>
+      <c r="J77" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10">
+      <c r="A78" t="s">
+        <v>27</v>
+      </c>
+      <c r="B78" t="s">
+        <v>35</v>
+      </c>
+      <c r="C78" t="s">
+        <v>39</v>
+      </c>
+      <c r="D78" t="s">
+        <v>44</v>
+      </c>
+      <c r="I78" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10">
+      <c r="E79" t="s">
+        <v>52</v>
+      </c>
+      <c r="F79" t="s">
+        <v>98</v>
+      </c>
+      <c r="G79" t="s">
+        <v>138</v>
+      </c>
+      <c r="H79" t="s">
+        <v>145</v>
+      </c>
+      <c r="I79" t="s">
+        <v>218</v>
+      </c>
+      <c r="J79" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10">
+      <c r="E80" t="s">
+        <v>52</v>
+      </c>
+      <c r="F80" t="s">
+        <v>99</v>
+      </c>
+      <c r="G80" t="s">
+        <v>139</v>
+      </c>
+      <c r="H80" t="s">
+        <v>145</v>
+      </c>
+      <c r="I80" t="s">
+        <v>219</v>
+      </c>
+      <c r="J80" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10">
+      <c r="A81" t="s">
+        <v>27</v>
+      </c>
+      <c r="B81" t="s">
+        <v>35</v>
+      </c>
+      <c r="C81" t="s">
+        <v>39</v>
+      </c>
+      <c r="D81" t="s">
+        <v>44</v>
+      </c>
+      <c r="G81" t="s">
+        <v>138</v>
+      </c>
+      <c r="I81" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10">
+      <c r="A82" t="s">
+        <v>28</v>
+      </c>
+      <c r="B82" t="s">
+        <v>32</v>
+      </c>
+      <c r="C82" t="s">
+        <v>39</v>
+      </c>
+      <c r="E82" t="s">
+        <v>63</v>
+      </c>
+      <c r="F82" t="s">
+        <v>100</v>
+      </c>
+      <c r="G82" t="s">
+        <v>140</v>
+      </c>
+      <c r="H82" t="s">
+        <v>145</v>
+      </c>
+      <c r="I82" t="s">
+        <v>221</v>
+      </c>
+      <c r="J82" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10">
+      <c r="A83" t="s">
+        <v>29</v>
+      </c>
+      <c r="B83" t="s">
+        <v>37</v>
+      </c>
+      <c r="C83" t="s">
+        <v>41</v>
+      </c>
+      <c r="E83" t="s">
+        <v>47</v>
+      </c>
+      <c r="F83" t="s">
+        <v>69</v>
+      </c>
+      <c r="G83" t="s">
+        <v>107</v>
+      </c>
+      <c r="H83" t="s">
+        <v>145</v>
+      </c>
+      <c r="I83" t="s">
+        <v>222</v>
+      </c>
+      <c r="J83" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10">
+      <c r="A84" t="s">
+        <v>29</v>
+      </c>
+      <c r="B84" t="s">
+        <v>37</v>
+      </c>
+      <c r="C84" t="s">
+        <v>41</v>
+      </c>
+      <c r="D84" t="s">
+        <v>45</v>
+      </c>
+      <c r="E84" t="s">
+        <v>47</v>
+      </c>
+      <c r="F84" t="s">
+        <v>101</v>
+      </c>
+      <c r="G84" t="s">
+        <v>127</v>
+      </c>
+      <c r="H84" t="s">
+        <v>150</v>
+      </c>
+      <c r="I84" t="s">
+        <v>223</v>
+      </c>
+      <c r="J84" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10">
+      <c r="E85" t="s">
+        <v>64</v>
+      </c>
+      <c r="F85" t="s">
+        <v>102</v>
+      </c>
+      <c r="G85" t="s">
+        <v>141</v>
+      </c>
+      <c r="H85" t="s">
+        <v>149</v>
+      </c>
+      <c r="I85" t="s">
+        <v>224</v>
+      </c>
+      <c r="J85" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10">
+      <c r="A86" t="s">
+        <v>30</v>
+      </c>
+      <c r="B86" t="s">
+        <v>35</v>
+      </c>
+      <c r="C86" t="s">
+        <v>39</v>
+      </c>
+      <c r="D86" t="s">
+        <v>44</v>
+      </c>
+      <c r="I86" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10">
+      <c r="A87" t="s">
+        <v>30</v>
+      </c>
+      <c r="E87" t="s">
+        <v>48</v>
+      </c>
+      <c r="F87" t="s">
+        <v>103</v>
+      </c>
+      <c r="G87" t="s">
+        <v>142</v>
+      </c>
+      <c r="I87" t="s">
+        <v>226</v>
+      </c>
+      <c r="J87" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10">
+      <c r="A88" t="s">
+        <v>11</v>
+      </c>
+      <c r="B88" t="s">
+        <v>36</v>
+      </c>
+      <c r="C88" t="s">
+        <v>41</v>
+      </c>
+      <c r="D88" t="s">
+        <v>44</v>
+      </c>
+      <c r="I88" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10">
+      <c r="B89" t="s">
+        <v>32</v>
+      </c>
+      <c r="C89" t="s">
+        <v>39</v>
+      </c>
+      <c r="D89" t="s">
+        <v>50</v>
+      </c>
+      <c r="E89" t="s">
+        <v>63</v>
+      </c>
+      <c r="H89" t="s">
+        <v>145</v>
+      </c>
+      <c r="I89" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10">
+      <c r="A90" t="s">
+        <v>31</v>
+      </c>
+      <c r="B90" t="s">
+        <v>34</v>
+      </c>
+      <c r="C90" t="s">
+        <v>39</v>
+      </c>
+      <c r="D90" t="s">
+        <v>44</v>
+      </c>
+      <c r="E90" t="s">
+        <v>65</v>
+      </c>
+      <c r="F90" t="s">
+        <v>93</v>
+      </c>
+      <c r="G90" t="s">
+        <v>132</v>
+      </c>
+      <c r="H90" t="s">
+        <v>145</v>
+      </c>
+      <c r="I90" t="s">
+        <v>229</v>
+      </c>
+      <c r="J90" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10">
+      <c r="A91" t="s">
+        <v>31</v>
+      </c>
+      <c r="B91" t="s">
+        <v>34</v>
+      </c>
+      <c r="C91" t="s">
+        <v>39</v>
+      </c>
+      <c r="D91" t="s">
+        <v>44</v>
+      </c>
+      <c r="E91" t="s">
+        <v>66</v>
+      </c>
+      <c r="F91" t="s">
+        <v>104</v>
+      </c>
+      <c r="G91" t="s">
+        <v>143</v>
+      </c>
+      <c r="H91" t="s">
+        <v>145</v>
+      </c>
+      <c r="I91" t="s">
+        <v>230</v>
+      </c>
+      <c r="J91" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10">
+      <c r="A92" t="s">
+        <v>31</v>
+      </c>
+      <c r="B92" t="s">
+        <v>32</v>
+      </c>
+      <c r="C92" t="s">
+        <v>39</v>
+      </c>
+      <c r="D92" t="s">
+        <v>44</v>
+      </c>
+      <c r="E92" t="s">
+        <v>67</v>
+      </c>
+      <c r="F92" t="s">
+        <v>80</v>
+      </c>
+      <c r="G92" t="s">
+        <v>118</v>
+      </c>
+      <c r="H92" t="s">
+        <v>145</v>
+      </c>
+      <c r="I92" t="s">
+        <v>231</v>
+      </c>
+      <c r="J92" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10">
+      <c r="A93" t="s">
+        <v>31</v>
+      </c>
+      <c r="B93" t="s">
+        <v>32</v>
+      </c>
+      <c r="C93" t="s">
+        <v>39</v>
+      </c>
+      <c r="D93" t="s">
+        <v>44</v>
+      </c>
+      <c r="E93" t="s">
+        <v>67</v>
+      </c>
+      <c r="F93" t="s">
+        <v>105</v>
+      </c>
+      <c r="G93" t="s">
+        <v>144</v>
+      </c>
+      <c r="H93" t="s">
+        <v>145</v>
+      </c>
+      <c r="I93" t="s">
+        <v>232</v>
+      </c>
+      <c r="J93" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10">
+      <c r="A94" t="s">
+        <v>31</v>
+      </c>
+      <c r="B94" t="s">
+        <v>34</v>
+      </c>
+      <c r="C94" t="s">
+        <v>39</v>
+      </c>
+      <c r="D94" t="s">
+        <v>44</v>
+      </c>
+      <c r="E94" t="s">
+        <v>66</v>
+      </c>
+      <c r="F94" t="s">
+        <v>106</v>
+      </c>
+      <c r="G94" t="s">
+        <v>125</v>
+      </c>
+      <c r="H94" t="s">
+        <v>145</v>
+      </c>
+      <c r="I94" t="s">
+        <v>233</v>
+      </c>
+      <c r="J94" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10">
+      <c r="F95" t="s">
+        <v>69</v>
+      </c>
+      <c r="G95" t="s">
+        <v>107</v>
+      </c>
+      <c r="H95" t="s">
+        <v>145</v>
+      </c>
+      <c r="I95" t="s">
+        <v>234</v>
+      </c>
+      <c r="J95" t="s">
+        <v>235</v>
       </c>
     </row>
   </sheetData>

--- a/output_orderan.xlsx
+++ b/output_orderan.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="547" uniqueCount="273">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="556" uniqueCount="278">
   <si>
     <t>DATE</t>
   </si>
@@ -112,6 +112,9 @@
     <t>06 maret 2026</t>
   </si>
   <si>
+    <t>18 : 00 05022026</t>
+  </si>
+  <si>
     <t>2</t>
   </si>
   <si>
@@ -337,6 +340,9 @@
     <t>nasip</t>
   </si>
   <si>
+    <t>syarial</t>
+  </si>
+  <si>
     <t>n 9549 ua</t>
   </si>
   <si>
@@ -449,6 +455,9 @@
   </si>
   <si>
     <t>bk 8330 vy</t>
+  </si>
+  <si>
+    <t>bm 8486 au</t>
   </si>
   <si>
     <t>segera</t>
@@ -1034,14 +1043,23 @@
 REQUER ORDER ULANG DAN TAMBAHAN ON CALL
 06 MARET 2026
 3 UNIT TWB 50 CBM
-Lokasi : ARGOPANTES
+ Lokasi : ARGOPANTES
 Rute / tujuan : CGK-SUB</t>
   </si>
   <si>
     <t>Waktu loading : SEGERA
 Nama 	: Wahyudi
-Nopol	: N 9549 UA
-No Tlp	:085784422398</t>
+Nopol		: N 9549 UA
+No Tlp	:085784422398
+5 UNIT TWB 50 CBM
+Lokasi : ARGOPANTES</t>
+  </si>
+  <si>
+    <t>Waktu loading : 18:00 05-02-2026
+Rute/tujuan : CGK - PKU
+driver  : Syarial
+Nopol  :BM 8486 AU
+No Hp :081317708658</t>
   </si>
   <si>
     <t>085784422398</t>
@@ -1156,6 +1174,9 @@
   </si>
   <si>
     <t>082382200400</t>
+  </si>
+  <si>
+    <t>081317708658</t>
   </si>
 </sst>
 </file>
@@ -1513,7 +1534,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J95"/>
+  <dimension ref="A1:J96"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:10">
@@ -1553,19 +1574,19 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I2" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -1573,19 +1594,19 @@
         <v>10</v>
       </c>
       <c r="E3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="I3" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="J3" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -1593,19 +1614,19 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I4" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -1613,22 +1634,22 @@
         <v>10</v>
       </c>
       <c r="E5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G5" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="H5" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="I5" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="J5" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -1636,44 +1657,44 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I6" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="I7" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="J7" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="E8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G8" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="H8" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="I8" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="J8" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -1681,36 +1702,36 @@
         <v>12</v>
       </c>
       <c r="B9" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C9" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E9" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I9" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="F10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G10" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="H10" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="I10" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="J10" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -1718,39 +1739,39 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C11" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E11" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F11" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I11" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="F12" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G12" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="H12" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="I12" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="J12" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -1758,39 +1779,39 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D13" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E13" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F13" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I13" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="F14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G14" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H14" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="I14" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="J14" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -1798,33 +1819,33 @@
         <v>12</v>
       </c>
       <c r="D15" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E15" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F15" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I15" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
     </row>
     <row r="16" spans="1:10">
       <c r="F16" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G16" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="H16" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="I16" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="J16" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -1832,39 +1853,39 @@
         <v>12</v>
       </c>
       <c r="B17" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C17" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D17" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E17" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F17" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I17" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
     </row>
     <row r="18" spans="1:10">
       <c r="F18" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G18" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="H18" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="I18" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="J18" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -1872,33 +1893,33 @@
         <v>13</v>
       </c>
       <c r="B19" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C19" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E19" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I19" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="F20" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G20" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="H20" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="I20" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="J20" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -1906,16 +1927,16 @@
         <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C21" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D21" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I21" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -1923,22 +1944,22 @@
         <v>14</v>
       </c>
       <c r="E22" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F22" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G22" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="H22" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="I22" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="J22" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -1946,36 +1967,36 @@
         <v>15</v>
       </c>
       <c r="B23" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C23" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E23" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I23" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
     </row>
     <row r="24" spans="1:10">
       <c r="E24" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F24" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G24" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="H24" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="I24" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="J24" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -1983,16 +2004,16 @@
         <v>16</v>
       </c>
       <c r="B25" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C25" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D25" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I25" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -2000,19 +2021,19 @@
         <v>16</v>
       </c>
       <c r="E26" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F26" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G26" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="I26" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="J26" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -2020,16 +2041,16 @@
         <v>16</v>
       </c>
       <c r="F27" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G27" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="I27" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="J27" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -2037,16 +2058,16 @@
         <v>16</v>
       </c>
       <c r="B28" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C28" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D28" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I28" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -2054,27 +2075,27 @@
         <v>17</v>
       </c>
       <c r="I29" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
     </row>
     <row r="30" spans="1:10">
       <c r="E30" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F30" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G30" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="H30" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="I30" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="J30" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
     </row>
     <row r="31" spans="1:10">
@@ -2082,15 +2103,15 @@
         <v>17</v>
       </c>
       <c r="I31" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
     </row>
     <row r="32" spans="1:10">
       <c r="H32" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="I32" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
     </row>
     <row r="33" spans="1:10">
@@ -2098,36 +2119,36 @@
         <v>15</v>
       </c>
       <c r="B33" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C33" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E33" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I33" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
     </row>
     <row r="34" spans="1:10">
       <c r="E34" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F34" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G34" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="H34" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="I34" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="J34" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
     </row>
     <row r="35" spans="1:10">
@@ -2135,16 +2156,16 @@
         <v>16</v>
       </c>
       <c r="B35" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C35" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D35" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I35" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="36" spans="1:10">
@@ -2152,18 +2173,18 @@
         <v>17</v>
       </c>
       <c r="I36" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
     </row>
     <row r="37" spans="1:10">
       <c r="E37" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H37" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="I37" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
     </row>
     <row r="38" spans="1:10">
@@ -2171,24 +2192,24 @@
         <v>17</v>
       </c>
       <c r="I38" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
     </row>
     <row r="39" spans="1:10">
       <c r="F39" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G39" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="H39" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="I39" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="J39" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
     </row>
     <row r="40" spans="1:10">
@@ -2196,19 +2217,19 @@
         <v>16</v>
       </c>
       <c r="B40" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C40" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D40" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E40" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I40" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
     </row>
     <row r="41" spans="1:10">
@@ -2216,19 +2237,19 @@
         <v>16</v>
       </c>
       <c r="F41" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G41" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="H41" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="I41" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="J41" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
     </row>
     <row r="42" spans="1:10">
@@ -2236,16 +2257,16 @@
         <v>18</v>
       </c>
       <c r="B42" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C42" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D42" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I42" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
     </row>
     <row r="43" spans="1:10">
@@ -2253,19 +2274,19 @@
         <v>18</v>
       </c>
       <c r="E43" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F43" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G43" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="I43" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="J43" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
     </row>
     <row r="44" spans="1:10">
@@ -2273,13 +2294,13 @@
         <v>18</v>
       </c>
       <c r="B44" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D44" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I44" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
     </row>
     <row r="45" spans="1:10">
@@ -2287,13 +2308,13 @@
         <v>18</v>
       </c>
       <c r="E45" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H45" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="I45" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
     </row>
     <row r="46" spans="1:10">
@@ -2301,16 +2322,16 @@
         <v>19</v>
       </c>
       <c r="F46" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G46" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="I46" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="J46" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
     </row>
     <row r="47" spans="1:10">
@@ -2318,16 +2339,16 @@
         <v>18</v>
       </c>
       <c r="F47" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G47" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="I47" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="J47" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
     </row>
     <row r="48" spans="1:10">
@@ -2335,13 +2356,13 @@
         <v>20</v>
       </c>
       <c r="B48" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D48" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I48" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
     </row>
     <row r="49" spans="1:10">
@@ -2349,27 +2370,27 @@
         <v>21</v>
       </c>
       <c r="I49" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
     </row>
     <row r="50" spans="1:10">
       <c r="E50" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F50" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G50" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="H50" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="I50" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="J50" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
     </row>
     <row r="51" spans="1:10">
@@ -2377,39 +2398,39 @@
         <v>22</v>
       </c>
       <c r="B51" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C51" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D51" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F51" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I51" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
     </row>
     <row r="52" spans="1:10">
       <c r="E52" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F52" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G52" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="H52" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="I52" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="J52" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
     </row>
     <row r="53" spans="1:10">
@@ -2417,39 +2438,39 @@
         <v>22</v>
       </c>
       <c r="B53" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C53" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E53" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F53" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I53" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
     </row>
     <row r="54" spans="1:10">
       <c r="E54" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F54" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G54" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="H54" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="I54" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="J54" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
     </row>
     <row r="55" spans="1:10">
@@ -2457,13 +2478,13 @@
         <v>20</v>
       </c>
       <c r="B55" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D55" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I55" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
     </row>
     <row r="56" spans="1:10">
@@ -2471,22 +2492,22 @@
         <v>20</v>
       </c>
       <c r="E56" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F56" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G56" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="H56" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="I56" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="J56" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
     </row>
     <row r="57" spans="1:10">
@@ -2494,16 +2515,16 @@
         <v>20</v>
       </c>
       <c r="B57" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C57" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D57" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I57" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
     </row>
     <row r="58" spans="1:10">
@@ -2511,19 +2532,19 @@
         <v>20</v>
       </c>
       <c r="E58" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F58" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G58" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="H58" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="I58" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
     </row>
     <row r="59" spans="1:10">
@@ -2531,16 +2552,16 @@
         <v>20</v>
       </c>
       <c r="B59" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C59" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D59" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I59" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
     </row>
     <row r="60" spans="1:10">
@@ -2548,22 +2569,22 @@
         <v>20</v>
       </c>
       <c r="E60" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F60" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G60" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="H60" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="I60" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="J60" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
     </row>
     <row r="61" spans="1:10">
@@ -2571,22 +2592,22 @@
         <v>20</v>
       </c>
       <c r="E61" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F61" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G61" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="H61" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="I61" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="J61" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
     </row>
     <row r="62" spans="1:10">
@@ -2594,25 +2615,25 @@
         <v>20</v>
       </c>
       <c r="B62" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C62" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D62" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F62" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G62" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="I62" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="J62" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
     </row>
     <row r="63" spans="1:10">
@@ -2620,22 +2641,22 @@
         <v>20</v>
       </c>
       <c r="E63" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F63" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G63" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="H63" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="I63" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="J63" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
     </row>
     <row r="64" spans="1:10">
@@ -2643,22 +2664,22 @@
         <v>20</v>
       </c>
       <c r="E64" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F64" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G64" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="H64" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="I64" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="J64" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
     </row>
     <row r="65" spans="1:10">
@@ -2666,19 +2687,19 @@
         <v>23</v>
       </c>
       <c r="D65" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F65" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G65" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="I65" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="J65" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
     </row>
     <row r="66" spans="1:10">
@@ -2686,16 +2707,16 @@
         <v>24</v>
       </c>
       <c r="B66" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C66" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D66" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I66" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
     </row>
     <row r="67" spans="1:10">
@@ -2703,19 +2724,19 @@
         <v>24</v>
       </c>
       <c r="E67" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F67" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G67" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="I67" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="J67" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
     </row>
     <row r="68" spans="1:10">
@@ -2723,10 +2744,10 @@
         <v>25</v>
       </c>
       <c r="E68" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I68" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
     </row>
     <row r="69" spans="1:10">
@@ -2734,16 +2755,16 @@
         <v>24</v>
       </c>
       <c r="B69" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C69" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D69" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I69" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
     </row>
     <row r="70" spans="1:10">
@@ -2751,19 +2772,19 @@
         <v>24</v>
       </c>
       <c r="E70" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F70" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G70" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="I70" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="J70" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
     </row>
     <row r="71" spans="1:10">
@@ -2771,16 +2792,16 @@
         <v>24</v>
       </c>
       <c r="B71" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C71" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D71" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I71" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
     </row>
     <row r="72" spans="1:10">
@@ -2788,19 +2809,19 @@
         <v>24</v>
       </c>
       <c r="E72" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F72" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G72" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="I72" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="J72" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
     </row>
     <row r="73" spans="1:10">
@@ -2808,16 +2829,16 @@
         <v>26</v>
       </c>
       <c r="B73" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C73" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D73" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I73" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
     </row>
     <row r="74" spans="1:10">
@@ -2825,19 +2846,19 @@
         <v>26</v>
       </c>
       <c r="E74" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F74" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G74" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="I74" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="J74" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
     </row>
     <row r="75" spans="1:10">
@@ -2845,16 +2866,16 @@
         <v>27</v>
       </c>
       <c r="B75" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C75" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D75" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I75" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
     </row>
     <row r="76" spans="1:10">
@@ -2862,28 +2883,28 @@
         <v>27</v>
       </c>
       <c r="B76" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C76" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D76" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F76" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G76" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="H76" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="I76" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="J76" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
     </row>
     <row r="77" spans="1:10">
@@ -2891,22 +2912,22 @@
         <v>27</v>
       </c>
       <c r="E77" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F77" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G77" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H77" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="I77" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="J77" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
     </row>
     <row r="78" spans="1:10">
@@ -2914,56 +2935,56 @@
         <v>27</v>
       </c>
       <c r="B78" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C78" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D78" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I78" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
     </row>
     <row r="79" spans="1:10">
       <c r="E79" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F79" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G79" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H79" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="I79" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="J79" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
     </row>
     <row r="80" spans="1:10">
       <c r="E80" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F80" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G80" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H80" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="I80" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="J80" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="81" spans="1:10">
@@ -2971,19 +2992,19 @@
         <v>27</v>
       </c>
       <c r="B81" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C81" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D81" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G81" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="I81" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
     </row>
     <row r="82" spans="1:10">
@@ -2991,28 +3012,28 @@
         <v>28</v>
       </c>
       <c r="B82" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C82" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E82" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F82" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G82" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H82" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="I82" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="J82" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="83" spans="1:10">
@@ -3020,28 +3041,28 @@
         <v>29</v>
       </c>
       <c r="B83" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C83" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E83" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F83" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G83" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="H83" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="I83" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="J83" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
     </row>
     <row r="84" spans="1:10">
@@ -3049,51 +3070,51 @@
         <v>29</v>
       </c>
       <c r="B84" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C84" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D84" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E84" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F84" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G84" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="H84" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="I84" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="J84" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="85" spans="1:10">
       <c r="E85" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F85" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G85" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="H85" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="I85" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="J85" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
     </row>
     <row r="86" spans="1:10">
@@ -3101,16 +3122,16 @@
         <v>30</v>
       </c>
       <c r="B86" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C86" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D86" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I86" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
     </row>
     <row r="87" spans="1:10">
@@ -3118,19 +3139,19 @@
         <v>30</v>
       </c>
       <c r="E87" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F87" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G87" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="I87" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="J87" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
     </row>
     <row r="88" spans="1:10">
@@ -3138,36 +3159,36 @@
         <v>11</v>
       </c>
       <c r="B88" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C88" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D88" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I88" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
     </row>
     <row r="89" spans="1:10">
       <c r="B89" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C89" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D89" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E89" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H89" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="I89" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
     </row>
     <row r="90" spans="1:10">
@@ -3175,31 +3196,31 @@
         <v>31</v>
       </c>
       <c r="B90" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C90" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D90" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E90" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F90" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G90" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H90" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="I90" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="J90" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
     </row>
     <row r="91" spans="1:10">
@@ -3207,31 +3228,31 @@
         <v>31</v>
       </c>
       <c r="B91" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C91" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D91" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E91" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F91" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G91" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H91" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="I91" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="J91" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
     </row>
     <row r="92" spans="1:10">
@@ -3239,31 +3260,31 @@
         <v>31</v>
       </c>
       <c r="B92" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C92" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D92" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E92" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F92" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G92" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="H92" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="I92" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="J92" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
     </row>
     <row r="93" spans="1:10">
@@ -3271,31 +3292,31 @@
         <v>31</v>
       </c>
       <c r="B93" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C93" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D93" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E93" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F93" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G93" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="H93" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="I93" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="J93" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
     </row>
     <row r="94" spans="1:10">
@@ -3303,48 +3324,77 @@
         <v>31</v>
       </c>
       <c r="B94" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C94" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D94" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E94" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F94" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G94" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="H94" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="I94" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="J94" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
     </row>
     <row r="95" spans="1:10">
+      <c r="B95" t="s">
+        <v>36</v>
+      </c>
+      <c r="C95" t="s">
+        <v>40</v>
+      </c>
+      <c r="D95" t="s">
+        <v>45</v>
+      </c>
       <c r="F95" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G95" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="H95" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="I95" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="J95" t="s">
-        <v>235</v>
+        <v>239</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10">
+      <c r="A96" t="s">
+        <v>32</v>
+      </c>
+      <c r="E96" t="s">
+        <v>54</v>
+      </c>
+      <c r="F96" t="s">
+        <v>108</v>
+      </c>
+      <c r="G96" t="s">
+        <v>147</v>
+      </c>
+      <c r="I96" t="s">
+        <v>238</v>
+      </c>
+      <c r="J96" t="s">
+        <v>277</v>
       </c>
     </row>
   </sheetData>

--- a/output_orderan.xlsx
+++ b/output_orderan.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="556" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="561" uniqueCount="282">
   <si>
     <t>DATE</t>
   </si>
@@ -70,6 +70,9 @@
     <t>10 / 02 / 2026</t>
   </si>
   <si>
+    <t>02 . 00 / 10</t>
+  </si>
+  <si>
     <t>11 februari 2026</t>
   </si>
   <si>
@@ -91,7 +94,7 @@
     <t>3 maret 2026</t>
   </si>
   <si>
-    <t>03 : 00 04032026</t>
+    <t>03 : 00 / 04</t>
   </si>
   <si>
     <t>03 maret 2026</t>
@@ -106,13 +109,16 @@
     <t>05 mar 26</t>
   </si>
   <si>
+    <t>06 mar 26</t>
+  </si>
+  <si>
     <t>05 maret 2026</t>
   </si>
   <si>
     <t>06 maret 2026</t>
   </si>
   <si>
-    <t>18 : 00 05022026</t>
+    <t>18 : 00 / 05</t>
   </si>
   <si>
     <t>2</t>
@@ -643,7 +649,7 @@
 NO HP :</t>
   </si>
   <si>
-    <t>Waktu loading : 02:00
+    <t>Waktu loading :  02.00/10
 Rute/tujuan : SRG-CGK
 Driver : Supriadi
 Nopol : B 9586 TXV
@@ -726,7 +732,7 @@
 Lokasi : Cikarang</t>
   </si>
   <si>
-    <t>Waktu loading : SEGERA
+    <t>Waktu loading : SEGERA 12 Feb 26
 Rute/tujuan : CKR-SUB-SUX 
 Driver   : AGENG
 Nopol  : B9654YU
@@ -822,7 +828,7 @@
 No hp  : 085218843366</t>
   </si>
   <si>
-    <t>Waktu loading : 03:00 04-03-2026
+    <t>Waktu loading :  03:00/04
 Rute/tujuan : CGK - MES 
 driver  :
 Nopol  :
@@ -938,6 +944,9 @@
 Lokasi : Cikarang</t>
   </si>
   <si>
+    <t>REQUEST ORDER KHUSUS 06 Mar 26</t>
+  </si>
+  <si>
     <t>Waktu loading : 06:00
 Rute/tujuan : CKR-JBR
 Driver   : miyanta
@@ -949,6 +958,9 @@
 Lokasi : Cikokol + Cikarang</t>
   </si>
   <si>
+    <t>REQUEST ORDER KHUSUS 06  Mar 26</t>
+  </si>
+  <si>
     <t>Waktu loading : 03:00
 Rute/tujuan : CGK-PSR
 Driver   : Davit
@@ -962,7 +974,7 @@
 Lokasi : ARGOPANTES</t>
   </si>
   <si>
-    <t>Waktu loading : 17:00 05-03-2026
+    <t>Waktu loading :  17:00/05
 Rute/tujuan : CGK - SUB
 driver  : Iwan Hariono
 Nopol  : BL 8188 JP
@@ -1055,7 +1067,7 @@
 Lokasi : ARGOPANTES</t>
   </si>
   <si>
-    <t>Waktu loading : 18:00 05-02-2026
+    <t>Waktu loading :  18:00/05
 Rute/tujuan : CGK - PKU
 driver  : Syarial
 Nopol  :BM 8486 AU
@@ -1534,7 +1546,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J96"/>
+  <dimension ref="A1:J98"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:10">
@@ -1574,19 +1586,19 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -1594,19 +1606,19 @@
         <v>10</v>
       </c>
       <c r="E3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G3" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="I3" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="J3" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -1614,19 +1626,19 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D4" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F4" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I4" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -1634,22 +1646,22 @@
         <v>10</v>
       </c>
       <c r="E5" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G5" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="H5" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="I5" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="J5" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -1657,44 +1669,44 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D6" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="I6" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="I7" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="J7" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="E8" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G8" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="H8" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="I8" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="J8" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -1702,36 +1714,36 @@
         <v>12</v>
       </c>
       <c r="B9" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C9" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D9" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E9" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="I9" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="F10" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G10" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H10" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="I10" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="J10" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -1739,39 +1751,39 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C11" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D11" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E11" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I11" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="F12" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G12" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="H12" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="I12" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="J12" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -1779,39 +1791,39 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C13" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D13" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E13" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F13" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I13" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="F14" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G14" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="H14" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="I14" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="J14" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -1819,33 +1831,33 @@
         <v>12</v>
       </c>
       <c r="D15" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E15" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F15" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I15" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="16" spans="1:10">
       <c r="F16" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G16" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="H16" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="I16" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="J16" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -1853,39 +1865,39 @@
         <v>12</v>
       </c>
       <c r="B17" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C17" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D17" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E17" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F17" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I17" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="18" spans="1:10">
       <c r="F18" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G18" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="H18" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="I18" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="J18" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -1893,33 +1905,33 @@
         <v>13</v>
       </c>
       <c r="B19" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C19" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E19" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="I19" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="F20" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G20" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="H20" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="I20" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="J20" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -1927,16 +1939,16 @@
         <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C21" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D21" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="I21" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -1944,22 +1956,22 @@
         <v>14</v>
       </c>
       <c r="E22" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F22" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G22" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="H22" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="I22" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="J22" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -1967,36 +1979,36 @@
         <v>15</v>
       </c>
       <c r="B23" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C23" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E23" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="I23" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="24" spans="1:10">
       <c r="E24" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F24" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G24" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="H24" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="I24" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="J24" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -2004,16 +2016,16 @@
         <v>16</v>
       </c>
       <c r="B25" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C25" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D25" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I25" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -2021,19 +2033,19 @@
         <v>16</v>
       </c>
       <c r="E26" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F26" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G26" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="I26" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="J26" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -2041,16 +2053,16 @@
         <v>16</v>
       </c>
       <c r="F27" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G27" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="I27" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="J27" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -2058,16 +2070,16 @@
         <v>16</v>
       </c>
       <c r="B28" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C28" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D28" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I28" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -2075,27 +2087,27 @@
         <v>17</v>
       </c>
       <c r="I29" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="30" spans="1:10">
       <c r="E30" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F30" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G30" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="H30" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="I30" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="J30" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
     </row>
     <row r="31" spans="1:10">
@@ -2103,15 +2115,15 @@
         <v>17</v>
       </c>
       <c r="I31" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="32" spans="1:10">
       <c r="H32" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="I32" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="33" spans="1:10">
@@ -2119,36 +2131,36 @@
         <v>15</v>
       </c>
       <c r="B33" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C33" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E33" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="I33" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="34" spans="1:10">
+      <c r="A34" t="s">
+        <v>18</v>
+      </c>
       <c r="E34" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F34" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="G34" t="s">
-        <v>122</v>
-      </c>
-      <c r="H34" t="s">
-        <v>151</v>
+        <v>124</v>
       </c>
       <c r="I34" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="J34" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
     </row>
     <row r="35" spans="1:10">
@@ -2156,16 +2168,16 @@
         <v>16</v>
       </c>
       <c r="B35" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C35" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D35" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I35" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="36" spans="1:10">
@@ -2173,18 +2185,18 @@
         <v>17</v>
       </c>
       <c r="I36" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="37" spans="1:10">
       <c r="E37" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="H37" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="I37" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="38" spans="1:10">
@@ -2192,24 +2204,24 @@
         <v>17</v>
       </c>
       <c r="I38" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="39" spans="1:10">
       <c r="F39" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G39" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="H39" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="I39" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="J39" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
     </row>
     <row r="40" spans="1:10">
@@ -2217,19 +2229,19 @@
         <v>16</v>
       </c>
       <c r="B40" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C40" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D40" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E40" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="I40" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="41" spans="1:10">
@@ -2237,1164 +2249,1183 @@
         <v>16</v>
       </c>
       <c r="F41" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G41" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="H41" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="I41" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="J41" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
     </row>
     <row r="42" spans="1:10">
       <c r="A42" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B42" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C42" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D42" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="I42" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="43" spans="1:10">
       <c r="A43" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E43" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F43" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="G43" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="I43" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="J43" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
     </row>
     <row r="44" spans="1:10">
       <c r="A44" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B44" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D44" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I44" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="45" spans="1:10">
       <c r="A45" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E45" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="H45" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="I45" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="46" spans="1:10">
       <c r="A46" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F46" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="G46" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="I46" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="J46" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
     </row>
     <row r="47" spans="1:10">
       <c r="A47" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F47" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G47" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="I47" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="J47" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
     </row>
     <row r="48" spans="1:10">
       <c r="A48" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B48" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D48" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I48" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="49" spans="1:10">
       <c r="A49" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I49" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="50" spans="1:10">
       <c r="E50" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F50" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G50" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="H50" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="I50" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="J50" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
     </row>
     <row r="51" spans="1:10">
       <c r="A51" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B51" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C51" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D51" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F51" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I51" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="52" spans="1:10">
+      <c r="A52" t="s">
+        <v>23</v>
+      </c>
       <c r="E52" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F52" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G52" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="H52" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="I52" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="J52" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
     </row>
     <row r="53" spans="1:10">
       <c r="A53" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B53" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C53" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E53" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F53" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I53" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="54" spans="1:10">
       <c r="E54" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F54" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G54" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="H54" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="I54" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="J54" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
     </row>
     <row r="55" spans="1:10">
       <c r="A55" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B55" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D55" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I55" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="56" spans="1:10">
       <c r="A56" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E56" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F56" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G56" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="H56" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="I56" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="J56" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
     </row>
     <row r="57" spans="1:10">
       <c r="A57" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B57" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C57" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D57" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I57" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="58" spans="1:10">
       <c r="A58" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E58" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F58" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G58" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="H58" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="I58" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="59" spans="1:10">
       <c r="A59" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B59" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C59" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D59" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="I59" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="60" spans="1:10">
       <c r="A60" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E60" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F60" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G60" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H60" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="I60" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="J60" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
     </row>
     <row r="61" spans="1:10">
       <c r="A61" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E61" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F61" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="G61" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="H61" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="I61" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="J61" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
     </row>
     <row r="62" spans="1:10">
       <c r="A62" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B62" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C62" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D62" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F62" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G62" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="I62" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="J62" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
     </row>
     <row r="63" spans="1:10">
       <c r="A63" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E63" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F63" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G63" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H63" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="I63" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="J63" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
     </row>
     <row r="64" spans="1:10">
       <c r="A64" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E64" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F64" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="G64" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="H64" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="I64" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="J64" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
     </row>
     <row r="65" spans="1:10">
       <c r="A65" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D65" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F65" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="G65" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="I65" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="J65" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
     </row>
     <row r="66" spans="1:10">
       <c r="A66" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B66" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C66" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D66" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="I66" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="67" spans="1:10">
       <c r="A67" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E67" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F67" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G67" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="I67" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="J67" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
     </row>
     <row r="68" spans="1:10">
       <c r="A68" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E68" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="I68" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="69" spans="1:10">
       <c r="A69" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B69" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C69" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D69" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="I69" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="70" spans="1:10">
       <c r="A70" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E70" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F70" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G70" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="I70" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J70" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
     </row>
     <row r="71" spans="1:10">
       <c r="A71" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B71" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C71" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D71" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="I71" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="72" spans="1:10">
       <c r="A72" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E72" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F72" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G72" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="I72" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="J72" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
     </row>
     <row r="73" spans="1:10">
       <c r="A73" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B73" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C73" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D73" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="I73" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="74" spans="1:10">
       <c r="A74" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E74" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F74" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G74" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="I74" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="J74" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="75" spans="1:10">
       <c r="A75" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B75" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C75" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D75" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="I75" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="76" spans="1:10">
       <c r="A76" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B76" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C76" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D76" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F76" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="G76" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H76" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="I76" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="J76" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="77" spans="1:10">
       <c r="A77" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E77" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F77" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G77" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H77" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="I77" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="J77" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="78" spans="1:10">
       <c r="A78" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B78" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C78" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D78" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="I78" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="79" spans="1:10">
       <c r="E79" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F79" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="G79" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H79" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="I79" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="J79" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
     </row>
     <row r="80" spans="1:10">
       <c r="E80" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F80" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G80" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="H80" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="I80" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="J80" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
     </row>
     <row r="81" spans="1:10">
       <c r="A81" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B81" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C81" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D81" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G81" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="I81" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="82" spans="1:10">
       <c r="A82" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B82" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C82" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E82" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F82" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G82" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H82" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="I82" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="J82" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
     </row>
     <row r="83" spans="1:10">
       <c r="A83" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B83" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C83" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E83" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F83" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G83" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="H83" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="I83" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="J83" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
     </row>
     <row r="84" spans="1:10">
       <c r="A84" t="s">
-        <v>29</v>
-      </c>
-      <c r="B84" t="s">
-        <v>38</v>
-      </c>
-      <c r="C84" t="s">
-        <v>42</v>
-      </c>
-      <c r="D84" t="s">
-        <v>46</v>
-      </c>
-      <c r="E84" t="s">
+        <v>31</v>
+      </c>
+      <c r="I84" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10">
+      <c r="A85" t="s">
+        <v>30</v>
+      </c>
+      <c r="B85" t="s">
+        <v>40</v>
+      </c>
+      <c r="C85" t="s">
+        <v>44</v>
+      </c>
+      <c r="D85" t="s">
         <v>48</v>
       </c>
-      <c r="F84" t="s">
-        <v>102</v>
-      </c>
-      <c r="G84" t="s">
-        <v>129</v>
-      </c>
-      <c r="H84" t="s">
-        <v>153</v>
-      </c>
-      <c r="I84" t="s">
-        <v>226</v>
-      </c>
-      <c r="J84" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="85" spans="1:10">
       <c r="E85" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="F85" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G85" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="H85" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="I85" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="J85" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
     </row>
     <row r="86" spans="1:10">
       <c r="A86" t="s">
-        <v>30</v>
-      </c>
-      <c r="B86" t="s">
-        <v>36</v>
-      </c>
-      <c r="C86" t="s">
-        <v>40</v>
-      </c>
-      <c r="D86" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="I86" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="87" spans="1:10">
-      <c r="A87" t="s">
-        <v>30</v>
-      </c>
       <c r="E87" t="s">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="F87" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G87" t="s">
-        <v>144</v>
+        <v>145</v>
+      </c>
+      <c r="H87" t="s">
+        <v>154</v>
       </c>
       <c r="I87" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="J87" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="88" spans="1:10">
       <c r="A88" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="B88" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C88" t="s">
         <v>42</v>
       </c>
       <c r="D88" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="I88" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="89" spans="1:10">
-      <c r="B89" t="s">
-        <v>33</v>
-      </c>
-      <c r="C89" t="s">
-        <v>40</v>
-      </c>
-      <c r="D89" t="s">
+      <c r="A89" t="s">
+        <v>32</v>
+      </c>
+      <c r="E89" t="s">
         <v>51</v>
       </c>
-      <c r="E89" t="s">
-        <v>64</v>
-      </c>
-      <c r="H89" t="s">
-        <v>148</v>
+      <c r="F89" t="s">
+        <v>106</v>
+      </c>
+      <c r="G89" t="s">
+        <v>146</v>
       </c>
       <c r="I89" t="s">
-        <v>231</v>
+        <v>233</v>
+      </c>
+      <c r="J89" t="s">
+        <v>278</v>
       </c>
     </row>
     <row r="90" spans="1:10">
       <c r="A90" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="B90" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C90" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D90" t="s">
-        <v>45</v>
-      </c>
-      <c r="E90" t="s">
-        <v>66</v>
-      </c>
-      <c r="F90" t="s">
-        <v>94</v>
-      </c>
-      <c r="G90" t="s">
-        <v>134</v>
-      </c>
-      <c r="H90" t="s">
-        <v>148</v>
+        <v>47</v>
       </c>
       <c r="I90" t="s">
-        <v>232</v>
-      </c>
-      <c r="J90" t="s">
-        <v>264</v>
+        <v>234</v>
       </c>
     </row>
     <row r="91" spans="1:10">
-      <c r="A91" t="s">
-        <v>31</v>
-      </c>
       <c r="B91" t="s">
         <v>35</v>
       </c>
       <c r="C91" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D91" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="E91" t="s">
-        <v>67</v>
-      </c>
-      <c r="F91" t="s">
-        <v>105</v>
-      </c>
-      <c r="G91" t="s">
-        <v>145</v>
+        <v>66</v>
       </c>
       <c r="H91" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="I91" t="s">
-        <v>233</v>
-      </c>
-      <c r="J91" t="s">
-        <v>275</v>
+        <v>235</v>
       </c>
     </row>
     <row r="92" spans="1:10">
       <c r="A92" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B92" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C92" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D92" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E92" t="s">
         <v>68</v>
       </c>
       <c r="F92" t="s">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="G92" t="s">
-        <v>120</v>
+        <v>136</v>
       </c>
       <c r="H92" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="I92" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="J92" t="s">
-        <v>251</v>
+        <v>268</v>
       </c>
     </row>
     <row r="93" spans="1:10">
       <c r="A93" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B93" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C93" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D93" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E93" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F93" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G93" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H93" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="I93" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="J93" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
     </row>
     <row r="94" spans="1:10">
       <c r="A94" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B94" t="s">
         <v>35</v>
       </c>
       <c r="C94" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D94" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E94" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F94" t="s">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="G94" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="H94" t="s">
+        <v>150</v>
+      </c>
+      <c r="I94" t="s">
+        <v>238</v>
+      </c>
+      <c r="J94" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10">
+      <c r="A95" t="s">
+        <v>33</v>
+      </c>
+      <c r="B95" t="s">
+        <v>35</v>
+      </c>
+      <c r="C95" t="s">
+        <v>42</v>
+      </c>
+      <c r="D95" t="s">
+        <v>47</v>
+      </c>
+      <c r="E95" t="s">
+        <v>70</v>
+      </c>
+      <c r="F95" t="s">
+        <v>108</v>
+      </c>
+      <c r="G95" t="s">
         <v>148</v>
       </c>
-      <c r="I94" t="s">
-        <v>236</v>
-      </c>
-      <c r="J94" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="95" spans="1:10">
-      <c r="B95" t="s">
-        <v>36</v>
-      </c>
-      <c r="C95" t="s">
-        <v>40</v>
-      </c>
-      <c r="D95" t="s">
-        <v>45</v>
-      </c>
-      <c r="F95" t="s">
-        <v>70</v>
-      </c>
-      <c r="G95" t="s">
-        <v>109</v>
-      </c>
       <c r="H95" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="I95" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="J95" t="s">
-        <v>239</v>
+        <v>280</v>
       </c>
     </row>
     <row r="96" spans="1:10">
       <c r="A96" t="s">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="B96" t="s">
+        <v>37</v>
+      </c>
+      <c r="C96" t="s">
+        <v>42</v>
+      </c>
+      <c r="D96" t="s">
+        <v>47</v>
       </c>
       <c r="E96" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="F96" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G96" t="s">
-        <v>147</v>
+        <v>129</v>
+      </c>
+      <c r="H96" t="s">
+        <v>150</v>
       </c>
       <c r="I96" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="J96" t="s">
-        <v>277</v>
+        <v>262</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10">
+      <c r="B97" t="s">
+        <v>38</v>
+      </c>
+      <c r="C97" t="s">
+        <v>42</v>
+      </c>
+      <c r="D97" t="s">
+        <v>47</v>
+      </c>
+      <c r="F97" t="s">
+        <v>72</v>
+      </c>
+      <c r="G97" t="s">
+        <v>111</v>
+      </c>
+      <c r="H97" t="s">
+        <v>150</v>
+      </c>
+      <c r="I97" t="s">
+        <v>241</v>
+      </c>
+      <c r="J97" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="98" spans="1:10">
+      <c r="A98" t="s">
+        <v>34</v>
+      </c>
+      <c r="E98" t="s">
+        <v>56</v>
+      </c>
+      <c r="F98" t="s">
+        <v>110</v>
+      </c>
+      <c r="G98" t="s">
+        <v>149</v>
+      </c>
+      <c r="I98" t="s">
+        <v>242</v>
+      </c>
+      <c r="J98" t="s">
+        <v>281</v>
       </c>
     </row>
   </sheetData>

--- a/output_orderan.xlsx
+++ b/output_orderan.xlsx
@@ -70,7 +70,7 @@
     <t>10 / 02 / 2026</t>
   </si>
   <si>
-    <t>02 . 00 / 10</t>
+    <t>02 : 00 100226</t>
   </si>
   <si>
     <t>11 februari 2026</t>
@@ -94,7 +94,7 @@
     <t>3 maret 2026</t>
   </si>
   <si>
-    <t>03 : 00 / 04</t>
+    <t>03 : 00 04032026</t>
   </si>
   <si>
     <t>03 maret 2026</t>
@@ -118,7 +118,7 @@
     <t>06 maret 2026</t>
   </si>
   <si>
-    <t>18 : 00 / 05</t>
+    <t>18 : 00 05022026</t>
   </si>
   <si>
     <t>2</t>
@@ -649,7 +649,7 @@
 NO HP :</t>
   </si>
   <si>
-    <t>Waktu loading :  02.00/10
+    <t>Waktu loading : 02:00 10-02-26
 Rute/tujuan : SRG-CGK
 Driver : Supriadi
 Nopol : B 9586 TXV
@@ -828,7 +828,7 @@
 No hp  : 085218843366</t>
   </si>
   <si>
-    <t>Waktu loading :  03:00/04
+    <t>Waktu loading : 03:00 04-03-2026
 Rute/tujuan : CGK - MES 
 driver  :
 Nopol  :
@@ -974,7 +974,7 @@
 Lokasi : ARGOPANTES</t>
   </si>
   <si>
-    <t>Waktu loading :  17:00/05
+    <t>Waktu loading : 17:00 05-03-2026
 Rute/tujuan : CGK - SUB
 driver  : Iwan Hariono
 Nopol  : BL 8188 JP
@@ -1067,7 +1067,7 @@
 Lokasi : ARGOPANTES</t>
   </si>
   <si>
-    <t>Waktu loading :  18:00/05
+    <t>Waktu loading : 18:00 05-02-2026
 Rute/tujuan : CGK - PKU
 driver  : Syarial
 Nopol  :BM 8486 AU

--- a/output_orderan.xlsx
+++ b/output_orderan.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="561" uniqueCount="282">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1166" uniqueCount="525">
   <si>
     <t>DATE</t>
   </si>
@@ -46,60 +46,123 @@
     <t>PHONE</t>
   </si>
   <si>
+    <t>04 februari 2026</t>
+  </si>
+  <si>
+    <t>05 / 02 / 2026</t>
+  </si>
+  <si>
+    <t>05 februari 2026</t>
+  </si>
+  <si>
+    <t>05 februari 2025</t>
+  </si>
+  <si>
+    <t>06 / 02 / 2026</t>
+  </si>
+  <si>
+    <t>05 feb 26</t>
+  </si>
+  <si>
+    <t>06 : 00 060226</t>
+  </si>
+  <si>
+    <t>03 : 00 060226</t>
+  </si>
+  <si>
     <t>06 febuary 2026</t>
   </si>
   <si>
     <t>06 feb 2026</t>
   </si>
   <si>
-    <t>06 febuari 2026</t>
-  </si>
-  <si>
-    <t>07 febuari 2026</t>
-  </si>
-  <si>
-    <t>08 februari 2025</t>
-  </si>
-  <si>
-    <t>09 feb</t>
-  </si>
-  <si>
-    <t>9 februari 2026</t>
-  </si>
-  <si>
-    <t>10 / 02 / 2026</t>
-  </si>
-  <si>
-    <t>02 : 00 100226</t>
-  </si>
-  <si>
-    <t>11 februari 2026</t>
-  </si>
-  <si>
-    <t>09 : 00 11 februari 2026</t>
+    <t>12 feb 26</t>
+  </si>
+  <si>
+    <t>03 : 00 130226</t>
   </si>
   <si>
     <t>12 februari 2026</t>
   </si>
   <si>
-    <t>12 / 02 / 2026</t>
-  </si>
-  <si>
-    <t>12 feb 26</t>
-  </si>
-  <si>
-    <t>03 : 00 12 februari 2026</t>
+    <t>13 februari 2026</t>
+  </si>
+  <si>
+    <t>23 : 00 13 februari 2026</t>
+  </si>
+  <si>
+    <t>14022026</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>15 februari 2026</t>
+  </si>
+  <si>
+    <t>16 feb 26</t>
+  </si>
+  <si>
+    <t>03 : 00 170226</t>
+  </si>
+  <si>
+    <t>17 februari 2026</t>
+  </si>
+  <si>
+    <t>26 feb 26</t>
+  </si>
+  <si>
+    <t>03 : 00 270226</t>
+  </si>
+  <si>
+    <t>26 febuari 2026</t>
+  </si>
+  <si>
+    <t>27 febuari 2026</t>
+  </si>
+  <si>
+    <t>27 februari 2026</t>
+  </si>
+  <si>
+    <t>27 feb 26</t>
+  </si>
+  <si>
+    <t>28 februari 2026</t>
+  </si>
+  <si>
+    <t>28 febuari 2026</t>
+  </si>
+  <si>
+    <t>23 : 00 28 februari 2026</t>
+  </si>
+  <si>
+    <t>28 / 02 / 206</t>
+  </si>
+  <si>
+    <t>1 maret 2026</t>
+  </si>
+  <si>
+    <t>28 / 02 / 2026</t>
+  </si>
+  <si>
+    <t>03 maret 2026</t>
   </si>
   <si>
     <t>3 maret 2026</t>
   </si>
   <si>
+    <t>02 : 00 04032026</t>
+  </si>
+  <si>
+    <t>03 mar 26</t>
+  </si>
+  <si>
+    <t>04 mar 26</t>
+  </si>
+  <si>
     <t>03 : 00 04032026</t>
   </si>
   <si>
-    <t>03 maret 2026</t>
-  </si>
-  <si>
     <t>04 maret 2026</t>
   </si>
   <si>
@@ -109,7 +172,7 @@
     <t>05 mar 26</t>
   </si>
   <si>
-    <t>06 mar 26</t>
+    <t>03 : 00 06 mar 26</t>
   </si>
   <si>
     <t>05 maret 2026</t>
@@ -121,91 +184,142 @@
     <t>18 : 00 05022026</t>
   </si>
   <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
     <t>2</t>
   </si>
   <si>
     <t>6</t>
   </si>
   <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
     <t>24</t>
   </si>
   <si>
-    <t>1</t>
-  </si>
-  <si>
     <t>50</t>
   </si>
   <si>
     <t>twb</t>
   </si>
   <si>
+    <t>cddl</t>
+  </si>
+  <si>
     <t>wb</t>
   </si>
   <si>
-    <t>cddl</t>
-  </si>
-  <si>
     <t>tronton</t>
   </si>
   <si>
+    <t>cddl cbm</t>
+  </si>
+  <si>
+    <t>cddl / cbm</t>
+  </si>
+  <si>
+    <t>cddl 24 cbm</t>
+  </si>
+  <si>
+    <t>argopantes</t>
+  </si>
+  <si>
+    <t>megahub</t>
+  </si>
+  <si>
+    <t>cikokol</t>
+  </si>
+  <si>
+    <t>cikarang</t>
+  </si>
+  <si>
+    <t>ckrjateng</t>
+  </si>
+  <si>
     <t>jne</t>
   </si>
   <si>
-    <t>argopantes</t>
-  </si>
-  <si>
-    <t>cikokol</t>
-  </si>
-  <si>
-    <t>megahub</t>
-  </si>
-  <si>
-    <t>cikarang</t>
+    <t>cgk</t>
+  </si>
+  <si>
+    <t>wangongateway</t>
+  </si>
+  <si>
+    <t>argo pantes</t>
+  </si>
+  <si>
+    <t>cgk pdg</t>
+  </si>
+  <si>
+    <t>cgk jateng</t>
   </si>
   <si>
     <t>cgk sub</t>
   </si>
   <si>
-    <t>argo pantes</t>
+    <t>cgk dps</t>
+  </si>
+  <si>
+    <t>cgk plm</t>
+  </si>
+  <si>
+    <t>cgk pku</t>
+  </si>
+  <si>
+    <t>cgk mes</t>
+  </si>
+  <si>
+    <t>sub</t>
+  </si>
+  <si>
+    <t>bm</t>
+  </si>
+  <si>
+    <t>subcgk</t>
+  </si>
+  <si>
+    <t>cgk tentatif</t>
+  </si>
+  <si>
+    <t>ckrsubsux</t>
+  </si>
+  <si>
+    <t>cgkjbr</t>
+  </si>
+  <si>
+    <t>cgkjateng</t>
+  </si>
+  <si>
+    <t>cgk denpasar</t>
+  </si>
+  <si>
+    <t>mes</t>
+  </si>
+  <si>
+    <t>pku</t>
+  </si>
+  <si>
+    <t>cgk jatim tentatif</t>
+  </si>
+  <si>
+    <t>plm</t>
+  </si>
+  <si>
+    <t>suxcgk</t>
   </si>
   <si>
     <t>cgk jatim</t>
   </si>
   <si>
-    <t>subcgk</t>
-  </si>
-  <si>
-    <t>cgk mes</t>
-  </si>
-  <si>
-    <t>cgk pku</t>
-  </si>
-  <si>
-    <t>srg sub</t>
-  </si>
-  <si>
-    <t>jne srg</t>
-  </si>
-  <si>
-    <t>srgcgk</t>
-  </si>
-  <si>
-    <t>cgk dps</t>
-  </si>
-  <si>
-    <t>cgk</t>
-  </si>
-  <si>
-    <t>ckrsubsux</t>
-  </si>
-  <si>
-    <t>cgkjbr</t>
+    <t>jateng tentatif</t>
+  </si>
+  <si>
+    <t>ckrmxg</t>
   </si>
   <si>
     <t>mes ddriver</t>
@@ -214,9 +328,6 @@
     <t>sub cgk</t>
   </si>
   <si>
-    <t>suxcgk</t>
-  </si>
-  <si>
     <t>cgkpsr</t>
   </si>
   <si>
@@ -226,12 +337,57 @@
     <t>cgksub</t>
   </si>
   <si>
-    <t>pku</t>
+    <t>sutrisno</t>
+  </si>
+  <si>
+    <t>karyadi</t>
+  </si>
+  <si>
+    <t>m syaichoni</t>
+  </si>
+  <si>
+    <t>lailan</t>
+  </si>
+  <si>
+    <t>agus</t>
+  </si>
+  <si>
+    <t>jatmiyanta</t>
+  </si>
+  <si>
+    <t>siswanto</t>
+  </si>
+  <si>
+    <t>feri irawan</t>
+  </si>
+  <si>
+    <t>hadi</t>
+  </si>
+  <si>
+    <t>a . sukur</t>
+  </si>
+  <si>
+    <t>akiyat</t>
+  </si>
+  <si>
+    <t>ryan</t>
+  </si>
+  <si>
+    <t>hendra s . p</t>
+  </si>
+  <si>
+    <t>sandri</t>
   </si>
   <si>
     <t>akbar</t>
   </si>
   <si>
+    <t>apar rahmat</t>
+  </si>
+  <si>
+    <t>m . ibnu</t>
+  </si>
+  <si>
     <t>wahyudi</t>
   </si>
   <si>
@@ -241,87 +397,159 @@
     <t>chandra</t>
   </si>
   <si>
-    <t>sentot</t>
-  </si>
-  <si>
-    <t>purwanto</t>
-  </si>
-  <si>
-    <t>didik</t>
-  </si>
-  <si>
-    <t>haryono</t>
-  </si>
-  <si>
-    <t>hermanto</t>
-  </si>
-  <si>
-    <t>wijaya</t>
-  </si>
-  <si>
-    <t>darmawan</t>
-  </si>
-  <si>
-    <t>arif r</t>
+    <t>ageng</t>
+  </si>
+  <si>
+    <t>ilham wahyudi</t>
+  </si>
+  <si>
+    <t>sri mardono</t>
+  </si>
+  <si>
+    <t>rosyit</t>
+  </si>
+  <si>
+    <t>dimas</t>
+  </si>
+  <si>
+    <t>herman</t>
+  </si>
+  <si>
+    <t>fajri</t>
+  </si>
+  <si>
+    <t>andi</t>
+  </si>
+  <si>
+    <t>noprianto</t>
+  </si>
+  <si>
+    <t>simare</t>
+  </si>
+  <si>
+    <t>nanang</t>
+  </si>
+  <si>
+    <t>mengri</t>
+  </si>
+  <si>
+    <t>sulis</t>
+  </si>
+  <si>
+    <t>agung</t>
+  </si>
+  <si>
+    <t>manulang</t>
+  </si>
+  <si>
+    <t>samsul</t>
+  </si>
+  <si>
+    <t>rajiev fikri</t>
+  </si>
+  <si>
+    <t>alex s</t>
+  </si>
+  <si>
+    <t>arif</t>
+  </si>
+  <si>
+    <t>anto</t>
+  </si>
+  <si>
+    <t>kudir</t>
+  </si>
+  <si>
+    <t>davit</t>
+  </si>
+  <si>
+    <t>hendra setiawan</t>
+  </si>
+  <si>
+    <t>febrianto</t>
+  </si>
+  <si>
+    <t>m doni saputra</t>
+  </si>
+  <si>
+    <t>habib</t>
+  </si>
+  <si>
+    <t>aris</t>
+  </si>
+  <si>
+    <t>supriyanto</t>
+  </si>
+  <si>
+    <t>agung prasetyo</t>
+  </si>
+  <si>
+    <t>rizki</t>
+  </si>
+  <si>
+    <t>dian saputra</t>
+  </si>
+  <si>
+    <t>yugik</t>
+  </si>
+  <si>
+    <t>muatim</t>
+  </si>
+  <si>
+    <t>ibnu</t>
+  </si>
+  <si>
+    <t>yusni gunawan</t>
+  </si>
+  <si>
+    <t>agus supriatna</t>
+  </si>
+  <si>
+    <t>rizky / aris</t>
+  </si>
+  <si>
+    <t>dedeng</t>
+  </si>
+  <si>
+    <t>indra</t>
+  </si>
+  <si>
+    <t>ariansyah</t>
+  </si>
+  <si>
+    <t>arbi</t>
+  </si>
+  <si>
+    <t>anton</t>
+  </si>
+  <si>
+    <t>mujito</t>
+  </si>
+  <si>
+    <t>jodi akbar</t>
+  </si>
+  <si>
+    <t>arizal</t>
+  </si>
+  <si>
+    <t>samosir</t>
+  </si>
+  <si>
+    <t>soni rahmat</t>
+  </si>
+  <si>
+    <t>nana hermawan</t>
   </si>
   <si>
     <t>yuda</t>
   </si>
   <si>
-    <t>aldi</t>
-  </si>
-  <si>
-    <t>supriadi</t>
-  </si>
-  <si>
-    <t>syafrizal</t>
-  </si>
-  <si>
-    <t>nizar</t>
-  </si>
-  <si>
-    <t>samosir</t>
-  </si>
-  <si>
-    <t>joni</t>
-  </si>
-  <si>
-    <t>nasip k</t>
-  </si>
-  <si>
-    <t>ageng</t>
-  </si>
-  <si>
-    <t>ilham wahyudi</t>
-  </si>
-  <si>
-    <t>sri mardono</t>
-  </si>
-  <si>
-    <t>rosyit</t>
-  </si>
-  <si>
-    <t>m . ibnu</t>
-  </si>
-  <si>
-    <t>akiyat</t>
-  </si>
-  <si>
-    <t>ahmad wahyudi</t>
-  </si>
-  <si>
     <t>ari purnama</t>
   </si>
   <si>
-    <t>dedeng</t>
-  </si>
-  <si>
     <t>jupri</t>
   </si>
   <si>
-    <t>andi</t>
-  </si>
-  <si>
     <t>misno</t>
   </si>
   <si>
@@ -331,9 +559,6 @@
     <t>miyanta</t>
   </si>
   <si>
-    <t>davit</t>
-  </si>
-  <si>
     <t>iwan hariono</t>
   </si>
   <si>
@@ -349,6 +574,51 @@
     <t>syarial</t>
   </si>
   <si>
+    <t>bm 8364 au</t>
+  </si>
+  <si>
+    <t>ad 8517 ba</t>
+  </si>
+  <si>
+    <t>n 8872 rk</t>
+  </si>
+  <si>
+    <t>s 9272 up</t>
+  </si>
+  <si>
+    <t>d 9667 af</t>
+  </si>
+  <si>
+    <t>f 9647 fh</t>
+  </si>
+  <si>
+    <t>b 9120 wxr</t>
+  </si>
+  <si>
+    <t>bk 8516 vv</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>b 9477 keu</t>
+  </si>
+  <si>
+    <t>l 9722 ue</t>
+  </si>
+  <si>
+    <t>b 9084 veh</t>
+  </si>
+  <si>
+    <t>d 9044 ag</t>
+  </si>
+  <si>
+    <t>e9406hb</t>
+  </si>
+  <si>
+    <t>l 9511 al</t>
+  </si>
+  <si>
     <t>n 9549 ua</t>
   </si>
   <si>
@@ -358,130 +628,462 @@
     <t>l 8601 uh</t>
   </si>
   <si>
-    <t>b 9231 ceu</t>
-  </si>
-  <si>
-    <t>b 9891 beu</t>
-  </si>
-  <si>
-    <t>b 9687 jm</t>
-  </si>
-  <si>
-    <t>b 8745 amr</t>
-  </si>
-  <si>
-    <t>s 8635 nj</t>
-  </si>
-  <si>
-    <t>h 9948 ra</t>
-  </si>
-  <si>
-    <t>ba 8829 bu</t>
-  </si>
-  <si>
-    <t>b 9787 xx</t>
+    <t>b9654yu</t>
+  </si>
+  <si>
+    <t>bk 8678 ve</t>
+  </si>
+  <si>
+    <t>b 9563 teu</t>
+  </si>
+  <si>
+    <t>h 9263 ov</t>
+  </si>
+  <si>
+    <t>b 9718 tj</t>
+  </si>
+  <si>
+    <t>b 9241 fxs</t>
+  </si>
+  <si>
+    <t>be 8794 amb</t>
+  </si>
+  <si>
+    <t>be 8251 foa</t>
+  </si>
+  <si>
+    <t>bk 8639 fj</t>
+  </si>
+  <si>
+    <t>ab 8053 ka</t>
+  </si>
+  <si>
+    <t>bm 8279 au</t>
+  </si>
+  <si>
+    <t>l 9579 uk</t>
+  </si>
+  <si>
+    <t>bk 8208 vy</t>
+  </si>
+  <si>
+    <t>b 9771 uew</t>
+  </si>
+  <si>
+    <t>b 9019 uex</t>
+  </si>
+  <si>
+    <t>b 9591 uxx</t>
+  </si>
+  <si>
+    <t>b 9411 vxr</t>
+  </si>
+  <si>
+    <t>b 9209 nck</t>
+  </si>
+  <si>
+    <t>b 9285 uex</t>
+  </si>
+  <si>
+    <t>b 9380 uex</t>
+  </si>
+  <si>
+    <t>b 9726 sxw</t>
+  </si>
+  <si>
+    <t>bk 8516 w</t>
+  </si>
+  <si>
+    <t>be 9636 bu</t>
+  </si>
+  <si>
+    <t>be 8023 wy</t>
+  </si>
+  <si>
+    <t>ba 9980 ps</t>
+  </si>
+  <si>
+    <t>bd 8423 b</t>
+  </si>
+  <si>
+    <t>l 8336 uv</t>
+  </si>
+  <si>
+    <t>b 9139 syt</t>
+  </si>
+  <si>
+    <t>be 8940 db</t>
+  </si>
+  <si>
+    <t>b 9739 seu</t>
+  </si>
+  <si>
+    <t>be 8831 cj</t>
+  </si>
+  <si>
+    <t>be 8334 gba</t>
+  </si>
+  <si>
+    <t>b 9562 teu</t>
+  </si>
+  <si>
+    <t>b 9810 ueu</t>
+  </si>
+  <si>
+    <t>h 9224 ma</t>
+  </si>
+  <si>
+    <t>be 8951 by</t>
+  </si>
+  <si>
+    <t>b 9546 kxx</t>
+  </si>
+  <si>
+    <t>b9091scj</t>
+  </si>
+  <si>
+    <t>e 9426 aa</t>
+  </si>
+  <si>
+    <t>b9588ym</t>
+  </si>
+  <si>
+    <t>be 8775 dy</t>
+  </si>
+  <si>
+    <t>be 8919 amn</t>
+  </si>
+  <si>
+    <t>be 9063 ar</t>
+  </si>
+  <si>
+    <t>be 8837 gk</t>
+  </si>
+  <si>
+    <t>be 8013 au</t>
+  </si>
+  <si>
+    <t>b 9895 uxx</t>
+  </si>
+  <si>
+    <t>b 9727 uex</t>
+  </si>
+  <si>
+    <t>bm 8142 ry</t>
+  </si>
+  <si>
+    <t>b 9658 tcp</t>
+  </si>
+  <si>
+    <t>b 9679wt</t>
   </si>
   <si>
     <t>w 8973 uq</t>
   </si>
   <si>
-    <t>bm 8350 au</t>
-  </si>
-  <si>
-    <t>b 9586 txv</t>
-  </si>
-  <si>
-    <t>bm 8479 au</t>
-  </si>
-  <si>
-    <t>b 9172 scp</t>
-  </si>
-  <si>
-    <t>b 9727 uex</t>
-  </si>
-  <si>
-    <t>b 9169 uex</t>
+    <t>b 9383 txv</t>
+  </si>
+  <si>
+    <t>bm 9273 ro</t>
+  </si>
+  <si>
+    <t>be 8610 db</t>
+  </si>
+  <si>
+    <t>bn 8038 rp</t>
+  </si>
+  <si>
+    <t>be 8456 fn</t>
+  </si>
+  <si>
+    <t>bl 8188 jp</t>
+  </si>
+  <si>
+    <t>l 8183uv</t>
+  </si>
+  <si>
+    <t>bk 8330 vy</t>
   </si>
   <si>
     <t>bh 8165 qi</t>
   </si>
   <si>
-    <t>b9654yu</t>
-  </si>
-  <si>
-    <t>f 9647 fh</t>
-  </si>
-  <si>
-    <t>bk 8678 ve</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>b 9563 teu</t>
-  </si>
-  <si>
-    <t>l 9511 al</t>
-  </si>
-  <si>
-    <t>l 9722 ue</t>
-  </si>
-  <si>
-    <t>w 8323 nv</t>
-  </si>
-  <si>
-    <t>b 9679wt</t>
-  </si>
-  <si>
-    <t>b 9383 txv</t>
-  </si>
-  <si>
-    <t>e 9426 aa</t>
-  </si>
-  <si>
-    <t>bm 9273 ro</t>
-  </si>
-  <si>
-    <t>be 8610 db</t>
-  </si>
-  <si>
-    <t>bn 8038 rp</t>
-  </si>
-  <si>
-    <t>be 8456 fn</t>
-  </si>
-  <si>
-    <t>b 9726 sxw</t>
-  </si>
-  <si>
-    <t>bl 8188 jp</t>
-  </si>
-  <si>
-    <t>l 8183uv</t>
-  </si>
-  <si>
-    <t>bk 8330 vy</t>
-  </si>
-  <si>
     <t>bm 8486 au</t>
   </si>
   <si>
     <t>segera</t>
   </si>
   <si>
+    <t>18 : 00</t>
+  </si>
+  <si>
+    <t>21 : 00</t>
+  </si>
+  <si>
+    <t>03 : 00</t>
+  </si>
+  <si>
     <t>07 : 00</t>
   </si>
   <si>
-    <t>22 : 00</t>
-  </si>
-  <si>
     <t>02 : 00</t>
   </si>
   <si>
-    <t>03 : 00</t>
-  </si>
-  <si>
-    <t>06 : 00</t>
+    <t>23 : 00</t>
+  </si>
+  <si>
+    <t>04 ; 00</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: Request Unit On Call
+RAFAY
+1 UNIT TWB 50 Cbm
+Lokasi : ARGOPANTES</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA
+Rute/tujuan : CGK- PDG
+driver  : SUTRISNO
+Nopol  : BM 8364 AU
+No hp  :0853-5388-6066</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: REQUEST ORDER ONCALL 04 FEBRUARI 2026:
+RAFAY
+3 unit Cddl 24 Cbm
+Lokasi : Megahub</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA 04 FEBRUARI 2026
+Rute/tujuan : CGK - JATENG
+driver  : KARYADI
+Nopol  : AD 8517 BA
+No hp  :085865762797</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: REQUEST ORDER ULANG ONCALL
+5 UNIT TWB 50 CBM
+Lokasi : ARGOPANTES</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA
+Rute/tujuan : CGK - SUB
+driver  :
+Nopol  :
+No hp  :</t>
+  </si>
+  <si>
+    <t>Waktu loading : 18:00
+Rute/tujuan : CGK - SUB
+driver  : m syaichoni
+Nopol  : N 8872 Rk
+No hp  : +62 812-3189-5971</t>
+  </si>
+  <si>
+    <t>Waktu loading : 21:00
+Rute/tujuan : CGK - SUB
+driver  :
+Nopol  :
+No hp  :</t>
+  </si>
+  <si>
+    <t>Waktu loading : 00:00
+Rute/tujuan : CGK - SUB
+driver  :
+Nopol  :
+No hp  :</t>
+  </si>
+  <si>
+    <t>REQUEST ORDER KHUSUS 05/02/2026</t>
+  </si>
+  <si>
+    <t>Waktu loading : 03:00
+Rute/tujuan : CGK -SUB
+driver  : Lailan
+Nopol  : S 9272 UP
+No hp  : +62 878-8686-1780</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: REQUEST TAMBAHAN ORDER ONCALL 04 FEBRUARI 2026:
+RAFAY
+2 UNIT TWB 50 CBM
+Lokasi : CIKOKOL</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA 04 FEBRUARI 2026
+Rute/tujuan : CGK - SUB
+driver  : AGUS
+Nopol  : D 9667 AF
+No hp  :08817021866
+Rev plat nomor pak @Nomor tidak dikenal @Nomor tidak dikenal @Nomor tidak dikenal 🙏🏻</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: REQUEST ORDER ONCALL 04 FEBRUARI 2026:
+RAFAY
+1 unit Cddl 24 Cbm
+Lokasi : Megahub</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA 04 FEBRUARI 2026
+Rute/tujuan : CGK - DPS
+driver 1 : Edi setiawan
+No hp  :0881023544597 
+Driver2 : Jatmiyanta
+No hp  :082118558105
+Nopol : F 9647 FH</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: REQUEST ULANG ORDER ONCALL 05 FEBRUARI 2026:
+2 UNIT TWB 50 CBM
+Lokasi : CIKOKOL</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA 05 FEBRUARI 2026
+Rute/tujuan : CGK - TKG
+driver  :
+Nopol  :
+No hp  :
+2 UNIT TWB 50 CBM
+Lokasi : CIKOKOL</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA 05 FEBRUARI 2026
+Rute/tujuan : CGK - PLM
+driver  :
+Nopol  :
+No hp  :
+2 UNIT TWB 50 CBM
+Lokasi : CIKOKOL</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA 05 FEBRUARI 2026
+Rute/tujuan : CGK - PKU
+driver  : Siswanto
+Nopol  : B 9120 WXR
+No hp  : 081943564062
+Lokasi : CIKOKOL</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA 05 FEBRUARI 2026
+Rute/tujuan : CGK - PKU
+driver  : 
+Nopol  : 
+No hp  : 
+2 UNIT TWB 50 CBM
+Lokasi : CIKOKOL</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA 05 FEBRUARI 2026
+Rute/tujuan : CGK - MES
+driver  : feri irawan
+Nopol  : BK 8516 VV
+No hp  : 085219216210</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: REQUEST ULANG ORDER ONCALL 05 FEBRUARI 2026:
+RAFAY
+2 UNIT TWB 50 CBM
+Lokasi : CIKOKOL</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA 05 FEBRUARI 2026
+Rute/tujuan : CGK - MES
+driver  : HADI
+Nopol  :B 9446 MV
+No hp  :+62 831-9621-8655</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA 05 FEBRUARI 2026
+Rute/tujuan : CGK - MES
+driver  : A. Sukur 
+Nopol  :B 9477 KEU
+No hp  : 083169525183</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA
+Rute/tujuan : CGK - SUB
+RAFAY
+driver  : AKIYAT
+Nopol  : L 9722 UE
+No hp  :081281122738</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: REQUEST ULANG ORDER ONCALL 05 FEBRUARI 2025
+RAFAY
+2 UNIT TWB 50 CBM
+Lokasi : CIKOKOL</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA 05 FEBRUARI 2025
+Rute/tujuan : CGK - PKU
+driver  : RYAN
+Nopol  : B 9084 VEH
+No hp  : 087837496810</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA
+Rute/tujuan : CGK - SUB
+driver  : HENDRA S.P
+Nopol  : D 9044 AG
+No hp  : +62 877-8667-6177</t>
+  </si>
+  <si>
+    <t>Waktu loading : 18:00
+Rute/tujuan : CGK - SUB
+driver  :
+Nopol  :
+No hp  :</t>
+  </si>
+  <si>
+    <t>REQUEST ORDER KHUSUS 06/02/2026</t>
+  </si>
+  <si>
+    <t>Waktu loading : 03:00
+Rute/tujuan : CGK -SUB
+driver  :
+Nopol  :
+No hp  :</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA 05 FEBRUARI 2026
+Rute/tujuan : CGK - PLM
+driver  : SANDRI
+Nopol  : BE 9636 BU
+No hp  :+62 889-0702-0037</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: Request Unit On Call Tgl 05 Feb 26
+2 Unit  Cddl / 24 Cbm
+Lokasi : Cikarang</t>
+  </si>
+  <si>
+    <t>Waktu loading : 06:00 06-02-26
+Rute/tujuan : CKR-Jateng Tentative
+Driver   : 
+Nopol  : 
+No Hp  :
+1 Unit  Cddl / 24 Cbm
+Lokasi : Cikarang</t>
+  </si>
+  <si>
+    <t>Waktu loading : 03:00 06-02-26
+Rute/tujuan : CKR-Jateng Tentative
+Nama : Apar Rahmat 
+Nopol : E9406HB 
+NO TLP : 085971812879</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: Request Unit On Call Tgl 06 febuary 2026
+RAFAY
+3 unit twb 50 CBM
+Lokasi : ARGOPANTES</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA 06 febuary 2026
+Rute/tujuan : CGK- Jl.perak surabaya-PT.BM
+driver  : M. iBNU
+Nopol  : L 9511 AL
+No hp  :082191633212</t>
   </si>
   <si>
     <t>[WA_TS] Akbar Rafay: Request Unit On Call Tgl 06 febuary 2026
@@ -519,212 +1121,14 @@
 No hp  : +62 852-3168-1470</t>
   </si>
   <si>
-    <t>[WA_TS] Akbar Rafay: REQUEST ORDER ONCAL
-06 FEBUARI 2026
-RAFAY
-3 unit TWB 50 Cbm
-Lokasi : ARGOPANTES
-Rute/ tuj : CGK - MES</t>
+    <t>[WA_TS] Akbar Rafay: REQUEST ORDER ULANG ONCALL
+06 FEB 2026
+10 UNIT CDDL/24 CBM
+Lokasi : ARGOPANTES</t>
   </si>
   <si>
     <t>Waktu loading : SEGERA
-DRIVER 1 : SENTOT
-NOPOL    : B 9231 CEU
-NOHP      :+62 812-8714-7789</t>
-  </si>
-  <si>
-    <t>[WA_TS] Akbar Rafay: REQUEST ORDER ONCAL
-06 FEBUARI 2026
-5 unit TWB 50 Cbm
-Lokasi : ARGOPANTES
-Rute/ tuj : CGK - SUB</t>
-  </si>
-  <si>
-    <t>Waktu loading : SEGERA
-RAFAY
-DRIVER 1 : PURWANTO
-NOPOL    : B 9891 BEU
-NOHP      :083142142113</t>
-  </si>
-  <si>
-    <t>Waktu loading : SEGERA
-DRIVER : DIDIK
-NOPOL    : B 9687 JM
-NOHP      :085385220743</t>
-  </si>
-  <si>
-    <t>[WA_TS] Akbar Rafay: REQUEST ORDER ONCAL
-06 FEBUARI 2026
-Lokasi : ARGOPANTES
-Rute/ tuj : CGK - PKU</t>
-  </si>
-  <si>
-    <t>Waktu loading : SEGERA
-DRIVER 1 : Haryono
-NOPOL    : B 8745 AMR
-NO HP      : 083166684195</t>
-  </si>
-  <si>
-    <t>Waktu loading : SEGERA
-DRIVER : HERMANTO
-NOPOL : S 8635 NJ
-NOHP :085194592825</t>
-  </si>
-  <si>
-    <t>[WA_TS] Akbar Rafay: REQUEST ORDER ONCAL
-07 FEBUARI 2026
-RAFAY
-1 unit CDDL 24 Cbm
-Lokasi : SEMARANG
-Rute/ tuj : SRG - SUB</t>
-  </si>
-  <si>
-    <t>Waktu loading : SEGERA
-DRIVER 1 :Agung
-DRIVER 2 :Wijaya
-NOPOL    :H 9948 RA
-NOHP      :0882016641381</t>
-  </si>
-  <si>
-    <t>[WA_TS] Akbar Rafay: REQUEST ORDER ONCALL 08 FEBRUARI 2025:
-3 UNIT TWB 50 CBM
-Lokasi : ARGOPANTES</t>
-  </si>
-  <si>
-    <t>Waktu loading : SEGERA 08 FEBRUARI 2025
-Rute/tujuan : CGK - MES
-driver  : DARMAWAN
-Nopol  : BA 8829 BU
-No hp  :082363564665</t>
-  </si>
-  <si>
-    <t>[WA_TS] Akbar Rafay: Request Order Oncall Tgl 09 Feb
-1 UNIT CDDL 24 CBM
-Lokasi  : JNE SRG</t>
-  </si>
-  <si>
-    <t>Waktu loading : 22:00
-Rute/tujuan : SRG-CGK
-Driver : Arif R
-Nopol :B 9787 XX
-No hp :089690885555</t>
-  </si>
-  <si>
-    <t>[WA_TS] Akbar Rafay: REQUEST ORDER  ONCALL 9 FEBRUARI 2026:
-2 unit TWB 50 Cbm
-Lokasi : cikokol</t>
-  </si>
-  <si>
-    <t>Waktu loading : 02:00 9 FEBRUARI 2026
-Rute/tujuan : CGK - SUB
-NAMA : WAHYUDI
-NOPOL: N 9549 UA
-NO HP :085784422398</t>
-  </si>
-  <si>
-    <t>Waktu loading : 03:00 9 FEBRUARI 2026
-NAMA : YUDA
-NOPOL: W 8973 UQ
-NO HP :089507296985</t>
-  </si>
-  <si>
-    <t>[WA_TS] Akbar Rafay: REQUEST ORDER  ONCALL 9 FEBRUARI 2026:
-2 unit  TWB 50 Cbm
-Lokasi : Cikokol</t>
-  </si>
-  <si>
-    <t>REQUEST ORDER KHUSUS 10/02/2026</t>
-  </si>
-  <si>
-    <t>Waktu loading : 02:00
-Rute/tujuan : CGK - PKU
-NAMA : ALDI
-NOPOL: BM 8350 AU
-NO HP :0831-6761-0479</t>
-  </si>
-  <si>
-    <t>Waktu loading : 03:00
-NAMA :
-NOPOL:
-NO HP :</t>
-  </si>
-  <si>
-    <t>Waktu loading : 02:00 10-02-26
-Rute/tujuan : SRG-CGK
-Driver : Supriadi
-Nopol : B 9586 TXV
-No hp :081350529712</t>
-  </si>
-  <si>
-    <t>Waktu loading : 02:00
-Rute/tujuan : CGK - PKU</t>
-  </si>
-  <si>
-    <t>Waktu loading : 03:00
-NAMA : SYAFRIZAL
-NOPOL: BM 8479 AU
-NO HP :082170733190</t>
-  </si>
-  <si>
-    <t>[WA_TS] Akbar Rafay: REQUEST ORDER  ONCALL 9 FEBRUARI 2026:
-RAFAY
-2 unit  TWB 50 Cbm
-Lokasi : Cikokol
-Rute/tujuan : CGK - PKU</t>
-  </si>
-  <si>
-    <t>Waktu loading : SEGERA 9 FEBRUARI 2026
-NAMA : SYAFRIZAL
-NOPOL: BM 8479 AU
-NO HP :082170733190</t>
-  </si>
-  <si>
-    <t>[WA_TS] Akbar Rafay: REQUEST ORDER ONCALL 11 FEBRUARI 2026:
-1 unit Cddl 24 Cbm
-Lokasi : Megahub</t>
-  </si>
-  <si>
-    <t>Waktu loading : 00:00 11 FEBRUARI 2026
-Rute/tujuan : CGK - DPS
-driver  :Nizar
-Nopol  :B 9172 SCP
-No hp  :081313444015</t>
-  </si>
-  <si>
-    <t>[WA_TS] Akbar Rafay: REQUEST ORDER ONCALL 11 FEBRUARI 2026:
-3 unit tronton 50 Cbm
-Lokasi : cikokol</t>
-  </si>
-  <si>
-    <t>Waktu loading : SEGERA 11 FEBRUARI 2026
-Rute/tujuan : CGK - MES</t>
-  </si>
-  <si>
-    <t>Waktu loading : 09:00 11 FEBRUARI 2026
-Driver : SAMOSIR
-Nopol : B 9727 UEX
-Hp :+62 822-7429-6236</t>
-  </si>
-  <si>
-    <t>Waktu loading : 12:00 11 FEBRUARI 2026
-Driver : JONI
-Nopol : B 9169 UEX
-Hp :+62 822-7638-5077</t>
-  </si>
-  <si>
-    <t>[WA_TS] Akbar Rafay: REQUEST ORDER TAMBAHAN ONCALL  12 FEBRUARI 2026:
-1 unit TRONTON 50 Cbm
-Lokasi : cikokol</t>
-  </si>
-  <si>
-    <t>REQUEST ORDER KHUSUS 12/02/2026</t>
-  </si>
-  <si>
-    <t>Waktu loading : 02:00
-Rute/tujuan : CGK - PKU
-Nama 	: NASIP K
-Nopol		: BH 8165 QI
-No Tlp		:‪+6281272463920</t>
+Rute/tujuan : CGK - JATIM TENTATIF</t>
   </si>
   <si>
     <t>[WA_TS] Akbar Rafay: Request Unit On Call Tgl 12 Feb 26
@@ -744,7 +1148,7 @@
 Lokasi : Cikokol + Cikarang</t>
   </si>
   <si>
-    <t>Waktu loading : 03:00
+    <t>Waktu loading : 03:00 13-02-26
 Rute/tujuan : CGK-JBR
 No pol.   : F 9647 FH
 Driver. 1 :  Jatmiyanta
@@ -801,24 +1205,643 @@
 Rute/tujuan : CGK - SUB
 driver  : Akiyat
 Nopol  : L 9722 UE
-No hp  :081281122738
-Akbar Rafay: REQUEST ORDER ONCALL 12 FEBRUARI 2026:
+No hp  :081281122738</t>
+  </si>
+  <si>
+    <t>Waktu loading : 03:00 12 FEBRUARI 2026
+Rute/tujuan : CGK - SUB</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: 3 UNIT CDDL 24 CBM
+Lokasi  : CIKOKOL</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA
+Rute/tujuan : CGK-JATENG TENTATIF
+Driver :
+Nopol :
+No hp :</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA
+Driver :
+Nopol :
+No hp :</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA
+Driver :Dimas
+Nopol :H 9263 OV
+No hp :082217785226</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: REQUEST ORDER ONCALL 13 FEBRUARI 2026:
+5 UNIT TWB 50 Cbm
+Lokasi : ARGOPANTES</t>
+  </si>
+  <si>
+    <t>Waktu loading : 15:00 13 FEBRUARI 2026
+Rute/tujuan : CGK - PKU
+driver  : HERMAN
+Nopol  : B 9718 TJ
+No hp  :087844510846</t>
+  </si>
+  <si>
+    <t>Waktu loading : 18:00 13 FEBRUARI 2026
+Rute/tujuan : CGK - PKU
+driver  : FAJRI
+Nopol  : B 9241 FXS
+No hp  :81382418508</t>
+  </si>
+  <si>
+    <t>Waktu loading : 23:00 13 FEBRUARI 2026
+Rute/tujuan : CGK - PKU
+driver  : ANDI
+Nopol  : BE 8794 AMB
+No hp  :082183783385</t>
+  </si>
+  <si>
+    <t>REQUEST ORDER KHUSUS 14-02-2026</t>
+  </si>
+  <si>
+    <t>Waktu loading : 02:00
+Rute/tujuan : CGK - PKU
+driver  : NOPRIANTO
+Nopol  : BE 8251 FOA
+No hp  :085758955627</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: REQUEST ORDER ONCALL ULANG 13 FEBRUARI 2026:
+3 UNIT TWB 50 CBM
+Lokasi : CIKOKOL</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA 13 FEBRUARI 2026
+Rute/tujuan : CGK - MES
+driver  :SIMARE
+Nopol  :BK 8639 FJ
+No hp  :+62 812-6934-5748</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: REQUEST ORDER ONCALL 13 FEBRUARI 2026:
+1 unit Cddl 24 Cbm
+Lokasi : Megahub</t>
+  </si>
+  <si>
+    <t>Waktu loading : 22:00 13 FEBRUARI 2026
+Rute/tujuan : CGK - DENPASAR
+driver  :Nanang
+Nopol  :AB 8053 KA
+No hp  :08889693664</t>
+  </si>
+  <si>
+    <t>Waktu loading : 02:00
+Rute/tujuan : CGK - PKU
+driver  : mengri
+Nopol : BM 8279 AU
+No hp : 085364056583</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA 13 FEBRUARI 2026
+Rute/tujuan : CGK - MES
+driver  :Sulis
+Nopol  :L 9579 UK
+No hp  :085225394209</t>
+  </si>
+  <si>
+    <t>Waktu loading : 23:00 13 FEBRUARI 2026
+Rute/tujuan : CGK - PKU
+driver  : Agung
+Nopol  : BK 8208 VY
+No hp  : 082385989323</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA 13 FEBRUARI 2026
+Rute/tujuan : CGK - MES
+driver  : Manulang
+Nopol  :B 9019 UEX
+No hp  : +62 813-7076-9496</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA 13 FEBRUARI 2026
+Rute/tujuan : CGK - MES
+driver  : SAMSUL
+Nopol  :B 9771 UEW
+No hp  : +62 822-2851-6922</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: REQUEST ORDER ONCALL
+Tanggal : 12 Februari 2026
+Rute/Tujuan : CGK – SUB
+Unit/Type : TWB 50 Cbm 
+Nopol : L 9722 UE
+Driver : Akiyat
+No HP : 0812-8112-2738
+Lokasi Loading : ARGOPANTES</t>
+  </si>
+  <si>
+    <t>Waktu loading : 03:00</t>
+  </si>
+  <si>
+    <t>REQUEST ORDER ONCALL ULANG
+Tanggal : 13 Februari 2026
+Rute/Tujuan : CGK – MES
+Unit/Type : TWB 50 CBM
+Nopol : BK 8639 FJ
+Driver : SIMARE
+No HP : +62 812-6934-5748
+Lokasi Loading : CIKOKOL</t>
+  </si>
+  <si>
+    <t>REQUEST ORDER ONCALL
+Tanggal : 13 Februari 2026
+Rute/Tujuan : CGK – PKU
+Unit/Type : TWB 50 CBM
+Nopol : B 9241 FXS
+Driver : FAJRI
+No HP : 081382418508
+Lokasi Loading : ARGOPANTES</t>
+  </si>
+  <si>
+    <t>Waktu loading : 18:00</t>
+  </si>
+  <si>
+    <t>REQUEST ORDER ONCALL
+Tanggal : 13 FEBRUARI 2026
+Rute/Tujuan : CGK - MES
+Unit/Type :  TWB 50 CBM
+Nopol : B 9019 UEX
+Driver : Manulang
+No…</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: REQUEST ORDER ONCALL 15 FEBRUARI 2026:
+2 unit Cddl 24 Cbm
+Lokasi : ARGOPANTES</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA 15 FEBRUARI 2026
+Rute/tujuan : CGK - JATIM TENTATIF
+driver  : Rajiev Fikri
+Nopol  : B 9591 UXX
+No hp  : 088290294126</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA 15 FEBRUARI 2026</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: REQUEST ORDER ONCALL 15 FEBRUARI 2026
+2 UNIT CDDL 24 Cbm
+Lokasi : MEGAHUB</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA 15 FEBRUARI 2026
+Rute/tujuan : CGK - JATENG
+driver  : Alex S
+Nopol  : B 9411 VXR
+No hp  : 088212698834</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: Request Unit On Call Tgl 16 Feb 26
+RAFAY
+1 Unit  Cddl / 24 Cbm
+Lokasi : Cikokol + Cikarang</t>
+  </si>
+  <si>
+    <t>Waktu loading : 03:00 17-02-26
+Rute/tujuan : CGK-JBR
+Driver   : Arif
+Nopol  :  B 9209 NCK
+No Hp :081328851819</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: REQUEST  ORDER  ONCALL  17 FEBRUARI 2026
+2 UNIT TWB 50 CBM
+Lokasi : ARGOPANTES
+Rute / tujuan : cgk - PKU</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA 17 FEBRUARI 2026
+Nama 	: SISWANTO
+Nopol	: B 9120 WXR
+No Tlp	:081943564062</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: REQUEST  ORDER  ONCALL  17 FEBRUARI 2026
+2 UNIT TWB 50 CBM
+Lokasi : ARGOPANTES
+Rute / tujuan : cgk - MES</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA 17 FEBRUARI 2026
+Nama 	: Anto
+Nopol	: B 9285 UEX
+No Tlp	:+62 823-7722-5563</t>
+  </si>
+  <si>
+    <t>Waktu loading : 07:00 17 FEBRUARI 2026
+Nama 	 : Kudir
+Nopol	: B 9380 UEX
+No Tlp	 :+62 812-6218-9242
+Request Unit On Call Tgl 26 Feb 26
+1 Unit  Cddl / 24 Cbm
+Lokasi : Cikokol + Cikarang</t>
+  </si>
+  <si>
+    <t>Waktu loading : 03:00 27-02-26
+Rute/tujuan : CGK-JBR
+Driver   : Davit
+Nopol  : B 9726 SXW
+No Hp  :082117275166</t>
+  </si>
+  <si>
+    <t>REQUEST ORDER ULANG ONCALL
+2 UNIT TWB 50 CBM
+Lokasi : ARGOPANTES</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA
+Rute/tujuan : CGK - MES
+driver  : Kudir
+Nopol  : B 9380 UEX
+No hp  : 0812-6218-9242
+Data yg lain menyusul
+REQUER ORDER ULANG DAN TAMBAHAN ON CALL
+26 FEBUARI 2026
+2 UNIT TWB 50 CBM 
+Lokasi : ARGOPANTES
+Rute / tujuan : PKU</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA
+Nama 	: SISWANTO
+Nopol		: B 9120 WXR
+No Tlp	:081943564062
+Rute / tujuan : PKU</t>
+  </si>
+  <si>
+    <t>Waktu loading : 23:00
+Nama 	: FERI IRAWAN
+Nopol		: BK 8516 W
+No Tlp	:085219216210
+REQUER ORDER ULANG DAN TAMBAHAN ON CALL
+26 FEBUARI 2026
+2 UNIT TWB 50 CBM 
+Lokasi : ARGOPANTES
+Rute / tujuan : PLM</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA
+Nama 	: SANDRI
+Nopol		:  BE 9636 BU
+No Tlp	:+62 889-0702-0037
+REQUER ORDER ULANG DAN TAMBAHAN ON CALL
+26 FEBUARI 2026
+2 UNIT TWB 50 CBM
+ Lokasi : ARGOPANTES
+Rute / tujuan : MES</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA
+Nama 	:Hendra setiawan
+Nopol		: BE 8023 WY
+No Tlp	:081280483919
+Rute / tujuan : MES</t>
+  </si>
+  <si>
+    <t>Waktu loading : 23:00
+Nama 	: FEBRIANTO
+Nopol		: BA 9980 PS
+No Tlp	: 082286523993
+REQUER ORDER ULANG DAN TAMBAHAN ON CALL
+26 FEBUARI 2026
+Rute / tujuan : PLM</t>
+  </si>
+  <si>
+    <t>Waktu loading : 23:00
+Nama 	: M Doni saputra
+Nopol		: BD 8423 B
+No Tlp	:082164544736
+Request Order Oncall  27 Febuari 2026
+2 UNIT TWB 50 CBM
+Lokasi : JNE SURABAYA
+Rute/ Tujuan   : SUX-CGK</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA 27 Febuari 2026
+NAMA   : HABIB 
+NOPOL : L 8336 UV
+NO HP  :081231540625
+Request Order Oncall  27 Febuari 2026
+3 UNIT TWB 50 CBM
+Lokasi : ARGOPANTES
+Rute/ Tujuan   : SUB</t>
+  </si>
+  <si>
+    <t>Waktu loading : 15:00 27 Febuari 2026
+NAMA   : ARIS
+NOPOL : B 9139 SYT
+NO HP  :081936963942
+Request Order Oncall  27 Febuari 2026
+2 UNIT TWB 50 CBM
+Lokasi : JNE SURABAYA
+Rute/ Tujuan   : SUX-CGK</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA 27 Febuari 2026
+NAMA   : WAHYUDI
+NOPOL : N 9549 UA
+NO HP  : 085784422398
+REQUER ORDER ULANG DAN TAMBAHAN ON CALL
+26 FEBUARI 2026
+2 UNIT TWB 50 CBM
+Lokasi : ARGOPANTES
+Nopol : BA 9980 PS
+Rute / tujuan : MES</t>
+  </si>
+  <si>
+    <t>Waktu loading : 23:00
+Nama 	: SUPRIYANTO
+Nopol		: BE 8940 DB
+No Tlp	: 082389746001
+ORDER ONCALL 27 FEBRUARI 2026:
+1 unit Cddl 24 Cbm
+Lokasi : WangonGateway</t>
+  </si>
+  <si>
+    <t>Waktu loading : 12:00 27 FEBRUARI 2026
+Rute/tujuan : WGX-MGL-JOG
+driver  : Agung prasetyo
+Nopol  : B 9739 SEU
+No hp  :085726344824
+Request Unit On Call Tgl 27 Feb 26
+1 Unit  Cddl / 24 Cbm
+Lokasi : Cikokol + Cikarang</t>
+  </si>
+  <si>
+    <t>Waktu loading : 03:00 28-02-26
+Rute/tujuan : CGK-JBR
+Driver   : Nana Hermawan
+Nopol  : B 9658 TCP
+No Hp  : 082261270165
+Driver. : Rizki 
+No hp. : 083180623289
+REQUER ORDER ULANG DAN TAMBAHAN ON CALL
+26 FEBUARI 2026
+2 UNIT TWB 50 CBM
+Lokasi : ARGOPANTES
+Nopol : BE 8831 CJ
+Rute / tujuan : MES</t>
+  </si>
+  <si>
+    <t>Waktu loading : 23:00
+Nama 	: DIAN SAPUTRA
+Nopol		: BE 8334 GBA
+No Tlp	: 08218218481
+Request Order Oncall  27 Febuari 2026
+2 UNIT TWB 50 CBM
+Lokasi : JNE SURABAYA
+Rute/ Tujuan   : SUX-CGK</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA 27 Febuari 2026
+NAMA : AKIYAT
+NOPOL : L 9722 UE
+NO HP :081281122738
+NAMA : ROSYIT
+NOPOL : B 9562 TEU
+NO HP :082313572678
+REQUES ULANG ORDER ON CALL DAN TAMBAHAN
+27 FEBUARI 2026
+2 UNIT TWB 50 CBM 
+Lokasi : ARGOPANTES
+Rute / tujuan : SUB</t>
+  </si>
+  <si>
+    <t>Waktu loading : 23:00
+Nama 	: Yugik
+Nopol		: B 9810 UEU
+No Tlp	:085855134933
+Rute / tujuan : SUB</t>
+  </si>
+  <si>
+    <t>Waktu loading : 23:00
+Nama 	: Muatim
+Nopol		: H 9224 MA
+No Tlp	:08121615206
+Request Order Oncall  27 Febuari 2026
+3 UNIT TWB 50 CBM
+Lokasi : ARGOPANTES
+Rute/ Tujuan   : SUB</t>
+  </si>
+  <si>
+    <t>Waktu loading : 15:00 27 Febuari 2026
+NAMA   : Jamaadi
+NOPOL : L 8786 BN
+NO HP  :082229973792
+NAMA : Ibnu
+NOPOL : L 9511 AL
+NO HP :082191633212
+REQUER ORDER ULANG DAN TAMBAHAN ON CALL
+26 FEBUARI 2026
+2 UNIT TWB 50 CBM 
+Lokasi : ARGOPANTES
+Rute / tujuan : PKU</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA
+Nama 	: Yusni gunawan
+Nopol		: BE 8951 BY
+No Hp ; 085382785486</t>
+  </si>
+  <si>
+    <t>REQUEST ULANG ORDER ONCALL 28 FEBRUARI 2026:
+3 unit Cddl 24 Cbm
+Lokasi : Megahub</t>
+  </si>
+  <si>
+    <t>Waktu loading : 11:00 28 FEBRUARI 2026
+Rute/tujuan : CGK - JATIM
+driver  : Agus Supriatna 
+Nopol  :B 9546 KXX
+No hp  :081511075588
+Data yg lain menyusul</t>
+  </si>
+  <si>
+    <t>REQUEST ULANG ORDER ONCALL 28 FEBRUARI 2026:
+1 unit Cddl 24 Cbm
+Lokasi : Megahub</t>
+  </si>
+  <si>
+    <t>Waktu loading : 11:00 28 FEBRUARI 2026
+Rute/tujuan : CGK - JATIM
+driver  : Rizky / Aris
+Nopol  : B9091SCJ
+No hp  : 081646057656 / 085601390708
+REQUER ORDER ULANG DAN TAMBAHAN ON CALL
+28 FEBUARI 2026
+5 UNIT CDDL 24 CBM 
+Lokasi : ARGOPANTES
+Rute / tujuan : JATENG TENTATIF</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA
+Nama : Dedeng
+Nopol :E 9426 Aa
+No.hp : 0895393659401</t>
+  </si>
+  <si>
+    <t>REQUEST ORDER ONCALL 28 FEBRUARI 2026:
+2 unit Cddl 24 Cbm
+Lokasi : Megahub</t>
+  </si>
+  <si>
+    <t>Waktu loading : 23:00 28 FEBRUARI 2026
+Rute/tujuan : CGK - JATENG
+Nama: indra
+Nopol:B9588YM
+No hp:082295768103</t>
+  </si>
+  <si>
+    <t>REQUEST ORDER ULANG ONCALL 28/02/206
+5 UNIT TWB 50 CBM
+Lokasi : ARGOPANTES</t>
+  </si>
+  <si>
+    <t>Waktu loading : 00:00 28/02/206
+Rute/tujuan : CGK - PKU
+driver  : ARIANSYAH
+Nopol  : BE 8775 DY
+No hp  :083142572937</t>
+  </si>
+  <si>
+    <t>REQUEST ORDER ONCALL 1 Maret 2026:
 3 UNIT TWB 50 Cbm
 Lokasi : ARGOPANTES</t>
   </si>
   <si>
-    <t>Waktu loading : 03:00 12 FEBRUARI 2026
-Rute/tujuan : CGK - SUB
-Revisi
-driver  : Ahmad Wahyudi
-Nopol  : W 8323 NV
-No hp  : 085792725002
-Posisi sudah dilokasi muat</t>
+    <t>REQUEST ORDER KHUSUS 28/02/2026</t>
+  </si>
+  <si>
+    <t>Waktu loading : 
+Rute/tujuan : CGK - MES
+driver : ARBI
+Nopol : BE 8919 AMN
+No hp :082237978236</t>
+  </si>
+  <si>
+    <t>Waktu loading : 12:00 28/02/2026
+Rute/tujuan : CGK - MES
+driver  : ANTON
+Nopol  : BE 9063 AR
+No hp  :083181833620
+REQUER ORDER ULANG DAN TAMBAHAN ON CALL
+26 FEBUARI 2026
+2 UNIT TWB 50 CBM 
+Lokasi : ARGOPANTES
+Rute / tujuan : PKU</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA
+Driver	: MUJITO
+Nopol   : BE 8837 GK
+No Hp : 081269087474</t>
+  </si>
+  <si>
+    <t>Waktu loading : 04;00
+Rute/tujuan : CGK - MES
+driver  : Jodi akbar 
+Nopol  : BE 8013 AU
+No hp  :085693461006</t>
+  </si>
+  <si>
+    <t>Waktu loading : 04;00
+Rute/tujuan : CGK - MES
+driver  : Jodi akbar 
+Nopol  : BE 8013 AU
+No hp  : 085693461007</t>
+  </si>
+  <si>
+    <t>REQUEST ORDER ONCALL 1 Maret 2026:</t>
+  </si>
+  <si>
+    <t>REQUEST ORDER ONCALL 03 maret 2026:
+1 unit Cddl 24 Cbm
+Lokasi : Megahub</t>
+  </si>
+  <si>
+    <t>Waktu loading : 15:00 03 maret 2026
+Rute/tujuan : CGK - DPS
+driver  :Arizal
+Nopol  :B 9895 UXX
+No hp  :081229080317</t>
   </si>
   <si>
     <t>REQUEST  ORDER  ONCALL  3 MARET 2026
 5 UNIT WB/50 CBM
 Lokasi : ARGOPANTES</t>
+  </si>
+  <si>
+    <t>Waktu loading : 23:00 3 MARET 2026
+Rute/tujuan : CGK - MES 
+driver  : SAMOSIR
+Nopol  : B 9727 UEX
+No hp  :+62 822-7429-6236</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA 3 MARET 2026
+Rute/tujuan : CGK - PKU
+driver  : Soni Rahmat
+Nopol  : BM 8142 RY
+No hp  : 082282001964</t>
+  </si>
+  <si>
+    <t>Waktu loading : 15;00 3 MARET 2026
+Rute/tujuan : CGK - PKU
+driver  :
+Nopol  :
+No hp  :</t>
+  </si>
+  <si>
+    <t>Waktu loading : 20:00 3 MARET 2026
+Rute/tujuan : CGK - PKU
+driver  :
+Nopol  :
+No hp  :</t>
+  </si>
+  <si>
+    <t>Waktu loading : 02:00 04-03-2026
+Rute/tujuan : CGK - PKU 
+driver  :
+Nopol  :
+No hp  :</t>
+  </si>
+  <si>
+    <t>Waktu loading : 07:00 04-03-2026
+Rute/tujuan : CGK - PKU 
+driver  :
+Nopol  :
+No hp  :
+Request Unit On Call Tgl 03 Mar 26
+1 Unit  Cddl / 24 Cbm
+Lokasi : Cikarang</t>
+  </si>
+  <si>
+    <t>Waktu loading : 06:00 04 Mar 26
+Rute/tujuan : CKR-JBR
+Driver   : Nana hermawan
+Nopol  : B 9658 TCP
+No Hp  :082261270165
+Request Unit On Call *Tgl 03 Mar 26
+1 Unit  Cddl / 24 Cbm
+Lokasi : Cikarang</t>
+  </si>
+  <si>
+    <t>Waktu loading : 06:00 04 Mar 26
+Rute/tujuan : CKR-MXG
+Driver   : Davit
+Nopol  : B 9726 SXW
+No Hp  :082117275166</t>
   </si>
   <si>
     <t>Waktu loading : 23:00 3 MARET 2026
@@ -919,7 +1942,6 @@
   <si>
     <t>REQUEST ORDER ONCALL
 04 MARET 2026:
-REVISI NOPOL BE 8610 DB
 5 UNIT TWB 50 CBM
 Lokasi : ARGOPANTES</t>
   </si>
@@ -944,10 +1966,7 @@
 Lokasi : Cikarang</t>
   </si>
   <si>
-    <t>REQUEST ORDER KHUSUS 06 Mar 26</t>
-  </si>
-  <si>
-    <t>Waktu loading : 06:00
+    <t>Waktu loading : 06:00 06 Mar 26
 Rute/tujuan : CKR-JBR
 Driver   : miyanta
 Nopol  : F 9647 FH
@@ -958,10 +1977,7 @@
 Lokasi : Cikokol + Cikarang</t>
   </si>
   <si>
-    <t>REQUEST ORDER KHUSUS 06  Mar 26</t>
-  </si>
-  <si>
-    <t>Waktu loading : 03:00
+    <t>Waktu loading : 03:00 06  Mar 26
 Rute/tujuan : CGK-PSR
 Driver   : Davit
 Nopol  : B 9726 SXW
@@ -979,36 +1995,26 @@
 driver  : Iwan Hariono
 Nopol  : BL 8188 JP
 No Hp :081389976421
-Request Order Oncall  05 Maret  2026</t>
-  </si>
-  <si>
-    <t>[WA_TS] Akbar Rafay: REQUEST ORDER ULANG ONCALL
-06 FEB 2026
-10 UNIT CDDL/24 CBM
-Lokasi : ARGOPANTES</t>
-  </si>
-  <si>
-    <t>Waktu loading : SEGERA
-Rute/tujuan : CGK - JATIM TENTATIF
+Request Order Oncall  05 Maret  2026
 2 UNIT TWB 50 CBM
 Lokasi : JNE SURABAYA
 Rute/ Tujuan   : SUX-CGK</t>
   </si>
   <si>
-    <t>Waktu loading : SEGERA
+    <t>Waktu loading : SEGERA 05 Maret  2026
 Driver : Akiyat
 Nopol : L 9722 UE
 No HP :081281122738
 REQUER ORDER ULANG DAN TAMBAHAN ON CALL
 06 MARET 2026
 3 UNIT TWB 50 CBM
- Lokasi : ARGOPANTES
+Lokasi : ARGOPANTES
 Rute / tujuan : *JATim TENTATIF</t>
   </si>
   <si>
     <t>Waktu loading : SEGERA
 Nama 	: M. Ibnu
-Nopol		: L 9511 AL
+Nopol   : L 9511 AL
 No Tlp	:082191633212
 Nama : Jamaadi
 Nopol : L 8786 BN
@@ -1019,13 +2025,13 @@
 REQUER ORDER ULANG DAN TAMBAHAN ON CALL
 06 MARET 2026
 3 UNIT TWB 50 CBM
- Lokasi : ARGOPANTES
+Lokasi : ARGOPANTES
 Rute / tujuan : CGK-SUB</t>
   </si>
   <si>
     <t>Waktu loading : SEGERA
 Nama 	: Yuda
-Nopol		: W 8973 UQ
+Nopol	: W 8973 UQ
 No Tlp	:089507296985
 REQUER ORDER ULANG DAN TAMBAHAN ON CALL
 06 MARET 2026
@@ -1039,18 +2045,18 @@
 Nama 	: Ridwan
 Nopol		: BK 8330 VY
 No Tlp	: 082382200400
-Fyi pak Sobar data tambahan nya
+Fyi pak @⁨Sobar JNE⁩ data tambahan nya
 REQUER ORDER ULANG DAN TAMBAHAN ON CALL
 06 MARET 2026
 DATA SUMATERA
 2 UNIT TWB 50 CBM
- Lokasi : ARGOPANTES
+Lokasi : ARGOPANTES
 Rute / tujuan : PKU</t>
   </si>
   <si>
     <t>Waktu loading : SEGERA
 Nama 	: Nasip
-Nopol		: BH 8165 QI
+Nopol	: BH 8165 QI
 No Tlp	:+6281272463920
 REQUER ORDER ULANG DAN TAMBAHAN ON CALL
 06 MARET 2026
@@ -1074,6 +2080,48 @@
 No Hp :081317708658</t>
   </si>
   <si>
+    <t>085353886066</t>
+  </si>
+  <si>
+    <t>085865762797</t>
+  </si>
+  <si>
+    <t>0 81231895971</t>
+  </si>
+  <si>
+    <t>0 87886861780</t>
+  </si>
+  <si>
+    <t>08817021866</t>
+  </si>
+  <si>
+    <t>082118558105</t>
+  </si>
+  <si>
+    <t>081943564062</t>
+  </si>
+  <si>
+    <t>085219216210</t>
+  </si>
+  <si>
+    <t>083169525183</t>
+  </si>
+  <si>
+    <t>081281122738</t>
+  </si>
+  <si>
+    <t>087837496810</t>
+  </si>
+  <si>
+    <t>0 87786676177</t>
+  </si>
+  <si>
+    <t>085971812879</t>
+  </si>
+  <si>
+    <t>082191633212</t>
+  </si>
+  <si>
     <t>085784422398</t>
   </si>
   <si>
@@ -1086,106 +2134,187 @@
     <t>0 85231681470</t>
   </si>
   <si>
-    <t>0 81287147789</t>
-  </si>
-  <si>
-    <t>083142142113</t>
-  </si>
-  <si>
-    <t>085385220743</t>
-  </si>
-  <si>
-    <t>083166684195</t>
-  </si>
-  <si>
-    <t>085194592825</t>
-  </si>
-  <si>
-    <t>0882016641381</t>
-  </si>
-  <si>
-    <t>082363564665</t>
-  </si>
-  <si>
-    <t>089690885555</t>
+    <t>0 85707380584</t>
+  </si>
+  <si>
+    <t>089519041791</t>
+  </si>
+  <si>
+    <t>085218843366</t>
+  </si>
+  <si>
+    <t>082313572678</t>
+  </si>
+  <si>
+    <t>082217785226</t>
+  </si>
+  <si>
+    <t>087844510846</t>
+  </si>
+  <si>
+    <t>81382418508</t>
+  </si>
+  <si>
+    <t>082183783385</t>
+  </si>
+  <si>
+    <t>085758955627</t>
+  </si>
+  <si>
+    <t>0 81269345748</t>
+  </si>
+  <si>
+    <t>08889693664</t>
+  </si>
+  <si>
+    <t>085364056583</t>
+  </si>
+  <si>
+    <t>085225394209</t>
+  </si>
+  <si>
+    <t>082385989323</t>
+  </si>
+  <si>
+    <t>0 82228516922</t>
+  </si>
+  <si>
+    <t>081382418508</t>
+  </si>
+  <si>
+    <t>088290294126</t>
+  </si>
+  <si>
+    <t>088212698834</t>
+  </si>
+  <si>
+    <t>081328851819</t>
+  </si>
+  <si>
+    <t>0 82377225563</t>
+  </si>
+  <si>
+    <t>0 81262189242</t>
+  </si>
+  <si>
+    <t>082117275166</t>
+  </si>
+  <si>
+    <t>081262189242</t>
+  </si>
+  <si>
+    <t>0 88907020037</t>
+  </si>
+  <si>
+    <t>081280483919</t>
+  </si>
+  <si>
+    <t>082286523993</t>
+  </si>
+  <si>
+    <t>082164544736</t>
+  </si>
+  <si>
+    <t>081231540625</t>
+  </si>
+  <si>
+    <t>081936963942</t>
+  </si>
+  <si>
+    <t>082389746001</t>
+  </si>
+  <si>
+    <t>085726344824</t>
+  </si>
+  <si>
+    <t>083180623289</t>
+  </si>
+  <si>
+    <t>08218218481</t>
+  </si>
+  <si>
+    <t>085855134933</t>
+  </si>
+  <si>
+    <t>08121615206</t>
+  </si>
+  <si>
+    <t>085382785486</t>
+  </si>
+  <si>
+    <t>081511075588</t>
+  </si>
+  <si>
+    <t>085601390708</t>
+  </si>
+  <si>
+    <t>0895393659401</t>
+  </si>
+  <si>
+    <t>082295768103</t>
+  </si>
+  <si>
+    <t>083142572937</t>
+  </si>
+  <si>
+    <t>082237978236</t>
+  </si>
+  <si>
+    <t>083181833620</t>
+  </si>
+  <si>
+    <t>081269087474</t>
+  </si>
+  <si>
+    <t>085693461006</t>
+  </si>
+  <si>
+    <t>085693461007</t>
+  </si>
+  <si>
+    <t>081229080317</t>
+  </si>
+  <si>
+    <t>0 82274296236</t>
+  </si>
+  <si>
+    <t>082282001964</t>
+  </si>
+  <si>
+    <t>082261270165</t>
   </si>
   <si>
     <t>089507296985</t>
   </si>
   <si>
-    <t>083167610479</t>
-  </si>
-  <si>
-    <t>081350529712</t>
-  </si>
-  <si>
-    <t>082170733190</t>
-  </si>
-  <si>
-    <t>081313444015</t>
-  </si>
-  <si>
-    <t>0 82274296236</t>
-  </si>
-  <si>
-    <t>0 82276385077</t>
+    <t>082136689169</t>
+  </si>
+  <si>
+    <t>082172471454</t>
+  </si>
+  <si>
+    <t>081374328877</t>
+  </si>
+  <si>
+    <t>082211762649</t>
+  </si>
+  <si>
+    <t>0 85373372594</t>
+  </si>
+  <si>
+    <t>08118558105</t>
+  </si>
+  <si>
+    <t>081389976421</t>
+  </si>
+  <si>
+    <t>085729113217</t>
+  </si>
+  <si>
+    <t>082382200400</t>
   </si>
   <si>
     <t>081272463920</t>
-  </si>
-  <si>
-    <t>0 85707380584</t>
-  </si>
-  <si>
-    <t>089519041791</t>
-  </si>
-  <si>
-    <t>085218843366</t>
-  </si>
-  <si>
-    <t>082313572678</t>
-  </si>
-  <si>
-    <t>082191633212</t>
-  </si>
-  <si>
-    <t>081281122738</t>
-  </si>
-  <si>
-    <t>085792725002</t>
-  </si>
-  <si>
-    <t>082136689169</t>
-  </si>
-  <si>
-    <t>0895393659401</t>
-  </si>
-  <si>
-    <t>082172471454</t>
-  </si>
-  <si>
-    <t>081374328877</t>
-  </si>
-  <si>
-    <t>082211762649</t>
-  </si>
-  <si>
-    <t>0 85373372594</t>
-  </si>
-  <si>
-    <t>08118558105</t>
-  </si>
-  <si>
-    <t>082117275166</t>
-  </si>
-  <si>
-    <t>081389976421</t>
-  </si>
-  <si>
-    <t>085729113217</t>
-  </si>
-  <si>
-    <t>082382200400</t>
   </si>
   <si>
     <t>081317708658</t>
@@ -1546,7 +2675,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J98"/>
+  <dimension ref="A1:J201"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:10">
@@ -1582,43 +2711,37 @@
       </c>
     </row>
     <row r="2" spans="1:10">
-      <c r="A2" t="s">
-        <v>10</v>
-      </c>
       <c r="B2" t="s">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="C2" t="s">
-        <v>42</v>
+        <v>63</v>
       </c>
       <c r="D2" t="s">
-        <v>46</v>
-      </c>
-      <c r="F2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I2" t="s">
-        <v>156</v>
+        <v>273</v>
       </c>
     </row>
     <row r="3" spans="1:10">
-      <c r="A3" t="s">
-        <v>10</v>
-      </c>
       <c r="E3" t="s">
-        <v>54</v>
+        <v>79</v>
       </c>
       <c r="F3" t="s">
-        <v>72</v>
+        <v>107</v>
       </c>
       <c r="G3" t="s">
-        <v>111</v>
+        <v>186</v>
+      </c>
+      <c r="H3" t="s">
+        <v>265</v>
       </c>
       <c r="I3" t="s">
-        <v>157</v>
+        <v>274</v>
       </c>
       <c r="J3" t="s">
-        <v>243</v>
+        <v>445</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -1626,19 +2749,16 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>35</v>
+        <v>57</v>
       </c>
       <c r="C4" t="s">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="D4" t="s">
-        <v>46</v>
-      </c>
-      <c r="F4" t="s">
         <v>71</v>
       </c>
       <c r="I4" t="s">
-        <v>156</v>
+        <v>275</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -1646,218 +2766,188 @@
         <v>10</v>
       </c>
       <c r="E5" t="s">
-        <v>54</v>
+        <v>80</v>
       </c>
       <c r="F5" t="s">
-        <v>73</v>
+        <v>108</v>
       </c>
       <c r="G5" t="s">
-        <v>112</v>
-      </c>
-      <c r="H5" t="s">
-        <v>150</v>
+        <v>187</v>
       </c>
       <c r="I5" t="s">
-        <v>158</v>
+        <v>276</v>
       </c>
       <c r="J5" t="s">
-        <v>244</v>
+        <v>446</v>
       </c>
     </row>
     <row r="6" spans="1:10">
-      <c r="A6" t="s">
-        <v>11</v>
-      </c>
       <c r="B6" t="s">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="C6" t="s">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="D6" t="s">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="I6" t="s">
-        <v>159</v>
+        <v>277</v>
       </c>
     </row>
     <row r="7" spans="1:10">
+      <c r="E7" t="s">
+        <v>81</v>
+      </c>
+      <c r="H7" t="s">
+        <v>265</v>
+      </c>
       <c r="I7" t="s">
-        <v>160</v>
-      </c>
-      <c r="J7" t="s">
-        <v>245</v>
+        <v>278</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="E8" t="s">
-        <v>51</v>
+        <v>81</v>
       </c>
       <c r="F8" t="s">
-        <v>74</v>
+        <v>109</v>
       </c>
       <c r="G8" t="s">
-        <v>113</v>
+        <v>188</v>
       </c>
       <c r="H8" t="s">
-        <v>151</v>
+        <v>266</v>
       </c>
       <c r="I8" t="s">
-        <v>161</v>
+        <v>279</v>
       </c>
       <c r="J8" t="s">
-        <v>246</v>
+        <v>447</v>
       </c>
     </row>
     <row r="9" spans="1:10">
-      <c r="A9" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9" t="s">
-        <v>37</v>
-      </c>
-      <c r="C9" t="s">
-        <v>42</v>
-      </c>
-      <c r="D9" t="s">
-        <v>47</v>
-      </c>
       <c r="E9" t="s">
-        <v>55</v>
+        <v>81</v>
+      </c>
+      <c r="H9" t="s">
+        <v>267</v>
       </c>
       <c r="I9" t="s">
-        <v>162</v>
+        <v>280</v>
       </c>
     </row>
     <row r="10" spans="1:10">
-      <c r="F10" t="s">
-        <v>75</v>
-      </c>
-      <c r="G10" t="s">
-        <v>114</v>
-      </c>
-      <c r="H10" t="s">
-        <v>150</v>
+      <c r="E10" t="s">
+        <v>81</v>
       </c>
       <c r="I10" t="s">
-        <v>163</v>
-      </c>
-      <c r="J10" t="s">
-        <v>247</v>
+        <v>281</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" t="s">
-        <v>12</v>
-      </c>
-      <c r="B11" t="s">
-        <v>38</v>
-      </c>
-      <c r="C11" t="s">
-        <v>42</v>
-      </c>
-      <c r="D11" t="s">
-        <v>47</v>
-      </c>
-      <c r="E11" t="s">
-        <v>51</v>
-      </c>
-      <c r="F11" t="s">
-        <v>71</v>
+        <v>11</v>
       </c>
       <c r="I11" t="s">
-        <v>164</v>
+        <v>282</v>
       </c>
     </row>
     <row r="12" spans="1:10">
+      <c r="E12" t="s">
+        <v>81</v>
+      </c>
       <c r="F12" t="s">
-        <v>76</v>
+        <v>110</v>
       </c>
       <c r="G12" t="s">
-        <v>115</v>
+        <v>189</v>
       </c>
       <c r="H12" t="s">
-        <v>150</v>
+        <v>268</v>
       </c>
       <c r="I12" t="s">
-        <v>165</v>
+        <v>283</v>
       </c>
       <c r="J12" t="s">
-        <v>248</v>
+        <v>448</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="C13" t="s">
-        <v>42</v>
+        <v>63</v>
       </c>
       <c r="D13" t="s">
-        <v>47</v>
-      </c>
-      <c r="E13" t="s">
-        <v>51</v>
-      </c>
-      <c r="F13" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I13" t="s">
-        <v>164</v>
+        <v>284</v>
       </c>
     </row>
     <row r="14" spans="1:10">
+      <c r="A14" t="s">
+        <v>10</v>
+      </c>
+      <c r="E14" t="s">
+        <v>81</v>
+      </c>
       <c r="F14" t="s">
-        <v>77</v>
+        <v>111</v>
       </c>
       <c r="G14" t="s">
-        <v>116</v>
+        <v>190</v>
       </c>
       <c r="H14" t="s">
-        <v>150</v>
+        <v>265</v>
       </c>
       <c r="I14" t="s">
-        <v>166</v>
+        <v>285</v>
       </c>
       <c r="J14" t="s">
-        <v>249</v>
+        <v>449</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" t="s">
-        <v>12</v>
+        <v>10</v>
+      </c>
+      <c r="B15" t="s">
+        <v>56</v>
+      </c>
+      <c r="C15" t="s">
+        <v>64</v>
       </c>
       <c r="D15" t="s">
-        <v>47</v>
-      </c>
-      <c r="E15" t="s">
-        <v>56</v>
-      </c>
-      <c r="F15" t="s">
         <v>71</v>
       </c>
       <c r="I15" t="s">
-        <v>167</v>
+        <v>286</v>
       </c>
     </row>
     <row r="16" spans="1:10">
+      <c r="A16" t="s">
+        <v>10</v>
+      </c>
+      <c r="E16" t="s">
+        <v>82</v>
+      </c>
       <c r="F16" t="s">
-        <v>78</v>
+        <v>112</v>
       </c>
       <c r="G16" t="s">
-        <v>117</v>
-      </c>
-      <c r="H16" t="s">
-        <v>150</v>
+        <v>191</v>
       </c>
       <c r="I16" t="s">
-        <v>168</v>
+        <v>287</v>
       </c>
       <c r="J16" t="s">
-        <v>250</v>
+        <v>450</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -1865,1567 +2955,3627 @@
         <v>12</v>
       </c>
       <c r="B17" t="s">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="C17" t="s">
-        <v>42</v>
+        <v>63</v>
       </c>
       <c r="D17" t="s">
-        <v>47</v>
-      </c>
-      <c r="E17" t="s">
-        <v>51</v>
-      </c>
-      <c r="F17" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I17" t="s">
-        <v>164</v>
+        <v>288</v>
       </c>
     </row>
     <row r="18" spans="1:10">
-      <c r="F18" t="s">
-        <v>79</v>
-      </c>
-      <c r="G18" t="s">
-        <v>118</v>
+      <c r="A18" t="s">
+        <v>12</v>
+      </c>
+      <c r="B18" t="s">
+        <v>59</v>
+      </c>
+      <c r="C18" t="s">
+        <v>63</v>
+      </c>
+      <c r="D18" t="s">
+        <v>72</v>
       </c>
       <c r="H18" t="s">
-        <v>150</v>
+        <v>265</v>
       </c>
       <c r="I18" t="s">
-        <v>169</v>
-      </c>
-      <c r="J18" t="s">
-        <v>251</v>
+        <v>289</v>
       </c>
     </row>
     <row r="19" spans="1:10">
       <c r="A19" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B19" t="s">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="C19" t="s">
-        <v>44</v>
+        <v>63</v>
+      </c>
+      <c r="D19" t="s">
+        <v>72</v>
       </c>
       <c r="E19" t="s">
-        <v>57</v>
+        <v>83</v>
+      </c>
+      <c r="H19" t="s">
+        <v>265</v>
       </c>
       <c r="I19" t="s">
-        <v>170</v>
+        <v>290</v>
       </c>
     </row>
     <row r="20" spans="1:10">
+      <c r="A20" t="s">
+        <v>12</v>
+      </c>
+      <c r="E20" t="s">
+        <v>72</v>
+      </c>
       <c r="F20" t="s">
-        <v>80</v>
+        <v>113</v>
       </c>
       <c r="G20" t="s">
-        <v>119</v>
+        <v>192</v>
       </c>
       <c r="H20" t="s">
-        <v>150</v>
+        <v>265</v>
       </c>
       <c r="I20" t="s">
-        <v>171</v>
+        <v>291</v>
       </c>
       <c r="J20" t="s">
-        <v>252</v>
+        <v>451</v>
       </c>
     </row>
     <row r="21" spans="1:10">
       <c r="A21" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B21" t="s">
-        <v>37</v>
+        <v>59</v>
       </c>
       <c r="C21" t="s">
-        <v>42</v>
+        <v>63</v>
       </c>
       <c r="D21" t="s">
-        <v>47</v>
+        <v>72</v>
+      </c>
+      <c r="E21" t="s">
+        <v>84</v>
+      </c>
+      <c r="H21" t="s">
+        <v>265</v>
       </c>
       <c r="I21" t="s">
-        <v>172</v>
+        <v>292</v>
       </c>
     </row>
     <row r="22" spans="1:10">
       <c r="A22" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E22" t="s">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="F22" t="s">
-        <v>81</v>
+        <v>114</v>
       </c>
       <c r="G22" t="s">
-        <v>120</v>
+        <v>193</v>
       </c>
       <c r="H22" t="s">
-        <v>150</v>
+        <v>265</v>
       </c>
       <c r="I22" t="s">
-        <v>173</v>
+        <v>293</v>
       </c>
       <c r="J22" t="s">
-        <v>253</v>
+        <v>452</v>
       </c>
     </row>
     <row r="23" spans="1:10">
       <c r="A23" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B23" t="s">
-        <v>40</v>
+        <v>59</v>
       </c>
       <c r="C23" t="s">
-        <v>44</v>
-      </c>
-      <c r="E23" t="s">
-        <v>58</v>
+        <v>63</v>
+      </c>
+      <c r="D23" t="s">
+        <v>72</v>
       </c>
       <c r="I23" t="s">
-        <v>174</v>
+        <v>294</v>
       </c>
     </row>
     <row r="24" spans="1:10">
+      <c r="A24" t="s">
+        <v>12</v>
+      </c>
       <c r="E24" t="s">
-        <v>59</v>
+        <v>85</v>
       </c>
       <c r="F24" t="s">
-        <v>82</v>
+        <v>115</v>
       </c>
       <c r="G24" t="s">
-        <v>121</v>
+        <v>194</v>
       </c>
       <c r="H24" t="s">
-        <v>152</v>
+        <v>265</v>
       </c>
       <c r="I24" t="s">
-        <v>175</v>
-      </c>
-      <c r="J24" t="s">
-        <v>254</v>
+        <v>295</v>
       </c>
     </row>
     <row r="25" spans="1:10">
       <c r="A25" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B25" t="s">
-        <v>35</v>
+        <v>59</v>
       </c>
       <c r="C25" t="s">
-        <v>42</v>
+        <v>63</v>
       </c>
       <c r="D25" t="s">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="I25" t="s">
-        <v>176</v>
+        <v>294</v>
       </c>
     </row>
     <row r="26" spans="1:10">
       <c r="A26" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E26" t="s">
-        <v>51</v>
+        <v>85</v>
       </c>
       <c r="F26" t="s">
-        <v>72</v>
+        <v>116</v>
       </c>
       <c r="G26" t="s">
-        <v>111</v>
+        <v>195</v>
+      </c>
+      <c r="H26" t="s">
+        <v>265</v>
       </c>
       <c r="I26" t="s">
-        <v>177</v>
+        <v>296</v>
       </c>
       <c r="J26" t="s">
-        <v>243</v>
+        <v>453</v>
       </c>
     </row>
     <row r="27" spans="1:10">
-      <c r="A27" t="s">
-        <v>16</v>
-      </c>
-      <c r="F27" t="s">
-        <v>83</v>
-      </c>
-      <c r="G27" t="s">
-        <v>122</v>
+      <c r="B27" t="s">
+        <v>58</v>
+      </c>
+      <c r="C27" t="s">
+        <v>63</v>
+      </c>
+      <c r="D27" t="s">
+        <v>70</v>
       </c>
       <c r="I27" t="s">
-        <v>178</v>
-      </c>
-      <c r="J27" t="s">
-        <v>255</v>
+        <v>277</v>
       </c>
     </row>
     <row r="28" spans="1:10">
-      <c r="A28" t="s">
-        <v>16</v>
-      </c>
-      <c r="B28" t="s">
-        <v>35</v>
-      </c>
-      <c r="C28" t="s">
-        <v>42</v>
-      </c>
-      <c r="D28" t="s">
-        <v>48</v>
+      <c r="E28" t="s">
+        <v>86</v>
+      </c>
+      <c r="F28" t="s">
+        <v>117</v>
+      </c>
+      <c r="G28" t="s">
+        <v>196</v>
+      </c>
+      <c r="H28" t="s">
+        <v>265</v>
       </c>
       <c r="I28" t="s">
-        <v>179</v>
+        <v>297</v>
+      </c>
+      <c r="J28" t="s">
+        <v>454</v>
       </c>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" t="s">
-        <v>17</v>
+        <v>13</v>
+      </c>
+      <c r="B29" t="s">
+        <v>59</v>
+      </c>
+      <c r="C29" t="s">
+        <v>63</v>
+      </c>
+      <c r="D29" t="s">
+        <v>72</v>
       </c>
       <c r="I29" t="s">
-        <v>180</v>
+        <v>298</v>
       </c>
     </row>
     <row r="30" spans="1:10">
+      <c r="A30" t="s">
+        <v>13</v>
+      </c>
       <c r="E30" t="s">
-        <v>56</v>
+        <v>84</v>
       </c>
       <c r="F30" t="s">
-        <v>84</v>
+        <v>118</v>
       </c>
       <c r="G30" t="s">
-        <v>123</v>
+        <v>197</v>
       </c>
       <c r="H30" t="s">
-        <v>153</v>
+        <v>265</v>
       </c>
       <c r="I30" t="s">
-        <v>181</v>
+        <v>299</v>
       </c>
       <c r="J30" t="s">
-        <v>256</v>
+        <v>455</v>
       </c>
     </row>
     <row r="31" spans="1:10">
-      <c r="A31" t="s">
-        <v>17</v>
+      <c r="B31" t="s">
+        <v>58</v>
+      </c>
+      <c r="C31" t="s">
+        <v>63</v>
+      </c>
+      <c r="D31" t="s">
+        <v>70</v>
       </c>
       <c r="I31" t="s">
-        <v>180</v>
+        <v>277</v>
       </c>
     </row>
     <row r="32" spans="1:10">
+      <c r="E32" t="s">
+        <v>81</v>
+      </c>
+      <c r="F32" t="s">
+        <v>119</v>
+      </c>
+      <c r="G32" t="s">
+        <v>198</v>
+      </c>
       <c r="H32" t="s">
-        <v>154</v>
+        <v>265</v>
       </c>
       <c r="I32" t="s">
-        <v>182</v>
+        <v>300</v>
+      </c>
+      <c r="J32" t="s">
+        <v>456</v>
       </c>
     </row>
     <row r="33" spans="1:10">
-      <c r="A33" t="s">
-        <v>15</v>
-      </c>
-      <c r="B33" t="s">
-        <v>40</v>
-      </c>
-      <c r="C33" t="s">
-        <v>44</v>
-      </c>
       <c r="E33" t="s">
-        <v>58</v>
+        <v>81</v>
+      </c>
+      <c r="H33" t="s">
+        <v>266</v>
       </c>
       <c r="I33" t="s">
-        <v>174</v>
+        <v>301</v>
       </c>
     </row>
     <row r="34" spans="1:10">
-      <c r="A34" t="s">
-        <v>18</v>
-      </c>
       <c r="E34" t="s">
-        <v>59</v>
-      </c>
-      <c r="F34" t="s">
-        <v>85</v>
-      </c>
-      <c r="G34" t="s">
-        <v>124</v>
+        <v>81</v>
+      </c>
+      <c r="H34" t="s">
+        <v>267</v>
       </c>
       <c r="I34" t="s">
-        <v>183</v>
-      </c>
-      <c r="J34" t="s">
-        <v>257</v>
+        <v>280</v>
       </c>
     </row>
     <row r="35" spans="1:10">
-      <c r="A35" t="s">
-        <v>16</v>
-      </c>
-      <c r="B35" t="s">
-        <v>35</v>
-      </c>
-      <c r="C35" t="s">
-        <v>42</v>
-      </c>
-      <c r="D35" t="s">
-        <v>48</v>
+      <c r="E35" t="s">
+        <v>81</v>
       </c>
       <c r="I35" t="s">
-        <v>179</v>
+        <v>281</v>
       </c>
     </row>
     <row r="36" spans="1:10">
       <c r="A36" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="I36" t="s">
-        <v>180</v>
+        <v>302</v>
       </c>
     </row>
     <row r="37" spans="1:10">
       <c r="E37" t="s">
-        <v>56</v>
+        <v>81</v>
       </c>
       <c r="H37" t="s">
-        <v>153</v>
+        <v>268</v>
       </c>
       <c r="I37" t="s">
-        <v>184</v>
+        <v>303</v>
       </c>
     </row>
     <row r="38" spans="1:10">
       <c r="A38" t="s">
-        <v>17</v>
+        <v>12</v>
+      </c>
+      <c r="B38" t="s">
+        <v>59</v>
+      </c>
+      <c r="C38" t="s">
+        <v>63</v>
+      </c>
+      <c r="D38" t="s">
+        <v>72</v>
       </c>
       <c r="I38" t="s">
-        <v>180</v>
+        <v>288</v>
       </c>
     </row>
     <row r="39" spans="1:10">
+      <c r="A39" t="s">
+        <v>12</v>
+      </c>
+      <c r="E39" t="s">
+        <v>83</v>
+      </c>
       <c r="F39" t="s">
-        <v>86</v>
+        <v>120</v>
       </c>
       <c r="G39" t="s">
-        <v>125</v>
+        <v>194</v>
       </c>
       <c r="H39" t="s">
-        <v>154</v>
+        <v>265</v>
       </c>
       <c r="I39" t="s">
-        <v>185</v>
-      </c>
-      <c r="J39" t="s">
-        <v>258</v>
+        <v>304</v>
       </c>
     </row>
     <row r="40" spans="1:10">
       <c r="A40" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B40" t="s">
-        <v>35</v>
+        <v>59</v>
       </c>
       <c r="C40" t="s">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="D40" t="s">
-        <v>48</v>
+        <v>73</v>
       </c>
       <c r="E40" t="s">
-        <v>56</v>
+        <v>61</v>
+      </c>
+      <c r="F40" t="s">
+        <v>121</v>
       </c>
       <c r="I40" t="s">
-        <v>186</v>
+        <v>305</v>
       </c>
     </row>
     <row r="41" spans="1:10">
       <c r="A41" t="s">
         <v>16</v>
       </c>
-      <c r="F41" t="s">
-        <v>86</v>
-      </c>
-      <c r="G41" t="s">
-        <v>125</v>
-      </c>
-      <c r="H41" t="s">
-        <v>150</v>
+      <c r="B41" t="s">
+        <v>56</v>
+      </c>
+      <c r="C41" t="s">
+        <v>64</v>
+      </c>
+      <c r="D41" t="s">
+        <v>74</v>
+      </c>
+      <c r="E41" t="s">
+        <v>73</v>
       </c>
       <c r="I41" t="s">
-        <v>187</v>
-      </c>
-      <c r="J41" t="s">
-        <v>258</v>
+        <v>306</v>
       </c>
     </row>
     <row r="42" spans="1:10">
       <c r="A42" t="s">
-        <v>19</v>
-      </c>
-      <c r="B42" t="s">
-        <v>40</v>
-      </c>
-      <c r="C42" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="D42" t="s">
-        <v>49</v>
+        <v>74</v>
+      </c>
+      <c r="F42" t="s">
+        <v>122</v>
+      </c>
+      <c r="G42" t="s">
+        <v>199</v>
       </c>
       <c r="I42" t="s">
-        <v>188</v>
+        <v>307</v>
+      </c>
+      <c r="J42" t="s">
+        <v>457</v>
       </c>
     </row>
     <row r="43" spans="1:10">
       <c r="A43" t="s">
-        <v>19</v>
-      </c>
-      <c r="E43" t="s">
-        <v>60</v>
+        <v>18</v>
+      </c>
+      <c r="B43" t="s">
+        <v>57</v>
+      </c>
+      <c r="C43" t="s">
+        <v>63</v>
+      </c>
+      <c r="D43" t="s">
+        <v>70</v>
       </c>
       <c r="F43" t="s">
-        <v>87</v>
-      </c>
-      <c r="G43" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="I43" t="s">
-        <v>189</v>
-      </c>
-      <c r="J43" t="s">
-        <v>259</v>
+        <v>308</v>
       </c>
     </row>
     <row r="44" spans="1:10">
       <c r="A44" t="s">
-        <v>19</v>
-      </c>
-      <c r="B44" t="s">
-        <v>41</v>
-      </c>
-      <c r="D44" t="s">
-        <v>48</v>
+        <v>18</v>
+      </c>
+      <c r="E44" t="s">
+        <v>87</v>
+      </c>
+      <c r="F44" t="s">
+        <v>123</v>
+      </c>
+      <c r="G44" t="s">
+        <v>200</v>
+      </c>
+      <c r="H44" t="s">
+        <v>265</v>
       </c>
       <c r="I44" t="s">
-        <v>190</v>
+        <v>309</v>
+      </c>
+      <c r="J44" t="s">
+        <v>458</v>
       </c>
     </row>
     <row r="45" spans="1:10">
       <c r="A45" t="s">
-        <v>19</v>
-      </c>
-      <c r="E45" t="s">
-        <v>61</v>
-      </c>
-      <c r="H45" t="s">
-        <v>150</v>
+        <v>18</v>
+      </c>
+      <c r="B45" t="s">
+        <v>59</v>
+      </c>
+      <c r="C45" t="s">
+        <v>63</v>
+      </c>
+      <c r="D45" t="s">
+        <v>75</v>
+      </c>
+      <c r="F45" t="s">
+        <v>121</v>
       </c>
       <c r="I45" t="s">
-        <v>191</v>
+        <v>310</v>
       </c>
     </row>
     <row r="46" spans="1:10">
       <c r="A46" t="s">
-        <v>20</v>
+        <v>18</v>
+      </c>
+      <c r="E46" t="s">
+        <v>88</v>
       </c>
       <c r="F46" t="s">
-        <v>88</v>
+        <v>124</v>
       </c>
       <c r="G46" t="s">
-        <v>127</v>
+        <v>201</v>
       </c>
       <c r="I46" t="s">
-        <v>192</v>
+        <v>311</v>
       </c>
       <c r="J46" t="s">
-        <v>260</v>
+        <v>459</v>
       </c>
     </row>
     <row r="47" spans="1:10">
       <c r="A47" t="s">
-        <v>19</v>
+        <v>18</v>
+      </c>
+      <c r="B47" t="s">
+        <v>59</v>
+      </c>
+      <c r="C47" t="s">
+        <v>63</v>
+      </c>
+      <c r="D47" t="s">
+        <v>75</v>
       </c>
       <c r="F47" t="s">
-        <v>89</v>
-      </c>
-      <c r="G47" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="I47" t="s">
-        <v>193</v>
-      </c>
-      <c r="J47" t="s">
-        <v>261</v>
+        <v>310</v>
       </c>
     </row>
     <row r="48" spans="1:10">
       <c r="A48" t="s">
-        <v>21</v>
-      </c>
-      <c r="B48" t="s">
-        <v>41</v>
-      </c>
-      <c r="D48" t="s">
-        <v>48</v>
+        <v>18</v>
+      </c>
+      <c r="E48" t="s">
+        <v>88</v>
+      </c>
+      <c r="F48" t="s">
+        <v>125</v>
+      </c>
+      <c r="G48" t="s">
+        <v>202</v>
+      </c>
+      <c r="H48" t="s">
+        <v>265</v>
       </c>
       <c r="I48" t="s">
-        <v>194</v>
+        <v>312</v>
+      </c>
+      <c r="J48" t="s">
+        <v>460</v>
       </c>
     </row>
     <row r="49" spans="1:10">
       <c r="A49" t="s">
-        <v>22</v>
+        <v>19</v>
+      </c>
+      <c r="B49" t="s">
+        <v>60</v>
+      </c>
+      <c r="C49" t="s">
+        <v>65</v>
+      </c>
+      <c r="D49" t="s">
+        <v>70</v>
       </c>
       <c r="I49" t="s">
-        <v>195</v>
+        <v>313</v>
       </c>
     </row>
     <row r="50" spans="1:10">
-      <c r="E50" t="s">
-        <v>56</v>
-      </c>
-      <c r="F50" t="s">
-        <v>90</v>
-      </c>
-      <c r="G50" t="s">
-        <v>129</v>
-      </c>
-      <c r="H50" t="s">
-        <v>153</v>
-      </c>
       <c r="I50" t="s">
-        <v>196</v>
+        <v>314</v>
       </c>
       <c r="J50" t="s">
-        <v>262</v>
+        <v>461</v>
       </c>
     </row>
     <row r="51" spans="1:10">
-      <c r="A51" t="s">
-        <v>23</v>
-      </c>
-      <c r="B51" t="s">
-        <v>40</v>
-      </c>
-      <c r="C51" t="s">
-        <v>42</v>
-      </c>
-      <c r="D51" t="s">
-        <v>50</v>
+      <c r="E51" t="s">
+        <v>81</v>
       </c>
       <c r="F51" t="s">
-        <v>71</v>
+        <v>126</v>
+      </c>
+      <c r="G51" t="s">
+        <v>203</v>
+      </c>
+      <c r="H51" t="s">
+        <v>269</v>
       </c>
       <c r="I51" t="s">
-        <v>197</v>
+        <v>315</v>
+      </c>
+      <c r="J51" t="s">
+        <v>462</v>
       </c>
     </row>
     <row r="52" spans="1:10">
       <c r="A52" t="s">
-        <v>23</v>
-      </c>
-      <c r="E52" t="s">
-        <v>62</v>
-      </c>
-      <c r="F52" t="s">
-        <v>91</v>
-      </c>
-      <c r="G52" t="s">
-        <v>130</v>
-      </c>
-      <c r="H52" t="s">
-        <v>150</v>
+        <v>19</v>
+      </c>
+      <c r="B52" t="s">
+        <v>61</v>
+      </c>
+      <c r="C52" t="s">
+        <v>64</v>
+      </c>
+      <c r="D52" t="s">
+        <v>70</v>
       </c>
       <c r="I52" t="s">
-        <v>198</v>
-      </c>
-      <c r="J52" t="s">
-        <v>263</v>
+        <v>316</v>
       </c>
     </row>
     <row r="53" spans="1:10">
-      <c r="A53" t="s">
-        <v>23</v>
-      </c>
-      <c r="B53" t="s">
-        <v>40</v>
-      </c>
-      <c r="C53" t="s">
-        <v>44</v>
-      </c>
       <c r="E53" t="s">
-        <v>50</v>
-      </c>
-      <c r="F53" t="s">
-        <v>71</v>
+        <v>89</v>
+      </c>
+      <c r="H53" t="s">
+        <v>265</v>
       </c>
       <c r="I53" t="s">
-        <v>199</v>
+        <v>317</v>
       </c>
     </row>
     <row r="54" spans="1:10">
-      <c r="E54" t="s">
+      <c r="A54" t="s">
+        <v>20</v>
+      </c>
+      <c r="B54" t="s">
+        <v>56</v>
+      </c>
+      <c r="C54" t="s">
         <v>63</v>
       </c>
+      <c r="D54" t="s">
+        <v>73</v>
+      </c>
       <c r="F54" t="s">
-        <v>92</v>
-      </c>
-      <c r="G54" t="s">
-        <v>131</v>
-      </c>
-      <c r="H54" t="s">
-        <v>154</v>
+        <v>121</v>
       </c>
       <c r="I54" t="s">
-        <v>200</v>
-      </c>
-      <c r="J54" t="s">
-        <v>264</v>
+        <v>318</v>
       </c>
     </row>
     <row r="55" spans="1:10">
       <c r="A55" t="s">
-        <v>21</v>
-      </c>
-      <c r="B55" t="s">
-        <v>37</v>
-      </c>
-      <c r="D55" t="s">
-        <v>48</v>
+        <v>20</v>
+      </c>
+      <c r="E55" t="s">
+        <v>90</v>
+      </c>
+      <c r="F55" t="s">
+        <v>127</v>
+      </c>
+      <c r="G55" t="s">
+        <v>204</v>
+      </c>
+      <c r="H55" t="s">
+        <v>265</v>
       </c>
       <c r="I55" t="s">
-        <v>201</v>
+        <v>319</v>
+      </c>
+      <c r="J55" t="s">
+        <v>463</v>
       </c>
     </row>
     <row r="56" spans="1:10">
       <c r="A56" t="s">
-        <v>21</v>
+        <v>20</v>
+      </c>
+      <c r="B56" t="s">
+        <v>56</v>
+      </c>
+      <c r="C56" t="s">
+        <v>64</v>
       </c>
       <c r="E56" t="s">
-        <v>55</v>
+        <v>73</v>
       </c>
       <c r="F56" t="s">
-        <v>93</v>
-      </c>
-      <c r="G56" t="s">
-        <v>132</v>
-      </c>
-      <c r="H56" t="s">
-        <v>150</v>
+        <v>121</v>
       </c>
       <c r="I56" t="s">
-        <v>202</v>
-      </c>
-      <c r="J56" t="s">
-        <v>265</v>
+        <v>320</v>
       </c>
     </row>
     <row r="57" spans="1:10">
       <c r="A57" t="s">
         <v>21</v>
       </c>
-      <c r="B57" t="s">
-        <v>41</v>
-      </c>
-      <c r="C57" t="s">
-        <v>45</v>
-      </c>
-      <c r="D57" t="s">
-        <v>48</v>
+      <c r="E57" t="s">
+        <v>91</v>
+      </c>
+      <c r="F57" t="s">
+        <v>128</v>
+      </c>
+      <c r="G57" t="s">
+        <v>191</v>
       </c>
       <c r="I57" t="s">
-        <v>203</v>
+        <v>321</v>
+      </c>
+      <c r="J57" t="s">
+        <v>464</v>
       </c>
     </row>
     <row r="58" spans="1:10">
       <c r="A58" t="s">
-        <v>21</v>
-      </c>
-      <c r="E58" t="s">
-        <v>51</v>
-      </c>
-      <c r="F58" t="s">
-        <v>91</v>
-      </c>
-      <c r="G58" t="s">
-        <v>133</v>
-      </c>
-      <c r="H58" t="s">
-        <v>150</v>
+        <v>22</v>
+      </c>
+      <c r="B58" t="s">
+        <v>57</v>
+      </c>
+      <c r="D58" t="s">
+        <v>72</v>
       </c>
       <c r="I58" t="s">
-        <v>204</v>
+        <v>322</v>
       </c>
     </row>
     <row r="59" spans="1:10">
       <c r="A59" t="s">
-        <v>21</v>
-      </c>
-      <c r="B59" t="s">
-        <v>37</v>
-      </c>
-      <c r="C59" t="s">
-        <v>42</v>
-      </c>
-      <c r="D59" t="s">
-        <v>47</v>
+        <v>22</v>
+      </c>
+      <c r="E59" t="s">
+        <v>85</v>
+      </c>
+      <c r="F59" t="s">
+        <v>129</v>
+      </c>
+      <c r="G59" t="s">
+        <v>205</v>
+      </c>
+      <c r="H59" t="s">
+        <v>265</v>
       </c>
       <c r="I59" t="s">
-        <v>205</v>
+        <v>323</v>
+      </c>
+      <c r="J59" t="s">
+        <v>465</v>
       </c>
     </row>
     <row r="60" spans="1:10">
       <c r="A60" t="s">
-        <v>21</v>
-      </c>
-      <c r="E60" t="s">
-        <v>51</v>
-      </c>
-      <c r="F60" t="s">
-        <v>94</v>
-      </c>
-      <c r="G60" t="s">
-        <v>134</v>
-      </c>
-      <c r="H60" t="s">
-        <v>150</v>
+        <v>22</v>
+      </c>
+      <c r="B60" t="s">
+        <v>62</v>
+      </c>
+      <c r="C60" t="s">
+        <v>66</v>
+      </c>
+      <c r="D60" t="s">
+        <v>72</v>
       </c>
       <c r="I60" t="s">
-        <v>206</v>
-      </c>
-      <c r="J60" t="s">
-        <v>266</v>
+        <v>324</v>
       </c>
     </row>
     <row r="61" spans="1:10">
       <c r="A61" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E61" t="s">
-        <v>51</v>
+        <v>81</v>
       </c>
       <c r="F61" t="s">
-        <v>95</v>
+        <v>127</v>
       </c>
       <c r="G61" t="s">
-        <v>135</v>
+        <v>194</v>
       </c>
       <c r="H61" t="s">
-        <v>150</v>
+        <v>265</v>
       </c>
       <c r="I61" t="s">
-        <v>207</v>
-      </c>
-      <c r="J61" t="s">
-        <v>267</v>
+        <v>325</v>
       </c>
     </row>
     <row r="62" spans="1:10">
       <c r="A62" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B62" t="s">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="C62" t="s">
-        <v>42</v>
+        <v>63</v>
       </c>
       <c r="D62" t="s">
-        <v>47</v>
-      </c>
-      <c r="F62" t="s">
-        <v>96</v>
-      </c>
-      <c r="G62" t="s">
-        <v>136</v>
+        <v>70</v>
       </c>
       <c r="I62" t="s">
-        <v>208</v>
-      </c>
-      <c r="J62" t="s">
-        <v>268</v>
+        <v>326</v>
       </c>
     </row>
     <row r="63" spans="1:10">
       <c r="A63" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E63" t="s">
-        <v>51</v>
+        <v>81</v>
       </c>
       <c r="F63" t="s">
-        <v>94</v>
+        <v>130</v>
       </c>
       <c r="G63" t="s">
-        <v>134</v>
+        <v>206</v>
       </c>
       <c r="H63" t="s">
-        <v>150</v>
+        <v>265</v>
       </c>
       <c r="I63" t="s">
-        <v>206</v>
+        <v>327</v>
       </c>
       <c r="J63" t="s">
-        <v>266</v>
+        <v>466</v>
       </c>
     </row>
     <row r="64" spans="1:10">
       <c r="A64" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E64" t="s">
-        <v>51</v>
+        <v>81</v>
       </c>
       <c r="F64" t="s">
-        <v>95</v>
+        <v>123</v>
       </c>
       <c r="G64" t="s">
-        <v>135</v>
+        <v>200</v>
       </c>
       <c r="H64" t="s">
-        <v>150</v>
+        <v>265</v>
       </c>
       <c r="I64" t="s">
-        <v>207</v>
+        <v>328</v>
       </c>
       <c r="J64" t="s">
-        <v>267</v>
+        <v>458</v>
       </c>
     </row>
     <row r="65" spans="1:10">
       <c r="A65" t="s">
-        <v>24</v>
-      </c>
-      <c r="D65" t="s">
-        <v>51</v>
+        <v>22</v>
+      </c>
+      <c r="E65" t="s">
+        <v>81</v>
       </c>
       <c r="F65" t="s">
-        <v>97</v>
+        <v>117</v>
       </c>
       <c r="G65" t="s">
-        <v>137</v>
+        <v>196</v>
       </c>
       <c r="I65" t="s">
-        <v>209</v>
+        <v>329</v>
       </c>
       <c r="J65" t="s">
-        <v>269</v>
+        <v>454</v>
       </c>
     </row>
     <row r="66" spans="1:10">
       <c r="A66" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B66" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="C66" t="s">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="D66" t="s">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="I66" t="s">
-        <v>210</v>
+        <v>326</v>
       </c>
     </row>
     <row r="67" spans="1:10">
       <c r="A67" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E67" t="s">
-        <v>64</v>
+        <v>81</v>
       </c>
       <c r="F67" t="s">
-        <v>93</v>
+        <v>130</v>
       </c>
       <c r="G67" t="s">
-        <v>132</v>
+        <v>206</v>
+      </c>
+      <c r="H67" t="s">
+        <v>265</v>
       </c>
       <c r="I67" t="s">
-        <v>211</v>
+        <v>327</v>
       </c>
       <c r="J67" t="s">
-        <v>265</v>
+        <v>466</v>
       </c>
     </row>
     <row r="68" spans="1:10">
       <c r="A68" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="E68" t="s">
-        <v>55</v>
+        <v>81</v>
+      </c>
+      <c r="F68" t="s">
+        <v>123</v>
+      </c>
+      <c r="G68" t="s">
+        <v>200</v>
+      </c>
+      <c r="H68" t="s">
+        <v>265</v>
       </c>
       <c r="I68" t="s">
-        <v>212</v>
+        <v>328</v>
+      </c>
+      <c r="J68" t="s">
+        <v>458</v>
       </c>
     </row>
     <row r="69" spans="1:10">
       <c r="A69" t="s">
-        <v>25</v>
-      </c>
-      <c r="B69" t="s">
-        <v>36</v>
-      </c>
-      <c r="C69" t="s">
-        <v>43</v>
-      </c>
-      <c r="D69" t="s">
-        <v>47</v>
+        <v>22</v>
+      </c>
+      <c r="E69" t="s">
+        <v>81</v>
       </c>
       <c r="I69" t="s">
-        <v>213</v>
+        <v>330</v>
       </c>
     </row>
     <row r="70" spans="1:10">
-      <c r="A70" t="s">
-        <v>25</v>
-      </c>
-      <c r="E70" t="s">
-        <v>51</v>
-      </c>
-      <c r="F70" t="s">
-        <v>73</v>
-      </c>
-      <c r="G70" t="s">
-        <v>138</v>
+      <c r="B70" t="s">
+        <v>61</v>
+      </c>
+      <c r="C70" t="s">
+        <v>64</v>
+      </c>
+      <c r="D70" t="s">
+        <v>72</v>
       </c>
       <c r="I70" t="s">
-        <v>214</v>
-      </c>
-      <c r="J70" t="s">
-        <v>244</v>
+        <v>331</v>
       </c>
     </row>
     <row r="71" spans="1:10">
-      <c r="A71" t="s">
-        <v>25</v>
-      </c>
-      <c r="B71" t="s">
-        <v>40</v>
-      </c>
-      <c r="C71" t="s">
-        <v>43</v>
-      </c>
-      <c r="D71" t="s">
-        <v>47</v>
+      <c r="E71" t="s">
+        <v>92</v>
+      </c>
+      <c r="H71" t="s">
+        <v>265</v>
       </c>
       <c r="I71" t="s">
-        <v>215</v>
+        <v>332</v>
       </c>
     </row>
     <row r="72" spans="1:10">
-      <c r="A72" t="s">
-        <v>25</v>
-      </c>
-      <c r="E72" t="s">
-        <v>65</v>
-      </c>
-      <c r="F72" t="s">
-        <v>83</v>
-      </c>
-      <c r="G72" t="s">
-        <v>122</v>
+      <c r="H72" t="s">
+        <v>265</v>
       </c>
       <c r="I72" t="s">
-        <v>216</v>
-      </c>
-      <c r="J72" t="s">
-        <v>255</v>
+        <v>333</v>
       </c>
     </row>
     <row r="73" spans="1:10">
-      <c r="A73" t="s">
-        <v>27</v>
-      </c>
-      <c r="B73" t="s">
-        <v>39</v>
-      </c>
-      <c r="C73" t="s">
-        <v>44</v>
-      </c>
-      <c r="D73" t="s">
-        <v>49</v>
+      <c r="F73" t="s">
+        <v>131</v>
+      </c>
+      <c r="G73" t="s">
+        <v>207</v>
+      </c>
+      <c r="H73" t="s">
+        <v>265</v>
       </c>
       <c r="I73" t="s">
-        <v>217</v>
+        <v>334</v>
+      </c>
+      <c r="J73" t="s">
+        <v>467</v>
       </c>
     </row>
     <row r="74" spans="1:10">
       <c r="A74" t="s">
-        <v>27</v>
-      </c>
-      <c r="E74" t="s">
-        <v>53</v>
-      </c>
-      <c r="F74" t="s">
-        <v>98</v>
-      </c>
-      <c r="G74" t="s">
-        <v>139</v>
+        <v>23</v>
+      </c>
+      <c r="B74" t="s">
+        <v>58</v>
+      </c>
+      <c r="C74" t="s">
+        <v>63</v>
+      </c>
+      <c r="D74" t="s">
+        <v>70</v>
       </c>
       <c r="I74" t="s">
-        <v>218</v>
-      </c>
-      <c r="J74" t="s">
-        <v>270</v>
+        <v>335</v>
       </c>
     </row>
     <row r="75" spans="1:10">
       <c r="A75" t="s">
-        <v>28</v>
-      </c>
-      <c r="B75" t="s">
-        <v>39</v>
-      </c>
-      <c r="C75" t="s">
-        <v>44</v>
-      </c>
-      <c r="D75" t="s">
-        <v>52</v>
+        <v>23</v>
+      </c>
+      <c r="E75" t="s">
+        <v>84</v>
+      </c>
+      <c r="F75" t="s">
+        <v>132</v>
+      </c>
+      <c r="G75" t="s">
+        <v>208</v>
       </c>
       <c r="I75" t="s">
-        <v>219</v>
+        <v>336</v>
+      </c>
+      <c r="J75" t="s">
+        <v>468</v>
       </c>
     </row>
     <row r="76" spans="1:10">
       <c r="A76" t="s">
-        <v>28</v>
-      </c>
-      <c r="B76" t="s">
-        <v>38</v>
-      </c>
-      <c r="C76" t="s">
-        <v>42</v>
-      </c>
-      <c r="D76" t="s">
-        <v>47</v>
+        <v>23</v>
+      </c>
+      <c r="E76" t="s">
+        <v>84</v>
       </c>
       <c r="F76" t="s">
-        <v>99</v>
+        <v>133</v>
       </c>
       <c r="G76" t="s">
-        <v>140</v>
-      </c>
-      <c r="H76" t="s">
-        <v>150</v>
+        <v>209</v>
       </c>
       <c r="I76" t="s">
-        <v>220</v>
+        <v>337</v>
       </c>
       <c r="J76" t="s">
-        <v>271</v>
+        <v>469</v>
       </c>
     </row>
     <row r="77" spans="1:10">
       <c r="A77" t="s">
-        <v>28</v>
-      </c>
-      <c r="E77" t="s">
-        <v>56</v>
-      </c>
-      <c r="F77" t="s">
-        <v>100</v>
-      </c>
-      <c r="G77" t="s">
-        <v>141</v>
-      </c>
-      <c r="H77" t="s">
-        <v>150</v>
+        <v>23</v>
+      </c>
+      <c r="B77" t="s">
+        <v>58</v>
+      </c>
+      <c r="C77" t="s">
+        <v>63</v>
+      </c>
+      <c r="D77" t="s">
+        <v>70</v>
       </c>
       <c r="I77" t="s">
-        <v>221</v>
-      </c>
-      <c r="J77" t="s">
-        <v>272</v>
+        <v>335</v>
       </c>
     </row>
     <row r="78" spans="1:10">
       <c r="A78" t="s">
-        <v>28</v>
-      </c>
-      <c r="B78" t="s">
-        <v>38</v>
-      </c>
-      <c r="C78" t="s">
-        <v>42</v>
-      </c>
-      <c r="D78" t="s">
-        <v>47</v>
+        <v>24</v>
+      </c>
+      <c r="E78" t="s">
+        <v>84</v>
+      </c>
+      <c r="F78" t="s">
+        <v>134</v>
+      </c>
+      <c r="G78" t="s">
+        <v>210</v>
       </c>
       <c r="I78" t="s">
-        <v>222</v>
+        <v>338</v>
+      </c>
+      <c r="J78" t="s">
+        <v>470</v>
       </c>
     </row>
     <row r="79" spans="1:10">
-      <c r="E79" t="s">
-        <v>55</v>
-      </c>
-      <c r="F79" t="s">
-        <v>101</v>
-      </c>
-      <c r="G79" t="s">
-        <v>142</v>
-      </c>
-      <c r="H79" t="s">
-        <v>150</v>
+      <c r="A79" t="s">
+        <v>25</v>
       </c>
       <c r="I79" t="s">
-        <v>223</v>
-      </c>
-      <c r="J79" t="s">
-        <v>273</v>
+        <v>339</v>
       </c>
     </row>
     <row r="80" spans="1:10">
       <c r="E80" t="s">
-        <v>55</v>
+        <v>84</v>
       </c>
       <c r="F80" t="s">
-        <v>102</v>
+        <v>135</v>
       </c>
       <c r="G80" t="s">
-        <v>143</v>
+        <v>211</v>
       </c>
       <c r="H80" t="s">
-        <v>150</v>
+        <v>270</v>
       </c>
       <c r="I80" t="s">
-        <v>224</v>
+        <v>340</v>
       </c>
       <c r="J80" t="s">
-        <v>274</v>
+        <v>471</v>
       </c>
     </row>
     <row r="81" spans="1:10">
       <c r="A81" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="B81" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="C81" t="s">
-        <v>42</v>
+        <v>63</v>
       </c>
       <c r="D81" t="s">
-        <v>47</v>
-      </c>
-      <c r="G81" t="s">
-        <v>142</v>
+        <v>72</v>
       </c>
       <c r="I81" t="s">
-        <v>225</v>
+        <v>341</v>
       </c>
     </row>
     <row r="82" spans="1:10">
       <c r="A82" t="s">
-        <v>29</v>
-      </c>
-      <c r="B82" t="s">
-        <v>35</v>
-      </c>
-      <c r="C82" t="s">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="E82" t="s">
-        <v>66</v>
+        <v>85</v>
       </c>
       <c r="F82" t="s">
-        <v>103</v>
+        <v>136</v>
       </c>
       <c r="G82" t="s">
-        <v>144</v>
+        <v>212</v>
       </c>
       <c r="H82" t="s">
-        <v>150</v>
+        <v>265</v>
       </c>
       <c r="I82" t="s">
-        <v>226</v>
+        <v>342</v>
       </c>
       <c r="J82" t="s">
-        <v>275</v>
+        <v>472</v>
       </c>
     </row>
     <row r="83" spans="1:10">
       <c r="A83" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="B83" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="C83" t="s">
-        <v>44</v>
-      </c>
-      <c r="E83" t="s">
-        <v>50</v>
-      </c>
-      <c r="F83" t="s">
-        <v>72</v>
-      </c>
-      <c r="G83" t="s">
-        <v>111</v>
-      </c>
-      <c r="H83" t="s">
-        <v>150</v>
+        <v>64</v>
+      </c>
+      <c r="D83" t="s">
+        <v>71</v>
       </c>
       <c r="I83" t="s">
-        <v>227</v>
-      </c>
-      <c r="J83" t="s">
-        <v>243</v>
+        <v>343</v>
       </c>
     </row>
     <row r="84" spans="1:10">
       <c r="A84" t="s">
-        <v>31</v>
+        <v>23</v>
+      </c>
+      <c r="E84" t="s">
+        <v>93</v>
+      </c>
+      <c r="F84" t="s">
+        <v>137</v>
+      </c>
+      <c r="G84" t="s">
+        <v>213</v>
       </c>
       <c r="I84" t="s">
-        <v>228</v>
+        <v>344</v>
+      </c>
+      <c r="J84" t="s">
+        <v>473</v>
       </c>
     </row>
     <row r="85" spans="1:10">
       <c r="A85" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="B85" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="C85" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="D85" t="s">
-        <v>48</v>
-      </c>
-      <c r="E85" t="s">
-        <v>50</v>
-      </c>
-      <c r="F85" t="s">
-        <v>104</v>
-      </c>
-      <c r="G85" t="s">
-        <v>131</v>
-      </c>
-      <c r="H85" t="s">
-        <v>155</v>
+        <v>70</v>
       </c>
       <c r="I85" t="s">
-        <v>229</v>
-      </c>
-      <c r="J85" t="s">
-        <v>276</v>
+        <v>335</v>
       </c>
     </row>
     <row r="86" spans="1:10">
       <c r="A86" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="I86" t="s">
-        <v>230</v>
+        <v>339</v>
       </c>
     </row>
     <row r="87" spans="1:10">
       <c r="E87" t="s">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="F87" t="s">
-        <v>105</v>
+        <v>138</v>
       </c>
       <c r="G87" t="s">
-        <v>145</v>
+        <v>214</v>
       </c>
       <c r="H87" t="s">
-        <v>154</v>
+        <v>270</v>
       </c>
       <c r="I87" t="s">
-        <v>231</v>
+        <v>345</v>
       </c>
       <c r="J87" t="s">
-        <v>277</v>
+        <v>474</v>
       </c>
     </row>
     <row r="88" spans="1:10">
       <c r="A88" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="B88" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="C88" t="s">
-        <v>42</v>
+        <v>63</v>
       </c>
       <c r="D88" t="s">
-        <v>47</v>
+        <v>72</v>
       </c>
       <c r="I88" t="s">
-        <v>232</v>
+        <v>341</v>
       </c>
     </row>
     <row r="89" spans="1:10">
       <c r="A89" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="E89" t="s">
-        <v>51</v>
+        <v>85</v>
       </c>
       <c r="F89" t="s">
-        <v>106</v>
+        <v>139</v>
       </c>
       <c r="G89" t="s">
-        <v>146</v>
+        <v>215</v>
+      </c>
+      <c r="H89" t="s">
+        <v>265</v>
       </c>
       <c r="I89" t="s">
-        <v>233</v>
+        <v>346</v>
       </c>
       <c r="J89" t="s">
-        <v>278</v>
+        <v>475</v>
       </c>
     </row>
     <row r="90" spans="1:10">
       <c r="A90" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="B90" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="C90" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="D90" t="s">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="I90" t="s">
-        <v>234</v>
+        <v>335</v>
       </c>
     </row>
     <row r="91" spans="1:10">
-      <c r="B91" t="s">
-        <v>35</v>
-      </c>
-      <c r="C91" t="s">
-        <v>42</v>
-      </c>
-      <c r="D91" t="s">
-        <v>53</v>
+      <c r="A91" t="s">
+        <v>23</v>
       </c>
       <c r="E91" t="s">
-        <v>66</v>
-      </c>
-      <c r="H91" t="s">
-        <v>150</v>
+        <v>84</v>
+      </c>
+      <c r="F91" t="s">
+        <v>140</v>
+      </c>
+      <c r="G91" t="s">
+        <v>216</v>
       </c>
       <c r="I91" t="s">
-        <v>235</v>
+        <v>347</v>
+      </c>
+      <c r="J91" t="s">
+        <v>476</v>
       </c>
     </row>
     <row r="92" spans="1:10">
       <c r="A92" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="B92" t="s">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="C92" t="s">
-        <v>42</v>
+        <v>63</v>
       </c>
       <c r="D92" t="s">
-        <v>47</v>
-      </c>
-      <c r="E92" t="s">
-        <v>68</v>
-      </c>
-      <c r="F92" t="s">
-        <v>96</v>
-      </c>
-      <c r="G92" t="s">
-        <v>136</v>
-      </c>
-      <c r="H92" t="s">
-        <v>150</v>
+        <v>72</v>
       </c>
       <c r="I92" t="s">
-        <v>236</v>
-      </c>
-      <c r="J92" t="s">
-        <v>268</v>
+        <v>341</v>
       </c>
     </row>
     <row r="93" spans="1:10">
       <c r="A93" t="s">
-        <v>33</v>
-      </c>
-      <c r="B93" t="s">
-        <v>37</v>
-      </c>
-      <c r="C93" t="s">
-        <v>42</v>
-      </c>
-      <c r="D93" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="E93" t="s">
-        <v>69</v>
+        <v>85</v>
       </c>
       <c r="F93" t="s">
-        <v>107</v>
+        <v>141</v>
       </c>
       <c r="G93" t="s">
-        <v>147</v>
+        <v>194</v>
       </c>
       <c r="H93" t="s">
-        <v>150</v>
+        <v>265</v>
       </c>
       <c r="I93" t="s">
-        <v>237</v>
-      </c>
-      <c r="J93" t="s">
-        <v>279</v>
+        <v>348</v>
       </c>
     </row>
     <row r="94" spans="1:10">
       <c r="A94" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="B94" t="s">
-        <v>35</v>
+        <v>57</v>
       </c>
       <c r="C94" t="s">
-        <v>42</v>
+        <v>63</v>
       </c>
       <c r="D94" t="s">
-        <v>47</v>
-      </c>
-      <c r="E94" t="s">
-        <v>70</v>
-      </c>
-      <c r="F94" t="s">
-        <v>83</v>
-      </c>
-      <c r="G94" t="s">
-        <v>122</v>
-      </c>
-      <c r="H94" t="s">
-        <v>150</v>
+        <v>72</v>
       </c>
       <c r="I94" t="s">
-        <v>238</v>
-      </c>
-      <c r="J94" t="s">
-        <v>255</v>
+        <v>341</v>
       </c>
     </row>
     <row r="95" spans="1:10">
       <c r="A95" t="s">
-        <v>33</v>
-      </c>
-      <c r="B95" t="s">
-        <v>35</v>
-      </c>
-      <c r="C95" t="s">
-        <v>42</v>
-      </c>
-      <c r="D95" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="E95" t="s">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="F95" t="s">
-        <v>108</v>
+        <v>142</v>
       </c>
       <c r="G95" t="s">
-        <v>148</v>
+        <v>217</v>
       </c>
       <c r="H95" t="s">
-        <v>150</v>
+        <v>265</v>
       </c>
       <c r="I95" t="s">
-        <v>239</v>
+        <v>349</v>
       </c>
       <c r="J95" t="s">
-        <v>280</v>
+        <v>477</v>
       </c>
     </row>
     <row r="96" spans="1:10">
       <c r="A96" t="s">
-        <v>33</v>
-      </c>
-      <c r="B96" t="s">
-        <v>37</v>
-      </c>
-      <c r="C96" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="D96" t="s">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="E96" t="s">
-        <v>69</v>
+        <v>86</v>
       </c>
       <c r="F96" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="G96" t="s">
-        <v>129</v>
-      </c>
-      <c r="H96" t="s">
-        <v>150</v>
+        <v>196</v>
       </c>
       <c r="I96" t="s">
-        <v>240</v>
+        <v>350</v>
       </c>
       <c r="J96" t="s">
-        <v>262</v>
+        <v>454</v>
       </c>
     </row>
     <row r="97" spans="1:10">
-      <c r="B97" t="s">
-        <v>38</v>
-      </c>
-      <c r="C97" t="s">
-        <v>42</v>
-      </c>
-      <c r="D97" t="s">
-        <v>47</v>
-      </c>
-      <c r="F97" t="s">
-        <v>72</v>
-      </c>
-      <c r="G97" t="s">
-        <v>111</v>
-      </c>
       <c r="H97" t="s">
-        <v>150</v>
+        <v>268</v>
       </c>
       <c r="I97" t="s">
-        <v>241</v>
-      </c>
-      <c r="J97" t="s">
-        <v>243</v>
+        <v>351</v>
       </c>
     </row>
     <row r="98" spans="1:10">
       <c r="A98" t="s">
+        <v>23</v>
+      </c>
+      <c r="D98" t="s">
+        <v>72</v>
+      </c>
+      <c r="E98" t="s">
+        <v>94</v>
+      </c>
+      <c r="F98" t="s">
+        <v>136</v>
+      </c>
+      <c r="G98" t="s">
+        <v>194</v>
+      </c>
+      <c r="I98" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="99" spans="1:10">
+      <c r="H99" t="s">
+        <v>268</v>
+      </c>
+      <c r="I99" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="100" spans="1:10">
+      <c r="A100" t="s">
+        <v>23</v>
+      </c>
+      <c r="D100" t="s">
+        <v>70</v>
+      </c>
+      <c r="E100" t="s">
+        <v>95</v>
+      </c>
+      <c r="F100" t="s">
+        <v>133</v>
+      </c>
+      <c r="G100" t="s">
+        <v>209</v>
+      </c>
+      <c r="I100" t="s">
+        <v>353</v>
+      </c>
+      <c r="J100" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="101" spans="1:10">
+      <c r="A101" t="s">
+        <v>26</v>
+      </c>
+      <c r="I101" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="102" spans="1:10">
+      <c r="A102" t="s">
+        <v>23</v>
+      </c>
+      <c r="D102" t="s">
+        <v>76</v>
+      </c>
+      <c r="E102" t="s">
+        <v>94</v>
+      </c>
+      <c r="F102" t="s">
+        <v>141</v>
+      </c>
+      <c r="G102" t="s">
+        <v>218</v>
+      </c>
+      <c r="I102" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="103" spans="1:10">
+      <c r="A103" t="s">
+        <v>27</v>
+      </c>
+      <c r="B103" t="s">
+        <v>59</v>
+      </c>
+      <c r="C103" t="s">
+        <v>67</v>
+      </c>
+      <c r="D103" t="s">
+        <v>70</v>
+      </c>
+      <c r="I103" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="104" spans="1:10">
+      <c r="A104" t="s">
+        <v>27</v>
+      </c>
+      <c r="E104" t="s">
+        <v>96</v>
+      </c>
+      <c r="F104" t="s">
+        <v>143</v>
+      </c>
+      <c r="G104" t="s">
+        <v>219</v>
+      </c>
+      <c r="I104" t="s">
+        <v>357</v>
+      </c>
+      <c r="J104" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="105" spans="1:10">
+      <c r="A105" t="s">
+        <v>27</v>
+      </c>
+      <c r="H105" t="s">
+        <v>265</v>
+      </c>
+      <c r="I105" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="106" spans="1:10">
+      <c r="A106" t="s">
+        <v>27</v>
+      </c>
+      <c r="B106" t="s">
+        <v>59</v>
+      </c>
+      <c r="C106" t="s">
+        <v>64</v>
+      </c>
+      <c r="D106" t="s">
+        <v>71</v>
+      </c>
+      <c r="I106" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="107" spans="1:10">
+      <c r="A107" t="s">
+        <v>27</v>
+      </c>
+      <c r="E107" t="s">
+        <v>80</v>
+      </c>
+      <c r="F107" t="s">
+        <v>144</v>
+      </c>
+      <c r="G107" t="s">
+        <v>220</v>
+      </c>
+      <c r="H107" t="s">
+        <v>265</v>
+      </c>
+      <c r="I107" t="s">
+        <v>360</v>
+      </c>
+      <c r="J107" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="108" spans="1:10">
+      <c r="A108" t="s">
+        <v>23</v>
+      </c>
+      <c r="B108" t="s">
+        <v>57</v>
+      </c>
+      <c r="C108" t="s">
+        <v>63</v>
+      </c>
+      <c r="D108" t="s">
+        <v>72</v>
+      </c>
+      <c r="I108" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="109" spans="1:10">
+      <c r="A109" t="s">
+        <v>23</v>
+      </c>
+      <c r="E109" t="s">
+        <v>85</v>
+      </c>
+      <c r="F109" t="s">
+        <v>141</v>
+      </c>
+      <c r="G109" t="s">
+        <v>194</v>
+      </c>
+      <c r="H109" t="s">
+        <v>265</v>
+      </c>
+      <c r="I109" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="110" spans="1:10">
+      <c r="A110" t="s">
+        <v>23</v>
+      </c>
+      <c r="B110" t="s">
+        <v>57</v>
+      </c>
+      <c r="C110" t="s">
+        <v>63</v>
+      </c>
+      <c r="D110" t="s">
+        <v>72</v>
+      </c>
+      <c r="I110" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="111" spans="1:10">
+      <c r="A111" t="s">
+        <v>23</v>
+      </c>
+      <c r="E111" t="s">
+        <v>85</v>
+      </c>
+      <c r="F111" t="s">
+        <v>142</v>
+      </c>
+      <c r="G111" t="s">
+        <v>217</v>
+      </c>
+      <c r="H111" t="s">
+        <v>265</v>
+      </c>
+      <c r="I111" t="s">
+        <v>349</v>
+      </c>
+      <c r="J111" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="112" spans="1:10">
+      <c r="A112" t="s">
+        <v>28</v>
+      </c>
+      <c r="B112" t="s">
+        <v>61</v>
+      </c>
+      <c r="C112" t="s">
+        <v>64</v>
+      </c>
+      <c r="E112" t="s">
+        <v>73</v>
+      </c>
+      <c r="I112" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="113" spans="1:10">
+      <c r="A113" t="s">
+        <v>29</v>
+      </c>
+      <c r="E113" t="s">
+        <v>91</v>
+      </c>
+      <c r="F113" t="s">
+        <v>145</v>
+      </c>
+      <c r="G113" t="s">
+        <v>221</v>
+      </c>
+      <c r="I113" t="s">
+        <v>362</v>
+      </c>
+      <c r="J113" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="114" spans="1:10">
+      <c r="A114" t="s">
+        <v>30</v>
+      </c>
+      <c r="B114" t="s">
+        <v>59</v>
+      </c>
+      <c r="C114" t="s">
+        <v>63</v>
+      </c>
+      <c r="D114" t="s">
+        <v>70</v>
+      </c>
+      <c r="E114" t="s">
+        <v>84</v>
+      </c>
+      <c r="I114" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="115" spans="1:10">
+      <c r="A115" t="s">
+        <v>30</v>
+      </c>
+      <c r="F115" t="s">
+        <v>113</v>
+      </c>
+      <c r="G115" t="s">
+        <v>192</v>
+      </c>
+      <c r="I115" t="s">
+        <v>364</v>
+      </c>
+      <c r="J115" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="116" spans="1:10">
+      <c r="A116" t="s">
+        <v>30</v>
+      </c>
+      <c r="B116" t="s">
+        <v>59</v>
+      </c>
+      <c r="C116" t="s">
+        <v>63</v>
+      </c>
+      <c r="D116" t="s">
+        <v>70</v>
+      </c>
+      <c r="E116" t="s">
+        <v>85</v>
+      </c>
+      <c r="I116" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="117" spans="1:10">
+      <c r="A117" t="s">
+        <v>30</v>
+      </c>
+      <c r="F117" t="s">
+        <v>146</v>
+      </c>
+      <c r="G117" t="s">
+        <v>222</v>
+      </c>
+      <c r="H117" t="s">
+        <v>265</v>
+      </c>
+      <c r="I117" t="s">
+        <v>366</v>
+      </c>
+      <c r="J117" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="118" spans="1:10">
+      <c r="A118" t="s">
+        <v>31</v>
+      </c>
+      <c r="B118" t="s">
+        <v>56</v>
+      </c>
+      <c r="C118" t="s">
+        <v>64</v>
+      </c>
+      <c r="D118" t="s">
+        <v>72</v>
+      </c>
+      <c r="E118" t="s">
+        <v>73</v>
+      </c>
+      <c r="F118" t="s">
+        <v>147</v>
+      </c>
+      <c r="G118" t="s">
+        <v>223</v>
+      </c>
+      <c r="I118" t="s">
+        <v>367</v>
+      </c>
+      <c r="J118" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="119" spans="1:10">
+      <c r="A119" t="s">
+        <v>32</v>
+      </c>
+      <c r="E119" t="s">
+        <v>91</v>
+      </c>
+      <c r="F119" t="s">
+        <v>148</v>
+      </c>
+      <c r="G119" t="s">
+        <v>224</v>
+      </c>
+      <c r="I119" t="s">
+        <v>368</v>
+      </c>
+      <c r="J119" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="120" spans="1:10">
+      <c r="B120" t="s">
+        <v>59</v>
+      </c>
+      <c r="C120" t="s">
+        <v>63</v>
+      </c>
+      <c r="D120" t="s">
+        <v>70</v>
+      </c>
+      <c r="I120" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="121" spans="1:10">
+      <c r="A121" t="s">
+        <v>33</v>
+      </c>
+      <c r="B121" t="s">
+        <v>59</v>
+      </c>
+      <c r="C121" t="s">
+        <v>63</v>
+      </c>
+      <c r="D121" t="s">
+        <v>70</v>
+      </c>
+      <c r="E121" t="s">
+        <v>95</v>
+      </c>
+      <c r="F121" t="s">
+        <v>147</v>
+      </c>
+      <c r="G121" t="s">
+        <v>223</v>
+      </c>
+      <c r="H121" t="s">
+        <v>265</v>
+      </c>
+      <c r="I121" t="s">
+        <v>370</v>
+      </c>
+      <c r="J121" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="122" spans="1:10">
+      <c r="E122" t="s">
+        <v>95</v>
+      </c>
+      <c r="F122" t="s">
+        <v>113</v>
+      </c>
+      <c r="G122" t="s">
+        <v>192</v>
+      </c>
+      <c r="H122" t="s">
+        <v>265</v>
+      </c>
+      <c r="I122" t="s">
+        <v>371</v>
+      </c>
+      <c r="J122" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="123" spans="1:10">
+      <c r="A123" t="s">
+        <v>33</v>
+      </c>
+      <c r="B123" t="s">
+        <v>59</v>
+      </c>
+      <c r="C123" t="s">
+        <v>63</v>
+      </c>
+      <c r="D123" t="s">
+        <v>70</v>
+      </c>
+      <c r="E123" t="s">
+        <v>97</v>
+      </c>
+      <c r="F123" t="s">
+        <v>114</v>
+      </c>
+      <c r="G123" t="s">
+        <v>225</v>
+      </c>
+      <c r="H123" t="s">
+        <v>271</v>
+      </c>
+      <c r="I123" t="s">
+        <v>372</v>
+      </c>
+      <c r="J123" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="124" spans="1:10">
+      <c r="A124" t="s">
+        <v>33</v>
+      </c>
+      <c r="B124" t="s">
+        <v>59</v>
+      </c>
+      <c r="C124" t="s">
+        <v>63</v>
+      </c>
+      <c r="D124" t="s">
+        <v>70</v>
+      </c>
+      <c r="E124" t="s">
+        <v>94</v>
+      </c>
+      <c r="F124" t="s">
+        <v>120</v>
+      </c>
+      <c r="G124" t="s">
+        <v>226</v>
+      </c>
+      <c r="H124" t="s">
+        <v>265</v>
+      </c>
+      <c r="I124" t="s">
+        <v>373</v>
+      </c>
+      <c r="J124" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="125" spans="1:10">
+      <c r="E125" t="s">
+        <v>94</v>
+      </c>
+      <c r="F125" t="s">
+        <v>149</v>
+      </c>
+      <c r="G125" t="s">
+        <v>227</v>
+      </c>
+      <c r="H125" t="s">
+        <v>265</v>
+      </c>
+      <c r="I125" t="s">
+        <v>374</v>
+      </c>
+      <c r="J125" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="126" spans="1:10">
+      <c r="A126" t="s">
+        <v>33</v>
+      </c>
+      <c r="E126" t="s">
+        <v>97</v>
+      </c>
+      <c r="F126" t="s">
+        <v>150</v>
+      </c>
+      <c r="G126" t="s">
+        <v>228</v>
+      </c>
+      <c r="H126" t="s">
+        <v>271</v>
+      </c>
+      <c r="I126" t="s">
+        <v>375</v>
+      </c>
+      <c r="J126" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="127" spans="1:10">
+      <c r="A127" t="s">
         <v>34</v>
       </c>
-      <c r="E98" t="s">
+      <c r="B127" t="s">
+        <v>59</v>
+      </c>
+      <c r="C127" t="s">
+        <v>63</v>
+      </c>
+      <c r="E127" t="s">
+        <v>98</v>
+      </c>
+      <c r="F127" t="s">
+        <v>151</v>
+      </c>
+      <c r="G127" t="s">
+        <v>229</v>
+      </c>
+      <c r="H127" t="s">
+        <v>271</v>
+      </c>
+      <c r="I127" t="s">
+        <v>376</v>
+      </c>
+      <c r="J127" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="128" spans="1:10">
+      <c r="A128" t="s">
+        <v>34</v>
+      </c>
+      <c r="B128" t="s">
+        <v>57</v>
+      </c>
+      <c r="C128" t="s">
+        <v>63</v>
+      </c>
+      <c r="D128" t="s">
+        <v>70</v>
+      </c>
+      <c r="E128" t="s">
+        <v>86</v>
+      </c>
+      <c r="F128" t="s">
+        <v>152</v>
+      </c>
+      <c r="G128" t="s">
+        <v>230</v>
+      </c>
+      <c r="H128" t="s">
+        <v>265</v>
+      </c>
+      <c r="I128" t="s">
+        <v>377</v>
+      </c>
+      <c r="J128" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="129" spans="1:10">
+      <c r="A129" t="s">
+        <v>34</v>
+      </c>
+      <c r="B129" t="s">
+        <v>59</v>
+      </c>
+      <c r="C129" t="s">
+        <v>63</v>
+      </c>
+      <c r="E129" t="s">
+        <v>98</v>
+      </c>
+      <c r="F129" t="s">
+        <v>153</v>
+      </c>
+      <c r="G129" t="s">
+        <v>231</v>
+      </c>
+      <c r="I129" t="s">
+        <v>378</v>
+      </c>
+      <c r="J129" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="130" spans="1:10">
+      <c r="A130" t="s">
+        <v>33</v>
+      </c>
+      <c r="B130" t="s">
+        <v>59</v>
+      </c>
+      <c r="C130" t="s">
+        <v>63</v>
+      </c>
+      <c r="D130" t="s">
+        <v>70</v>
+      </c>
+      <c r="E130" t="s">
+        <v>94</v>
+      </c>
+      <c r="F130" t="s">
+        <v>124</v>
+      </c>
+      <c r="G130" t="s">
+        <v>228</v>
+      </c>
+      <c r="H130" t="s">
+        <v>265</v>
+      </c>
+      <c r="I130" t="s">
+        <v>379</v>
+      </c>
+      <c r="J130" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="131" spans="1:10">
+      <c r="A131" t="s">
+        <v>35</v>
+      </c>
+      <c r="B131" t="s">
         <v>56</v>
       </c>
-      <c r="F98" t="s">
-        <v>110</v>
-      </c>
-      <c r="G98" t="s">
-        <v>149</v>
-      </c>
-      <c r="I98" t="s">
+      <c r="C131" t="s">
+        <v>67</v>
+      </c>
+      <c r="D131" t="s">
+        <v>77</v>
+      </c>
+      <c r="F131" t="s">
+        <v>154</v>
+      </c>
+      <c r="G131" t="s">
+        <v>232</v>
+      </c>
+      <c r="H131" t="s">
+        <v>271</v>
+      </c>
+      <c r="I131" t="s">
+        <v>380</v>
+      </c>
+      <c r="J131" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="132" spans="1:10">
+      <c r="A132" t="s">
+        <v>36</v>
+      </c>
+      <c r="B132" t="s">
+        <v>56</v>
+      </c>
+      <c r="C132" t="s">
+        <v>64</v>
+      </c>
+      <c r="D132" t="s">
+        <v>72</v>
+      </c>
+      <c r="E132" t="s">
+        <v>73</v>
+      </c>
+      <c r="F132" t="s">
+        <v>155</v>
+      </c>
+      <c r="G132" t="s">
+        <v>233</v>
+      </c>
+      <c r="I132" t="s">
+        <v>381</v>
+      </c>
+      <c r="J132" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="133" spans="1:10">
+      <c r="A133" t="s">
+        <v>33</v>
+      </c>
+      <c r="B133" t="s">
+        <v>59</v>
+      </c>
+      <c r="C133" t="s">
+        <v>63</v>
+      </c>
+      <c r="D133" t="s">
+        <v>70</v>
+      </c>
+      <c r="E133" t="s">
+        <v>94</v>
+      </c>
+      <c r="F133" t="s">
+        <v>156</v>
+      </c>
+      <c r="G133" t="s">
+        <v>234</v>
+      </c>
+      <c r="I133" t="s">
+        <v>382</v>
+      </c>
+      <c r="J133" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="134" spans="1:10">
+      <c r="A134" t="s">
+        <v>34</v>
+      </c>
+      <c r="B134" t="s">
+        <v>59</v>
+      </c>
+      <c r="C134" t="s">
+        <v>63</v>
+      </c>
+      <c r="E134" t="s">
+        <v>98</v>
+      </c>
+      <c r="F134" t="s">
+        <v>157</v>
+      </c>
+      <c r="G134" t="s">
+        <v>235</v>
+      </c>
+      <c r="H134" t="s">
+        <v>271</v>
+      </c>
+      <c r="I134" t="s">
+        <v>383</v>
+      </c>
+      <c r="J134" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="135" spans="1:10">
+      <c r="A135" t="s">
+        <v>34</v>
+      </c>
+      <c r="B135" t="s">
+        <v>59</v>
+      </c>
+      <c r="C135" t="s">
+        <v>63</v>
+      </c>
+      <c r="D135" t="s">
+        <v>70</v>
+      </c>
+      <c r="E135" t="s">
+        <v>86</v>
+      </c>
+      <c r="F135" t="s">
+        <v>130</v>
+      </c>
+      <c r="G135" t="s">
+        <v>236</v>
+      </c>
+      <c r="H135" t="s">
+        <v>265</v>
+      </c>
+      <c r="I135" t="s">
+        <v>384</v>
+      </c>
+      <c r="J135" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="136" spans="1:10">
+      <c r="E136" t="s">
+        <v>86</v>
+      </c>
+      <c r="F136" t="s">
+        <v>158</v>
+      </c>
+      <c r="G136" t="s">
+        <v>237</v>
+      </c>
+      <c r="H136" t="s">
+        <v>271</v>
+      </c>
+      <c r="I136" t="s">
+        <v>385</v>
+      </c>
+      <c r="J136" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="137" spans="1:10">
+      <c r="A137" t="s">
+        <v>34</v>
+      </c>
+      <c r="B137" t="s">
+        <v>57</v>
+      </c>
+      <c r="C137" t="s">
+        <v>63</v>
+      </c>
+      <c r="D137" t="s">
+        <v>70</v>
+      </c>
+      <c r="E137" t="s">
+        <v>86</v>
+      </c>
+      <c r="F137" t="s">
+        <v>159</v>
+      </c>
+      <c r="G137" t="s">
+        <v>238</v>
+      </c>
+      <c r="H137" t="s">
+        <v>271</v>
+      </c>
+      <c r="I137" t="s">
+        <v>386</v>
+      </c>
+      <c r="J137" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="138" spans="1:10">
+      <c r="A138" t="s">
+        <v>33</v>
+      </c>
+      <c r="B138" t="s">
+        <v>59</v>
+      </c>
+      <c r="C138" t="s">
+        <v>63</v>
+      </c>
+      <c r="D138" t="s">
+        <v>70</v>
+      </c>
+      <c r="E138" t="s">
+        <v>95</v>
+      </c>
+      <c r="F138" t="s">
+        <v>160</v>
+      </c>
+      <c r="G138" t="s">
+        <v>200</v>
+      </c>
+      <c r="I138" t="s">
+        <v>387</v>
+      </c>
+      <c r="J138" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="139" spans="1:10">
+      <c r="F139" t="s">
+        <v>161</v>
+      </c>
+      <c r="G139" t="s">
+        <v>239</v>
+      </c>
+      <c r="H139" t="s">
+        <v>265</v>
+      </c>
+      <c r="I139" t="s">
+        <v>388</v>
+      </c>
+      <c r="J139" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="140" spans="1:10">
+      <c r="A140" t="s">
+        <v>37</v>
+      </c>
+      <c r="B140" t="s">
+        <v>61</v>
+      </c>
+      <c r="C140" t="s">
+        <v>64</v>
+      </c>
+      <c r="D140" t="s">
+        <v>71</v>
+      </c>
+      <c r="I140" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="141" spans="1:10">
+      <c r="A141" t="s">
+        <v>37</v>
+      </c>
+      <c r="E141" t="s">
+        <v>99</v>
+      </c>
+      <c r="F141" t="s">
+        <v>162</v>
+      </c>
+      <c r="G141" t="s">
+        <v>240</v>
+      </c>
+      <c r="I141" t="s">
+        <v>390</v>
+      </c>
+      <c r="J141" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="142" spans="1:10">
+      <c r="A142" t="s">
+        <v>37</v>
+      </c>
+      <c r="B142" t="s">
+        <v>61</v>
+      </c>
+      <c r="C142" t="s">
+        <v>64</v>
+      </c>
+      <c r="D142" t="s">
+        <v>71</v>
+      </c>
+      <c r="I142" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="143" spans="1:10">
+      <c r="A143" t="s">
+        <v>38</v>
+      </c>
+      <c r="B143" t="s">
+        <v>58</v>
+      </c>
+      <c r="C143" t="s">
+        <v>67</v>
+      </c>
+      <c r="D143" t="s">
+        <v>70</v>
+      </c>
+      <c r="E143" t="s">
+        <v>100</v>
+      </c>
+      <c r="F143" t="s">
+        <v>163</v>
+      </c>
+      <c r="G143" t="s">
+        <v>241</v>
+      </c>
+      <c r="I143" t="s">
+        <v>392</v>
+      </c>
+      <c r="J143" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="144" spans="1:10">
+      <c r="F144" t="s">
+        <v>164</v>
+      </c>
+      <c r="G144" t="s">
         <v>242</v>
       </c>
-      <c r="J98" t="s">
-        <v>281</v>
+      <c r="H144" t="s">
+        <v>265</v>
+      </c>
+      <c r="I144" t="s">
+        <v>393</v>
+      </c>
+      <c r="J144" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="145" spans="1:10">
+      <c r="A145" t="s">
+        <v>37</v>
+      </c>
+      <c r="B145" t="s">
+        <v>61</v>
+      </c>
+      <c r="C145" t="s">
+        <v>64</v>
+      </c>
+      <c r="D145" t="s">
+        <v>71</v>
+      </c>
+      <c r="I145" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="146" spans="1:10">
+      <c r="A146" t="s">
+        <v>39</v>
+      </c>
+      <c r="E146" t="s">
+        <v>80</v>
+      </c>
+      <c r="F146" t="s">
+        <v>165</v>
+      </c>
+      <c r="G146" t="s">
+        <v>243</v>
+      </c>
+      <c r="I146" t="s">
+        <v>395</v>
+      </c>
+      <c r="J146" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="147" spans="1:10">
+      <c r="A147" t="s">
+        <v>40</v>
+      </c>
+      <c r="B147" t="s">
+        <v>58</v>
+      </c>
+      <c r="C147" t="s">
+        <v>63</v>
+      </c>
+      <c r="D147" t="s">
+        <v>70</v>
+      </c>
+      <c r="I147" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="148" spans="1:10">
+      <c r="A148" t="s">
+        <v>40</v>
+      </c>
+      <c r="E148" t="s">
+        <v>84</v>
+      </c>
+      <c r="F148" t="s">
+        <v>166</v>
+      </c>
+      <c r="G148" t="s">
+        <v>244</v>
+      </c>
+      <c r="I148" t="s">
+        <v>397</v>
+      </c>
+      <c r="J148" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="149" spans="1:10">
+      <c r="A149" t="s">
+        <v>41</v>
+      </c>
+      <c r="B149" t="s">
+        <v>57</v>
+      </c>
+      <c r="C149" t="s">
+        <v>63</v>
+      </c>
+      <c r="D149" t="s">
+        <v>70</v>
+      </c>
+      <c r="I149" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="150" spans="1:10">
+      <c r="A150" t="s">
+        <v>42</v>
+      </c>
+      <c r="I150" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="151" spans="1:10">
+      <c r="E151" t="s">
+        <v>85</v>
+      </c>
+      <c r="F151" t="s">
+        <v>167</v>
+      </c>
+      <c r="G151" t="s">
+        <v>245</v>
+      </c>
+      <c r="I151" t="s">
+        <v>400</v>
+      </c>
+      <c r="J151" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="152" spans="1:10">
+      <c r="A152" t="s">
+        <v>33</v>
+      </c>
+      <c r="B152" t="s">
+        <v>59</v>
+      </c>
+      <c r="C152" t="s">
+        <v>63</v>
+      </c>
+      <c r="D152" t="s">
+        <v>70</v>
+      </c>
+      <c r="E152" t="s">
+        <v>95</v>
+      </c>
+      <c r="F152" t="s">
+        <v>168</v>
+      </c>
+      <c r="G152" t="s">
+        <v>246</v>
+      </c>
+      <c r="I152" t="s">
+        <v>401</v>
+      </c>
+      <c r="J152" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="153" spans="1:10">
+      <c r="F153" t="s">
+        <v>169</v>
+      </c>
+      <c r="G153" t="s">
+        <v>247</v>
+      </c>
+      <c r="H153" t="s">
+        <v>265</v>
+      </c>
+      <c r="I153" t="s">
+        <v>402</v>
+      </c>
+      <c r="J153" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="154" spans="1:10">
+      <c r="A154" t="s">
+        <v>41</v>
+      </c>
+      <c r="B154" t="s">
+        <v>57</v>
+      </c>
+      <c r="C154" t="s">
+        <v>63</v>
+      </c>
+      <c r="D154" t="s">
+        <v>70</v>
+      </c>
+      <c r="I154" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="155" spans="1:10">
+      <c r="A155" t="s">
+        <v>42</v>
+      </c>
+      <c r="I155" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="156" spans="1:10">
+      <c r="E156" t="s">
+        <v>85</v>
+      </c>
+      <c r="F156" t="s">
+        <v>170</v>
+      </c>
+      <c r="G156" t="s">
+        <v>248</v>
+      </c>
+      <c r="H156" t="s">
+        <v>272</v>
+      </c>
+      <c r="I156" t="s">
+        <v>403</v>
+      </c>
+      <c r="J156" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="157" spans="1:10">
+      <c r="A157" t="s">
+        <v>41</v>
+      </c>
+      <c r="B157" t="s">
+        <v>57</v>
+      </c>
+      <c r="C157" t="s">
+        <v>63</v>
+      </c>
+      <c r="D157" t="s">
+        <v>70</v>
+      </c>
+      <c r="I157" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="158" spans="1:10">
+      <c r="A158" t="s">
+        <v>42</v>
+      </c>
+      <c r="I158" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="159" spans="1:10">
+      <c r="E159" t="s">
+        <v>85</v>
+      </c>
+      <c r="F159" t="s">
+        <v>170</v>
+      </c>
+      <c r="G159" t="s">
+        <v>248</v>
+      </c>
+      <c r="H159" t="s">
+        <v>272</v>
+      </c>
+      <c r="I159" t="s">
+        <v>404</v>
+      </c>
+      <c r="J159" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="160" spans="1:10">
+      <c r="A160" t="s">
+        <v>41</v>
+      </c>
+      <c r="I160" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="161" spans="1:10">
+      <c r="A161" t="s">
+        <v>43</v>
+      </c>
+      <c r="B161" t="s">
+        <v>61</v>
+      </c>
+      <c r="C161" t="s">
+        <v>64</v>
+      </c>
+      <c r="D161" t="s">
+        <v>71</v>
+      </c>
+      <c r="I161" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="162" spans="1:10">
+      <c r="A162" t="s">
+        <v>43</v>
+      </c>
+      <c r="E162" t="s">
+        <v>82</v>
+      </c>
+      <c r="F162" t="s">
+        <v>171</v>
+      </c>
+      <c r="G162" t="s">
+        <v>249</v>
+      </c>
+      <c r="I162" t="s">
+        <v>407</v>
+      </c>
+      <c r="J162" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="163" spans="1:10">
+      <c r="A163" t="s">
+        <v>44</v>
+      </c>
+      <c r="B163" t="s">
+        <v>58</v>
+      </c>
+      <c r="C163" t="s">
+        <v>65</v>
+      </c>
+      <c r="D163" t="s">
+        <v>70</v>
+      </c>
+      <c r="I163" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="164" spans="1:10">
+      <c r="A164" t="s">
+        <v>44</v>
+      </c>
+      <c r="E164" t="s">
+        <v>85</v>
+      </c>
+      <c r="F164" t="s">
+        <v>172</v>
+      </c>
+      <c r="G164" t="s">
+        <v>250</v>
+      </c>
+      <c r="I164" t="s">
+        <v>409</v>
+      </c>
+      <c r="J164" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="165" spans="1:10">
+      <c r="A165" t="s">
+        <v>44</v>
+      </c>
+      <c r="B165" t="s">
+        <v>58</v>
+      </c>
+      <c r="C165" t="s">
+        <v>65</v>
+      </c>
+      <c r="D165" t="s">
+        <v>70</v>
+      </c>
+      <c r="I165" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="166" spans="1:10">
+      <c r="A166" t="s">
+        <v>44</v>
+      </c>
+      <c r="E166" t="s">
+        <v>84</v>
+      </c>
+      <c r="F166" t="s">
+        <v>173</v>
+      </c>
+      <c r="G166" t="s">
+        <v>251</v>
+      </c>
+      <c r="H166" t="s">
+        <v>265</v>
+      </c>
+      <c r="I166" t="s">
+        <v>410</v>
+      </c>
+      <c r="J166" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="167" spans="1:10">
+      <c r="A167" t="s">
+        <v>44</v>
+      </c>
+      <c r="E167" t="s">
+        <v>84</v>
+      </c>
+      <c r="I167" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="168" spans="1:10">
+      <c r="A168" t="s">
+        <v>44</v>
+      </c>
+      <c r="E168" t="s">
+        <v>84</v>
+      </c>
+      <c r="I168" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="169" spans="1:10">
+      <c r="A169" t="s">
+        <v>45</v>
+      </c>
+      <c r="E169" t="s">
+        <v>84</v>
+      </c>
+      <c r="I169" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="170" spans="1:10">
+      <c r="A170" t="s">
+        <v>46</v>
+      </c>
+      <c r="B170" t="s">
+        <v>56</v>
+      </c>
+      <c r="C170" t="s">
+        <v>68</v>
+      </c>
+      <c r="E170" t="s">
+        <v>73</v>
+      </c>
+      <c r="I170" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="171" spans="1:10">
+      <c r="A171" t="s">
+        <v>46</v>
+      </c>
+      <c r="B171" t="s">
+        <v>56</v>
+      </c>
+      <c r="C171" t="s">
+        <v>69</v>
+      </c>
+      <c r="D171" t="s">
+        <v>73</v>
+      </c>
+      <c r="F171" t="s">
+        <v>174</v>
+      </c>
+      <c r="G171" t="s">
+        <v>252</v>
+      </c>
+      <c r="I171" t="s">
+        <v>415</v>
+      </c>
+      <c r="J171" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="172" spans="1:10">
+      <c r="A172" t="s">
+        <v>47</v>
+      </c>
+      <c r="E172" t="s">
+        <v>101</v>
+      </c>
+      <c r="F172" t="s">
+        <v>148</v>
+      </c>
+      <c r="G172" t="s">
+        <v>224</v>
+      </c>
+      <c r="I172" t="s">
+        <v>416</v>
+      </c>
+      <c r="J172" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="173" spans="1:10">
+      <c r="A173" t="s">
+        <v>44</v>
+      </c>
+      <c r="B173" t="s">
+        <v>58</v>
+      </c>
+      <c r="C173" t="s">
+        <v>65</v>
+      </c>
+      <c r="D173" t="s">
+        <v>70</v>
+      </c>
+      <c r="I173" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="174" spans="1:10">
+      <c r="A174" t="s">
+        <v>44</v>
+      </c>
+      <c r="E174" t="s">
+        <v>102</v>
+      </c>
+      <c r="F174" t="s">
+        <v>129</v>
+      </c>
+      <c r="G174" t="s">
+        <v>205</v>
+      </c>
+      <c r="I174" t="s">
+        <v>417</v>
+      </c>
+      <c r="J174" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="175" spans="1:10">
+      <c r="A175" t="s">
+        <v>48</v>
+      </c>
+      <c r="E175" t="s">
+        <v>85</v>
+      </c>
+      <c r="I175" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="176" spans="1:10">
+      <c r="A176" t="s">
+        <v>44</v>
+      </c>
+      <c r="B176" t="s">
+        <v>60</v>
+      </c>
+      <c r="C176" t="s">
+        <v>65</v>
+      </c>
+      <c r="D176" t="s">
+        <v>70</v>
+      </c>
+      <c r="I176" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="177" spans="1:10">
+      <c r="A177" t="s">
+        <v>44</v>
+      </c>
+      <c r="E177" t="s">
+        <v>81</v>
+      </c>
+      <c r="F177" t="s">
+        <v>125</v>
+      </c>
+      <c r="G177" t="s">
+        <v>253</v>
+      </c>
+      <c r="I177" t="s">
+        <v>420</v>
+      </c>
+      <c r="J177" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="178" spans="1:10">
+      <c r="A178" t="s">
+        <v>44</v>
+      </c>
+      <c r="B178" t="s">
+        <v>56</v>
+      </c>
+      <c r="C178" t="s">
+        <v>65</v>
+      </c>
+      <c r="D178" t="s">
+        <v>70</v>
+      </c>
+      <c r="I178" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="179" spans="1:10">
+      <c r="A179" t="s">
+        <v>44</v>
+      </c>
+      <c r="E179" t="s">
+        <v>103</v>
+      </c>
+      <c r="F179" t="s">
+        <v>175</v>
+      </c>
+      <c r="G179" t="s">
+        <v>254</v>
+      </c>
+      <c r="I179" t="s">
+        <v>422</v>
+      </c>
+      <c r="J179" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="180" spans="1:10">
+      <c r="A180" t="s">
+        <v>43</v>
+      </c>
+      <c r="B180" t="s">
+        <v>61</v>
+      </c>
+      <c r="C180" t="s">
+        <v>64</v>
+      </c>
+      <c r="D180" t="s">
+        <v>71</v>
+      </c>
+      <c r="I180" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="181" spans="1:10">
+      <c r="A181" t="s">
+        <v>43</v>
+      </c>
+      <c r="E181" t="s">
+        <v>99</v>
+      </c>
+      <c r="F181" t="s">
+        <v>176</v>
+      </c>
+      <c r="G181" t="s">
+        <v>255</v>
+      </c>
+      <c r="I181" t="s">
+        <v>424</v>
+      </c>
+      <c r="J181" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="182" spans="1:10">
+      <c r="A182" t="s">
+        <v>49</v>
+      </c>
+      <c r="B182" t="s">
+        <v>61</v>
+      </c>
+      <c r="C182" t="s">
+        <v>64</v>
+      </c>
+      <c r="D182" t="s">
+        <v>78</v>
+      </c>
+      <c r="I182" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="183" spans="1:10">
+      <c r="A183" t="s">
+        <v>49</v>
+      </c>
+      <c r="B183" t="s">
+        <v>58</v>
+      </c>
+      <c r="C183" t="s">
+        <v>63</v>
+      </c>
+      <c r="D183" t="s">
+        <v>70</v>
+      </c>
+      <c r="F183" t="s">
+        <v>164</v>
+      </c>
+      <c r="G183" t="s">
+        <v>242</v>
+      </c>
+      <c r="H183" t="s">
+        <v>265</v>
+      </c>
+      <c r="I183" t="s">
+        <v>426</v>
+      </c>
+      <c r="J183" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="184" spans="1:10">
+      <c r="A184" t="s">
+        <v>49</v>
+      </c>
+      <c r="E184" t="s">
+        <v>84</v>
+      </c>
+      <c r="F184" t="s">
+        <v>177</v>
+      </c>
+      <c r="G184" t="s">
+        <v>256</v>
+      </c>
+      <c r="H184" t="s">
+        <v>265</v>
+      </c>
+      <c r="I184" t="s">
+        <v>427</v>
+      </c>
+      <c r="J184" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="185" spans="1:10">
+      <c r="A185" t="s">
+        <v>49</v>
+      </c>
+      <c r="B185" t="s">
+        <v>58</v>
+      </c>
+      <c r="C185" t="s">
+        <v>63</v>
+      </c>
+      <c r="D185" t="s">
+        <v>70</v>
+      </c>
+      <c r="I185" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="186" spans="1:10">
+      <c r="E186" t="s">
+        <v>85</v>
+      </c>
+      <c r="F186" t="s">
+        <v>134</v>
+      </c>
+      <c r="G186" t="s">
+        <v>257</v>
+      </c>
+      <c r="H186" t="s">
+        <v>265</v>
+      </c>
+      <c r="I186" t="s">
+        <v>429</v>
+      </c>
+      <c r="J186" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="187" spans="1:10">
+      <c r="E187" t="s">
+        <v>85</v>
+      </c>
+      <c r="F187" t="s">
+        <v>178</v>
+      </c>
+      <c r="G187" t="s">
+        <v>258</v>
+      </c>
+      <c r="H187" t="s">
+        <v>265</v>
+      </c>
+      <c r="I187" t="s">
+        <v>430</v>
+      </c>
+      <c r="J187" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="188" spans="1:10">
+      <c r="A188" t="s">
+        <v>49</v>
+      </c>
+      <c r="B188" t="s">
+        <v>58</v>
+      </c>
+      <c r="C188" t="s">
+        <v>63</v>
+      </c>
+      <c r="D188" t="s">
+        <v>70</v>
+      </c>
+      <c r="I188" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="189" spans="1:10">
+      <c r="A189" t="s">
+        <v>50</v>
+      </c>
+      <c r="B189" t="s">
+        <v>59</v>
+      </c>
+      <c r="C189" t="s">
+        <v>63</v>
+      </c>
+      <c r="E189" t="s">
+        <v>98</v>
+      </c>
+      <c r="F189" t="s">
+        <v>179</v>
+      </c>
+      <c r="G189" t="s">
+        <v>259</v>
+      </c>
+      <c r="H189" t="s">
+        <v>265</v>
+      </c>
+      <c r="I189" t="s">
+        <v>432</v>
+      </c>
+      <c r="J189" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="190" spans="1:10">
+      <c r="A190" t="s">
+        <v>51</v>
+      </c>
+      <c r="B190" t="s">
+        <v>56</v>
+      </c>
+      <c r="C190" t="s">
+        <v>64</v>
+      </c>
+      <c r="E190" t="s">
+        <v>73</v>
+      </c>
+      <c r="F190" t="s">
+        <v>124</v>
+      </c>
+      <c r="G190" t="s">
+        <v>201</v>
+      </c>
+      <c r="H190" t="s">
+        <v>265</v>
+      </c>
+      <c r="I190" t="s">
+        <v>433</v>
+      </c>
+      <c r="J190" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="191" spans="1:10">
+      <c r="A191" t="s">
+        <v>51</v>
+      </c>
+      <c r="B191" t="s">
+        <v>56</v>
+      </c>
+      <c r="C191" t="s">
+        <v>64</v>
+      </c>
+      <c r="D191" t="s">
+        <v>72</v>
+      </c>
+      <c r="E191" t="s">
+        <v>73</v>
+      </c>
+      <c r="F191" t="s">
+        <v>180</v>
+      </c>
+      <c r="G191" t="s">
+        <v>191</v>
+      </c>
+      <c r="I191" t="s">
+        <v>434</v>
+      </c>
+      <c r="J191" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="192" spans="1:10">
+      <c r="A192" t="s">
+        <v>52</v>
+      </c>
+      <c r="E192" t="s">
+        <v>104</v>
+      </c>
+      <c r="F192" t="s">
+        <v>148</v>
+      </c>
+      <c r="G192" t="s">
+        <v>224</v>
+      </c>
+      <c r="I192" t="s">
+        <v>435</v>
+      </c>
+      <c r="J192" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="193" spans="1:10">
+      <c r="A193" t="s">
+        <v>53</v>
+      </c>
+      <c r="B193" t="s">
+        <v>58</v>
+      </c>
+      <c r="C193" t="s">
+        <v>63</v>
+      </c>
+      <c r="D193" t="s">
+        <v>70</v>
+      </c>
+      <c r="I193" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="194" spans="1:10">
+      <c r="A194" t="s">
+        <v>53</v>
+      </c>
+      <c r="B194" t="s">
+        <v>59</v>
+      </c>
+      <c r="C194" t="s">
+        <v>63</v>
+      </c>
+      <c r="E194" t="s">
+        <v>98</v>
+      </c>
+      <c r="F194" t="s">
+        <v>181</v>
+      </c>
+      <c r="G194" t="s">
+        <v>260</v>
+      </c>
+      <c r="I194" t="s">
+        <v>437</v>
+      </c>
+      <c r="J194" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="195" spans="1:10">
+      <c r="A195" t="s">
+        <v>54</v>
+      </c>
+      <c r="B195" t="s">
+        <v>57</v>
+      </c>
+      <c r="C195" t="s">
+        <v>63</v>
+      </c>
+      <c r="D195" t="s">
+        <v>70</v>
+      </c>
+      <c r="E195" t="s">
+        <v>105</v>
+      </c>
+      <c r="F195" t="s">
+        <v>117</v>
+      </c>
+      <c r="G195" t="s">
+        <v>196</v>
+      </c>
+      <c r="H195" t="s">
+        <v>265</v>
+      </c>
+      <c r="I195" t="s">
+        <v>438</v>
+      </c>
+      <c r="J195" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="196" spans="1:10">
+      <c r="A196" t="s">
+        <v>54</v>
+      </c>
+      <c r="B196" t="s">
+        <v>57</v>
+      </c>
+      <c r="C196" t="s">
+        <v>63</v>
+      </c>
+      <c r="D196" t="s">
+        <v>70</v>
+      </c>
+      <c r="E196" t="s">
+        <v>106</v>
+      </c>
+      <c r="F196" t="s">
+        <v>182</v>
+      </c>
+      <c r="G196" t="s">
+        <v>261</v>
+      </c>
+      <c r="H196" t="s">
+        <v>265</v>
+      </c>
+      <c r="I196" t="s">
+        <v>439</v>
+      </c>
+      <c r="J196" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="197" spans="1:10">
+      <c r="A197" t="s">
+        <v>54</v>
+      </c>
+      <c r="B197" t="s">
+        <v>59</v>
+      </c>
+      <c r="C197" t="s">
+        <v>63</v>
+      </c>
+      <c r="D197" t="s">
+        <v>70</v>
+      </c>
+      <c r="E197" t="s">
+        <v>95</v>
+      </c>
+      <c r="F197" t="s">
+        <v>175</v>
+      </c>
+      <c r="G197" t="s">
+        <v>254</v>
+      </c>
+      <c r="H197" t="s">
+        <v>265</v>
+      </c>
+      <c r="I197" t="s">
+        <v>440</v>
+      </c>
+      <c r="J197" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="198" spans="1:10">
+      <c r="A198" t="s">
+        <v>54</v>
+      </c>
+      <c r="B198" t="s">
+        <v>59</v>
+      </c>
+      <c r="C198" t="s">
+        <v>63</v>
+      </c>
+      <c r="D198" t="s">
+        <v>70</v>
+      </c>
+      <c r="E198" t="s">
+        <v>95</v>
+      </c>
+      <c r="F198" t="s">
+        <v>183</v>
+      </c>
+      <c r="G198" t="s">
+        <v>262</v>
+      </c>
+      <c r="H198" t="s">
+        <v>265</v>
+      </c>
+      <c r="I198" t="s">
+        <v>441</v>
+      </c>
+      <c r="J198" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="199" spans="1:10">
+      <c r="A199" t="s">
+        <v>54</v>
+      </c>
+      <c r="B199" t="s">
+        <v>57</v>
+      </c>
+      <c r="C199" t="s">
+        <v>63</v>
+      </c>
+      <c r="D199" t="s">
+        <v>70</v>
+      </c>
+      <c r="E199" t="s">
+        <v>106</v>
+      </c>
+      <c r="F199" t="s">
+        <v>184</v>
+      </c>
+      <c r="G199" t="s">
+        <v>263</v>
+      </c>
+      <c r="H199" t="s">
+        <v>265</v>
+      </c>
+      <c r="I199" t="s">
+        <v>442</v>
+      </c>
+      <c r="J199" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="200" spans="1:10">
+      <c r="B200" t="s">
+        <v>58</v>
+      </c>
+      <c r="C200" t="s">
+        <v>63</v>
+      </c>
+      <c r="D200" t="s">
+        <v>70</v>
+      </c>
+      <c r="F200" t="s">
+        <v>124</v>
+      </c>
+      <c r="G200" t="s">
+        <v>201</v>
+      </c>
+      <c r="H200" t="s">
+        <v>265</v>
+      </c>
+      <c r="I200" t="s">
+        <v>443</v>
+      </c>
+      <c r="J200" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="201" spans="1:10">
+      <c r="A201" t="s">
+        <v>55</v>
+      </c>
+      <c r="E201" t="s">
+        <v>84</v>
+      </c>
+      <c r="F201" t="s">
+        <v>185</v>
+      </c>
+      <c r="G201" t="s">
+        <v>264</v>
+      </c>
+      <c r="I201" t="s">
+        <v>444</v>
+      </c>
+      <c r="J201" t="s">
+        <v>524</v>
       </c>
     </row>
   </sheetData>

--- a/output_orderan.xlsx
+++ b/output_orderan.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1168" uniqueCount="526">
   <si>
     <t>DATE</t>
   </si>
@@ -37,31 +37,346 @@
     <t>PLATE</t>
   </si>
   <si>
+    <t>TIME</t>
+  </si>
+  <si>
     <t>Original_Text</t>
   </si>
   <si>
     <t>PHONE</t>
   </si>
   <si>
+    <t>04 februari 2026</t>
+  </si>
+  <si>
+    <t>05 / 02 / 2026</t>
+  </si>
+  <si>
+    <t>05 februari 2026</t>
+  </si>
+  <si>
+    <t>05 februari 2025</t>
+  </si>
+  <si>
+    <t>06 / 02 / 2026</t>
+  </si>
+  <si>
     <t>05 feb 26</t>
   </si>
   <si>
+    <t>06 : 00 060226</t>
+  </si>
+  <si>
     <t>03 : 00 060226</t>
   </si>
   <si>
+    <t>06 febuary 2026</t>
+  </si>
+  <si>
+    <t>06 feb 2026</t>
+  </si>
+  <si>
+    <t>12 feb 26</t>
+  </si>
+  <si>
+    <t>03 : 00 130226</t>
+  </si>
+  <si>
+    <t>12 februari 2026</t>
+  </si>
+  <si>
+    <t>13 februari 2026</t>
+  </si>
+  <si>
+    <t>23 : 00 13 februari 2026</t>
+  </si>
+  <si>
+    <t>14022026</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>15 februari 2026</t>
+  </si>
+  <si>
+    <t>16 feb 26</t>
+  </si>
+  <si>
+    <t>03 : 00 170226</t>
+  </si>
+  <si>
+    <t>17 februari 2026</t>
+  </si>
+  <si>
+    <t>26 feb 26</t>
+  </si>
+  <si>
+    <t>03 : 00 270226</t>
+  </si>
+  <si>
+    <t>26 febuari 2026</t>
+  </si>
+  <si>
+    <t>27 febuari 2026</t>
+  </si>
+  <si>
+    <t>27 februari 2026</t>
+  </si>
+  <si>
+    <t>27 feb 26</t>
+  </si>
+  <si>
+    <t>28 februari 2026</t>
+  </si>
+  <si>
+    <t>28 febuari 2026</t>
+  </si>
+  <si>
+    <t>23 : 00 28 februari 2026</t>
+  </si>
+  <si>
+    <t>28 / 02 / 206</t>
+  </si>
+  <si>
+    <t>1 maret 2026</t>
+  </si>
+  <si>
+    <t>28 / 02 / 2026</t>
+  </si>
+  <si>
+    <t>03 maret 2026</t>
+  </si>
+  <si>
+    <t>3 maret 2026</t>
+  </si>
+  <si>
+    <t>02 : 00 04032026</t>
+  </si>
+  <si>
+    <t>03 mar 26</t>
+  </si>
+  <si>
+    <t>04 mar 26</t>
+  </si>
+  <si>
+    <t>03 : 00 04032026</t>
+  </si>
+  <si>
+    <t>04 maret 2026</t>
+  </si>
+  <si>
+    <t>04 mar 2026</t>
+  </si>
+  <si>
+    <t>05 mar 26</t>
+  </si>
+  <si>
+    <t>03 : 00 06 mar 26</t>
+  </si>
+  <si>
+    <t>05 maret 2026</t>
+  </si>
+  <si>
+    <t>06 maret 2026</t>
+  </si>
+  <si>
+    <t>18 : 00 05022026</t>
+  </si>
+  <si>
     <t>1</t>
   </si>
   <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>twb</t>
+  </si>
+  <si>
     <t>cddl</t>
   </si>
   <si>
+    <t>wb</t>
+  </si>
+  <si>
+    <t>tronton</t>
+  </si>
+  <si>
+    <t>cddl cbm</t>
+  </si>
+  <si>
+    <t>cddl / cbm</t>
+  </si>
+  <si>
+    <t>cddl 24 cbm</t>
+  </si>
+  <si>
+    <t>argopantes</t>
+  </si>
+  <si>
+    <t>megahub</t>
+  </si>
+  <si>
+    <t>cikokol</t>
+  </si>
+  <si>
+    <t>cgk sub</t>
+  </si>
+  <si>
     <t>cikarang</t>
   </si>
   <si>
     <t>ckrjateng</t>
   </si>
   <si>
-    <t>24</t>
+    <t>jne</t>
+  </si>
+  <si>
+    <t>cgk</t>
+  </si>
+  <si>
+    <t>wangongateway</t>
+  </si>
+  <si>
+    <t>argo pantes</t>
+  </si>
+  <si>
+    <t>cgk pdg</t>
+  </si>
+  <si>
+    <t>cgk jateng</t>
+  </si>
+  <si>
+    <t>cgk dps</t>
+  </si>
+  <si>
+    <t>cgk plm</t>
+  </si>
+  <si>
+    <t>cgk pku</t>
+  </si>
+  <si>
+    <t>cgk mes</t>
+  </si>
+  <si>
+    <t>sub</t>
+  </si>
+  <si>
+    <t>bm</t>
+  </si>
+  <si>
+    <t>subcgk</t>
+  </si>
+  <si>
+    <t>cgk tentatif</t>
+  </si>
+  <si>
+    <t>ckrsubsux</t>
+  </si>
+  <si>
+    <t>cgkjbr</t>
+  </si>
+  <si>
+    <t>cgkjateng</t>
+  </si>
+  <si>
+    <t>cgk denpasar</t>
+  </si>
+  <si>
+    <t>mes</t>
+  </si>
+  <si>
+    <t>cgk jatim tentatif</t>
+  </si>
+  <si>
+    <t>pku</t>
+  </si>
+  <si>
+    <t>plm</t>
+  </si>
+  <si>
+    <t>suxcgk</t>
+  </si>
+  <si>
+    <t>cgk jatim</t>
+  </si>
+  <si>
+    <t>jateng tentatif</t>
+  </si>
+  <si>
+    <t>ckrmxg</t>
+  </si>
+  <si>
+    <t>mes ddriver</t>
+  </si>
+  <si>
+    <t>sub cgk</t>
+  </si>
+  <si>
+    <t>cgkpsr</t>
+  </si>
+  <si>
+    <t>jatim tentatif</t>
+  </si>
+  <si>
+    <t>cgksub</t>
+  </si>
+  <si>
+    <t>sutrisno</t>
+  </si>
+  <si>
+    <t>karyadi</t>
+  </si>
+  <si>
+    <t>m syaichoni</t>
+  </si>
+  <si>
+    <t>lailan</t>
+  </si>
+  <si>
+    <t>agus</t>
+  </si>
+  <si>
+    <t>jatmiyanta</t>
+  </si>
+  <si>
+    <t>siswanto</t>
+  </si>
+  <si>
+    <t>feri irawan</t>
+  </si>
+  <si>
+    <t>hadi</t>
+  </si>
+  <si>
+    <t>a . sukur</t>
+  </si>
+  <si>
+    <t>akiyat</t>
+  </si>
+  <si>
+    <t>ryan</t>
+  </si>
+  <si>
+    <t>hendra s . p</t>
+  </si>
+  <si>
+    <t>sandri</t>
   </si>
   <si>
     <t>akbar</t>
@@ -70,10 +385,686 @@
     <t>apar rahmat</t>
   </si>
   <si>
+    <t>m . ibnu</t>
+  </si>
+  <si>
+    <t>wahyudi</t>
+  </si>
+  <si>
+    <t>sofyan</t>
+  </si>
+  <si>
+    <t>chandra</t>
+  </si>
+  <si>
+    <t>ageng</t>
+  </si>
+  <si>
+    <t>ilham wahyudi</t>
+  </si>
+  <si>
+    <t>sri mardono</t>
+  </si>
+  <si>
+    <t>rosyit</t>
+  </si>
+  <si>
+    <t>dimas</t>
+  </si>
+  <si>
+    <t>herman</t>
+  </si>
+  <si>
+    <t>fajri</t>
+  </si>
+  <si>
+    <t>andi</t>
+  </si>
+  <si>
+    <t>noprianto</t>
+  </si>
+  <si>
+    <t>simare</t>
+  </si>
+  <si>
+    <t>nanang</t>
+  </si>
+  <si>
+    <t>mengri</t>
+  </si>
+  <si>
+    <t>sulis</t>
+  </si>
+  <si>
+    <t>agung</t>
+  </si>
+  <si>
+    <t>manulang</t>
+  </si>
+  <si>
+    <t>samsul</t>
+  </si>
+  <si>
+    <t>manulang noa€¦</t>
+  </si>
+  <si>
+    <t>rajiev fikri</t>
+  </si>
+  <si>
+    <t>alex s</t>
+  </si>
+  <si>
+    <t>arif</t>
+  </si>
+  <si>
+    <t>anto</t>
+  </si>
+  <si>
+    <t>kudir</t>
+  </si>
+  <si>
+    <t>davit</t>
+  </si>
+  <si>
+    <t>hendra setiawan</t>
+  </si>
+  <si>
+    <t>febrianto</t>
+  </si>
+  <si>
+    <t>m doni saputra</t>
+  </si>
+  <si>
+    <t>habib</t>
+  </si>
+  <si>
+    <t>aris</t>
+  </si>
+  <si>
+    <t>supriyanto</t>
+  </si>
+  <si>
+    <t>agung prasetyo</t>
+  </si>
+  <si>
+    <t>rizki</t>
+  </si>
+  <si>
+    <t>dian saputra</t>
+  </si>
+  <si>
+    <t>yugik</t>
+  </si>
+  <si>
+    <t>muatim</t>
+  </si>
+  <si>
+    <t>ibnu</t>
+  </si>
+  <si>
+    <t>yusni gunawan</t>
+  </si>
+  <si>
+    <t>agus supriatna</t>
+  </si>
+  <si>
+    <t>rizky / aris</t>
+  </si>
+  <si>
+    <t>dedeng</t>
+  </si>
+  <si>
+    <t>indra</t>
+  </si>
+  <si>
+    <t>ariansyah</t>
+  </si>
+  <si>
+    <t>arbi</t>
+  </si>
+  <si>
+    <t>anton</t>
+  </si>
+  <si>
+    <t>mujito</t>
+  </si>
+  <si>
+    <t>jodi akbar</t>
+  </si>
+  <si>
+    <t>arizal</t>
+  </si>
+  <si>
+    <t>samosir</t>
+  </si>
+  <si>
+    <t>soni rahmat</t>
+  </si>
+  <si>
+    <t>nana hermawan</t>
+  </si>
+  <si>
+    <t>yuda</t>
+  </si>
+  <si>
+    <t>ari purnama</t>
+  </si>
+  <si>
+    <t>jupri</t>
+  </si>
+  <si>
+    <t>misno</t>
+  </si>
+  <si>
+    <t>usman afandi</t>
+  </si>
+  <si>
+    <t>miyanta</t>
+  </si>
+  <si>
+    <t>iwan hariono</t>
+  </si>
+  <si>
+    <t>suryadi</t>
+  </si>
+  <si>
+    <t>ridwan</t>
+  </si>
+  <si>
+    <t>nasip</t>
+  </si>
+  <si>
+    <t>syarial</t>
+  </si>
+  <si>
+    <t>bm 8364 au</t>
+  </si>
+  <si>
+    <t>ad 8517 ba</t>
+  </si>
+  <si>
+    <t>n 8872 rk</t>
+  </si>
+  <si>
+    <t>s 9272 up</t>
+  </si>
+  <si>
+    <t>d 9667 af</t>
+  </si>
+  <si>
+    <t>f 9647 fh</t>
+  </si>
+  <si>
+    <t>b 9120 wxr</t>
+  </si>
+  <si>
+    <t>bk 8516 vv</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>b 9477 keu</t>
+  </si>
+  <si>
+    <t>l 9722 ue</t>
+  </si>
+  <si>
+    <t>b 9084 veh</t>
+  </si>
+  <si>
+    <t>d 9044 ag</t>
+  </si>
+  <si>
     <t>e9406hb</t>
   </si>
   <si>
+    <t>l 9511 al</t>
+  </si>
+  <si>
+    <t>n 9549 ua</t>
+  </si>
+  <si>
+    <t>b 9679 wt</t>
+  </si>
+  <si>
+    <t>l 8601 uh</t>
+  </si>
+  <si>
+    <t>b9654yu</t>
+  </si>
+  <si>
+    <t>bk 8678 ve</t>
+  </si>
+  <si>
+    <t>b 9563 teu</t>
+  </si>
+  <si>
+    <t>h 9263 ov</t>
+  </si>
+  <si>
+    <t>b 9718 tj</t>
+  </si>
+  <si>
+    <t>b 9241 fxs</t>
+  </si>
+  <si>
+    <t>be 8794 amb</t>
+  </si>
+  <si>
+    <t>be 8251 foa</t>
+  </si>
+  <si>
+    <t>bk 8639 fj</t>
+  </si>
+  <si>
+    <t>ab 8053 ka</t>
+  </si>
+  <si>
+    <t>bm 8279 au</t>
+  </si>
+  <si>
+    <t>l 9579 uk</t>
+  </si>
+  <si>
+    <t>bk 8208 vy</t>
+  </si>
+  <si>
+    <t>b 9771 uew</t>
+  </si>
+  <si>
+    <t>b 9019 uex</t>
+  </si>
+  <si>
+    <t>b 9591 uxx</t>
+  </si>
+  <si>
+    <t>b 9411 vxr</t>
+  </si>
+  <si>
+    <t>b 9209 nck</t>
+  </si>
+  <si>
+    <t>b 9285 uex</t>
+  </si>
+  <si>
+    <t>b 9380 uex</t>
+  </si>
+  <si>
+    <t>b 9726 sxw</t>
+  </si>
+  <si>
+    <t>bk 8516 w</t>
+  </si>
+  <si>
+    <t>be 9636 bu</t>
+  </si>
+  <si>
+    <t>be 8023 wy</t>
+  </si>
+  <si>
+    <t>ba 9980 ps</t>
+  </si>
+  <si>
+    <t>bd 8423 b</t>
+  </si>
+  <si>
+    <t>l 8336 uv</t>
+  </si>
+  <si>
+    <t>b 9139 syt</t>
+  </si>
+  <si>
+    <t>be 8940 db</t>
+  </si>
+  <si>
+    <t>b 9739 seu</t>
+  </si>
+  <si>
+    <t>be 8831 cj</t>
+  </si>
+  <si>
+    <t>be 8334 gba</t>
+  </si>
+  <si>
+    <t>b 9562 teu</t>
+  </si>
+  <si>
+    <t>b 9810 ueu</t>
+  </si>
+  <si>
+    <t>h 9224 ma</t>
+  </si>
+  <si>
+    <t>be 8951 by</t>
+  </si>
+  <si>
+    <t>b 9546 kxx</t>
+  </si>
+  <si>
+    <t>b9091scj</t>
+  </si>
+  <si>
+    <t>e 9426 aa</t>
+  </si>
+  <si>
+    <t>b9588ym</t>
+  </si>
+  <si>
+    <t>be 8775 dy</t>
+  </si>
+  <si>
+    <t>be 8919 amn</t>
+  </si>
+  <si>
+    <t>be 9063 ar</t>
+  </si>
+  <si>
+    <t>be 8837 gk</t>
+  </si>
+  <si>
+    <t>be 8013 au</t>
+  </si>
+  <si>
+    <t>b 9895 uxx</t>
+  </si>
+  <si>
+    <t>b 9727 uex</t>
+  </si>
+  <si>
+    <t>bm 8142 ry</t>
+  </si>
+  <si>
+    <t>b 9658 tcp</t>
+  </si>
+  <si>
+    <t>b 9679wt</t>
+  </si>
+  <si>
+    <t>w 8973 uq</t>
+  </si>
+  <si>
+    <t>b 9383 txv</t>
+  </si>
+  <si>
+    <t>bm 9273 ro</t>
+  </si>
+  <si>
+    <t>be 8610 db</t>
+  </si>
+  <si>
+    <t>bn 8038 rp</t>
+  </si>
+  <si>
+    <t>be 8456 fn</t>
+  </si>
+  <si>
+    <t>bl 8188 jp</t>
+  </si>
+  <si>
+    <t>l 8183uv</t>
+  </si>
+  <si>
+    <t>bk 8330 vy</t>
+  </si>
+  <si>
+    <t>bh 8165 qi</t>
+  </si>
+  <si>
+    <t>bm 8486 au</t>
+  </si>
+  <si>
+    <t>segera</t>
+  </si>
+  <si>
+    <t>07 : 00</t>
+  </si>
+  <si>
+    <t>18 : 00</t>
+  </si>
+  <si>
+    <t>21 : 00</t>
+  </si>
+  <si>
+    <t>03 : 00</t>
+  </si>
+  <si>
+    <t>02 : 00</t>
+  </si>
+  <si>
+    <t>23 : 00</t>
+  </si>
+  <si>
+    <t>04 ; 00</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: Request Unit On Call
+RAFAY
+1 UNIT TWB 50 Cbm
+Lokasi : ARGOPANTES</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA
+Rute/tujuan : CGK- PDG
+driver  : SUTRISNO
+Nopol  : BM 8364 AU
+No hp  :0853-5388-6066</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: REQUEST ORDER ONCALL 04 FEBRUARI 2026:
+RAFAY
+3 unit Cddl 24 Cbm
+Lokasi : Megahub</t>
+  </si>
+  <si>
+    <t>REQUEST ORDER KHUSUS 05/02/2026</t>
+  </si>
+  <si>
+    <t>Waktu loading : 07:00
+Rute/tujuan : CGK - JATENG
+driver  : KARYADI
+Nopol  : AD 8517 BA
+No hp  :085865762797</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: REQUEST ORDER ULANG ONCALL
+5 UNIT TWB 50 CBM
+Lokasi : ARGOPANTES</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA
+Rute/tujuan : CGK - SUB
+driver  :
+Nopol  :
+No hp  :</t>
+  </si>
+  <si>
+    <t>Waktu loading : 18:00
+Rute/tujuan : CGK - SUB
+driver  : m syaichoni
+Nopol  : N 8872 Rk
+No hp  : +62 812-3189-5971</t>
+  </si>
+  <si>
+    <t>Waktu loading : 21:00
+Rute/tujuan : CGK - SUB
+driver  :
+Nopol  :
+No hp  :</t>
+  </si>
+  <si>
+    <t>Waktu loading : 00:00
+Rute/tujuan : CGK - SUB
+driver  :
+Nopol  :
+No hp  :</t>
+  </si>
+  <si>
+    <t>Waktu loading : 03:00
+Rute/tujuan : CGK -SUB
+driver  : Lailan
+Nopol  : S 9272 UP
+No hp  : +62 878-8686-1780</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: REQUEST TAMBAHAN ORDER ONCALL 04 FEBRUARI 2026:
+RAFAY
+2 UNIT TWB 50 CBM
+Lokasi : CIKOKOL</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA 04 FEBRUARI 2026
+Rute/tujuan : CGK - SUB
+driver  : AGUS
+Nopol  : D 9667 AF
+No hp  :08817021866
+Rev plat nomor pak @Nomor tidak dikenal @Nomor tidak dikenal @Nomor tidak dikenal ðŸ™ðŸ»</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: REQUEST ORDER ONCALL 04 FEBRUARI 2026:
+RAFAY
+1 unit Cddl 24 Cbm
+Lokasi : Megahub</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA 04 FEBRUARI 2026
+Rute/tujuan : CGK - DPS
+driver 1 : Edi setiawan
+No hp  :0881023544597 
+Driver2 : Jatmiyanta
+No hp  :082118558105
+Nopol : F 9647 FH</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: REQUEST ULANG ORDER ONCALL 05 FEBRUARI 2026:
+2 UNIT TWB 50 CBM
+Lokasi : CIKOKOL</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA 05 FEBRUARI 2026
+Rute/tujuan : CGK - TKG
+driver  :
+Nopol  :
+No hp  :
+2 UNIT TWB 50 CBM
+Lokasi : CIKOKOL</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA 05 FEBRUARI 2026
+Rute/tujuan : CGK - PLM
+driver  :
+Nopol  :
+No hp  :
+2 UNIT TWB 50 CBM
+Lokasi : CIKOKOL</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA 05 FEBRUARI 2026
+Rute/tujuan : CGK - PKU
+driver  : Siswanto
+Nopol  : B 9120 WXR
+No hp  : 081943564062
+Lokasi : CIKOKOL</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA 05 FEBRUARI 2026
+Rute/tujuan : CGK - PKU
+driver  : 
+Nopol  : 
+No hp  : 
+2 UNIT TWB 50 CBM
+Lokasi : CIKOKOL</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA 05 FEBRUARI 2026
+Rute/tujuan : CGK - MES
+driver  : feri irawan
+Nopol  : BK 8516 VV
+No hp  : 085219216210</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: REQUEST ULANG ORDER ONCALL 05 FEBRUARI 2026:
+RAFAY
+2 UNIT TWB 50 CBM
+Lokasi : CIKOKOL</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA 05 FEBRUARI 2026
+Rute/tujuan : CGK - MES
+driver  : HADI
+Nopol  :B 9446 MV
+No hp  :+62 831-9621-8655</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA 05 FEBRUARI 2026
+Rute/tujuan : CGK - MES
+driver  : A. Sukur 
+Nopol  :B 9477 KEU
+No hp  : 083169525183</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA
+Rute/tujuan : CGK - SUB
+RAFAY
+driver  : AKIYAT
+Nopol  : L 9722 UE
+No hp  :081281122738</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: REQUEST ULANG ORDER ONCALL 05 FEBRUARI 2025
+RAFAY
+2 UNIT TWB 50 CBM
+Lokasi : CIKOKOL</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA 05 FEBRUARI 2025
+Rute/tujuan : CGK - PKU
+driver  : RYAN
+Nopol  : B 9084 VEH
+No hp  : 087837496810</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA
+Rute/tujuan : CGK - SUB
+driver  : HENDRA S.P
+Nopol  : D 9044 AG
+No hp  : +62 877-8667-6177</t>
+  </si>
+  <si>
+    <t>Waktu loading : 18:00
+Rute/tujuan : CGK - SUB
+driver  :
+Nopol  :
+No hp  :</t>
+  </si>
+  <si>
+    <t>REQUEST ORDER KHUSUS 06/02/2026</t>
+  </si>
+  <si>
+    <t>Waktu loading : 03:00
+Rute/tujuan : CGK -SUB
+driver  :
+Nopol  :
+No hp  :</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA 05 FEBRUARI 2026
+Rute/tujuan : CGK - PLM
+driver  : SANDRI
+Nopol  : BE 9636 BU
+No hp  :+62 889-0702-0037</t>
+  </si>
+  <si>
     <t>[WA_TS] Akbar Rafay: Request Unit On Call Tgl 05 Feb 26
+2 Unit  Cddl / 24 Cbm
+Lokasi : Cikarang</t>
+  </si>
+  <si>
+    <t>Waktu loading : 06:00 06-02-26
+Rute/tujuan : CKR-Jateng Tentative
+Driver   : 
+Nopol  : 
+No Hp  :
 1 Unit  Cddl / 24 Cbm
 Lokasi : Cikarang</t>
   </si>
@@ -85,7 +1076,1251 @@
 NO TLP : 085971812879</t>
   </si>
   <si>
+    <t>[WA_TS] Akbar Rafay: Request Unit On Call Tgl 06 febuary 2026
+RAFAY
+3 unit twb 50 CBM
+Lokasi : ARGOPANTES</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA 06 febuary 2026
+Rute/tujuan : CGK- Jl.perak surabaya-PT.BM
+driver  : M. iBNU
+Nopol  : L 9511 AL
+No hp  :082191633212</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: Request Unit On Call Tgl 06 febuary 2026
+2 unit twb 50 CBM
+Lokasi : JNE SUB</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA 06 febuary 2026
+Rute/tujuan : SUB-CGK
+driver  : WAHYUDI
+Nopol  : N 9549 UA
+No hp  :085784422398</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA 06 febuary 2026
+Rute/tujuan : SUB-CGK
+driver  : SOFYAN
+Nopol  : B 9679 WT
+No hp  : 082231837381</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: REQUEST ORDER ULANG ONCALL
+06 FEB 2026
+6 UNIT WB/50 CBM
+Lokasi : ARGOPANTES</t>
+  </si>
+  <si>
+    <t>REQUEST ORDER KHUSUS 07-02-2026</t>
+  </si>
+  <si>
+    <t>Waktu loading : 07:00
+Rute/tujuan : CGK - SUB
+driver  : Chandra
+Nopol  : L 8601 UH
+No hp  : +62 852-3168-1470</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: REQUEST ORDER ULANG ONCALL
+06 FEB 2026
+10 UNIT CDDL/24 CBM
+Lokasi : ARGOPANTES</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA
+Rute/tujuan : CGK - JATIM TENTATIF</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: Request Unit On Call Tgl 12 Feb 26
+1 Unit  TWB 50 Cbm
+Lokasi : Cikarang</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA 12 Feb 26
+Rute/tujuan : CKR-SUB-SUX 
+Driver   : AGENG
+Nopol  : B9654YU
+No Hp  : +62 857-0738-0584</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: Request Unit On Call Tgl 12 Feb 26
+1 Unit  Cddl / 24 Cbm
+Lokasi : Cikokol + Cikarang</t>
+  </si>
+  <si>
+    <t>Waktu loading : 03:00 13-02-26
+Rute/tujuan : CGK-JBR
+No pol.   : F 9647 FH
+Driver. 1 :  Jatmiyanta
+No hp :  : 082118558105
+Driver 2  : Ilham Wahyudi
+No hp.    : 089519041791</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: REQUEST ORDER ONCALL 12 FEBRUARI 2026:
+RAFAY
+3 unit tronton 50 Cbm
+Lokasi : cikokol</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA 12 FEBRUARI 2026
+Rute/tujuan : CGK - MES
+driver  : SRI MARDONO
+Nopol  : BK 8678 VE
+No hp  :085218843366</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: REQUEST ORDER ONCALL 12 FEBRUARI 2026:
+2 unit tronton 50 Cbm
+Lokasi : cikokol</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA 12 FEBRUARI 2026
+Rute/tujuan : CGK - SUB
+driver  : AGENG
+Nopol  : B 9654 YU
+No hp  : +62 857-0738-0584</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: REQUEST ORDER ONCALL 12 FEBRUARI 2026:
+3 UNIT TWB 50 Cbm
+Lokasi : ARGOPANTES</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA 12 FEBRUARI 2026
+Rute/tujuan : CGK - SUB
+driver  : Rosyit
+Nopol  : B 9563 TEU
+No hp  : 082313572678</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA 12 FEBRUARI 2026
+Rute/tujuan : CGK - SUB
+driver  : M.ibnu
+Nopol  : L 9511 AL
+No hp  : 082191633212</t>
+  </si>
+  <si>
+    <t>Waktu loading : 03:00 12 FEBRUARI 2026
+Rute/tujuan : CGK - SUB
+driver  : Akiyat
+Nopol  : L 9722 UE
+No hp  :081281122738</t>
+  </si>
+  <si>
+    <t>Waktu loading : 03:00 12 FEBRUARI 2026
+Rute/tujuan : CGK - SUB</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: 3 UNIT CDDL 24 CBM
+Lokasi  : CIKOKOL</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA
+Rute/tujuan : CGK-JATENG TENTATIF
+Driver :
+Nopol :
+No hp :</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA
+Driver :
+Nopol :
+No hp :</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA
+Driver :Dimas
+Nopol :H 9263 OV
+No hp :082217785226</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: REQUEST ORDER ONCALL 13 FEBRUARI 2026:
+5 UNIT TWB 50 Cbm
+Lokasi : ARGOPANTES</t>
+  </si>
+  <si>
+    <t>Waktu loading : 15:00 13 FEBRUARI 2026
+Rute/tujuan : CGK - PKU
+driver  : HERMAN
+Nopol  : B 9718 TJ
+No hp  :087844510846</t>
+  </si>
+  <si>
+    <t>Waktu loading : 18:00 13 FEBRUARI 2026
+Rute/tujuan : CGK - PKU
+driver  : FAJRI
+Nopol  : B 9241 FXS
+No hp  :81382418508</t>
+  </si>
+  <si>
+    <t>Waktu loading : 23:00 13 FEBRUARI 2026
+Rute/tujuan : CGK - PKU
+driver  : ANDI
+Nopol  : BE 8794 AMB
+No hp  :082183783385</t>
+  </si>
+  <si>
+    <t>REQUEST ORDER KHUSUS 14-02-2026</t>
+  </si>
+  <si>
+    <t>Waktu loading : 02:00
+Rute/tujuan : CGK - PKU
+driver  : NOPRIANTO
+Nopol  : BE 8251 FOA
+No hp  :085758955627</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: REQUEST ORDER ONCALL ULANG 13 FEBRUARI 2026:
+3 UNIT TWB 50 CBM
+Lokasi : CIKOKOL</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA 13 FEBRUARI 2026
+Rute/tujuan : CGK - MES
+driver  :SIMARE
+Nopol  :BK 8639 FJ
+No hp  :+62 812-6934-5748</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: REQUEST ORDER ONCALL 13 FEBRUARI 2026:
+1 unit Cddl 24 Cbm
+Lokasi : Megahub</t>
+  </si>
+  <si>
+    <t>Waktu loading : 22:00 13 FEBRUARI 2026
+Rute/tujuan : CGK - DENPASAR
+driver  :Nanang
+Nopol  :AB 8053 KA
+No hp  :08889693664</t>
+  </si>
+  <si>
+    <t>Waktu loading : 02:00
+Rute/tujuan : CGK - PKU
+driver  : mengri
+Nopol : BM 8279 AU
+No hp : 085364056583</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA 13 FEBRUARI 2026
+Rute/tujuan : CGK - MES
+driver  :Sulis
+Nopol  :L 9579 UK
+No hp  :085225394209</t>
+  </si>
+  <si>
+    <t>Waktu loading : 23:00 13 FEBRUARI 2026
+Rute/tujuan : CGK - PKU
+driver  : Agung
+Nopol  : BK 8208 VY
+No hp  : 082385989323</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA 13 FEBRUARI 2026
+Rute/tujuan : CGK - MES
+driver  : Manulang
+Nopol  :B 9019 UEX
+No hp  : +62 813-7076-9496</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA 13 FEBRUARI 2026
+Rute/tujuan : CGK - MES
+driver  : SAMSUL
+Nopol  :B 9771 UEW
+No hp  : +62 822-2851-6922</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: REQUEST ORDER ONCALL
+Tanggal : 12 Februari 2026
+Rute/Tujuan : CGK - SUB
+Unit/Type : TWB 50 Cbm 
+Nopol : L 9722 UE
+Driver : Akiyat
+No HP : 0812-8112-2738
+Lokasi Loading : ARGOPANTES</t>
+  </si>
+  <si>
+    <t>Waktu loading : 03:00</t>
+  </si>
+  <si>
+    <t>REQUEST ORDER ONCALL ULANG
+Tanggal : 13 Februari 2026
+Rute/Tujuan : CGK - MES
+Unit/Type : TWB 50 CBM
+Nopol : BK 8639 FJ
+Driver : SIMARE
+No HP : +62 812-6934-5748
+Lokasi Loading : CIKOKOL</t>
+  </si>
+  <si>
+    <t>REQUEST ORDER ONCALL
+Tanggal : 13 Februari 2026
+Rute/Tujuan : CGK - PKU
+Unit/Type : TWB 50 CBM
+Nopol : B 9241 FXS
+Driver : FAJRI
+No HP : 081382418508
+Lokasi Loading : ARGOPANTES</t>
+  </si>
+  <si>
+    <t>Waktu loading : 18:00</t>
+  </si>
+  <si>
+    <t>REQUEST ORDER ONCALL
+Tanggal : 13 FEBRUARI 2026
+Rute/Tujuan : CGK - MES
+Unit/Type :  TWB 50 CBM
+Nopol : B 9019 UEX
+Driver : Manulang
+Noâ€¦</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: REQUEST ORDER ONCALL 15 FEBRUARI 2026:
+2 unit Cddl 24 Cbm
+Lokasi : ARGOPANTES</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA 15 FEBRUARI 2026
+Rute/tujuan : CGK - JATIM TENTATIF
+driver  : Rajiev Fikri
+Nopol  : B 9591 UXX
+No hp  : 088290294126</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA 15 FEBRUARI 2026</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: REQUEST ORDER ONCALL 15 FEBRUARI 2026
+2 UNIT CDDL 24 Cbm
+Lokasi : MEGAHUB</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA 15 FEBRUARI 2026
+Rute/tujuan : CGK - JATENG
+driver  : Alex S
+Nopol  : B 9411 VXR
+No hp  : 088212698834</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: Request Unit On Call Tgl 16 Feb 26
+RAFAY
+1 Unit  Cddl / 24 Cbm
+Lokasi : Cikokol + Cikarang</t>
+  </si>
+  <si>
+    <t>Waktu loading : 03:00 17-02-26
+Rute/tujuan : CGK-JBR
+Driver   : Arif
+Nopol  :  B 9209 NCK
+No Hp :081328851819</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: REQUEST  ORDER  ONCALL  17 FEBRUARI 2026
+2 UNIT TWB 50 CBM
+Lokasi : ARGOPANTES
+Rute / tujuan : cgk - PKU</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA 17 FEBRUARI 2026
+Nama 	: SISWANTO
+Nopol	: B 9120 WXR
+No Tlp	:081943564062</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: REQUEST  ORDER  ONCALL  17 FEBRUARI 2026
+2 UNIT TWB 50 CBM
+Lokasi : ARGOPANTES
+Rute / tujuan : cgk - MES</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA 17 FEBRUARI 2026
+Nama 	: Anto
+Nopol	: B 9285 UEX
+No Tlp	:+62 823-7722-5563</t>
+  </si>
+  <si>
+    <t>Waktu loading : 07:00 17 FEBRUARI 2026
+Nama 	 : Kudir
+Nopol	: B 9380 UEX
+No Tlp	 :+62 812-6218-9242
+Request Unit On Call Tgl 26 Feb 26
+1 Unit  Cddl / 24 Cbm
+Lokasi : Cikokol + Cikarang</t>
+  </si>
+  <si>
+    <t>Waktu loading : 03:00 27-02-26
+Rute/tujuan : CGK-JBR
+Driver   : Davit
+Nopol  : B 9726 SXW
+No Hp  :082117275166</t>
+  </si>
+  <si>
+    <t>REQUEST ORDER ULANG ONCALL
+2 UNIT TWB 50 CBM
+Lokasi : ARGOPANTES</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA
+Rute/tujuan : CGK - MES
+driver  : Kudir
+Nopol  : B 9380 UEX
+No hp  : 0812-6218-9242
+Data yg lain menyusul
+REQUER ORDER ULANG DAN TAMBAHAN ON CALL
+26 FEBUARI 2026
+2 UNIT TWB 50 CBM 
+Lokasi : ARGOPANTES
+Rute / tujuan : PKU</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA
+Nama 	: SISWANTO
+Nopol		: B 9120 WXR
+No Tlp	:081943564062
+Rute / tujuan : PKU</t>
+  </si>
+  <si>
+    <t>Waktu loading : 23:00
+Nama 	: FERI IRAWAN
+Nopol		: BK 8516 W
+No Tlp	:085219216210
+REQUER ORDER ULANG DAN TAMBAHAN ON CALL
+26 FEBUARI 2026
+2 UNIT TWB 50 CBM 
+Lokasi : ARGOPANTES
+Rute / tujuan : PLM</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA
+Nama 	: SANDRI
+Nopol		:  BE 9636 BU
+No Tlp	:+62 889-0702-0037
+REQUER ORDER ULANG DAN TAMBAHAN ON CALL
+26 FEBUARI 2026
+2 UNIT TWB 50 CBM
+ Lokasi : ARGOPANTES
+Rute / tujuan : MES</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA
+Nama 	:Hendra setiawan
+Nopol		: BE 8023 WY
+No Tlp	:081280483919
+Rute / tujuan : MES</t>
+  </si>
+  <si>
+    <t>Waktu loading : 23:00
+Nama 	: FEBRIANTO
+Nopol		: BA 9980 PS
+No Tlp	: 082286523993
+REQUER ORDER ULANG DAN TAMBAHAN ON CALL
+26 FEBUARI 2026
+Rute / tujuan : PLM</t>
+  </si>
+  <si>
+    <t>Waktu loading : 23:00
+Nama 	: M Doni saputra
+Nopol		: BD 8423 B
+No Tlp	:082164544736
+Request Order Oncall  27 Febuari 2026
+2 UNIT TWB 50 CBM
+Lokasi : JNE SURABAYA
+Rute/ Tujuan   : SUX-CGK</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA 27 Febuari 2026
+NAMA   : HABIB 
+NOPOL : L 8336 UV
+NO HP  :081231540625
+Request Order Oncall  27 Febuari 2026
+3 UNIT TWB 50 CBM
+Lokasi : ARGOPANTES
+Rute/ Tujuan   : SUB</t>
+  </si>
+  <si>
+    <t>Waktu loading : 15:00 27 Febuari 2026
+NAMA   : ARIS
+NOPOL : B 9139 SYT
+NO HP  :081936963942
+Request Order Oncall  27 Febuari 2026
+2 UNIT TWB 50 CBM
+Lokasi : JNE SURABAYA
+Rute/ Tujuan   : SUX-CGK</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA 27 Febuari 2026
+NAMA   : WAHYUDI
+NOPOL : N 9549 UA
+NO HP  : 085784422398
+REQUER ORDER ULANG DAN TAMBAHAN ON CALL
+26 FEBUARI 2026
+2 UNIT TWB 50 CBM
+Lokasi : ARGOPANTES
+Nopol : BA 9980 PS
+Rute / tujuan : MES</t>
+  </si>
+  <si>
+    <t>Waktu loading : 23:00
+Nama 	: SUPRIYANTO
+Nopol		: BE 8940 DB
+No Tlp	: 082389746001
+ORDER ONCALL 27 FEBRUARI 2026:
+1 unit Cddl 24 Cbm
+Lokasi : WangonGateway</t>
+  </si>
+  <si>
+    <t>Waktu loading : 12:00 27 FEBRUARI 2026
+Rute/tujuan : WGX-MGL-JOG
+driver  : Agung prasetyo
+Nopol  : B 9739 SEU
+No hp  :085726344824
+Request Unit On Call Tgl 27 Feb 26
+1 Unit  Cddl / 24 Cbm
+Lokasi : Cikokol + Cikarang</t>
+  </si>
+  <si>
+    <t>Waktu loading : 03:00 28-02-26
+Rute/tujuan : CGK-JBR
+Driver   : Nana Hermawan
+Nopol  : B 9658 TCP
+No Hp  : 082261270165
+Driver. : Rizki 
+No hp. : 083180623289
+REQUER ORDER ULANG DAN TAMBAHAN ON CALL
+26 FEBUARI 2026
+2 UNIT TWB 50 CBM
+Lokasi : ARGOPANTES
+Nopol : BE 8831 CJ
+Rute / tujuan : MES</t>
+  </si>
+  <si>
+    <t>Waktu loading : 23:00
+Nama 	: DIAN SAPUTRA
+Nopol		: BE 8334 GBA
+No Tlp	: 08218218481
+Request Order Oncall  27 Febuari 2026
+2 UNIT TWB 50 CBM
+Lokasi : JNE SURABAYA
+Rute/ Tujuan   : SUX-CGK</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA 27 Febuari 2026
+NAMA : AKIYAT
+NOPOL : L 9722 UE
+NO HP :081281122738
+NAMA : ROSYIT
+NOPOL : B 9562 TEU
+NO HP :082313572678
+REQUES ULANG ORDER ON CALL DAN TAMBAHAN
+27 FEBUARI 2026
+2 UNIT TWB 50 CBM 
+Lokasi : ARGOPANTES
+Rute / tujuan : SUB</t>
+  </si>
+  <si>
+    <t>Waktu loading : 23:00
+Nama 	: Yugik
+Nopol		: B 9810 UEU
+No Tlp	:085855134933
+Rute / tujuan : SUB</t>
+  </si>
+  <si>
+    <t>Waktu loading : 23:00
+Nama 	: Muatim
+Nopol		: H 9224 MA
+No Tlp	:08121615206
+Request Order Oncall  27 Febuari 2026
+3 UNIT TWB 50 CBM
+Lokasi : ARGOPANTES
+Rute/ Tujuan   : SUB</t>
+  </si>
+  <si>
+    <t>Waktu loading : 15:00 27 Febuari 2026
+NAMA   : Jamaadi
+NOPOL : L 8786 BN
+NO HP  :082229973792
+NAMA : Ibnu
+NOPOL : L 9511 AL
+NO HP :082191633212
+REQUER ORDER ULANG DAN TAMBAHAN ON CALL
+26 FEBUARI 2026
+2 UNIT TWB 50 CBM 
+Lokasi : ARGOPANTES
+Rute / tujuan : PKU</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA
+Nama 	: Yusni gunawan
+Nopol		: BE 8951 BY
+No Hp ; 085382785486</t>
+  </si>
+  <si>
+    <t>REQUEST ULANG ORDER ONCALL 28 FEBRUARI 2026:
+3 unit Cddl 24 Cbm
+Lokasi : Megahub</t>
+  </si>
+  <si>
+    <t>Waktu loading : 11:00 28 FEBRUARI 2026
+Rute/tujuan : CGK - JATIM
+driver  : Agus Supriatna 
+Nopol  :B 9546 KXX
+No hp  :081511075588
+Data yg lain menyusul</t>
+  </si>
+  <si>
+    <t>REQUEST ULANG ORDER ONCALL 28 FEBRUARI 2026:
+1 unit Cddl 24 Cbm
+Lokasi : Megahub</t>
+  </si>
+  <si>
+    <t>Waktu loading : 11:00 28 FEBRUARI 2026
+Rute/tujuan : CGK - JATIM
+driver  : Rizky / Aris
+Nopol  : B9091SCJ
+No hp  : 081646057656 / 085601390708
+REQUER ORDER ULANG DAN TAMBAHAN ON CALL
+28 FEBUARI 2026
+5 UNIT CDDL 24 CBM 
+Lokasi : ARGOPANTES
+Rute / tujuan : JATENG TENTATIF</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA
+Nama : Dedeng
+Nopol :E 9426 Aa
+No.hp : 0895393659401</t>
+  </si>
+  <si>
+    <t>REQUEST ORDER ONCALL 28 FEBRUARI 2026:
+2 unit Cddl 24 Cbm
+Lokasi : Megahub</t>
+  </si>
+  <si>
+    <t>Waktu loading : 23:00 28 FEBRUARI 2026
+Rute/tujuan : CGK - JATENG
+Nama: indra
+Nopol:B9588YM
+No hp:082295768103</t>
+  </si>
+  <si>
+    <t>REQUEST ORDER ULANG ONCALL 28/02/206
+5 UNIT TWB 50 CBM
+Lokasi : ARGOPANTES</t>
+  </si>
+  <si>
+    <t>Waktu loading : 00:00 28/02/206
+Rute/tujuan : CGK - PKU
+driver  : ARIANSYAH
+Nopol  : BE 8775 DY
+No hp  :083142572937</t>
+  </si>
+  <si>
+    <t>REQUEST ORDER ONCALL 1 Maret 2026:
+3 UNIT TWB 50 Cbm
+Lokasi : ARGOPANTES</t>
+  </si>
+  <si>
+    <t>REQUEST ORDER KHUSUS 28/02/2026</t>
+  </si>
+  <si>
+    <t>Waktu loading : 
+Rute/tujuan : CGK - MES
+driver : ARBI
+Nopol : BE 8919 AMN
+No hp :082237978236</t>
+  </si>
+  <si>
+    <t>Waktu loading : 12:00 28/02/2026
+Rute/tujuan : CGK - MES
+driver  : ANTON
+Nopol  : BE 9063 AR
+No hp  :083181833620
+REQUER ORDER ULANG DAN TAMBAHAN ON CALL
+26 FEBUARI 2026
+2 UNIT TWB 50 CBM 
+Lokasi : ARGOPANTES
+Rute / tujuan : PKU</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA
+Driver	: MUJITO
+Nopol   : BE 8837 GK
+No Hp : 081269087474</t>
+  </si>
+  <si>
+    <t>Waktu loading : 04;00
+Rute/tujuan : CGK - MES
+driver  : Jodi akbar 
+Nopol  : BE 8013 AU
+No hp  :085693461006</t>
+  </si>
+  <si>
+    <t>Waktu loading : 04;00
+Rute/tujuan : CGK - MES
+driver  : Jodi akbar 
+Nopol  : BE 8013 AU
+No hp  : 085693461007</t>
+  </si>
+  <si>
+    <t>REQUEST ORDER ONCALL 1 Maret 2026:</t>
+  </si>
+  <si>
+    <t>REQUEST ORDER ONCALL 03 maret 2026:
+1 unit Cddl 24 Cbm
+Lokasi : Megahub</t>
+  </si>
+  <si>
+    <t>Waktu loading : 15:00 03 maret 2026
+Rute/tujuan : CGK - DPS
+driver  :Arizal
+Nopol  :B 9895 UXX
+No hp  :081229080317</t>
+  </si>
+  <si>
+    <t>REQUEST  ORDER  ONCALL  3 MARET 2026
+5 UNIT WB/50 CBM
+Lokasi : ARGOPANTES</t>
+  </si>
+  <si>
+    <t>Waktu loading : 23:00 3 MARET 2026
+Rute/tujuan : CGK - MES 
+driver  : SAMOSIR
+Nopol  : B 9727 UEX
+No hp  :+62 822-7429-6236</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA 3 MARET 2026
+Rute/tujuan : CGK - PKU
+driver  : Soni Rahmat
+Nopol  : BM 8142 RY
+No hp  : 082282001964</t>
+  </si>
+  <si>
+    <t>Waktu loading : 15;00 3 MARET 2026
+Rute/tujuan : CGK - PKU
+driver  :
+Nopol  :
+No hp  :</t>
+  </si>
+  <si>
+    <t>Waktu loading : 20:00 3 MARET 2026
+Rute/tujuan : CGK - PKU
+driver  :
+Nopol  :
+No hp  :</t>
+  </si>
+  <si>
+    <t>Waktu loading : 02:00 04-03-2026
+Rute/tujuan : CGK - PKU 
+driver  :
+Nopol  :
+No hp  :</t>
+  </si>
+  <si>
+    <t>Waktu loading : 07:00 04-03-2026
+Rute/tujuan : CGK - PKU 
+driver  :
+Nopol  :
+No hp  :
+Request Unit On Call Tgl 03 Mar 26
+1 Unit  Cddl / 24 Cbm
+Lokasi : Cikarang</t>
+  </si>
+  <si>
+    <t>Waktu loading : 06:00 04 Mar 26
+Rute/tujuan : CKR-JBR
+Driver   : Nana hermawan
+Nopol  : B 9658 TCP
+No Hp  :082261270165
+Request Unit On Call *Tgl 03 Mar 26
+1 Unit  Cddl / 24 Cbm
+Lokasi : Cikarang</t>
+  </si>
+  <si>
+    <t>Waktu loading : 06:00 04 Mar 26
+Rute/tujuan : CKR-MXG
+Driver   : Davit
+Nopol  : B 9726 SXW
+No Hp  :082117275166</t>
+  </si>
+  <si>
+    <t>Waktu loading : 23:00 3 MARET 2026
+Rute/tujuan : CGK - MES 
+ddriver  : Sri Mardono
+Nopol  : BK 8678 VE
+No hp  : 085218843366</t>
+  </si>
+  <si>
+    <t>Waktu loading : 03:00 04-03-2026
+Rute/tujuan : CGK - MES 
+driver  :
+Nopol  :
+No hp  :</t>
+  </si>
+  <si>
+    <t>REQUEST  ORDER  ONCALL  3 MARET 2026
+6 UNIT WB/50 CBM
+Lokasi : ARGOPANTES</t>
+  </si>
+  <si>
+    <t>Waktu loading : 23:00 3 MARET 2026
+Rute/tujuan : CGK - SUB 
+driver  : Rosyit
+Nopol  : B 9562 TEU
+No hp  : 082313572678
+Driver : sofyan
+Nopol : B 9679WT
+No Hp : 082231837381</t>
+  </si>
+  <si>
+    <t>REQUEST  ORDER  ONCALL  3 MARET 2026
+1 UNIT WB/50 CBM
+Lokasi : ARGOPANTES</t>
+  </si>
+  <si>
+    <t>Waktu loading : 23:00 3 MARET 2026
+Rute/tujuan : SUB - CGK
+driver  : Yuda
+Nopol  : W 8973 UQ
+No hp  : 089507296985</t>
+  </si>
+  <si>
+    <t>REQUEST ORDER ONCALL 03 maret 2026:
+3 unit Cddl 24 Cbm
+Lokasi : Megahub</t>
+  </si>
+  <si>
+    <t>Waktu loading : 23:00 03 maret 2026
+Rute/tujuan : CGK - JATIM
+driver  : Ari purnama
+Nopol  : B 9383 TXV
+No hp : 082136689169
+Fyi pak  @Nomor tidak dikenal@Nomor tidak dikenal</t>
+  </si>
+  <si>
+    <t>REQUEST ULANG ORDER ONCALL 04 MARET 2026:
+8 unit Cddl 24 Cbm
+Lokasi : *argo pantes *</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA 04 MARET 2026
+Rute/tujuan : *CGK - Jateng tentatif
+Nama : Dedeng
+Nopol :E 9426 Aa
+No.hp : 0895393659401
+Request Unit On Call Tgl 04 Maret 2026
+5 UNIT TWB 50 CBM
+Lokasi : ARGOPANTES</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA 04 Maret 2026
+Rute/tujuan : CGK - PKU
+driver  : Jupri
+Nopol  : BM 9273 RO
+No Hp :082172471454</t>
+  </si>
+  <si>
+    <t>REQUEST ORDER ONCALL
+04 MARET 2026:
+5 UNIT TWB 50 CBM
+Lokasi : ARGOPANTES</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA
+Rute/tujuan : CGK - MES
+driver  : Andi
+Nopol  : BE 8610 DB
+No Hp :081374328877</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA
+Rute/tujuan : CGK - MES
+driver  : Misno
+Nopol  : BN 8038 RP
+No Hp :082211762649</t>
+  </si>
+  <si>
+    <t>REQUEST ORDER ONCALL
+04 MARET 2026:
+5 UNIT TWB 50 CBM
+Lokasi : ARGOPANTES</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA
+Rute/tujuan : CGK - MES
+driver  : Usman Afandi
+Nopol  : BE 8456 FN
+No Hp : +62 853-7337-2594
+Request Order Oncall  04 Mar 2026
+2 UNIT TWB 50 CBM
+Lokasi : JNE SURABAYA
+Rute/ Tujuan   : SUX-CGK</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA 04 Mar 2026
+NAMA   : Wahyudi
+NOPOL : N 9549 UA
+NO HP : 085784422398
+Request Unit On Call Tgl 05 Mar 26
+1 Unit  Cddl / 24 Cbm
+Lokasi : Cikarang</t>
+  </si>
+  <si>
+    <t>Waktu loading : 06:00 06 Mar 26
+Rute/tujuan : CKR-JBR
+Driver   : miyanta
+Nopol  : F 9647 FH
+No Hp  :08118558105
+Request Unit On Call Tgl 05 Mar 26
+RAFAY
+1 Unit  Cddl / 24 Cbm
+Lokasi : Cikokol + Cikarang</t>
+  </si>
+  <si>
+    <t>Waktu loading : 03:00 06  Mar 26
+Rute/tujuan : CGK-PSR
+Driver   : Davit
+Nopol  : B 9726 SXW
+No Hp  :082117275166</t>
+  </si>
+  <si>
+    <t>REQUEST ORDER ONCALL
+05 MARET 2026:
+5 UNIT TWB 50 CBM
+Lokasi : ARGOPANTES</t>
+  </si>
+  <si>
+    <t>Waktu loading : 17:00 05-03-2026
+Rute/tujuan : CGK - SUB
+driver  : Iwan Hariono
+Nopol  : BL 8188 JP
+No Hp :081389976421
+Request Order Oncall  05 Maret  2026
+2 UNIT TWB 50 CBM
+Lokasi : JNE SURABAYA
+Rute/ Tujuan   : SUX-CGK</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA 05 Maret  2026
+Driver : Akiyat
+Nopol : L 9722 UE
+No HP :081281122738
+REQUER ORDER ULANG DAN TAMBAHAN ON CALL
+06 MARET 2026
+3 UNIT TWB 50 CBM
+Lokasi : ARGOPANTES
+Rute / tujuan : *JATim TENTATIF</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA
+Nama 	: M. Ibnu
+Nopol   : L 9511 AL
+No Tlp	:082191633212
+Nama : Jamaadi
+Nopol : L 8786 BN
+No Hp :082229973792
+Nama : Suryadi 
+Nopol : L 8183UV
+No hp :085729113217
+REQUER ORDER ULANG DAN TAMBAHAN ON CALL
+06 MARET 2026
+3 UNIT TWB 50 CBM
+Lokasi : ARGOPANTES
+Rute / tujuan : CGK-SUB</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA
+Nama 	: Yuda
+Nopol	: W 8973 UQ
+No Tlp	:089507296985
+REQUER ORDER ULANG DAN TAMBAHAN ON CALL
+06 MARET 2026
+DATA SUMATERA
+2 UNIT TWB 50 CBM
+ Lokasi : ARGOPANTES
+Rute / tujuan : PKU</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA
+Nama 	: Ridwan
+Nopol		: BK 8330 VY
+No Tlp	: 082382200400
+Fyi pak @â¨Sobar JNEâ© data tambahan nya
+REQUER ORDER ULANG DAN TAMBAHAN ON CALL
+06 MARET 2026
+DATA SUMATERA
+2 UNIT TWB 50 CBM
+Lokasi : ARGOPANTES
+Rute / tujuan : PKU</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA
+Nama 	: Nasip
+Nopol	: BH 8165 QI
+No Tlp	:+6281272463920
+REQUER ORDER ULANG DAN TAMBAHAN ON CALL
+06 MARET 2026
+3 UNIT TWB 50 CBM
+ Lokasi : ARGOPANTES
+Rute / tujuan : CGK-SUB</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA
+Nama 	: Wahyudi
+Nopol		: N 9549 UA
+No Tlp	:085784422398
+5 UNIT TWB 50 CBM
+Lokasi : ARGOPANTES</t>
+  </si>
+  <si>
+    <t>Waktu loading : 18:00 05-02-2026
+Rute/tujuan : CGK - PKU
+driver  : Syarial
+Nopol  :BM 8486 AU
+No Hp :081317708658</t>
+  </si>
+  <si>
+    <t>085353886066</t>
+  </si>
+  <si>
+    <t>085865762797</t>
+  </si>
+  <si>
+    <t>0 81231895971</t>
+  </si>
+  <si>
+    <t>0 87886861780</t>
+  </si>
+  <si>
+    <t>08817021866</t>
+  </si>
+  <si>
+    <t>082118558105</t>
+  </si>
+  <si>
+    <t>081943564062</t>
+  </si>
+  <si>
+    <t>085219216210</t>
+  </si>
+  <si>
+    <t>083169525183</t>
+  </si>
+  <si>
+    <t>081281122738</t>
+  </si>
+  <si>
+    <t>087837496810</t>
+  </si>
+  <si>
+    <t>0 87786676177</t>
+  </si>
+  <si>
     <t>085971812879</t>
+  </si>
+  <si>
+    <t>082191633212</t>
+  </si>
+  <si>
+    <t>085784422398</t>
+  </si>
+  <si>
+    <t>082231837381</t>
+  </si>
+  <si>
+    <t>07022026</t>
+  </si>
+  <si>
+    <t>0 85231681470</t>
+  </si>
+  <si>
+    <t>0 85707380584</t>
+  </si>
+  <si>
+    <t>089519041791</t>
+  </si>
+  <si>
+    <t>085218843366</t>
+  </si>
+  <si>
+    <t>082313572678</t>
+  </si>
+  <si>
+    <t>082217785226</t>
+  </si>
+  <si>
+    <t>087844510846</t>
+  </si>
+  <si>
+    <t>81382418508</t>
+  </si>
+  <si>
+    <t>082183783385</t>
+  </si>
+  <si>
+    <t>085758955627</t>
+  </si>
+  <si>
+    <t>0 81269345748</t>
+  </si>
+  <si>
+    <t>08889693664</t>
+  </si>
+  <si>
+    <t>085364056583</t>
+  </si>
+  <si>
+    <t>085225394209</t>
+  </si>
+  <si>
+    <t>082385989323</t>
+  </si>
+  <si>
+    <t>0 82228516922</t>
+  </si>
+  <si>
+    <t>081382418508</t>
+  </si>
+  <si>
+    <t>088290294126</t>
+  </si>
+  <si>
+    <t>088212698834</t>
+  </si>
+  <si>
+    <t>081328851819</t>
+  </si>
+  <si>
+    <t>0 82377225563</t>
+  </si>
+  <si>
+    <t>0 81262189242</t>
+  </si>
+  <si>
+    <t>082117275166</t>
+  </si>
+  <si>
+    <t>081262189242</t>
+  </si>
+  <si>
+    <t>0 88907020037</t>
+  </si>
+  <si>
+    <t>081280483919</t>
+  </si>
+  <si>
+    <t>082286523993</t>
+  </si>
+  <si>
+    <t>082164544736</t>
+  </si>
+  <si>
+    <t>081231540625</t>
+  </si>
+  <si>
+    <t>081936963942</t>
+  </si>
+  <si>
+    <t>082389746001</t>
+  </si>
+  <si>
+    <t>085726344824</t>
+  </si>
+  <si>
+    <t>083180623289</t>
+  </si>
+  <si>
+    <t>08218218481</t>
+  </si>
+  <si>
+    <t>085855134933</t>
+  </si>
+  <si>
+    <t>08121615206</t>
+  </si>
+  <si>
+    <t>085382785486</t>
+  </si>
+  <si>
+    <t>081511075588</t>
+  </si>
+  <si>
+    <t>085601390708</t>
+  </si>
+  <si>
+    <t>0895393659401</t>
+  </si>
+  <si>
+    <t>082295768103</t>
+  </si>
+  <si>
+    <t>083142572937</t>
+  </si>
+  <si>
+    <t>082237978236</t>
+  </si>
+  <si>
+    <t>083181833620</t>
+  </si>
+  <si>
+    <t>081269087474</t>
+  </si>
+  <si>
+    <t>085693461006</t>
+  </si>
+  <si>
+    <t>085693461007</t>
+  </si>
+  <si>
+    <t>081229080317</t>
+  </si>
+  <si>
+    <t>0 82274296236</t>
+  </si>
+  <si>
+    <t>082282001964</t>
+  </si>
+  <si>
+    <t>082261270165</t>
+  </si>
+  <si>
+    <t>089507296985</t>
+  </si>
+  <si>
+    <t>082136689169</t>
+  </si>
+  <si>
+    <t>082172471454</t>
+  </si>
+  <si>
+    <t>081374328877</t>
+  </si>
+  <si>
+    <t>082211762649</t>
+  </si>
+  <si>
+    <t>0 85373372594</t>
+  </si>
+  <si>
+    <t>08118558105</t>
+  </si>
+  <si>
+    <t>081389976421</t>
+  </si>
+  <si>
+    <t>085729113217</t>
+  </si>
+  <si>
+    <t>082382200400</t>
+  </si>
+  <si>
+    <t>081272463920</t>
+  </si>
+  <si>
+    <t>081317708658</t>
   </si>
 </sst>
 </file>
@@ -443,10 +2678,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:J202"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -474,48 +2709,3884 @@
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
+    </row>
+    <row r="2" spans="1:10">
       <c r="B2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D2" t="s">
+        <v>70</v>
+      </c>
+      <c r="I2" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="E3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F3" t="s">
+        <v>107</v>
+      </c>
+      <c r="G3" t="s">
+        <v>187</v>
+      </c>
+      <c r="H3" t="s">
+        <v>266</v>
+      </c>
+      <c r="I3" t="s">
+        <v>275</v>
+      </c>
+      <c r="J3" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D4" t="s">
+        <v>71</v>
+      </c>
+      <c r="I4" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" t="s">
         <v>11</v>
       </c>
-      <c r="C2" t="s">
+      <c r="I5" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="E6" t="s">
+        <v>81</v>
+      </c>
+      <c r="F6" t="s">
+        <v>108</v>
+      </c>
+      <c r="G6" t="s">
+        <v>188</v>
+      </c>
+      <c r="H6" t="s">
+        <v>267</v>
+      </c>
+      <c r="I6" t="s">
+        <v>278</v>
+      </c>
+      <c r="J6" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="B7" t="s">
+        <v>58</v>
+      </c>
+      <c r="C7" t="s">
+        <v>63</v>
+      </c>
+      <c r="D7" t="s">
+        <v>70</v>
+      </c>
+      <c r="I7" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="E8" t="s">
+        <v>73</v>
+      </c>
+      <c r="H8" t="s">
+        <v>266</v>
+      </c>
+      <c r="I8" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="E9" t="s">
+        <v>73</v>
+      </c>
+      <c r="F9" t="s">
+        <v>109</v>
+      </c>
+      <c r="G9" t="s">
+        <v>189</v>
+      </c>
+      <c r="H9" t="s">
+        <v>268</v>
+      </c>
+      <c r="I9" t="s">
+        <v>281</v>
+      </c>
+      <c r="J9" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="E10" t="s">
+        <v>73</v>
+      </c>
+      <c r="H10" t="s">
+        <v>269</v>
+      </c>
+      <c r="I10" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="E11" t="s">
+        <v>73</v>
+      </c>
+      <c r="I11" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" t="s">
+        <v>11</v>
+      </c>
+      <c r="I12" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="E13" t="s">
+        <v>73</v>
+      </c>
+      <c r="F13" t="s">
+        <v>110</v>
+      </c>
+      <c r="G13" t="s">
+        <v>190</v>
+      </c>
+      <c r="H13" t="s">
+        <v>270</v>
+      </c>
+      <c r="I13" t="s">
+        <v>284</v>
+      </c>
+      <c r="J13" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B14" t="s">
+        <v>59</v>
+      </c>
+      <c r="C14" t="s">
+        <v>63</v>
+      </c>
+      <c r="D14" t="s">
+        <v>72</v>
+      </c>
+      <c r="I14" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D15" t="s">
+        <v>73</v>
+      </c>
+      <c r="F15" t="s">
+        <v>111</v>
+      </c>
+      <c r="G15" t="s">
+        <v>191</v>
+      </c>
+      <c r="H15" t="s">
+        <v>266</v>
+      </c>
+      <c r="I15" t="s">
+        <v>286</v>
+      </c>
+      <c r="J15" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" t="s">
+        <v>10</v>
+      </c>
+      <c r="B16" t="s">
+        <v>56</v>
+      </c>
+      <c r="C16" t="s">
+        <v>64</v>
+      </c>
+      <c r="D16" t="s">
+        <v>71</v>
+      </c>
+      <c r="I16" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="A17" t="s">
+        <v>10</v>
+      </c>
+      <c r="E17" t="s">
+        <v>82</v>
+      </c>
+      <c r="F17" t="s">
+        <v>112</v>
+      </c>
+      <c r="G17" t="s">
+        <v>192</v>
+      </c>
+      <c r="I17" t="s">
+        <v>288</v>
+      </c>
+      <c r="J17" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="A18" t="s">
         <v>12</v>
       </c>
-      <c r="D2" t="s">
+      <c r="B18" t="s">
+        <v>59</v>
+      </c>
+      <c r="C18" t="s">
+        <v>63</v>
+      </c>
+      <c r="D18" t="s">
+        <v>72</v>
+      </c>
+      <c r="I18" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
+      <c r="A19" t="s">
+        <v>12</v>
+      </c>
+      <c r="B19" t="s">
+        <v>59</v>
+      </c>
+      <c r="C19" t="s">
+        <v>63</v>
+      </c>
+      <c r="D19" t="s">
+        <v>72</v>
+      </c>
+      <c r="H19" t="s">
+        <v>266</v>
+      </c>
+      <c r="I19" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="A20" t="s">
+        <v>12</v>
+      </c>
+      <c r="B20" t="s">
+        <v>59</v>
+      </c>
+      <c r="C20" t="s">
+        <v>63</v>
+      </c>
+      <c r="D20" t="s">
+        <v>72</v>
+      </c>
+      <c r="E20" t="s">
+        <v>83</v>
+      </c>
+      <c r="H20" t="s">
+        <v>266</v>
+      </c>
+      <c r="I20" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="A21" t="s">
+        <v>12</v>
+      </c>
+      <c r="E21" t="s">
+        <v>72</v>
+      </c>
+      <c r="F21" t="s">
+        <v>113</v>
+      </c>
+      <c r="G21" t="s">
+        <v>193</v>
+      </c>
+      <c r="H21" t="s">
+        <v>266</v>
+      </c>
+      <c r="I21" t="s">
+        <v>292</v>
+      </c>
+      <c r="J21" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
+      <c r="A22" t="s">
+        <v>12</v>
+      </c>
+      <c r="B22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C22" t="s">
+        <v>63</v>
+      </c>
+      <c r="D22" t="s">
+        <v>72</v>
+      </c>
+      <c r="E22" t="s">
+        <v>84</v>
+      </c>
+      <c r="H22" t="s">
+        <v>266</v>
+      </c>
+      <c r="I22" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
+      <c r="A23" t="s">
+        <v>12</v>
+      </c>
+      <c r="E23" t="s">
+        <v>85</v>
+      </c>
+      <c r="F23" t="s">
+        <v>114</v>
+      </c>
+      <c r="G23" t="s">
+        <v>194</v>
+      </c>
+      <c r="H23" t="s">
+        <v>266</v>
+      </c>
+      <c r="I23" t="s">
+        <v>294</v>
+      </c>
+      <c r="J23" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
+      <c r="A24" t="s">
+        <v>12</v>
+      </c>
+      <c r="B24" t="s">
+        <v>59</v>
+      </c>
+      <c r="C24" t="s">
+        <v>63</v>
+      </c>
+      <c r="D24" t="s">
+        <v>72</v>
+      </c>
+      <c r="I24" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
+      <c r="A25" t="s">
+        <v>12</v>
+      </c>
+      <c r="E25" t="s">
+        <v>85</v>
+      </c>
+      <c r="F25" t="s">
+        <v>115</v>
+      </c>
+      <c r="G25" t="s">
+        <v>195</v>
+      </c>
+      <c r="H25" t="s">
+        <v>266</v>
+      </c>
+      <c r="I25" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
+      <c r="A26" t="s">
+        <v>12</v>
+      </c>
+      <c r="B26" t="s">
+        <v>59</v>
+      </c>
+      <c r="C26" t="s">
+        <v>63</v>
+      </c>
+      <c r="D26" t="s">
+        <v>72</v>
+      </c>
+      <c r="I26" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
+      <c r="A27" t="s">
+        <v>12</v>
+      </c>
+      <c r="E27" t="s">
+        <v>85</v>
+      </c>
+      <c r="F27" t="s">
+        <v>116</v>
+      </c>
+      <c r="G27" t="s">
+        <v>196</v>
+      </c>
+      <c r="H27" t="s">
+        <v>266</v>
+      </c>
+      <c r="I27" t="s">
+        <v>297</v>
+      </c>
+      <c r="J27" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10">
+      <c r="B28" t="s">
+        <v>58</v>
+      </c>
+      <c r="C28" t="s">
+        <v>63</v>
+      </c>
+      <c r="D28" t="s">
+        <v>70</v>
+      </c>
+      <c r="I28" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10">
+      <c r="E29" t="s">
+        <v>86</v>
+      </c>
+      <c r="F29" t="s">
+        <v>117</v>
+      </c>
+      <c r="G29" t="s">
+        <v>197</v>
+      </c>
+      <c r="H29" t="s">
+        <v>266</v>
+      </c>
+      <c r="I29" t="s">
+        <v>298</v>
+      </c>
+      <c r="J29" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
+      <c r="A30" t="s">
         <v>13</v>
       </c>
-      <c r="E2" t="s">
+      <c r="B30" t="s">
+        <v>59</v>
+      </c>
+      <c r="C30" t="s">
+        <v>63</v>
+      </c>
+      <c r="D30" t="s">
+        <v>72</v>
+      </c>
+      <c r="I30" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10">
+      <c r="A31" t="s">
+        <v>13</v>
+      </c>
+      <c r="E31" t="s">
+        <v>84</v>
+      </c>
+      <c r="F31" t="s">
+        <v>118</v>
+      </c>
+      <c r="G31" t="s">
+        <v>198</v>
+      </c>
+      <c r="H31" t="s">
+        <v>266</v>
+      </c>
+      <c r="I31" t="s">
+        <v>300</v>
+      </c>
+      <c r="J31" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10">
+      <c r="B32" t="s">
+        <v>58</v>
+      </c>
+      <c r="C32" t="s">
+        <v>63</v>
+      </c>
+      <c r="D32" t="s">
+        <v>70</v>
+      </c>
+      <c r="I32" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10">
+      <c r="E33" t="s">
+        <v>73</v>
+      </c>
+      <c r="F33" t="s">
+        <v>119</v>
+      </c>
+      <c r="G33" t="s">
+        <v>199</v>
+      </c>
+      <c r="H33" t="s">
+        <v>266</v>
+      </c>
+      <c r="I33" t="s">
+        <v>301</v>
+      </c>
+      <c r="J33" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10">
+      <c r="E34" t="s">
+        <v>73</v>
+      </c>
+      <c r="H34" t="s">
+        <v>268</v>
+      </c>
+      <c r="I34" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10">
+      <c r="E35" t="s">
+        <v>73</v>
+      </c>
+      <c r="H35" t="s">
+        <v>269</v>
+      </c>
+      <c r="I35" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10">
+      <c r="E36" t="s">
+        <v>73</v>
+      </c>
+      <c r="I36" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10">
+      <c r="A37" t="s">
+        <v>14</v>
+      </c>
+      <c r="I37" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10">
+      <c r="E38" t="s">
+        <v>73</v>
+      </c>
+      <c r="H38" t="s">
+        <v>270</v>
+      </c>
+      <c r="I38" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10">
+      <c r="A39" t="s">
+        <v>12</v>
+      </c>
+      <c r="B39" t="s">
+        <v>59</v>
+      </c>
+      <c r="C39" t="s">
+        <v>63</v>
+      </c>
+      <c r="D39" t="s">
+        <v>72</v>
+      </c>
+      <c r="I39" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10">
+      <c r="A40" t="s">
+        <v>12</v>
+      </c>
+      <c r="E40" t="s">
+        <v>83</v>
+      </c>
+      <c r="F40" t="s">
+        <v>120</v>
+      </c>
+      <c r="G40" t="s">
+        <v>195</v>
+      </c>
+      <c r="H40" t="s">
+        <v>266</v>
+      </c>
+      <c r="I40" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10">
+      <c r="A41" t="s">
         <v>15</v>
       </c>
-      <c r="F2" t="s">
+      <c r="B41" t="s">
+        <v>59</v>
+      </c>
+      <c r="C41" t="s">
+        <v>64</v>
+      </c>
+      <c r="D41" t="s">
+        <v>74</v>
+      </c>
+      <c r="E41" t="s">
+        <v>61</v>
+      </c>
+      <c r="F41" t="s">
+        <v>121</v>
+      </c>
+      <c r="I41" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10">
+      <c r="A42" t="s">
         <v>16</v>
       </c>
-      <c r="H2" t="s">
+      <c r="B42" t="s">
+        <v>56</v>
+      </c>
+      <c r="C42" t="s">
+        <v>64</v>
+      </c>
+      <c r="D42" t="s">
+        <v>75</v>
+      </c>
+      <c r="E42" t="s">
+        <v>74</v>
+      </c>
+      <c r="I42" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10">
+      <c r="A43" t="s">
+        <v>17</v>
+      </c>
+      <c r="D43" t="s">
+        <v>75</v>
+      </c>
+      <c r="F43" t="s">
+        <v>122</v>
+      </c>
+      <c r="G43" t="s">
+        <v>200</v>
+      </c>
+      <c r="I43" t="s">
+        <v>308</v>
+      </c>
+      <c r="J43" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10">
+      <c r="A44" t="s">
+        <v>18</v>
+      </c>
+      <c r="B44" t="s">
+        <v>57</v>
+      </c>
+      <c r="C44" t="s">
+        <v>63</v>
+      </c>
+      <c r="D44" t="s">
+        <v>70</v>
+      </c>
+      <c r="F44" t="s">
+        <v>121</v>
+      </c>
+      <c r="I44" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10">
+      <c r="A45" t="s">
+        <v>18</v>
+      </c>
+      <c r="E45" t="s">
+        <v>87</v>
+      </c>
+      <c r="F45" t="s">
+        <v>123</v>
+      </c>
+      <c r="G45" t="s">
+        <v>201</v>
+      </c>
+      <c r="H45" t="s">
+        <v>266</v>
+      </c>
+      <c r="I45" t="s">
+        <v>310</v>
+      </c>
+      <c r="J45" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10">
+      <c r="A46" t="s">
+        <v>18</v>
+      </c>
+      <c r="B46" t="s">
+        <v>59</v>
+      </c>
+      <c r="C46" t="s">
+        <v>63</v>
+      </c>
+      <c r="D46" t="s">
+        <v>76</v>
+      </c>
+      <c r="F46" t="s">
+        <v>121</v>
+      </c>
+      <c r="I46" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10">
+      <c r="A47" t="s">
+        <v>18</v>
+      </c>
+      <c r="E47" t="s">
+        <v>88</v>
+      </c>
+      <c r="F47" t="s">
+        <v>124</v>
+      </c>
+      <c r="G47" t="s">
+        <v>202</v>
+      </c>
+      <c r="I47" t="s">
+        <v>312</v>
+      </c>
+      <c r="J47" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10">
+      <c r="A48" t="s">
+        <v>18</v>
+      </c>
+      <c r="B48" t="s">
+        <v>59</v>
+      </c>
+      <c r="C48" t="s">
+        <v>63</v>
+      </c>
+      <c r="D48" t="s">
+        <v>76</v>
+      </c>
+      <c r="F48" t="s">
+        <v>121</v>
+      </c>
+      <c r="I48" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10">
+      <c r="A49" t="s">
+        <v>18</v>
+      </c>
+      <c r="E49" t="s">
+        <v>88</v>
+      </c>
+      <c r="F49" t="s">
+        <v>125</v>
+      </c>
+      <c r="G49" t="s">
+        <v>203</v>
+      </c>
+      <c r="H49" t="s">
+        <v>266</v>
+      </c>
+      <c r="I49" t="s">
+        <v>313</v>
+      </c>
+      <c r="J49" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10">
+      <c r="A50" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="3" spans="1:9">
-      <c r="A3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G3" t="s">
-        <v>18</v>
-      </c>
-      <c r="H3" t="s">
+      <c r="B50" t="s">
+        <v>60</v>
+      </c>
+      <c r="C50" t="s">
+        <v>65</v>
+      </c>
+      <c r="D50" t="s">
+        <v>70</v>
+      </c>
+      <c r="I50" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10">
+      <c r="I51" t="s">
+        <v>315</v>
+      </c>
+      <c r="J51" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10">
+      <c r="E52" t="s">
+        <v>73</v>
+      </c>
+      <c r="F52" t="s">
+        <v>126</v>
+      </c>
+      <c r="G52" t="s">
+        <v>204</v>
+      </c>
+      <c r="H52" t="s">
+        <v>267</v>
+      </c>
+      <c r="I52" t="s">
+        <v>316</v>
+      </c>
+      <c r="J52" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10">
+      <c r="A53" t="s">
+        <v>19</v>
+      </c>
+      <c r="B53" t="s">
+        <v>61</v>
+      </c>
+      <c r="C53" t="s">
+        <v>64</v>
+      </c>
+      <c r="D53" t="s">
+        <v>70</v>
+      </c>
+      <c r="I53" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10">
+      <c r="E54" t="s">
+        <v>89</v>
+      </c>
+      <c r="H54" t="s">
+        <v>266</v>
+      </c>
+      <c r="I54" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10">
+      <c r="A55" t="s">
         <v>20</v>
       </c>
-      <c r="I3" t="s">
+      <c r="B55" t="s">
+        <v>56</v>
+      </c>
+      <c r="C55" t="s">
+        <v>63</v>
+      </c>
+      <c r="D55" t="s">
+        <v>74</v>
+      </c>
+      <c r="F55" t="s">
+        <v>121</v>
+      </c>
+      <c r="I55" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10">
+      <c r="A56" t="s">
+        <v>20</v>
+      </c>
+      <c r="E56" t="s">
+        <v>90</v>
+      </c>
+      <c r="F56" t="s">
+        <v>127</v>
+      </c>
+      <c r="G56" t="s">
+        <v>205</v>
+      </c>
+      <c r="H56" t="s">
+        <v>266</v>
+      </c>
+      <c r="I56" t="s">
+        <v>320</v>
+      </c>
+      <c r="J56" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10">
+      <c r="A57" t="s">
+        <v>20</v>
+      </c>
+      <c r="B57" t="s">
+        <v>56</v>
+      </c>
+      <c r="C57" t="s">
+        <v>64</v>
+      </c>
+      <c r="E57" t="s">
+        <v>74</v>
+      </c>
+      <c r="F57" t="s">
+        <v>121</v>
+      </c>
+      <c r="I57" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10">
+      <c r="A58" t="s">
         <v>21</v>
+      </c>
+      <c r="E58" t="s">
+        <v>91</v>
+      </c>
+      <c r="F58" t="s">
+        <v>128</v>
+      </c>
+      <c r="G58" t="s">
+        <v>192</v>
+      </c>
+      <c r="I58" t="s">
+        <v>322</v>
+      </c>
+      <c r="J58" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10">
+      <c r="A59" t="s">
+        <v>22</v>
+      </c>
+      <c r="B59" t="s">
+        <v>57</v>
+      </c>
+      <c r="D59" t="s">
+        <v>72</v>
+      </c>
+      <c r="I59" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10">
+      <c r="A60" t="s">
+        <v>22</v>
+      </c>
+      <c r="E60" t="s">
+        <v>85</v>
+      </c>
+      <c r="F60" t="s">
+        <v>129</v>
+      </c>
+      <c r="G60" t="s">
+        <v>206</v>
+      </c>
+      <c r="H60" t="s">
+        <v>266</v>
+      </c>
+      <c r="I60" t="s">
+        <v>324</v>
+      </c>
+      <c r="J60" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10">
+      <c r="A61" t="s">
+        <v>22</v>
+      </c>
+      <c r="B61" t="s">
+        <v>62</v>
+      </c>
+      <c r="C61" t="s">
+        <v>66</v>
+      </c>
+      <c r="D61" t="s">
+        <v>72</v>
+      </c>
+      <c r="I61" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10">
+      <c r="A62" t="s">
+        <v>22</v>
+      </c>
+      <c r="E62" t="s">
+        <v>73</v>
+      </c>
+      <c r="F62" t="s">
+        <v>127</v>
+      </c>
+      <c r="G62" t="s">
+        <v>195</v>
+      </c>
+      <c r="H62" t="s">
+        <v>266</v>
+      </c>
+      <c r="I62" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10">
+      <c r="A63" t="s">
+        <v>22</v>
+      </c>
+      <c r="B63" t="s">
+        <v>57</v>
+      </c>
+      <c r="C63" t="s">
+        <v>63</v>
+      </c>
+      <c r="D63" t="s">
+        <v>70</v>
+      </c>
+      <c r="I63" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10">
+      <c r="A64" t="s">
+        <v>22</v>
+      </c>
+      <c r="E64" t="s">
+        <v>73</v>
+      </c>
+      <c r="F64" t="s">
+        <v>130</v>
+      </c>
+      <c r="G64" t="s">
+        <v>207</v>
+      </c>
+      <c r="H64" t="s">
+        <v>266</v>
+      </c>
+      <c r="I64" t="s">
+        <v>328</v>
+      </c>
+      <c r="J64" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10">
+      <c r="A65" t="s">
+        <v>22</v>
+      </c>
+      <c r="E65" t="s">
+        <v>73</v>
+      </c>
+      <c r="F65" t="s">
+        <v>123</v>
+      </c>
+      <c r="G65" t="s">
+        <v>201</v>
+      </c>
+      <c r="H65" t="s">
+        <v>266</v>
+      </c>
+      <c r="I65" t="s">
+        <v>329</v>
+      </c>
+      <c r="J65" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10">
+      <c r="A66" t="s">
+        <v>22</v>
+      </c>
+      <c r="E66" t="s">
+        <v>73</v>
+      </c>
+      <c r="F66" t="s">
+        <v>117</v>
+      </c>
+      <c r="G66" t="s">
+        <v>197</v>
+      </c>
+      <c r="I66" t="s">
+        <v>330</v>
+      </c>
+      <c r="J66" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10">
+      <c r="A67" t="s">
+        <v>22</v>
+      </c>
+      <c r="B67" t="s">
+        <v>57</v>
+      </c>
+      <c r="C67" t="s">
+        <v>63</v>
+      </c>
+      <c r="D67" t="s">
+        <v>70</v>
+      </c>
+      <c r="I67" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10">
+      <c r="A68" t="s">
+        <v>22</v>
+      </c>
+      <c r="E68" t="s">
+        <v>73</v>
+      </c>
+      <c r="F68" t="s">
+        <v>130</v>
+      </c>
+      <c r="G68" t="s">
+        <v>207</v>
+      </c>
+      <c r="H68" t="s">
+        <v>266</v>
+      </c>
+      <c r="I68" t="s">
+        <v>328</v>
+      </c>
+      <c r="J68" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10">
+      <c r="A69" t="s">
+        <v>22</v>
+      </c>
+      <c r="E69" t="s">
+        <v>73</v>
+      </c>
+      <c r="F69" t="s">
+        <v>123</v>
+      </c>
+      <c r="G69" t="s">
+        <v>201</v>
+      </c>
+      <c r="H69" t="s">
+        <v>266</v>
+      </c>
+      <c r="I69" t="s">
+        <v>329</v>
+      </c>
+      <c r="J69" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10">
+      <c r="A70" t="s">
+        <v>22</v>
+      </c>
+      <c r="E70" t="s">
+        <v>73</v>
+      </c>
+      <c r="I70" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10">
+      <c r="B71" t="s">
+        <v>61</v>
+      </c>
+      <c r="C71" t="s">
+        <v>64</v>
+      </c>
+      <c r="D71" t="s">
+        <v>72</v>
+      </c>
+      <c r="I71" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10">
+      <c r="E72" t="s">
+        <v>92</v>
+      </c>
+      <c r="H72" t="s">
+        <v>266</v>
+      </c>
+      <c r="I72" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10">
+      <c r="H73" t="s">
+        <v>266</v>
+      </c>
+      <c r="I73" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10">
+      <c r="F74" t="s">
+        <v>131</v>
+      </c>
+      <c r="G74" t="s">
+        <v>208</v>
+      </c>
+      <c r="H74" t="s">
+        <v>266</v>
+      </c>
+      <c r="I74" t="s">
+        <v>335</v>
+      </c>
+      <c r="J74" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10">
+      <c r="A75" t="s">
+        <v>23</v>
+      </c>
+      <c r="B75" t="s">
+        <v>58</v>
+      </c>
+      <c r="C75" t="s">
+        <v>63</v>
+      </c>
+      <c r="D75" t="s">
+        <v>70</v>
+      </c>
+      <c r="I75" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10">
+      <c r="A76" t="s">
+        <v>23</v>
+      </c>
+      <c r="E76" t="s">
+        <v>84</v>
+      </c>
+      <c r="F76" t="s">
+        <v>132</v>
+      </c>
+      <c r="G76" t="s">
+        <v>209</v>
+      </c>
+      <c r="I76" t="s">
+        <v>337</v>
+      </c>
+      <c r="J76" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10">
+      <c r="A77" t="s">
+        <v>23</v>
+      </c>
+      <c r="E77" t="s">
+        <v>84</v>
+      </c>
+      <c r="F77" t="s">
+        <v>133</v>
+      </c>
+      <c r="G77" t="s">
+        <v>210</v>
+      </c>
+      <c r="I77" t="s">
+        <v>338</v>
+      </c>
+      <c r="J77" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10">
+      <c r="A78" t="s">
+        <v>23</v>
+      </c>
+      <c r="B78" t="s">
+        <v>58</v>
+      </c>
+      <c r="C78" t="s">
+        <v>63</v>
+      </c>
+      <c r="D78" t="s">
+        <v>70</v>
+      </c>
+      <c r="I78" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10">
+      <c r="A79" t="s">
+        <v>24</v>
+      </c>
+      <c r="E79" t="s">
+        <v>84</v>
+      </c>
+      <c r="F79" t="s">
+        <v>134</v>
+      </c>
+      <c r="G79" t="s">
+        <v>211</v>
+      </c>
+      <c r="I79" t="s">
+        <v>339</v>
+      </c>
+      <c r="J79" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10">
+      <c r="A80" t="s">
+        <v>25</v>
+      </c>
+      <c r="I80" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10">
+      <c r="E81" t="s">
+        <v>84</v>
+      </c>
+      <c r="F81" t="s">
+        <v>135</v>
+      </c>
+      <c r="G81" t="s">
+        <v>212</v>
+      </c>
+      <c r="H81" t="s">
+        <v>271</v>
+      </c>
+      <c r="I81" t="s">
+        <v>341</v>
+      </c>
+      <c r="J81" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10">
+      <c r="A82" t="s">
+        <v>23</v>
+      </c>
+      <c r="B82" t="s">
+        <v>57</v>
+      </c>
+      <c r="C82" t="s">
+        <v>63</v>
+      </c>
+      <c r="D82" t="s">
+        <v>72</v>
+      </c>
+      <c r="I82" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10">
+      <c r="A83" t="s">
+        <v>23</v>
+      </c>
+      <c r="E83" t="s">
+        <v>85</v>
+      </c>
+      <c r="F83" t="s">
+        <v>136</v>
+      </c>
+      <c r="G83" t="s">
+        <v>213</v>
+      </c>
+      <c r="H83" t="s">
+        <v>266</v>
+      </c>
+      <c r="I83" t="s">
+        <v>343</v>
+      </c>
+      <c r="J83" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10">
+      <c r="A84" t="s">
+        <v>23</v>
+      </c>
+      <c r="B84" t="s">
+        <v>56</v>
+      </c>
+      <c r="C84" t="s">
+        <v>64</v>
+      </c>
+      <c r="D84" t="s">
+        <v>71</v>
+      </c>
+      <c r="I84" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10">
+      <c r="A85" t="s">
+        <v>23</v>
+      </c>
+      <c r="E85" t="s">
+        <v>93</v>
+      </c>
+      <c r="F85" t="s">
+        <v>137</v>
+      </c>
+      <c r="G85" t="s">
+        <v>214</v>
+      </c>
+      <c r="I85" t="s">
+        <v>345</v>
+      </c>
+      <c r="J85" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10">
+      <c r="A86" t="s">
+        <v>23</v>
+      </c>
+      <c r="B86" t="s">
+        <v>58</v>
+      </c>
+      <c r="C86" t="s">
+        <v>63</v>
+      </c>
+      <c r="D86" t="s">
+        <v>70</v>
+      </c>
+      <c r="I86" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10">
+      <c r="A87" t="s">
+        <v>25</v>
+      </c>
+      <c r="I87" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10">
+      <c r="E88" t="s">
+        <v>84</v>
+      </c>
+      <c r="F88" t="s">
+        <v>138</v>
+      </c>
+      <c r="G88" t="s">
+        <v>215</v>
+      </c>
+      <c r="H88" t="s">
+        <v>271</v>
+      </c>
+      <c r="I88" t="s">
+        <v>346</v>
+      </c>
+      <c r="J88" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10">
+      <c r="A89" t="s">
+        <v>23</v>
+      </c>
+      <c r="B89" t="s">
+        <v>57</v>
+      </c>
+      <c r="C89" t="s">
+        <v>63</v>
+      </c>
+      <c r="D89" t="s">
+        <v>72</v>
+      </c>
+      <c r="I89" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10">
+      <c r="A90" t="s">
+        <v>23</v>
+      </c>
+      <c r="E90" t="s">
+        <v>85</v>
+      </c>
+      <c r="F90" t="s">
+        <v>139</v>
+      </c>
+      <c r="G90" t="s">
+        <v>216</v>
+      </c>
+      <c r="H90" t="s">
+        <v>266</v>
+      </c>
+      <c r="I90" t="s">
+        <v>347</v>
+      </c>
+      <c r="J90" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10">
+      <c r="A91" t="s">
+        <v>23</v>
+      </c>
+      <c r="B91" t="s">
+        <v>58</v>
+      </c>
+      <c r="C91" t="s">
+        <v>63</v>
+      </c>
+      <c r="D91" t="s">
+        <v>70</v>
+      </c>
+      <c r="I91" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10">
+      <c r="A92" t="s">
+        <v>23</v>
+      </c>
+      <c r="E92" t="s">
+        <v>84</v>
+      </c>
+      <c r="F92" t="s">
+        <v>140</v>
+      </c>
+      <c r="G92" t="s">
+        <v>217</v>
+      </c>
+      <c r="I92" t="s">
+        <v>348</v>
+      </c>
+      <c r="J92" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10">
+      <c r="A93" t="s">
+        <v>23</v>
+      </c>
+      <c r="B93" t="s">
+        <v>57</v>
+      </c>
+      <c r="C93" t="s">
+        <v>63</v>
+      </c>
+      <c r="D93" t="s">
+        <v>72</v>
+      </c>
+      <c r="I93" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10">
+      <c r="A94" t="s">
+        <v>23</v>
+      </c>
+      <c r="E94" t="s">
+        <v>85</v>
+      </c>
+      <c r="F94" t="s">
+        <v>141</v>
+      </c>
+      <c r="G94" t="s">
+        <v>195</v>
+      </c>
+      <c r="H94" t="s">
+        <v>266</v>
+      </c>
+      <c r="I94" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10">
+      <c r="A95" t="s">
+        <v>23</v>
+      </c>
+      <c r="B95" t="s">
+        <v>57</v>
+      </c>
+      <c r="C95" t="s">
+        <v>63</v>
+      </c>
+      <c r="D95" t="s">
+        <v>72</v>
+      </c>
+      <c r="I95" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10">
+      <c r="A96" t="s">
+        <v>23</v>
+      </c>
+      <c r="E96" t="s">
+        <v>85</v>
+      </c>
+      <c r="F96" t="s">
+        <v>142</v>
+      </c>
+      <c r="G96" t="s">
+        <v>218</v>
+      </c>
+      <c r="H96" t="s">
+        <v>266</v>
+      </c>
+      <c r="I96" t="s">
+        <v>350</v>
+      </c>
+      <c r="J96" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10">
+      <c r="A97" t="s">
+        <v>22</v>
+      </c>
+      <c r="D97" t="s">
+        <v>70</v>
+      </c>
+      <c r="E97" t="s">
+        <v>77</v>
+      </c>
+      <c r="F97" t="s">
+        <v>117</v>
+      </c>
+      <c r="G97" t="s">
+        <v>197</v>
+      </c>
+      <c r="I97" t="s">
+        <v>351</v>
+      </c>
+      <c r="J97" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="98" spans="1:10">
+      <c r="H98" t="s">
+        <v>270</v>
+      </c>
+      <c r="I98" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="99" spans="1:10">
+      <c r="A99" t="s">
+        <v>23</v>
+      </c>
+      <c r="D99" t="s">
+        <v>72</v>
+      </c>
+      <c r="E99" t="s">
+        <v>94</v>
+      </c>
+      <c r="F99" t="s">
+        <v>136</v>
+      </c>
+      <c r="G99" t="s">
+        <v>195</v>
+      </c>
+      <c r="I99" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="100" spans="1:10">
+      <c r="H100" t="s">
+        <v>270</v>
+      </c>
+      <c r="I100" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="101" spans="1:10">
+      <c r="A101" t="s">
+        <v>23</v>
+      </c>
+      <c r="D101" t="s">
+        <v>70</v>
+      </c>
+      <c r="F101" t="s">
+        <v>133</v>
+      </c>
+      <c r="G101" t="s">
+        <v>210</v>
+      </c>
+      <c r="I101" t="s">
+        <v>354</v>
+      </c>
+      <c r="J101" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="102" spans="1:10">
+      <c r="A102" t="s">
+        <v>26</v>
+      </c>
+      <c r="I102" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="103" spans="1:10">
+      <c r="A103" t="s">
+        <v>23</v>
+      </c>
+      <c r="C103" t="s">
+        <v>63</v>
+      </c>
+      <c r="D103" t="s">
+        <v>77</v>
+      </c>
+      <c r="E103" t="s">
+        <v>94</v>
+      </c>
+      <c r="F103" t="s">
+        <v>143</v>
+      </c>
+      <c r="G103" t="s">
+        <v>219</v>
+      </c>
+      <c r="I103" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="104" spans="1:10">
+      <c r="A104" t="s">
+        <v>27</v>
+      </c>
+      <c r="B104" t="s">
+        <v>59</v>
+      </c>
+      <c r="C104" t="s">
+        <v>67</v>
+      </c>
+      <c r="D104" t="s">
+        <v>70</v>
+      </c>
+      <c r="I104" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="105" spans="1:10">
+      <c r="A105" t="s">
+        <v>27</v>
+      </c>
+      <c r="E105" t="s">
+        <v>95</v>
+      </c>
+      <c r="F105" t="s">
+        <v>144</v>
+      </c>
+      <c r="G105" t="s">
+        <v>220</v>
+      </c>
+      <c r="I105" t="s">
+        <v>358</v>
+      </c>
+      <c r="J105" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="106" spans="1:10">
+      <c r="A106" t="s">
+        <v>27</v>
+      </c>
+      <c r="H106" t="s">
+        <v>266</v>
+      </c>
+      <c r="I106" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="107" spans="1:10">
+      <c r="A107" t="s">
+        <v>27</v>
+      </c>
+      <c r="B107" t="s">
+        <v>59</v>
+      </c>
+      <c r="C107" t="s">
+        <v>64</v>
+      </c>
+      <c r="D107" t="s">
+        <v>71</v>
+      </c>
+      <c r="I107" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="108" spans="1:10">
+      <c r="A108" t="s">
+        <v>27</v>
+      </c>
+      <c r="E108" t="s">
+        <v>81</v>
+      </c>
+      <c r="F108" t="s">
+        <v>145</v>
+      </c>
+      <c r="G108" t="s">
+        <v>221</v>
+      </c>
+      <c r="H108" t="s">
+        <v>266</v>
+      </c>
+      <c r="I108" t="s">
+        <v>361</v>
+      </c>
+      <c r="J108" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="109" spans="1:10">
+      <c r="A109" t="s">
+        <v>23</v>
+      </c>
+      <c r="B109" t="s">
+        <v>57</v>
+      </c>
+      <c r="C109" t="s">
+        <v>63</v>
+      </c>
+      <c r="D109" t="s">
+        <v>72</v>
+      </c>
+      <c r="I109" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="110" spans="1:10">
+      <c r="A110" t="s">
+        <v>23</v>
+      </c>
+      <c r="E110" t="s">
+        <v>85</v>
+      </c>
+      <c r="F110" t="s">
+        <v>141</v>
+      </c>
+      <c r="G110" t="s">
+        <v>195</v>
+      </c>
+      <c r="H110" t="s">
+        <v>266</v>
+      </c>
+      <c r="I110" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="111" spans="1:10">
+      <c r="A111" t="s">
+        <v>23</v>
+      </c>
+      <c r="B111" t="s">
+        <v>57</v>
+      </c>
+      <c r="C111" t="s">
+        <v>63</v>
+      </c>
+      <c r="D111" t="s">
+        <v>72</v>
+      </c>
+      <c r="I111" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="112" spans="1:10">
+      <c r="A112" t="s">
+        <v>23</v>
+      </c>
+      <c r="E112" t="s">
+        <v>85</v>
+      </c>
+      <c r="F112" t="s">
+        <v>142</v>
+      </c>
+      <c r="G112" t="s">
+        <v>218</v>
+      </c>
+      <c r="H112" t="s">
+        <v>266</v>
+      </c>
+      <c r="I112" t="s">
+        <v>350</v>
+      </c>
+      <c r="J112" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="113" spans="1:10">
+      <c r="A113" t="s">
+        <v>28</v>
+      </c>
+      <c r="B113" t="s">
+        <v>61</v>
+      </c>
+      <c r="C113" t="s">
+        <v>64</v>
+      </c>
+      <c r="E113" t="s">
+        <v>74</v>
+      </c>
+      <c r="I113" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="114" spans="1:10">
+      <c r="A114" t="s">
+        <v>29</v>
+      </c>
+      <c r="E114" t="s">
+        <v>91</v>
+      </c>
+      <c r="F114" t="s">
+        <v>146</v>
+      </c>
+      <c r="G114" t="s">
+        <v>222</v>
+      </c>
+      <c r="I114" t="s">
+        <v>363</v>
+      </c>
+      <c r="J114" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="115" spans="1:10">
+      <c r="A115" t="s">
+        <v>30</v>
+      </c>
+      <c r="B115" t="s">
+        <v>59</v>
+      </c>
+      <c r="C115" t="s">
+        <v>63</v>
+      </c>
+      <c r="D115" t="s">
+        <v>70</v>
+      </c>
+      <c r="E115" t="s">
+        <v>84</v>
+      </c>
+      <c r="I115" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="116" spans="1:10">
+      <c r="A116" t="s">
+        <v>30</v>
+      </c>
+      <c r="F116" t="s">
+        <v>113</v>
+      </c>
+      <c r="G116" t="s">
+        <v>193</v>
+      </c>
+      <c r="I116" t="s">
+        <v>365</v>
+      </c>
+      <c r="J116" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="117" spans="1:10">
+      <c r="A117" t="s">
+        <v>30</v>
+      </c>
+      <c r="B117" t="s">
+        <v>59</v>
+      </c>
+      <c r="C117" t="s">
+        <v>63</v>
+      </c>
+      <c r="D117" t="s">
+        <v>70</v>
+      </c>
+      <c r="E117" t="s">
+        <v>85</v>
+      </c>
+      <c r="I117" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="118" spans="1:10">
+      <c r="A118" t="s">
+        <v>30</v>
+      </c>
+      <c r="F118" t="s">
+        <v>147</v>
+      </c>
+      <c r="G118" t="s">
+        <v>223</v>
+      </c>
+      <c r="H118" t="s">
+        <v>266</v>
+      </c>
+      <c r="I118" t="s">
+        <v>367</v>
+      </c>
+      <c r="J118" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="119" spans="1:10">
+      <c r="A119" t="s">
+        <v>31</v>
+      </c>
+      <c r="B119" t="s">
+        <v>56</v>
+      </c>
+      <c r="C119" t="s">
+        <v>64</v>
+      </c>
+      <c r="D119" t="s">
+        <v>72</v>
+      </c>
+      <c r="E119" t="s">
+        <v>74</v>
+      </c>
+      <c r="F119" t="s">
+        <v>148</v>
+      </c>
+      <c r="G119" t="s">
+        <v>224</v>
+      </c>
+      <c r="I119" t="s">
+        <v>368</v>
+      </c>
+      <c r="J119" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="120" spans="1:10">
+      <c r="A120" t="s">
+        <v>32</v>
+      </c>
+      <c r="E120" t="s">
+        <v>91</v>
+      </c>
+      <c r="F120" t="s">
+        <v>149</v>
+      </c>
+      <c r="G120" t="s">
+        <v>225</v>
+      </c>
+      <c r="I120" t="s">
+        <v>369</v>
+      </c>
+      <c r="J120" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="121" spans="1:10">
+      <c r="B121" t="s">
+        <v>59</v>
+      </c>
+      <c r="C121" t="s">
+        <v>63</v>
+      </c>
+      <c r="D121" t="s">
+        <v>70</v>
+      </c>
+      <c r="I121" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="122" spans="1:10">
+      <c r="A122" t="s">
+        <v>33</v>
+      </c>
+      <c r="B122" t="s">
+        <v>59</v>
+      </c>
+      <c r="C122" t="s">
+        <v>63</v>
+      </c>
+      <c r="D122" t="s">
+        <v>70</v>
+      </c>
+      <c r="E122" t="s">
+        <v>96</v>
+      </c>
+      <c r="F122" t="s">
+        <v>148</v>
+      </c>
+      <c r="G122" t="s">
+        <v>224</v>
+      </c>
+      <c r="H122" t="s">
+        <v>266</v>
+      </c>
+      <c r="I122" t="s">
+        <v>371</v>
+      </c>
+      <c r="J122" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="123" spans="1:10">
+      <c r="E123" t="s">
+        <v>96</v>
+      </c>
+      <c r="F123" t="s">
+        <v>113</v>
+      </c>
+      <c r="G123" t="s">
+        <v>193</v>
+      </c>
+      <c r="H123" t="s">
+        <v>266</v>
+      </c>
+      <c r="I123" t="s">
+        <v>372</v>
+      </c>
+      <c r="J123" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="124" spans="1:10">
+      <c r="A124" t="s">
+        <v>33</v>
+      </c>
+      <c r="B124" t="s">
+        <v>59</v>
+      </c>
+      <c r="C124" t="s">
+        <v>63</v>
+      </c>
+      <c r="D124" t="s">
+        <v>70</v>
+      </c>
+      <c r="E124" t="s">
+        <v>97</v>
+      </c>
+      <c r="F124" t="s">
+        <v>114</v>
+      </c>
+      <c r="G124" t="s">
+        <v>226</v>
+      </c>
+      <c r="H124" t="s">
+        <v>272</v>
+      </c>
+      <c r="I124" t="s">
+        <v>373</v>
+      </c>
+      <c r="J124" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="125" spans="1:10">
+      <c r="A125" t="s">
+        <v>33</v>
+      </c>
+      <c r="B125" t="s">
+        <v>59</v>
+      </c>
+      <c r="C125" t="s">
+        <v>63</v>
+      </c>
+      <c r="D125" t="s">
+        <v>70</v>
+      </c>
+      <c r="E125" t="s">
+        <v>94</v>
+      </c>
+      <c r="F125" t="s">
+        <v>120</v>
+      </c>
+      <c r="G125" t="s">
+        <v>227</v>
+      </c>
+      <c r="H125" t="s">
+        <v>266</v>
+      </c>
+      <c r="I125" t="s">
+        <v>374</v>
+      </c>
+      <c r="J125" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="126" spans="1:10">
+      <c r="E126" t="s">
+        <v>94</v>
+      </c>
+      <c r="F126" t="s">
+        <v>150</v>
+      </c>
+      <c r="G126" t="s">
+        <v>228</v>
+      </c>
+      <c r="H126" t="s">
+        <v>266</v>
+      </c>
+      <c r="I126" t="s">
+        <v>375</v>
+      </c>
+      <c r="J126" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="127" spans="1:10">
+      <c r="A127" t="s">
+        <v>33</v>
+      </c>
+      <c r="E127" t="s">
+        <v>97</v>
+      </c>
+      <c r="F127" t="s">
+        <v>151</v>
+      </c>
+      <c r="G127" t="s">
+        <v>229</v>
+      </c>
+      <c r="H127" t="s">
+        <v>272</v>
+      </c>
+      <c r="I127" t="s">
+        <v>376</v>
+      </c>
+      <c r="J127" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="128" spans="1:10">
+      <c r="A128" t="s">
+        <v>34</v>
+      </c>
+      <c r="B128" t="s">
+        <v>59</v>
+      </c>
+      <c r="C128" t="s">
+        <v>63</v>
+      </c>
+      <c r="E128" t="s">
+        <v>98</v>
+      </c>
+      <c r="F128" t="s">
+        <v>152</v>
+      </c>
+      <c r="G128" t="s">
+        <v>230</v>
+      </c>
+      <c r="H128" t="s">
+        <v>272</v>
+      </c>
+      <c r="I128" t="s">
+        <v>377</v>
+      </c>
+      <c r="J128" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="129" spans="1:10">
+      <c r="A129" t="s">
+        <v>34</v>
+      </c>
+      <c r="B129" t="s">
+        <v>57</v>
+      </c>
+      <c r="C129" t="s">
+        <v>63</v>
+      </c>
+      <c r="D129" t="s">
+        <v>70</v>
+      </c>
+      <c r="E129" t="s">
+        <v>86</v>
+      </c>
+      <c r="F129" t="s">
+        <v>153</v>
+      </c>
+      <c r="G129" t="s">
+        <v>231</v>
+      </c>
+      <c r="H129" t="s">
+        <v>266</v>
+      </c>
+      <c r="I129" t="s">
+        <v>378</v>
+      </c>
+      <c r="J129" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="130" spans="1:10">
+      <c r="A130" t="s">
+        <v>34</v>
+      </c>
+      <c r="B130" t="s">
+        <v>59</v>
+      </c>
+      <c r="C130" t="s">
+        <v>63</v>
+      </c>
+      <c r="E130" t="s">
+        <v>98</v>
+      </c>
+      <c r="F130" t="s">
+        <v>154</v>
+      </c>
+      <c r="G130" t="s">
+        <v>232</v>
+      </c>
+      <c r="I130" t="s">
+        <v>379</v>
+      </c>
+      <c r="J130" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="131" spans="1:10">
+      <c r="A131" t="s">
+        <v>33</v>
+      </c>
+      <c r="B131" t="s">
+        <v>59</v>
+      </c>
+      <c r="C131" t="s">
+        <v>63</v>
+      </c>
+      <c r="D131" t="s">
+        <v>70</v>
+      </c>
+      <c r="E131" t="s">
+        <v>94</v>
+      </c>
+      <c r="F131" t="s">
+        <v>124</v>
+      </c>
+      <c r="G131" t="s">
+        <v>229</v>
+      </c>
+      <c r="H131" t="s">
+        <v>266</v>
+      </c>
+      <c r="I131" t="s">
+        <v>380</v>
+      </c>
+      <c r="J131" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="132" spans="1:10">
+      <c r="A132" t="s">
+        <v>35</v>
+      </c>
+      <c r="B132" t="s">
+        <v>56</v>
+      </c>
+      <c r="C132" t="s">
+        <v>67</v>
+      </c>
+      <c r="D132" t="s">
+        <v>78</v>
+      </c>
+      <c r="F132" t="s">
+        <v>155</v>
+      </c>
+      <c r="G132" t="s">
+        <v>233</v>
+      </c>
+      <c r="H132" t="s">
+        <v>272</v>
+      </c>
+      <c r="I132" t="s">
+        <v>381</v>
+      </c>
+      <c r="J132" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="133" spans="1:10">
+      <c r="A133" t="s">
+        <v>36</v>
+      </c>
+      <c r="B133" t="s">
+        <v>56</v>
+      </c>
+      <c r="C133" t="s">
+        <v>64</v>
+      </c>
+      <c r="D133" t="s">
+        <v>72</v>
+      </c>
+      <c r="E133" t="s">
+        <v>74</v>
+      </c>
+      <c r="F133" t="s">
+        <v>156</v>
+      </c>
+      <c r="G133" t="s">
+        <v>234</v>
+      </c>
+      <c r="I133" t="s">
+        <v>382</v>
+      </c>
+      <c r="J133" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="134" spans="1:10">
+      <c r="A134" t="s">
+        <v>33</v>
+      </c>
+      <c r="B134" t="s">
+        <v>59</v>
+      </c>
+      <c r="C134" t="s">
+        <v>63</v>
+      </c>
+      <c r="D134" t="s">
+        <v>70</v>
+      </c>
+      <c r="E134" t="s">
+        <v>94</v>
+      </c>
+      <c r="F134" t="s">
+        <v>157</v>
+      </c>
+      <c r="G134" t="s">
+        <v>235</v>
+      </c>
+      <c r="I134" t="s">
+        <v>383</v>
+      </c>
+      <c r="J134" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="135" spans="1:10">
+      <c r="A135" t="s">
+        <v>34</v>
+      </c>
+      <c r="B135" t="s">
+        <v>59</v>
+      </c>
+      <c r="C135" t="s">
+        <v>63</v>
+      </c>
+      <c r="E135" t="s">
+        <v>98</v>
+      </c>
+      <c r="F135" t="s">
+        <v>158</v>
+      </c>
+      <c r="G135" t="s">
+        <v>236</v>
+      </c>
+      <c r="H135" t="s">
+        <v>272</v>
+      </c>
+      <c r="I135" t="s">
+        <v>384</v>
+      </c>
+      <c r="J135" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="136" spans="1:10">
+      <c r="A136" t="s">
+        <v>34</v>
+      </c>
+      <c r="B136" t="s">
+        <v>59</v>
+      </c>
+      <c r="C136" t="s">
+        <v>63</v>
+      </c>
+      <c r="D136" t="s">
+        <v>70</v>
+      </c>
+      <c r="E136" t="s">
+        <v>86</v>
+      </c>
+      <c r="F136" t="s">
+        <v>130</v>
+      </c>
+      <c r="G136" t="s">
+        <v>237</v>
+      </c>
+      <c r="H136" t="s">
+        <v>266</v>
+      </c>
+      <c r="I136" t="s">
+        <v>385</v>
+      </c>
+      <c r="J136" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="137" spans="1:10">
+      <c r="E137" t="s">
+        <v>86</v>
+      </c>
+      <c r="F137" t="s">
+        <v>159</v>
+      </c>
+      <c r="G137" t="s">
+        <v>238</v>
+      </c>
+      <c r="H137" t="s">
+        <v>272</v>
+      </c>
+      <c r="I137" t="s">
+        <v>386</v>
+      </c>
+      <c r="J137" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="138" spans="1:10">
+      <c r="A138" t="s">
+        <v>34</v>
+      </c>
+      <c r="B138" t="s">
+        <v>57</v>
+      </c>
+      <c r="C138" t="s">
+        <v>63</v>
+      </c>
+      <c r="D138" t="s">
+        <v>70</v>
+      </c>
+      <c r="E138" t="s">
+        <v>86</v>
+      </c>
+      <c r="F138" t="s">
+        <v>160</v>
+      </c>
+      <c r="G138" t="s">
+        <v>239</v>
+      </c>
+      <c r="H138" t="s">
+        <v>272</v>
+      </c>
+      <c r="I138" t="s">
+        <v>387</v>
+      </c>
+      <c r="J138" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="139" spans="1:10">
+      <c r="A139" t="s">
+        <v>33</v>
+      </c>
+      <c r="B139" t="s">
+        <v>59</v>
+      </c>
+      <c r="C139" t="s">
+        <v>63</v>
+      </c>
+      <c r="D139" t="s">
+        <v>70</v>
+      </c>
+      <c r="E139" t="s">
+        <v>96</v>
+      </c>
+      <c r="F139" t="s">
+        <v>161</v>
+      </c>
+      <c r="G139" t="s">
+        <v>201</v>
+      </c>
+      <c r="I139" t="s">
+        <v>388</v>
+      </c>
+      <c r="J139" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="140" spans="1:10">
+      <c r="F140" t="s">
+        <v>162</v>
+      </c>
+      <c r="G140" t="s">
+        <v>240</v>
+      </c>
+      <c r="H140" t="s">
+        <v>266</v>
+      </c>
+      <c r="I140" t="s">
+        <v>389</v>
+      </c>
+      <c r="J140" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="141" spans="1:10">
+      <c r="A141" t="s">
+        <v>37</v>
+      </c>
+      <c r="B141" t="s">
+        <v>61</v>
+      </c>
+      <c r="C141" t="s">
+        <v>64</v>
+      </c>
+      <c r="D141" t="s">
+        <v>71</v>
+      </c>
+      <c r="I141" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="142" spans="1:10">
+      <c r="A142" t="s">
+        <v>37</v>
+      </c>
+      <c r="E142" t="s">
+        <v>99</v>
+      </c>
+      <c r="F142" t="s">
+        <v>163</v>
+      </c>
+      <c r="G142" t="s">
+        <v>241</v>
+      </c>
+      <c r="I142" t="s">
+        <v>391</v>
+      </c>
+      <c r="J142" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="143" spans="1:10">
+      <c r="A143" t="s">
+        <v>37</v>
+      </c>
+      <c r="B143" t="s">
+        <v>61</v>
+      </c>
+      <c r="C143" t="s">
+        <v>64</v>
+      </c>
+      <c r="D143" t="s">
+        <v>71</v>
+      </c>
+      <c r="I143" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="144" spans="1:10">
+      <c r="A144" t="s">
+        <v>38</v>
+      </c>
+      <c r="B144" t="s">
+        <v>58</v>
+      </c>
+      <c r="C144" t="s">
+        <v>67</v>
+      </c>
+      <c r="D144" t="s">
+        <v>70</v>
+      </c>
+      <c r="E144" t="s">
+        <v>100</v>
+      </c>
+      <c r="F144" t="s">
+        <v>164</v>
+      </c>
+      <c r="G144" t="s">
+        <v>242</v>
+      </c>
+      <c r="I144" t="s">
+        <v>393</v>
+      </c>
+      <c r="J144" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="145" spans="1:10">
+      <c r="F145" t="s">
+        <v>165</v>
+      </c>
+      <c r="G145" t="s">
+        <v>243</v>
+      </c>
+      <c r="H145" t="s">
+        <v>266</v>
+      </c>
+      <c r="I145" t="s">
+        <v>394</v>
+      </c>
+      <c r="J145" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="146" spans="1:10">
+      <c r="A146" t="s">
+        <v>37</v>
+      </c>
+      <c r="B146" t="s">
+        <v>61</v>
+      </c>
+      <c r="C146" t="s">
+        <v>64</v>
+      </c>
+      <c r="D146" t="s">
+        <v>71</v>
+      </c>
+      <c r="I146" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="147" spans="1:10">
+      <c r="A147" t="s">
+        <v>39</v>
+      </c>
+      <c r="E147" t="s">
+        <v>81</v>
+      </c>
+      <c r="F147" t="s">
+        <v>166</v>
+      </c>
+      <c r="G147" t="s">
+        <v>244</v>
+      </c>
+      <c r="I147" t="s">
+        <v>396</v>
+      </c>
+      <c r="J147" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="148" spans="1:10">
+      <c r="A148" t="s">
+        <v>40</v>
+      </c>
+      <c r="B148" t="s">
+        <v>58</v>
+      </c>
+      <c r="C148" t="s">
+        <v>63</v>
+      </c>
+      <c r="D148" t="s">
+        <v>70</v>
+      </c>
+      <c r="I148" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="149" spans="1:10">
+      <c r="A149" t="s">
+        <v>40</v>
+      </c>
+      <c r="E149" t="s">
+        <v>84</v>
+      </c>
+      <c r="F149" t="s">
+        <v>167</v>
+      </c>
+      <c r="G149" t="s">
+        <v>245</v>
+      </c>
+      <c r="I149" t="s">
+        <v>398</v>
+      </c>
+      <c r="J149" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="150" spans="1:10">
+      <c r="A150" t="s">
+        <v>41</v>
+      </c>
+      <c r="B150" t="s">
+        <v>57</v>
+      </c>
+      <c r="C150" t="s">
+        <v>63</v>
+      </c>
+      <c r="D150" t="s">
+        <v>70</v>
+      </c>
+      <c r="I150" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="151" spans="1:10">
+      <c r="A151" t="s">
+        <v>42</v>
+      </c>
+      <c r="I151" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="152" spans="1:10">
+      <c r="E152" t="s">
+        <v>85</v>
+      </c>
+      <c r="F152" t="s">
+        <v>168</v>
+      </c>
+      <c r="G152" t="s">
+        <v>246</v>
+      </c>
+      <c r="I152" t="s">
+        <v>401</v>
+      </c>
+      <c r="J152" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="153" spans="1:10">
+      <c r="A153" t="s">
+        <v>33</v>
+      </c>
+      <c r="B153" t="s">
+        <v>59</v>
+      </c>
+      <c r="C153" t="s">
+        <v>63</v>
+      </c>
+      <c r="D153" t="s">
+        <v>70</v>
+      </c>
+      <c r="E153" t="s">
+        <v>96</v>
+      </c>
+      <c r="F153" t="s">
+        <v>169</v>
+      </c>
+      <c r="G153" t="s">
+        <v>247</v>
+      </c>
+      <c r="I153" t="s">
+        <v>402</v>
+      </c>
+      <c r="J153" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="154" spans="1:10">
+      <c r="F154" t="s">
+        <v>170</v>
+      </c>
+      <c r="G154" t="s">
+        <v>248</v>
+      </c>
+      <c r="H154" t="s">
+        <v>266</v>
+      </c>
+      <c r="I154" t="s">
+        <v>403</v>
+      </c>
+      <c r="J154" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="155" spans="1:10">
+      <c r="A155" t="s">
+        <v>41</v>
+      </c>
+      <c r="B155" t="s">
+        <v>57</v>
+      </c>
+      <c r="C155" t="s">
+        <v>63</v>
+      </c>
+      <c r="D155" t="s">
+        <v>70</v>
+      </c>
+      <c r="I155" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="156" spans="1:10">
+      <c r="A156" t="s">
+        <v>42</v>
+      </c>
+      <c r="I156" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="157" spans="1:10">
+      <c r="E157" t="s">
+        <v>85</v>
+      </c>
+      <c r="F157" t="s">
+        <v>171</v>
+      </c>
+      <c r="G157" t="s">
+        <v>249</v>
+      </c>
+      <c r="H157" t="s">
+        <v>273</v>
+      </c>
+      <c r="I157" t="s">
+        <v>404</v>
+      </c>
+      <c r="J157" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="158" spans="1:10">
+      <c r="A158" t="s">
+        <v>41</v>
+      </c>
+      <c r="B158" t="s">
+        <v>57</v>
+      </c>
+      <c r="C158" t="s">
+        <v>63</v>
+      </c>
+      <c r="D158" t="s">
+        <v>70</v>
+      </c>
+      <c r="I158" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="159" spans="1:10">
+      <c r="A159" t="s">
+        <v>42</v>
+      </c>
+      <c r="I159" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="160" spans="1:10">
+      <c r="E160" t="s">
+        <v>85</v>
+      </c>
+      <c r="F160" t="s">
+        <v>171</v>
+      </c>
+      <c r="G160" t="s">
+        <v>249</v>
+      </c>
+      <c r="H160" t="s">
+        <v>273</v>
+      </c>
+      <c r="I160" t="s">
+        <v>405</v>
+      </c>
+      <c r="J160" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="161" spans="1:10">
+      <c r="A161" t="s">
+        <v>41</v>
+      </c>
+      <c r="I161" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="162" spans="1:10">
+      <c r="A162" t="s">
+        <v>43</v>
+      </c>
+      <c r="B162" t="s">
+        <v>61</v>
+      </c>
+      <c r="C162" t="s">
+        <v>64</v>
+      </c>
+      <c r="D162" t="s">
+        <v>71</v>
+      </c>
+      <c r="I162" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="163" spans="1:10">
+      <c r="A163" t="s">
+        <v>43</v>
+      </c>
+      <c r="E163" t="s">
+        <v>82</v>
+      </c>
+      <c r="F163" t="s">
+        <v>172</v>
+      </c>
+      <c r="G163" t="s">
+        <v>250</v>
+      </c>
+      <c r="I163" t="s">
+        <v>408</v>
+      </c>
+      <c r="J163" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="164" spans="1:10">
+      <c r="A164" t="s">
+        <v>44</v>
+      </c>
+      <c r="B164" t="s">
+        <v>58</v>
+      </c>
+      <c r="C164" t="s">
+        <v>65</v>
+      </c>
+      <c r="D164" t="s">
+        <v>70</v>
+      </c>
+      <c r="I164" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="165" spans="1:10">
+      <c r="A165" t="s">
+        <v>44</v>
+      </c>
+      <c r="E165" t="s">
+        <v>85</v>
+      </c>
+      <c r="F165" t="s">
+        <v>173</v>
+      </c>
+      <c r="G165" t="s">
+        <v>251</v>
+      </c>
+      <c r="I165" t="s">
+        <v>410</v>
+      </c>
+      <c r="J165" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="166" spans="1:10">
+      <c r="A166" t="s">
+        <v>44</v>
+      </c>
+      <c r="B166" t="s">
+        <v>58</v>
+      </c>
+      <c r="C166" t="s">
+        <v>65</v>
+      </c>
+      <c r="D166" t="s">
+        <v>70</v>
+      </c>
+      <c r="I166" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="167" spans="1:10">
+      <c r="A167" t="s">
+        <v>44</v>
+      </c>
+      <c r="E167" t="s">
+        <v>84</v>
+      </c>
+      <c r="F167" t="s">
+        <v>174</v>
+      </c>
+      <c r="G167" t="s">
+        <v>252</v>
+      </c>
+      <c r="H167" t="s">
+        <v>266</v>
+      </c>
+      <c r="I167" t="s">
+        <v>411</v>
+      </c>
+      <c r="J167" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="168" spans="1:10">
+      <c r="A168" t="s">
+        <v>44</v>
+      </c>
+      <c r="E168" t="s">
+        <v>84</v>
+      </c>
+      <c r="I168" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="169" spans="1:10">
+      <c r="A169" t="s">
+        <v>44</v>
+      </c>
+      <c r="E169" t="s">
+        <v>84</v>
+      </c>
+      <c r="I169" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="170" spans="1:10">
+      <c r="A170" t="s">
+        <v>45</v>
+      </c>
+      <c r="E170" t="s">
+        <v>84</v>
+      </c>
+      <c r="I170" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="171" spans="1:10">
+      <c r="A171" t="s">
+        <v>46</v>
+      </c>
+      <c r="B171" t="s">
+        <v>56</v>
+      </c>
+      <c r="C171" t="s">
+        <v>68</v>
+      </c>
+      <c r="E171" t="s">
+        <v>74</v>
+      </c>
+      <c r="I171" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="172" spans="1:10">
+      <c r="A172" t="s">
+        <v>46</v>
+      </c>
+      <c r="B172" t="s">
+        <v>56</v>
+      </c>
+      <c r="C172" t="s">
+        <v>69</v>
+      </c>
+      <c r="D172" t="s">
+        <v>74</v>
+      </c>
+      <c r="F172" t="s">
+        <v>175</v>
+      </c>
+      <c r="G172" t="s">
+        <v>253</v>
+      </c>
+      <c r="I172" t="s">
+        <v>416</v>
+      </c>
+      <c r="J172" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="173" spans="1:10">
+      <c r="A173" t="s">
+        <v>47</v>
+      </c>
+      <c r="E173" t="s">
+        <v>101</v>
+      </c>
+      <c r="F173" t="s">
+        <v>149</v>
+      </c>
+      <c r="G173" t="s">
+        <v>225</v>
+      </c>
+      <c r="I173" t="s">
+        <v>417</v>
+      </c>
+      <c r="J173" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="174" spans="1:10">
+      <c r="A174" t="s">
+        <v>44</v>
+      </c>
+      <c r="B174" t="s">
+        <v>58</v>
+      </c>
+      <c r="C174" t="s">
+        <v>65</v>
+      </c>
+      <c r="D174" t="s">
+        <v>70</v>
+      </c>
+      <c r="I174" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="175" spans="1:10">
+      <c r="A175" t="s">
+        <v>44</v>
+      </c>
+      <c r="E175" t="s">
+        <v>102</v>
+      </c>
+      <c r="F175" t="s">
+        <v>129</v>
+      </c>
+      <c r="G175" t="s">
+        <v>206</v>
+      </c>
+      <c r="I175" t="s">
+        <v>418</v>
+      </c>
+      <c r="J175" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="176" spans="1:10">
+      <c r="A176" t="s">
+        <v>48</v>
+      </c>
+      <c r="E176" t="s">
+        <v>85</v>
+      </c>
+      <c r="I176" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="177" spans="1:10">
+      <c r="A177" t="s">
+        <v>44</v>
+      </c>
+      <c r="B177" t="s">
+        <v>60</v>
+      </c>
+      <c r="C177" t="s">
+        <v>65</v>
+      </c>
+      <c r="D177" t="s">
+        <v>70</v>
+      </c>
+      <c r="I177" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="178" spans="1:10">
+      <c r="A178" t="s">
+        <v>44</v>
+      </c>
+      <c r="E178" t="s">
+        <v>73</v>
+      </c>
+      <c r="F178" t="s">
+        <v>125</v>
+      </c>
+      <c r="G178" t="s">
+        <v>254</v>
+      </c>
+      <c r="I178" t="s">
+        <v>421</v>
+      </c>
+      <c r="J178" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="179" spans="1:10">
+      <c r="A179" t="s">
+        <v>44</v>
+      </c>
+      <c r="B179" t="s">
+        <v>56</v>
+      </c>
+      <c r="C179" t="s">
+        <v>65</v>
+      </c>
+      <c r="D179" t="s">
+        <v>70</v>
+      </c>
+      <c r="I179" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="180" spans="1:10">
+      <c r="A180" t="s">
+        <v>44</v>
+      </c>
+      <c r="E180" t="s">
+        <v>103</v>
+      </c>
+      <c r="F180" t="s">
+        <v>176</v>
+      </c>
+      <c r="G180" t="s">
+        <v>255</v>
+      </c>
+      <c r="I180" t="s">
+        <v>423</v>
+      </c>
+      <c r="J180" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="181" spans="1:10">
+      <c r="A181" t="s">
+        <v>43</v>
+      </c>
+      <c r="B181" t="s">
+        <v>61</v>
+      </c>
+      <c r="C181" t="s">
+        <v>64</v>
+      </c>
+      <c r="D181" t="s">
+        <v>71</v>
+      </c>
+      <c r="I181" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="182" spans="1:10">
+      <c r="A182" t="s">
+        <v>43</v>
+      </c>
+      <c r="E182" t="s">
+        <v>99</v>
+      </c>
+      <c r="F182" t="s">
+        <v>177</v>
+      </c>
+      <c r="G182" t="s">
+        <v>256</v>
+      </c>
+      <c r="I182" t="s">
+        <v>425</v>
+      </c>
+      <c r="J182" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="183" spans="1:10">
+      <c r="A183" t="s">
+        <v>49</v>
+      </c>
+      <c r="B183" t="s">
+        <v>61</v>
+      </c>
+      <c r="C183" t="s">
+        <v>64</v>
+      </c>
+      <c r="D183" t="s">
+        <v>79</v>
+      </c>
+      <c r="I183" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="184" spans="1:10">
+      <c r="A184" t="s">
+        <v>49</v>
+      </c>
+      <c r="B184" t="s">
+        <v>58</v>
+      </c>
+      <c r="C184" t="s">
+        <v>63</v>
+      </c>
+      <c r="D184" t="s">
+        <v>70</v>
+      </c>
+      <c r="F184" t="s">
+        <v>165</v>
+      </c>
+      <c r="G184" t="s">
+        <v>243</v>
+      </c>
+      <c r="H184" t="s">
+        <v>266</v>
+      </c>
+      <c r="I184" t="s">
+        <v>427</v>
+      </c>
+      <c r="J184" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="185" spans="1:10">
+      <c r="A185" t="s">
+        <v>49</v>
+      </c>
+      <c r="E185" t="s">
+        <v>84</v>
+      </c>
+      <c r="F185" t="s">
+        <v>178</v>
+      </c>
+      <c r="G185" t="s">
+        <v>257</v>
+      </c>
+      <c r="H185" t="s">
+        <v>266</v>
+      </c>
+      <c r="I185" t="s">
+        <v>428</v>
+      </c>
+      <c r="J185" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="186" spans="1:10">
+      <c r="A186" t="s">
+        <v>49</v>
+      </c>
+      <c r="B186" t="s">
+        <v>58</v>
+      </c>
+      <c r="C186" t="s">
+        <v>63</v>
+      </c>
+      <c r="D186" t="s">
+        <v>70</v>
+      </c>
+      <c r="I186" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="187" spans="1:10">
+      <c r="E187" t="s">
+        <v>85</v>
+      </c>
+      <c r="F187" t="s">
+        <v>134</v>
+      </c>
+      <c r="G187" t="s">
+        <v>258</v>
+      </c>
+      <c r="H187" t="s">
+        <v>266</v>
+      </c>
+      <c r="I187" t="s">
+        <v>430</v>
+      </c>
+      <c r="J187" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="188" spans="1:10">
+      <c r="E188" t="s">
+        <v>85</v>
+      </c>
+      <c r="F188" t="s">
+        <v>179</v>
+      </c>
+      <c r="G188" t="s">
+        <v>259</v>
+      </c>
+      <c r="H188" t="s">
+        <v>266</v>
+      </c>
+      <c r="I188" t="s">
+        <v>431</v>
+      </c>
+      <c r="J188" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="189" spans="1:10">
+      <c r="A189" t="s">
+        <v>49</v>
+      </c>
+      <c r="B189" t="s">
+        <v>58</v>
+      </c>
+      <c r="C189" t="s">
+        <v>63</v>
+      </c>
+      <c r="D189" t="s">
+        <v>70</v>
+      </c>
+      <c r="I189" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="190" spans="1:10">
+      <c r="A190" t="s">
+        <v>50</v>
+      </c>
+      <c r="B190" t="s">
+        <v>59</v>
+      </c>
+      <c r="C190" t="s">
+        <v>63</v>
+      </c>
+      <c r="E190" t="s">
+        <v>98</v>
+      </c>
+      <c r="F190" t="s">
+        <v>180</v>
+      </c>
+      <c r="G190" t="s">
+        <v>260</v>
+      </c>
+      <c r="H190" t="s">
+        <v>266</v>
+      </c>
+      <c r="I190" t="s">
+        <v>433</v>
+      </c>
+      <c r="J190" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="191" spans="1:10">
+      <c r="A191" t="s">
+        <v>51</v>
+      </c>
+      <c r="B191" t="s">
+        <v>56</v>
+      </c>
+      <c r="C191" t="s">
+        <v>64</v>
+      </c>
+      <c r="E191" t="s">
+        <v>74</v>
+      </c>
+      <c r="F191" t="s">
+        <v>124</v>
+      </c>
+      <c r="G191" t="s">
+        <v>202</v>
+      </c>
+      <c r="H191" t="s">
+        <v>266</v>
+      </c>
+      <c r="I191" t="s">
+        <v>434</v>
+      </c>
+      <c r="J191" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="192" spans="1:10">
+      <c r="A192" t="s">
+        <v>51</v>
+      </c>
+      <c r="B192" t="s">
+        <v>56</v>
+      </c>
+      <c r="C192" t="s">
+        <v>64</v>
+      </c>
+      <c r="D192" t="s">
+        <v>72</v>
+      </c>
+      <c r="E192" t="s">
+        <v>74</v>
+      </c>
+      <c r="F192" t="s">
+        <v>181</v>
+      </c>
+      <c r="G192" t="s">
+        <v>192</v>
+      </c>
+      <c r="I192" t="s">
+        <v>435</v>
+      </c>
+      <c r="J192" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="193" spans="1:10">
+      <c r="A193" t="s">
+        <v>52</v>
+      </c>
+      <c r="E193" t="s">
+        <v>104</v>
+      </c>
+      <c r="F193" t="s">
+        <v>149</v>
+      </c>
+      <c r="G193" t="s">
+        <v>225</v>
+      </c>
+      <c r="I193" t="s">
+        <v>436</v>
+      </c>
+      <c r="J193" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="194" spans="1:10">
+      <c r="A194" t="s">
+        <v>53</v>
+      </c>
+      <c r="B194" t="s">
+        <v>58</v>
+      </c>
+      <c r="C194" t="s">
+        <v>63</v>
+      </c>
+      <c r="D194" t="s">
+        <v>70</v>
+      </c>
+      <c r="I194" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="195" spans="1:10">
+      <c r="A195" t="s">
+        <v>53</v>
+      </c>
+      <c r="B195" t="s">
+        <v>59</v>
+      </c>
+      <c r="C195" t="s">
+        <v>63</v>
+      </c>
+      <c r="E195" t="s">
+        <v>98</v>
+      </c>
+      <c r="F195" t="s">
+        <v>182</v>
+      </c>
+      <c r="G195" t="s">
+        <v>261</v>
+      </c>
+      <c r="I195" t="s">
+        <v>438</v>
+      </c>
+      <c r="J195" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="196" spans="1:10">
+      <c r="A196" t="s">
+        <v>54</v>
+      </c>
+      <c r="B196" t="s">
+        <v>57</v>
+      </c>
+      <c r="C196" t="s">
+        <v>63</v>
+      </c>
+      <c r="D196" t="s">
+        <v>70</v>
+      </c>
+      <c r="E196" t="s">
+        <v>105</v>
+      </c>
+      <c r="F196" t="s">
+        <v>117</v>
+      </c>
+      <c r="G196" t="s">
+        <v>197</v>
+      </c>
+      <c r="H196" t="s">
+        <v>266</v>
+      </c>
+      <c r="I196" t="s">
+        <v>439</v>
+      </c>
+      <c r="J196" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="197" spans="1:10">
+      <c r="A197" t="s">
+        <v>54</v>
+      </c>
+      <c r="B197" t="s">
+        <v>57</v>
+      </c>
+      <c r="C197" t="s">
+        <v>63</v>
+      </c>
+      <c r="D197" t="s">
+        <v>70</v>
+      </c>
+      <c r="E197" t="s">
+        <v>106</v>
+      </c>
+      <c r="F197" t="s">
+        <v>183</v>
+      </c>
+      <c r="G197" t="s">
+        <v>262</v>
+      </c>
+      <c r="H197" t="s">
+        <v>266</v>
+      </c>
+      <c r="I197" t="s">
+        <v>440</v>
+      </c>
+      <c r="J197" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="198" spans="1:10">
+      <c r="A198" t="s">
+        <v>54</v>
+      </c>
+      <c r="B198" t="s">
+        <v>59</v>
+      </c>
+      <c r="C198" t="s">
+        <v>63</v>
+      </c>
+      <c r="D198" t="s">
+        <v>70</v>
+      </c>
+      <c r="E198" t="s">
+        <v>96</v>
+      </c>
+      <c r="F198" t="s">
+        <v>176</v>
+      </c>
+      <c r="G198" t="s">
+        <v>255</v>
+      </c>
+      <c r="H198" t="s">
+        <v>266</v>
+      </c>
+      <c r="I198" t="s">
+        <v>441</v>
+      </c>
+      <c r="J198" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="199" spans="1:10">
+      <c r="A199" t="s">
+        <v>54</v>
+      </c>
+      <c r="B199" t="s">
+        <v>59</v>
+      </c>
+      <c r="C199" t="s">
+        <v>63</v>
+      </c>
+      <c r="D199" t="s">
+        <v>70</v>
+      </c>
+      <c r="E199" t="s">
+        <v>96</v>
+      </c>
+      <c r="F199" t="s">
+        <v>184</v>
+      </c>
+      <c r="G199" t="s">
+        <v>263</v>
+      </c>
+      <c r="H199" t="s">
+        <v>266</v>
+      </c>
+      <c r="I199" t="s">
+        <v>442</v>
+      </c>
+      <c r="J199" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="200" spans="1:10">
+      <c r="A200" t="s">
+        <v>54</v>
+      </c>
+      <c r="B200" t="s">
+        <v>57</v>
+      </c>
+      <c r="C200" t="s">
+        <v>63</v>
+      </c>
+      <c r="D200" t="s">
+        <v>70</v>
+      </c>
+      <c r="E200" t="s">
+        <v>106</v>
+      </c>
+      <c r="F200" t="s">
+        <v>185</v>
+      </c>
+      <c r="G200" t="s">
+        <v>264</v>
+      </c>
+      <c r="H200" t="s">
+        <v>266</v>
+      </c>
+      <c r="I200" t="s">
+        <v>443</v>
+      </c>
+      <c r="J200" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="201" spans="1:10">
+      <c r="B201" t="s">
+        <v>58</v>
+      </c>
+      <c r="C201" t="s">
+        <v>63</v>
+      </c>
+      <c r="D201" t="s">
+        <v>70</v>
+      </c>
+      <c r="F201" t="s">
+        <v>124</v>
+      </c>
+      <c r="G201" t="s">
+        <v>202</v>
+      </c>
+      <c r="H201" t="s">
+        <v>266</v>
+      </c>
+      <c r="I201" t="s">
+        <v>444</v>
+      </c>
+      <c r="J201" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="202" spans="1:10">
+      <c r="A202" t="s">
+        <v>55</v>
+      </c>
+      <c r="E202" t="s">
+        <v>84</v>
+      </c>
+      <c r="F202" t="s">
+        <v>186</v>
+      </c>
+      <c r="G202" t="s">
+        <v>265</v>
+      </c>
+      <c r="I202" t="s">
+        <v>445</v>
+      </c>
+      <c r="J202" t="s">
+        <v>525</v>
       </c>
     </row>
   </sheetData>

--- a/output_orderan.xlsx
+++ b/output_orderan.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="49">
   <si>
     <t>DATE</t>
   </si>
@@ -46,71 +46,156 @@
     <t>PHONE</t>
   </si>
   <si>
-    <t>06 maret 2026</t>
-  </si>
-  <si>
-    <t>18 : 00 05022026</t>
-  </si>
-  <si>
-    <t>3</t>
+    <t>04 mar 2026</t>
+  </si>
+  <si>
+    <t>05 mar 26</t>
+  </si>
+  <si>
+    <t>03 : 00 06 mar 26</t>
+  </si>
+  <si>
+    <t>05 maret 2026</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>1</t>
   </si>
   <si>
     <t>5</t>
   </si>
   <si>
+    <t>twb cbm</t>
+  </si>
+  <si>
+    <t>cddl</t>
+  </si>
+  <si>
     <t>twb</t>
   </si>
   <si>
+    <t>jne</t>
+  </si>
+  <si>
+    <t>cikokol</t>
+  </si>
+  <si>
     <t>argopantes</t>
   </si>
   <si>
-    <t>cgksub</t>
-  </si>
-  <si>
-    <t>cgk pku</t>
+    <t>suxcgk</t>
+  </si>
+  <si>
+    <t>cikarang</t>
+  </si>
+  <si>
+    <t>cgkpsr</t>
   </si>
   <si>
     <t>wahyudi</t>
   </si>
   <si>
-    <t>syarial</t>
+    <t>miyanta</t>
+  </si>
+  <si>
+    <t>davit</t>
+  </si>
+  <si>
+    <t>iwan hariono</t>
+  </si>
+  <si>
+    <t>akiyat</t>
   </si>
   <si>
     <t>n 9549 ua</t>
   </si>
   <si>
-    <t>bm 8486 au</t>
+    <t>f 9647 fh</t>
+  </si>
+  <si>
+    <t>b 9726 sxw</t>
+  </si>
+  <si>
+    <t>bl 8188 jp</t>
+  </si>
+  <si>
+    <t>l 9722 ue</t>
   </si>
   <si>
     <t>segera</t>
   </si>
   <si>
-    <t>REQUER ORDER ULANG DAN TAMBAHAN ON CALL
-06 MARET 2026
-3 UNIT TWB 50 CBM
- Lokasi : ARGOPANTES
-Rute / tujuan : CGK-SUB</t>
-  </si>
-  <si>
-    <t>Waktu loading : SEGERA
-Nama 	: Wahyudi
-Nopol		: N 9549 UA
-No Tlp	:085784422398
+    <t>Request Order Oncall  04 Mar 2026
+2 UNIT TWB 50 CBM
+Lokasi : JNE SURABAYA
+Rute/ Tujuan   : SUX-CGK</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA 04 Mar 2026
+NAMA   : Wahyudi
+NOPOL : N 9549 UA
+NO HP : 085784422398
+Request Unit On Call Tgl 05 Mar 26
+1 Unit  Cddl / 24 Cbm
+Lokasi : Cikarang</t>
+  </si>
+  <si>
+    <t>Waktu loading : 06:00 06 Mar 26
+Rute/tujuan : CKR-JBR
+Driver   : miyanta
+Nopol  : F 9647 FH
+No Hp  :08118558105
+Request Unit On Call Tgl 05 Mar 26
+RAFAY
+1 Unit  Cddl / 24 Cbm
+Lokasi : Cikokol + Cikarang</t>
+  </si>
+  <si>
+    <t>Waktu loading : 03:00 06  Mar 26
+Rute/tujuan : CGK-PSR
+Driver   : Davit
+Nopol  : B 9726 SXW
+No Hp  :082117275166</t>
+  </si>
+  <si>
+    <t>REQUEST ORDER ONCALL
+05 MARET 2026:
 5 UNIT TWB 50 CBM
 Lokasi : ARGOPANTES</t>
   </si>
   <si>
-    <t>Waktu loading : 18:00 05-02-2026
-Rute/tujuan : CGK - PKU
-driver  : Syarial
-Nopol  :BM 8486 AU
-No Hp :081317708658</t>
+    <t>Waktu loading : 17:00 05-03-2026
+Rute/tujuan : CGK - SUB
+driver  : Iwan Hariono
+Nopol  : BL 8188 JP
+No Hp :081389976421
+Request Order Oncall  05 Maret  2026
+2 UNIT TWB 50 CBM
+Lokasi : JNE SURABAYA
+Rute/ Tujuan   : SUX-CGK</t>
+  </si>
+  <si>
+    <t>Waktu loading : SEGERA 05 Maret  2026
+Driver : Akiyat
+Nopol : L 9722 UE
+No HP :081281122738</t>
   </si>
   <si>
     <t>085784422398</t>
   </si>
   <si>
-    <t>081317708658</t>
+    <t>08118558105</t>
+  </si>
+  <si>
+    <t>082117275166</t>
+  </si>
+  <si>
+    <t>081389976421</t>
+  </si>
+  <si>
+    <t>081281122738</t>
   </si>
 </sst>
 </file>
@@ -468,7 +553,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:10">
@@ -508,65 +593,160 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D2" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E2" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="I2" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:10">
+      <c r="A3" t="s">
+        <v>11</v>
+      </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" t="s">
-        <v>15</v>
+        <v>18</v>
+      </c>
+      <c r="E3" t="s">
+        <v>24</v>
       </c>
       <c r="F3" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="G3" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="H3" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="I3" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="J3" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
         <v>11</v>
       </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" t="s">
+        <v>21</v>
+      </c>
       <c r="E4" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G4" t="s">
+        <v>32</v>
+      </c>
+      <c r="I4" t="s">
+        <v>39</v>
+      </c>
+      <c r="J4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5" t="s">
+        <v>28</v>
+      </c>
+      <c r="G5" t="s">
+        <v>33</v>
+      </c>
+      <c r="I5" t="s">
+        <v>40</v>
+      </c>
+      <c r="J5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" t="s">
         <v>19</v>
       </c>
-      <c r="G4" t="s">
-        <v>21</v>
-      </c>
-      <c r="I4" t="s">
-        <v>25</v>
-      </c>
-      <c r="J4" t="s">
-        <v>27</v>
+      <c r="D6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I6" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F7" t="s">
+        <v>29</v>
+      </c>
+      <c r="G7" t="s">
+        <v>34</v>
+      </c>
+      <c r="I7" t="s">
+        <v>42</v>
+      </c>
+      <c r="J7" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F8" t="s">
+        <v>30</v>
+      </c>
+      <c r="G8" t="s">
+        <v>35</v>
+      </c>
+      <c r="H8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I8" t="s">
+        <v>43</v>
+      </c>
+      <c r="J8" t="s">
+        <v>48</v>
       </c>
     </row>
   </sheetData>

--- a/output_orderan.xlsx
+++ b/output_orderan.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="117">
   <si>
     <t>DATE</t>
   </si>
@@ -46,25 +46,40 @@
     <t>PHONE</t>
   </si>
   <si>
-    <t>04 mar 2026</t>
-  </si>
-  <si>
-    <t>05 mar 26</t>
-  </si>
-  <si>
-    <t>03 : 00 06 mar 26</t>
-  </si>
-  <si>
-    <t>05 maret 2026</t>
+    <t>04 febuari 2026</t>
+  </si>
+  <si>
+    <t>05 / 02 / 2026</t>
+  </si>
+  <si>
+    <t>04 februari 2026</t>
+  </si>
+  <si>
+    <t>05 februari 2026</t>
+  </si>
+  <si>
+    <t>05 februari 2025</t>
+  </si>
+  <si>
+    <t>05 feb 26</t>
+  </si>
+  <si>
+    <t>06 febuary 2026</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>5</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>5</t>
+    <t>3</t>
   </si>
   <si>
     <t>twb cbm</t>
@@ -73,129 +88,484 @@
     <t>cddl</t>
   </si>
   <si>
+    <t>cbm</t>
+  </si>
+  <si>
     <t>twb</t>
   </si>
   <si>
-    <t>jne</t>
+    <t>argopantes</t>
+  </si>
+  <si>
+    <t>megahub</t>
   </si>
   <si>
     <t>cikokol</t>
   </si>
   <si>
-    <t>argopantes</t>
-  </si>
-  <si>
-    <t>suxcgk</t>
-  </si>
-  <si>
     <t>cikarang</t>
   </si>
   <si>
-    <t>cgkpsr</t>
+    <t>jne sub</t>
+  </si>
+  <si>
+    <t>cgk pdg</t>
+  </si>
+  <si>
+    <t>cgk jateng</t>
+  </si>
+  <si>
+    <t>cgk sub</t>
+  </si>
+  <si>
+    <t>cgk dps</t>
+  </si>
+  <si>
+    <t>cgk tkg</t>
+  </si>
+  <si>
+    <t>cgk plm</t>
+  </si>
+  <si>
+    <t>cgk pku</t>
+  </si>
+  <si>
+    <t>cgk mes</t>
+  </si>
+  <si>
+    <t>ckrjateng</t>
+  </si>
+  <si>
+    <t>subcgk</t>
+  </si>
+  <si>
+    <t>sutrisno</t>
+  </si>
+  <si>
+    <t>karyadi</t>
+  </si>
+  <si>
+    <t>m syaichoni</t>
+  </si>
+  <si>
+    <t>agus</t>
+  </si>
+  <si>
+    <t>jatmiyanta</t>
+  </si>
+  <si>
+    <t>siswanto</t>
+  </si>
+  <si>
+    <t>feri irawan</t>
+  </si>
+  <si>
+    <t>hadi</t>
+  </si>
+  <si>
+    <t>a . sukur</t>
+  </si>
+  <si>
+    <t>akiyat</t>
+  </si>
+  <si>
+    <t>ryan</t>
+  </si>
+  <si>
+    <t>hendra s . p</t>
+  </si>
+  <si>
+    <t>sandri</t>
+  </si>
+  <si>
+    <t>apar rahmat</t>
+  </si>
+  <si>
+    <t>m . ibnu</t>
   </si>
   <si>
     <t>wahyudi</t>
   </si>
   <si>
-    <t>miyanta</t>
-  </si>
-  <si>
-    <t>davit</t>
-  </si>
-  <si>
-    <t>iwan hariono</t>
-  </si>
-  <si>
-    <t>akiyat</t>
+    <t>sofyan</t>
+  </si>
+  <si>
+    <t>bm 8364 au</t>
+  </si>
+  <si>
+    <t>ad 8517 ba</t>
+  </si>
+  <si>
+    <t>n 8872 rk</t>
+  </si>
+  <si>
+    <t>d 9667 af</t>
+  </si>
+  <si>
+    <t>f 9647 fh</t>
+  </si>
+  <si>
+    <t>b 9120 wxr</t>
+  </si>
+  <si>
+    <t>bk 8516 vv</t>
+  </si>
+  <si>
+    <t>b 9446 mv</t>
+  </si>
+  <si>
+    <t>b 9477 keu</t>
+  </si>
+  <si>
+    <t>l 9722 ue</t>
+  </si>
+  <si>
+    <t>b 9084 veh</t>
+  </si>
+  <si>
+    <t>d 9044 ag</t>
+  </si>
+  <si>
+    <t>be 9636 bu</t>
+  </si>
+  <si>
+    <t>e9406hb</t>
+  </si>
+  <si>
+    <t>l 9511 al</t>
   </si>
   <si>
     <t>n 9549 ua</t>
   </si>
   <si>
-    <t>f 9647 fh</t>
-  </si>
-  <si>
-    <t>b 9726 sxw</t>
-  </si>
-  <si>
-    <t>bl 8188 jp</t>
-  </si>
-  <si>
-    <t>l 9722 ue</t>
+    <t>b 9679 wt</t>
   </si>
   <si>
     <t>segera</t>
   </si>
   <si>
-    <t>Request Order Oncall  04 Mar 2026
+    <t>07 : 00</t>
+  </si>
+  <si>
+    <t>00 : 00</t>
+  </si>
+  <si>
+    <t>06 : 00</t>
+  </si>
+  <si>
+    <t>03 : 00</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: Request Unit On Call 04 FEBUARI 2026
+RAFAY
+1 UNIT TWB 50 Cbm
+Lokasi : ARGOPANTES
+Waktu loading : SEGERA 04 FEBUARI 2026
+Rute/tujuan : CGK- PDG
+driver  : SUTRISNO
+Nopol  : BM 8364 AU
+No hp  :0853-5388-6066</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: REQUEST ORDER ONCALL 04 FEBRUARI 2026:
+RAFAY
+3 unit Cddl 24 Cbm
+Lokasi : Megahub
+REQUEST ORDER KHUSUS 05/02/2026
+Waktu loading : 07:00
+Rute/tujuan : CGK - JATENG
+driver  : KARYADI
+Nopol  : AD 8517 BA
+No hp  :085865762797</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: REQUEST ORDER ULANG ONCALL
+5 UNIT TWB 50 CBM
+Lokasi : ARGOPANTES 
+Waktu loading : SEGERA
+Rute/tujuan : CGK - SUB
+driver  :
+Nopol  :
+No hp  :
+Waktu loading : 18:00
+Rute/tujuan : CGK - SUB
+driver  : m syaichoni
+Nopol  : N 8872 Rk
+No hp  : +62 812-3189-5971
+Waktu loading : 21:00
+Rute/tujuan : CGK - SUB
+driver  :
+Nopol  :
+No hp  :
+Waktu loading : 00:00
+Rute/tujuan : CGK - SUB
+driver  :
+Nopol  :
+No hp  :
+REQUEST ORDER KHUSUS 05/02/2026
+Waktu loading : 03:00
+Rute/tujuan : CGK -SUB
+driver  : Lailan
+Nopol  : S 9272 UP
+No hp  : +62 878-8686-1780</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: REQUEST TAMBAHAN ORDER ONCALL 04 FEBRUARI 2026:
+RAFAY
 2 UNIT TWB 50 CBM
-Lokasi : JNE SURABAYA
-Rute/ Tujuan   : SUX-CGK</t>
-  </si>
-  <si>
-    <t>Waktu loading : SEGERA 04 Mar 2026
-NAMA   : Wahyudi
-NOPOL : N 9549 UA
-NO HP : 085784422398
-Request Unit On Call Tgl 05 Mar 26
+Lokasi : CIKOKOL
+Waktu loading : SEGERA 04 FEBRUARI 2026
+Rute/tujuan : CGK - SUB
+driver  : AGUS
+Nopol  : D 9667 AF
+No hp  :08817021866
+Rev plat nomor pak @Nomor tidak dikenal @Nomor tidak dikenal @Nomor tidak dikenal ðŸ™ðŸ»</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: REQUEST ORDER ONCALL 04 FEBRUARI 2026:
+RAFAY
+1 unit Cddl 24 Cbm
+Lokasi : Megahub
+Waktu loading : SEGERA 04 FEBRUARI 2026
+Rute/tujuan : CGK - DPS
+driver 1 : Edi setiawan
+No hp  :0881023544597 
+Driver2 : Jatmiyanta
+No hp  :082118558105
+Nopol : F 9647 FH</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: REQUEST ULANG ORDER ONCALL 05 FEBRUARI 2026:
+2 UNIT TWB 50 CBM
+Lokasi : CIKOKOL
+Waktu loading : SEGERA 05 FEBRUARI 2026
+Rute/tujuan : CGK - TKG
+driver  :
+Nopol  :
+No hp  :</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: REQUEST ULANG ORDER ONCALL 05 FEBRUARI 2026:
+2 UNIT TWB 50 CBM
+Lokasi : CIKOKOL
+Waktu loading : SEGERA 05 FEBRUARI 2026
+Rute/tujuan : CGK - PLM
+driver  :
+Nopol  :
+No hp  :</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: REQUEST ULANG ORDER ONCALL 05 FEBRUARI 2026:
+2 UNIT TWB 50 CBM
+Lokasi : CIKOKOL
+Waktu loading : SEGERA 05 FEBRUARI 2026
+Rute/tujuan : CGK - PKU
+driver  : Siswanto
+Nopol  : B 9120 WXR
+No hp  : 081943564062
+Lokasi : CIKOKOL
+Waktu loading : SEGERA 05 FEBRUARI 2026
+Rute/tujuan : CGK - PKU
+driver  : 
+Nopol  : 
+No hp  :</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: REQUEST ULANG ORDER ONCALL 05 FEBRUARI 2026:
+2 UNIT TWB 50 CBM
+Lokasi : CIKOKOL
+Waktu loading : SEGERA 05 FEBRUARI 2026
+Rute/tujuan : CGK - MES
+driver  : feri irawan
+Nopol  : BK 8516 VV
+No hp  : 085219216210</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: REQUEST ULANG ORDER ONCALL 05 FEBRUARI 2026:
+RAFAY
+2 UNIT TWB 50 CBM
+Lokasi : CIKOKOL
+Waktu loading : SEGERA 05 FEBRUARI 2026
+Rute/tujuan : CGK - MES
+driver  : HADI
+Nopol  :B 9446 MV
+No hp  :+62 831-9621-8655</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: REQUEST ULANG ORDER ONCALL 05 FEBRUARI 2026:
+RAFAY
+2 UNIT TWB 50 CBM
+Lokasi : CIKOKOL
+Waktu loading : SEGERA 05 FEBRUARI 2026
+Rute/tujuan : CGK - MES
+driver  : A. Sukur 
+Nopol  :B 9477 KEU
+No hp  : 083169525183</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: REQUEST ORDER ULANG ONCALL
+5 UNIT TWB 50 CBM
+Lokasi : ARGOPANTES 
+Waktu loading : SEGERA
+Rute/tujuan : CGK - SUB
+RAFAY
+driver  : AKIYAT
+Nopol  : L 9722 UE
+No hp  :081281122738</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: REQUEST ULANG ORDER ONCALL 05 FEBRUARI 2025
+RAFAY
+2 UNIT TWB 50 CBM
+Lokasi : CIKOKOL
+Waktu loading : SEGERA 05 FEBRUARI 2025
+Rute/tujuan : CGK - PKU
+driver  : RYAN
+Nopol  : B 9084 VEH
+No hp  : 087837496810</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: REQUEST ORDER ULANG ONCALL
+5 UNIT TWB 50 CBM
+Lokasi : ARGOPANTES 
+Waktu loading : SEGERA
+Rute/tujuan : CGK - SUB
+driver  : HENDRA S.P
+Nopol  : D 9044 AG
+No hp  : +62 877-8667-6177
+Waktu loading : 18:00
+Rute/tujuan : CGK - SUB
+driver  :
+Nopol  :
+No hp  :
+Waktu loading : 21:00
+Rute/tujuan : CGK - SUB
+driver  :
+Nopol  :
+No hp  :
+Waktu loading : 00:00
+Rute/tujuan : CGK - SUB
+driver  :
+Nopol  :
+No hp  :
+REQUEST ORDER KHUSUS 06/02/2026
+Waktu loading : 03:00
+Rute/tujuan : CGK -SUB
+driver  :
+Nopol  :
+No hp  :</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: REQUEST ULANG ORDER ONCALL 05 FEBRUARI 2026:
+2 UNIT TWB 50 CBM
+Lokasi : CIKOKOL
+Waktu loading : SEGERA 05 FEBRUARI 2026
+Rute/tujuan : CGK - PLM
+driver  : SANDRI
+Nopol  : BE 9636 BU
+No hp  :+62 889-0702-0037</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: Request Unit On Call Tgl 05 Feb 26
+2 Unit  Cddl / 24 Cbm
+Lokasi : Cikarang
+Waktu loading : 06:00 06-02-26
+Rute/tujuan : CKR-Jateng Tentative
+Driver   : 
+Nopol  : 
+No Hp  :</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: Request Unit On Call Tgl 05 Feb 26
 1 Unit  Cddl / 24 Cbm
-Lokasi : Cikarang</t>
-  </si>
-  <si>
-    <t>Waktu loading : 06:00 06 Mar 26
-Rute/tujuan : CKR-JBR
-Driver   : miyanta
-Nopol  : F 9647 FH
-No Hp  :08118558105
-Request Unit On Call Tgl 05 Mar 26
+Lokasi : Cikarang
+Waktu loading : 03:00 06-02-26
+Rute/tujuan : CKR-Jateng Tentative
+Nama : Apar Rahmat 
+Nopol : E9406HB 
+NO TLP : 085971812879</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: Request Unit On Call Tgl 06 febuary 2026
 RAFAY
-1 Unit  Cddl / 24 Cbm
-Lokasi : Cikokol + Cikarang</t>
-  </si>
-  <si>
-    <t>Waktu loading : 03:00 06  Mar 26
-Rute/tujuan : CGK-PSR
-Driver   : Davit
-Nopol  : B 9726 SXW
-No Hp  :082117275166</t>
-  </si>
-  <si>
-    <t>REQUEST ORDER ONCALL
-05 MARET 2026:
-5 UNIT TWB 50 CBM
-Lokasi : ARGOPANTES</t>
-  </si>
-  <si>
-    <t>Waktu loading : 17:00 05-03-2026
-Rute/tujuan : CGK - SUB
-driver  : Iwan Hariono
-Nopol  : BL 8188 JP
-No Hp :081389976421
-Request Order Oncall  05 Maret  2026
-2 UNIT TWB 50 CBM
-Lokasi : JNE SURABAYA
-Rute/ Tujuan   : SUX-CGK</t>
-  </si>
-  <si>
-    <t>Waktu loading : SEGERA 05 Maret  2026
-Driver : Akiyat
-Nopol : L 9722 UE
-No HP :081281122738</t>
+3 unit twb 50 CBM
+Lokasi : ARGOPANTES 
+Waktu loading : SEGERA 06 febuary 2026
+Rute/tujuan : CGK- SUB
+driver  : M. iBNU
+Nopol  : L 9511 AL
+No hp  :082191633212</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: Request Unit On Call Tgl 06 febuary 2026
+2 unit twb 50 CBM
+Lokasi : JNE SUB
+Waktu loading : SEGERA 06 febuary 2026
+Rute/tujuan : SUB-CGK
+driver  : WAHYUDI
+Nopol  : N 9549 UA
+No hp  :085784422398</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: Request Unit On Call Tgl 06 febuary 2026
+2 unit twb 50 CBM
+Lokasi : JNE SUB
+Waktu loading : SEGERA 06 febuary 2026
+Rute/tujuan : SUB-CGK
+driver  : SOFYAN
+Nopol  : B 9679 WT
+No hp  : 082231837381</t>
+  </si>
+  <si>
+    <t>085353886066</t>
+  </si>
+  <si>
+    <t>085865762797</t>
+  </si>
+  <si>
+    <t>0 81231895971</t>
+  </si>
+  <si>
+    <t>08817021866</t>
+  </si>
+  <si>
+    <t>082118558105</t>
+  </si>
+  <si>
+    <t>081943564062</t>
+  </si>
+  <si>
+    <t>085219216210</t>
+  </si>
+  <si>
+    <t>0 83196218655</t>
+  </si>
+  <si>
+    <t>083169525183</t>
+  </si>
+  <si>
+    <t>081281122738</t>
+  </si>
+  <si>
+    <t>087837496810</t>
+  </si>
+  <si>
+    <t>0 87786676177</t>
+  </si>
+  <si>
+    <t>0 88907020037</t>
+  </si>
+  <si>
+    <t>085971812879</t>
+  </si>
+  <si>
+    <t>082191633212</t>
   </si>
   <si>
     <t>085784422398</t>
   </si>
   <si>
-    <t>08118558105</t>
-  </si>
-  <si>
-    <t>082117275166</t>
-  </si>
-  <si>
-    <t>081389976421</t>
-  </si>
-  <si>
-    <t>081281122738</t>
+    <t>082231837381</t>
   </si>
 </sst>
 </file>
@@ -553,7 +923,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:10">
@@ -593,19 +963,31 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="E2" t="s">
-        <v>23</v>
+        <v>31</v>
+      </c>
+      <c r="F2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G2" t="s">
+        <v>58</v>
+      </c>
+      <c r="H2" t="s">
+        <v>75</v>
       </c>
       <c r="I2" t="s">
-        <v>37</v>
+        <v>80</v>
+      </c>
+      <c r="J2" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -613,94 +995,124 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>18</v>
+        <v>23</v>
+      </c>
+      <c r="D3" t="s">
+        <v>27</v>
       </c>
       <c r="E3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G3" t="s">
+        <v>59</v>
+      </c>
+      <c r="H3" t="s">
+        <v>76</v>
+      </c>
+      <c r="I3" t="s">
+        <v>81</v>
+      </c>
+      <c r="J3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="B4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" t="s">
         <v>24</v>
       </c>
-      <c r="F3" t="s">
+      <c r="D4" t="s">
         <v>26</v>
       </c>
-      <c r="G3" t="s">
-        <v>31</v>
-      </c>
-      <c r="H3" t="s">
-        <v>36</v>
-      </c>
-      <c r="I3" t="s">
-        <v>38</v>
-      </c>
-      <c r="J3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" t="s">
-        <v>21</v>
-      </c>
       <c r="E4" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="F4" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="G4" t="s">
-        <v>32</v>
+        <v>60</v>
+      </c>
+      <c r="H4" t="s">
+        <v>77</v>
       </c>
       <c r="I4" t="s">
-        <v>39</v>
+        <v>82</v>
       </c>
       <c r="J4" t="s">
-        <v>45</v>
+        <v>102</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
         <v>12</v>
       </c>
+      <c r="B5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" t="s">
+        <v>28</v>
+      </c>
       <c r="E5" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="F5" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="G5" t="s">
-        <v>33</v>
+        <v>61</v>
+      </c>
+      <c r="H5" t="s">
+        <v>75</v>
       </c>
       <c r="I5" t="s">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="J5" t="s">
-        <v>46</v>
+        <v>103</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C6" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D6" t="s">
-        <v>22</v>
+        <v>27</v>
+      </c>
+      <c r="E6" t="s">
+        <v>34</v>
+      </c>
+      <c r="F6" t="s">
+        <v>45</v>
+      </c>
+      <c r="G6" t="s">
+        <v>62</v>
+      </c>
+      <c r="H6" t="s">
+        <v>75</v>
       </c>
       <c r="I6" t="s">
-        <v>41</v>
+        <v>84</v>
+      </c>
+      <c r="J6" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -708,45 +1120,446 @@
         <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C7" t="s">
-        <v>19</v>
+        <v>22</v>
+      </c>
+      <c r="D7" t="s">
+        <v>28</v>
       </c>
       <c r="E7" t="s">
-        <v>23</v>
-      </c>
-      <c r="F7" t="s">
-        <v>29</v>
-      </c>
-      <c r="G7" t="s">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="H7" t="s">
+        <v>75</v>
       </c>
       <c r="I7" t="s">
-        <v>42</v>
-      </c>
-      <c r="J7" t="s">
-        <v>47</v>
+        <v>85</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
         <v>13</v>
       </c>
-      <c r="F8" t="s">
+      <c r="B8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" t="s">
+        <v>22</v>
+      </c>
+      <c r="D8" t="s">
+        <v>28</v>
+      </c>
+      <c r="E8" t="s">
+        <v>36</v>
+      </c>
+      <c r="H8" t="s">
+        <v>75</v>
+      </c>
+      <c r="I8" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" t="s">
+        <v>28</v>
+      </c>
+      <c r="E9" t="s">
+        <v>37</v>
+      </c>
+      <c r="F9" t="s">
+        <v>46</v>
+      </c>
+      <c r="G9" t="s">
+        <v>63</v>
+      </c>
+      <c r="H9" t="s">
+        <v>75</v>
+      </c>
+      <c r="I9" t="s">
+        <v>87</v>
+      </c>
+      <c r="J9" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" t="s">
+        <v>22</v>
+      </c>
+      <c r="D10" t="s">
+        <v>28</v>
+      </c>
+      <c r="E10" t="s">
+        <v>38</v>
+      </c>
+      <c r="F10" t="s">
+        <v>47</v>
+      </c>
+      <c r="G10" t="s">
+        <v>64</v>
+      </c>
+      <c r="H10" t="s">
+        <v>75</v>
+      </c>
+      <c r="I10" t="s">
+        <v>88</v>
+      </c>
+      <c r="J10" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" t="s">
+        <v>25</v>
+      </c>
+      <c r="D11" t="s">
+        <v>28</v>
+      </c>
+      <c r="E11" t="s">
+        <v>38</v>
+      </c>
+      <c r="F11" t="s">
+        <v>48</v>
+      </c>
+      <c r="G11" t="s">
+        <v>65</v>
+      </c>
+      <c r="H11" t="s">
+        <v>75</v>
+      </c>
+      <c r="I11" t="s">
+        <v>89</v>
+      </c>
+      <c r="J11" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12" t="s">
+        <v>25</v>
+      </c>
+      <c r="D12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E12" t="s">
+        <v>38</v>
+      </c>
+      <c r="F12" t="s">
+        <v>49</v>
+      </c>
+      <c r="G12" t="s">
+        <v>66</v>
+      </c>
+      <c r="H12" t="s">
+        <v>75</v>
+      </c>
+      <c r="I12" t="s">
+        <v>90</v>
+      </c>
+      <c r="J12" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="B13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C13" t="s">
+        <v>24</v>
+      </c>
+      <c r="D13" t="s">
+        <v>26</v>
+      </c>
+      <c r="E13" t="s">
+        <v>33</v>
+      </c>
+      <c r="F13" t="s">
+        <v>50</v>
+      </c>
+      <c r="G13" t="s">
+        <v>67</v>
+      </c>
+      <c r="H13" t="s">
+        <v>75</v>
+      </c>
+      <c r="I13" t="s">
+        <v>91</v>
+      </c>
+      <c r="J13" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" t="s">
+        <v>20</v>
+      </c>
+      <c r="C14" t="s">
+        <v>22</v>
+      </c>
+      <c r="D14" t="s">
+        <v>28</v>
+      </c>
+      <c r="E14" t="s">
+        <v>37</v>
+      </c>
+      <c r="F14" t="s">
+        <v>51</v>
+      </c>
+      <c r="G14" t="s">
+        <v>68</v>
+      </c>
+      <c r="H14" t="s">
+        <v>75</v>
+      </c>
+      <c r="I14" t="s">
+        <v>92</v>
+      </c>
+      <c r="J14" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="B15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C15" t="s">
+        <v>24</v>
+      </c>
+      <c r="D15" t="s">
+        <v>26</v>
+      </c>
+      <c r="E15" t="s">
+        <v>33</v>
+      </c>
+      <c r="F15" t="s">
+        <v>52</v>
+      </c>
+      <c r="G15" t="s">
+        <v>69</v>
+      </c>
+      <c r="H15" t="s">
+        <v>77</v>
+      </c>
+      <c r="I15" t="s">
+        <v>93</v>
+      </c>
+      <c r="J15" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16" t="s">
+        <v>22</v>
+      </c>
+      <c r="D16" t="s">
+        <v>28</v>
+      </c>
+      <c r="E16" t="s">
+        <v>36</v>
+      </c>
+      <c r="F16" t="s">
+        <v>53</v>
+      </c>
+      <c r="G16" t="s">
+        <v>70</v>
+      </c>
+      <c r="H16" t="s">
+        <v>75</v>
+      </c>
+      <c r="I16" t="s">
+        <v>94</v>
+      </c>
+      <c r="J16" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="A17" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17" t="s">
+        <v>24</v>
+      </c>
+      <c r="D17" t="s">
+        <v>29</v>
+      </c>
+      <c r="E17" t="s">
+        <v>39</v>
+      </c>
+      <c r="H17" t="s">
+        <v>78</v>
+      </c>
+      <c r="I17" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="A18" t="s">
+        <v>15</v>
+      </c>
+      <c r="B18" t="s">
+        <v>17</v>
+      </c>
+      <c r="C18" t="s">
+        <v>24</v>
+      </c>
+      <c r="D18" t="s">
+        <v>29</v>
+      </c>
+      <c r="E18" t="s">
+        <v>39</v>
+      </c>
+      <c r="F18" t="s">
+        <v>54</v>
+      </c>
+      <c r="G18" t="s">
+        <v>71</v>
+      </c>
+      <c r="H18" t="s">
+        <v>79</v>
+      </c>
+      <c r="I18" t="s">
+        <v>96</v>
+      </c>
+      <c r="J18" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
+      <c r="A19" t="s">
+        <v>16</v>
+      </c>
+      <c r="B19" t="s">
+        <v>21</v>
+      </c>
+      <c r="C19" t="s">
+        <v>22</v>
+      </c>
+      <c r="D19" t="s">
+        <v>26</v>
+      </c>
+      <c r="E19" t="s">
+        <v>33</v>
+      </c>
+      <c r="F19" t="s">
+        <v>55</v>
+      </c>
+      <c r="G19" t="s">
+        <v>72</v>
+      </c>
+      <c r="H19" t="s">
+        <v>75</v>
+      </c>
+      <c r="I19" t="s">
+        <v>97</v>
+      </c>
+      <c r="J19" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="A20" t="s">
+        <v>16</v>
+      </c>
+      <c r="B20" t="s">
+        <v>20</v>
+      </c>
+      <c r="C20" t="s">
+        <v>22</v>
+      </c>
+      <c r="D20" t="s">
         <v>30</v>
       </c>
-      <c r="G8" t="s">
-        <v>35</v>
-      </c>
-      <c r="H8" t="s">
-        <v>36</v>
-      </c>
-      <c r="I8" t="s">
-        <v>43</v>
-      </c>
-      <c r="J8" t="s">
-        <v>48</v>
+      <c r="E20" t="s">
+        <v>40</v>
+      </c>
+      <c r="F20" t="s">
+        <v>56</v>
+      </c>
+      <c r="G20" t="s">
+        <v>73</v>
+      </c>
+      <c r="H20" t="s">
+        <v>75</v>
+      </c>
+      <c r="I20" t="s">
+        <v>98</v>
+      </c>
+      <c r="J20" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="A21" t="s">
+        <v>16</v>
+      </c>
+      <c r="B21" t="s">
+        <v>20</v>
+      </c>
+      <c r="C21" t="s">
+        <v>22</v>
+      </c>
+      <c r="D21" t="s">
+        <v>30</v>
+      </c>
+      <c r="E21" t="s">
+        <v>40</v>
+      </c>
+      <c r="F21" t="s">
+        <v>57</v>
+      </c>
+      <c r="G21" t="s">
+        <v>74</v>
+      </c>
+      <c r="H21" t="s">
+        <v>75</v>
+      </c>
+      <c r="I21" t="s">
+        <v>99</v>
+      </c>
+      <c r="J21" t="s">
+        <v>116</v>
       </c>
     </row>
   </sheetData>

--- a/output_orderan.xlsx
+++ b/output_orderan.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="120">
   <si>
     <t>DATE</t>
   </si>
@@ -52,15 +52,24 @@
     <t>05 / 02 / 2026</t>
   </si>
   <si>
+    <t>09 maret 2026</t>
+  </si>
+  <si>
     <t>04 februari 2026</t>
   </si>
   <si>
     <t>05 februari 2026</t>
   </si>
   <si>
+    <t>7 / 3 / 2026</t>
+  </si>
+  <si>
     <t>05 februari 2025</t>
   </si>
   <si>
+    <t>7 / 02 / 2026</t>
+  </si>
+  <si>
     <t>05 feb 26</t>
   </si>
   <si>
@@ -88,12 +97,12 @@
     <t>cddl</t>
   </si>
   <si>
+    <t>twb</t>
+  </si>
+  <si>
     <t>cbm</t>
   </si>
   <si>
-    <t>twb</t>
-  </si>
-  <si>
     <t>argopantes</t>
   </si>
   <si>
@@ -247,7 +256,7 @@
     <t>07 : 00</t>
   </si>
   <si>
-    <t>00 : 00</t>
+    <t>21</t>
   </si>
   <si>
     <t>06 : 00</t>
@@ -279,25 +288,25 @@
 No hp  :085865762797</t>
   </si>
   <si>
-    <t>[WA_TS] Akbar Rafay: REQUEST ORDER ULANG ONCALL
+    <t>[WA_TS] Akbar Rafay: REQUEST ORDER ULANG ONCALL 09 MARET 2026
 5 UNIT TWB 50 CBM
 Lokasi : ARGOPANTES 
-Waktu loading : SEGERA
+Waktu loading : SEGERA 09 MARET 2026
 Rute/tujuan : CGK - SUB
 driver  :
 Nopol  :
 No hp  :
-Waktu loading : 18:00
+Waktu loading : 18:00 09 MARET 2026
 Rute/tujuan : CGK - SUB
 driver  : m syaichoni
 Nopol  : N 8872 Rk
 No hp  : +62 812-3189-5971
-Waktu loading : 21:00
+Waktu loading : 21:00 09 MARET 2026
 Rute/tujuan : CGK - SUB
 driver  :
 Nopol  :
 No hp  :
-Waktu loading : 00:00
+Waktu loading : 00:00 09 MARET 2026
 Rute/tujuan : CGK - SUB
 driver  :
 Nopol  :
@@ -318,8 +327,7 @@
 Rute/tujuan : CGK - SUB
 driver  : AGUS
 Nopol  : D 9667 AF
-No hp  :08817021866
-Rev plat nomor pak @Nomor tidak dikenal @Nomor tidak dikenal @Nomor tidak dikenal ðŸ™ðŸ»</t>
+No hp  :08817021866</t>
   </si>
   <si>
     <t>[WA_TS] Akbar Rafay: REQUEST ORDER ONCALL 04 FEBRUARI 2026:
@@ -406,7 +414,7 @@
     <t>[WA_TS] Akbar Rafay: REQUEST ORDER ULANG ONCALL
 5 UNIT TWB 50 CBM
 Lokasi : ARGOPANTES 
-Waktu loading : SEGERA
+Waktu loading : SEGERA 7/3/2026
 Rute/tujuan : CGK - SUB
 RAFAY
 driver  : AKIYAT
@@ -428,22 +436,22 @@
     <t>[WA_TS] Akbar Rafay: REQUEST ORDER ULANG ONCALL
 5 UNIT TWB 50 CBM
 Lokasi : ARGOPANTES 
-Waktu loading : SEGERA
+Waktu loading : SEGERA 7/02/2026
 Rute/tujuan : CGK - SUB
 driver  : HENDRA S.P
 Nopol  : D 9044 AG
 No hp  : +62 877-8667-6177
-Waktu loading : 18:00
+Waktu loading : 18:00 7/02/2026
 Rute/tujuan : CGK - SUB
 driver  :
 Nopol  :
 No hp  :
-Waktu loading : 21:00
+Waktu loading : 21:00 7/02/2026
 Rute/tujuan : CGK - SUB
 driver  :
 Nopol  :
 No hp  :
-Waktu loading : 00:00
+Waktu loading : 00:00 7/02/2026
 Rute/tujuan : CGK - SUB
 driver  :
 Nopol  :
@@ -963,31 +971,31 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="H2" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="J2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -995,571 +1003,580 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D3" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E3" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F3" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="G3" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="H3" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="I3" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="J3" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="4" spans="1:10">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
       <c r="B4" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D4" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E4" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F4" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="G4" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="H4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I4" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="J4" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D5" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E5" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F5" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G5" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="H5" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I5" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="J5" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C6" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D6" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E6" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F6" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G6" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="H6" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I6" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J6" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C7" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D7" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E7" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="H7" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I7" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C8" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D8" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E8" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="H8" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I8" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C9" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D9" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E9" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F9" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="G9" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="H9" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I9" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="J9" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C10" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D10" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E10" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F10" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="G10" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="H10" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I10" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="J10" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D11" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E11" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F11" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="G11" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="H11" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I11" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="J11" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C12" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D12" t="s">
+        <v>31</v>
+      </c>
+      <c r="E12" t="s">
+        <v>41</v>
+      </c>
+      <c r="F12" t="s">
+        <v>52</v>
+      </c>
+      <c r="G12" t="s">
+        <v>69</v>
+      </c>
+      <c r="H12" t="s">
+        <v>78</v>
+      </c>
+      <c r="I12" t="s">
+        <v>93</v>
+      </c>
+      <c r="J12" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" t="s">
+        <v>22</v>
+      </c>
+      <c r="C13" t="s">
         <v>28</v>
       </c>
-      <c r="E12" t="s">
-        <v>38</v>
-      </c>
-      <c r="F12" t="s">
-        <v>49</v>
-      </c>
-      <c r="G12" t="s">
-        <v>66</v>
-      </c>
-      <c r="H12" t="s">
-        <v>75</v>
-      </c>
-      <c r="I12" t="s">
-        <v>90</v>
-      </c>
-      <c r="J12" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
-      <c r="B13" t="s">
-        <v>19</v>
-      </c>
-      <c r="C13" t="s">
-        <v>24</v>
-      </c>
       <c r="D13" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E13" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F13" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G13" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="H13" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I13" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="J13" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B14" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C14" t="s">
+        <v>25</v>
+      </c>
+      <c r="D14" t="s">
+        <v>31</v>
+      </c>
+      <c r="E14" t="s">
+        <v>40</v>
+      </c>
+      <c r="F14" t="s">
+        <v>54</v>
+      </c>
+      <c r="G14" t="s">
+        <v>71</v>
+      </c>
+      <c r="H14" t="s">
+        <v>78</v>
+      </c>
+      <c r="I14" t="s">
+        <v>95</v>
+      </c>
+      <c r="J14" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" t="s">
+        <v>17</v>
+      </c>
+      <c r="B15" t="s">
         <v>22</v>
       </c>
-      <c r="D14" t="s">
+      <c r="C15" t="s">
         <v>28</v>
       </c>
-      <c r="E14" t="s">
-        <v>37</v>
-      </c>
-      <c r="F14" t="s">
-        <v>51</v>
-      </c>
-      <c r="G14" t="s">
-        <v>68</v>
-      </c>
-      <c r="H14" t="s">
-        <v>75</v>
-      </c>
-      <c r="I14" t="s">
-        <v>92</v>
-      </c>
-      <c r="J14" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10">
-      <c r="B15" t="s">
-        <v>19</v>
-      </c>
-      <c r="C15" t="s">
-        <v>24</v>
-      </c>
       <c r="D15" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E15" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F15" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="G15" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="H15" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="I15" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="J15" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16" spans="1:10">
       <c r="A16" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C16" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D16" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E16" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F16" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G16" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="H16" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I16" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="J16" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C17" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D17" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E17" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="H17" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="I17" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
     </row>
     <row r="18" spans="1:10">
       <c r="A18" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B18" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C18" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D18" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E18" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F18" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G18" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H18" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="I18" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="J18" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
     </row>
     <row r="19" spans="1:10">
       <c r="A19" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B19" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C19" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D19" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E19" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F19" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G19" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="H19" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I19" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="J19" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C20" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D20" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E20" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F20" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="G20" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="H20" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I20" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="J20" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="21" spans="1:10">
       <c r="A21" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C21" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D21" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E21" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F21" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G21" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="H21" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I21" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="J21" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>

--- a/output_orderan.xlsx
+++ b/output_orderan.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>DATE</t>
   </si>
@@ -46,180 +46,54 @@
     <t>PHONE</t>
   </si>
   <si>
-    <t>3 maret 2026</t>
-  </si>
-  <si>
-    <t>03 maret 2026</t>
-  </si>
-  <si>
-    <t>04 maret 2026</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>cbm</t>
-  </si>
-  <si>
-    <t>cddl</t>
-  </si>
-  <si>
-    <t>twb 50 cbm</t>
+    <t>05 / 02</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>twb cbm</t>
   </si>
   <si>
     <t>argopantes</t>
   </si>
   <si>
-    <t>megahub</t>
-  </si>
-  <si>
-    <t>argo pantes</t>
-  </si>
-  <si>
-    <t>sub cgk</t>
-  </si>
-  <si>
-    <t>cgk jatim</t>
-  </si>
-  <si>
-    <t>cgk jateng tentatif</t>
-  </si>
-  <si>
-    <t>cgk pku</t>
-  </si>
-  <si>
-    <t>cgk mes</t>
-  </si>
-  <si>
-    <t>yuda</t>
-  </si>
-  <si>
-    <t>ari purnama</t>
-  </si>
-  <si>
-    <t>dedeng</t>
-  </si>
-  <si>
-    <t>jupri</t>
-  </si>
-  <si>
-    <t>misno</t>
-  </si>
-  <si>
-    <t>usman afandi</t>
-  </si>
-  <si>
-    <t>w 8973 uq</t>
-  </si>
-  <si>
-    <t>b 9383 txv</t>
-  </si>
-  <si>
-    <t>e 9426 aa</t>
-  </si>
-  <si>
-    <t>bm 9273 ro</t>
-  </si>
-  <si>
-    <t>bn 8038 rp</t>
-  </si>
-  <si>
-    <t>be 8456 fn</t>
+    <t>cgk pdg</t>
+  </si>
+  <si>
+    <t>ahmad</t>
+  </si>
+  <si>
+    <t>bm 8364 bb</t>
   </si>
   <si>
     <t>segera</t>
   </si>
   <si>
-    <t>REQUEST  ORDER  ONCALL  3 MARET 2026
-1 UNIT WB/50 CBM
-Lokasi : ARGOPANTES 
-Waktu loading : 23:00 3 MARET 2026
-Rute/tujuan : SUB - CGK
-driver  : Yuda
-Nopol  : W 8973 UQ
-No hp  : 089507296985</t>
-  </si>
-  <si>
-    <t>REQUEST ORDER ONCALL 03 maret 2026:
-3 unit Cddl 24 Cbm
-Lokasi : Megahub
-Waktu loading : 23:00 03 maret 2026
-Rute/tujuan : CGK - JATIM
-driver  : Ari purnama
-Nopol  : B 9383 TXV
-No hp : 082136689169
-Fyi pak  @Nomor tidak dikenal@Nomor tidak dikenal</t>
-  </si>
-  <si>
-    <t>REQUEST ULANG ORDER ONCALL 04 MARET 2026:
-8 unit Cddl 24 Cbm
-Lokasi : *argo pantes *
-Waktu loading : SEGERA 04 MARET 2026
-Rute/tujuan : *CGK - Jateng tentatif
-Nama : Dedeng
-Nopol :E 9426 Aa
-No.hp : 0895393659401</t>
-  </si>
-  <si>
-    <t>Request Unit On Call Tgl 04 Maret 2026
-5 UNIT TWB 50 CBM
+    <t>[WA_TS] Akbar Rafay: Request Unit On Call 04 FEBUARI 2026
+RAFAY
+3 UNIT TWB 50 Cbm
 Lokasi : ARGOPANTES
-Waktu loading : SEGERA 04 Maret 2026
-Rute/tujuan : CGK - PKU
-driver  : Jupri
-Nopol  : BM 9273 RO
-No Hp :082172471454</t>
-  </si>
-  <si>
-    <t>REQUEST ORDER ONCALL
-04 MARET 2026:
-5 UNIT TWB 50 CBM
+Waktu loading : SEGERA 04 FEBUARI 2026
+Rute/tujuan : CGK- PDG
+driver  : SUTRISNO
+Nopol  : BM 8364 AU
+No hp  :0853-5388-6066
 Lokasi : ARGOPANTES
-Waktu loading : SEGERA
-Rute/tujuan : CGK - MES
-driver  : Andi
-Nopol  : BE 8610 DB
-No Hp :081374328877
-Waktu loading : SEGERA
-Rute/tujuan : CGK - MES
-driver  : Misno
-Nopol  : BN 8038 RP
-No Hp :082211762649</t>
-  </si>
-  <si>
-    <t>REQUEST ORDER ONCALL
-04 MARET 2026:
-5 UNIT TWB 50 CBM
+Waktu loading : SEGERA 04 FEBUARI 2026
+Rute/tujuan : CGK- PDG
+driver  : AHMAD
+Nopol  : BM 8364 BB
+No hp  :0853-5388-6077
 Lokasi : ARGOPANTES
-Waktu loading : SEGERA
-Rute/tujuan : CGK - MES
-driver  : Usman Afandi
-Nopol  : BE 8456 FN
-No Hp : +62 853-7337-2594</t>
-  </si>
-  <si>
-    <t>089507296985</t>
-  </si>
-  <si>
-    <t>082136689169</t>
-  </si>
-  <si>
-    <t>0895393659401</t>
-  </si>
-  <si>
-    <t>082172471454</t>
-  </si>
-  <si>
-    <t>082211762649</t>
-  </si>
-  <si>
-    <t>0 85373372594</t>
+Waktu loading : 05/02/2026
+Rute/tujuan : CGK- PDG
+driver  : wahyudi
+Nopol  : BM 8364 BB
+No hp  :0853-5388-6077</t>
+  </si>
+  <si>
+    <t>085353886077</t>
   </si>
 </sst>
 </file>
@@ -577,7 +451,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:10">
@@ -617,185 +491,31 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" t="s">
         <v>13</v>
       </c>
-      <c r="C2" t="s">
+      <c r="E2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" t="s">
         <v>16</v>
       </c>
-      <c r="D2" t="s">
+      <c r="H2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" t="s">
         <v>19</v>
-      </c>
-      <c r="E2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F2" t="s">
-        <v>27</v>
-      </c>
-      <c r="G2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I2" t="s">
-        <v>40</v>
-      </c>
-      <c r="J2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G3" t="s">
-        <v>34</v>
-      </c>
-      <c r="I3" t="s">
-        <v>41</v>
-      </c>
-      <c r="J3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F4" t="s">
-        <v>29</v>
-      </c>
-      <c r="G4" t="s">
-        <v>35</v>
-      </c>
-      <c r="H4" t="s">
-        <v>39</v>
-      </c>
-      <c r="I4" t="s">
-        <v>42</v>
-      </c>
-      <c r="J4" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F5" t="s">
-        <v>30</v>
-      </c>
-      <c r="G5" t="s">
-        <v>36</v>
-      </c>
-      <c r="H5" t="s">
-        <v>39</v>
-      </c>
-      <c r="I5" t="s">
-        <v>43</v>
-      </c>
-      <c r="J5" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E6" t="s">
-        <v>26</v>
-      </c>
-      <c r="F6" t="s">
-        <v>31</v>
-      </c>
-      <c r="G6" t="s">
-        <v>37</v>
-      </c>
-      <c r="H6" t="s">
-        <v>39</v>
-      </c>
-      <c r="I6" t="s">
-        <v>44</v>
-      </c>
-      <c r="J6" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" t="s">
-        <v>18</v>
-      </c>
-      <c r="D7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E7" t="s">
-        <v>26</v>
-      </c>
-      <c r="F7" t="s">
-        <v>32</v>
-      </c>
-      <c r="G7" t="s">
-        <v>38</v>
-      </c>
-      <c r="H7" t="s">
-        <v>39</v>
-      </c>
-      <c r="I7" t="s">
-        <v>45</v>
-      </c>
-      <c r="J7" t="s">
-        <v>51</v>
       </c>
     </row>
   </sheetData>

--- a/output_orderan.xlsx
+++ b/output_orderan.xlsx
@@ -14,10 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
-  <si>
-    <t>DATE</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="120">
   <si>
     <t>UNIT_QTY</t>
   </si>
@@ -43,57 +40,540 @@
     <t>Original_Text</t>
   </si>
   <si>
+    <t>RO_DATE</t>
+  </si>
+  <si>
+    <t>LOAD_DATE</t>
+  </si>
+  <si>
     <t>PHONE</t>
   </si>
   <si>
-    <t>05 / 02</t>
+    <t>1</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>twb cbm</t>
+    <t>5</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>twb</t>
+  </si>
+  <si>
+    <t>cddl</t>
   </si>
   <si>
     <t>argopantes</t>
   </si>
   <si>
+    <t>megahub</t>
+  </si>
+  <si>
+    <t>cikokol</t>
+  </si>
+  <si>
+    <t>cikarang</t>
+  </si>
+  <si>
+    <t>jne sub</t>
+  </si>
+  <si>
     <t>cgk pdg</t>
   </si>
   <si>
-    <t>ahmad</t>
-  </si>
-  <si>
-    <t>bm 8364 bb</t>
+    <t>cgk jateng</t>
+  </si>
+  <si>
+    <t>cgk sub</t>
+  </si>
+  <si>
+    <t>cgk dps</t>
+  </si>
+  <si>
+    <t>cgk tkg</t>
+  </si>
+  <si>
+    <t>cgk plm</t>
+  </si>
+  <si>
+    <t>cgk pku</t>
+  </si>
+  <si>
+    <t>cgk mes</t>
+  </si>
+  <si>
+    <t>cgk sub rafay</t>
+  </si>
+  <si>
+    <t>ckrjateng tentative</t>
+  </si>
+  <si>
+    <t>subcgk</t>
+  </si>
+  <si>
+    <t>sutrisno</t>
+  </si>
+  <si>
+    <t>karyadi</t>
+  </si>
+  <si>
+    <t>m syaichoni</t>
+  </si>
+  <si>
+    <t>agus</t>
+  </si>
+  <si>
+    <t>jatmiyanta</t>
+  </si>
+  <si>
+    <t>siswanto</t>
+  </si>
+  <si>
+    <t>feri irawan</t>
+  </si>
+  <si>
+    <t>hadi</t>
+  </si>
+  <si>
+    <t>a . sukur</t>
+  </si>
+  <si>
+    <t>akiyat</t>
+  </si>
+  <si>
+    <t>ryan</t>
+  </si>
+  <si>
+    <t>hendra s . p</t>
+  </si>
+  <si>
+    <t>sandri</t>
+  </si>
+  <si>
+    <t>apar rahmat</t>
+  </si>
+  <si>
+    <t>m . ibnu</t>
+  </si>
+  <si>
+    <t>wahyudi</t>
+  </si>
+  <si>
+    <t>sofyan</t>
+  </si>
+  <si>
+    <t>bm 8364 au</t>
+  </si>
+  <si>
+    <t>ad 8517 ba</t>
+  </si>
+  <si>
+    <t>n 8872 rk</t>
+  </si>
+  <si>
+    <t>d 9667 af</t>
+  </si>
+  <si>
+    <t>f 9647 fh</t>
+  </si>
+  <si>
+    <t>b 9120 wxr</t>
+  </si>
+  <si>
+    <t>bk 8516 vv</t>
+  </si>
+  <si>
+    <t>b 9446 mv</t>
+  </si>
+  <si>
+    <t>b 9477 keu</t>
+  </si>
+  <si>
+    <t>l 9722 ue</t>
+  </si>
+  <si>
+    <t>b 9084 veh</t>
+  </si>
+  <si>
+    <t>d 9044 ag</t>
+  </si>
+  <si>
+    <t>be 9636 bu</t>
+  </si>
+  <si>
+    <t>e9406hb</t>
+  </si>
+  <si>
+    <t>l 9511 al</t>
+  </si>
+  <si>
+    <t>n 9549 ua</t>
+  </si>
+  <si>
+    <t>b 9679 wt</t>
   </si>
   <si>
     <t>segera</t>
+  </si>
+  <si>
+    <t>07 : 00</t>
+  </si>
+  <si>
+    <t>21 : 00</t>
+  </si>
+  <si>
+    <t>06 : 00</t>
+  </si>
+  <si>
+    <t>03 : 00</t>
   </si>
   <si>
     <t>[WA_TS] Akbar Rafay: Request Unit On Call 04 FEBUARI 2026
 RAFAY
-3 UNIT TWB 50 Cbm
+1 UNIT TWB 50 Cbm
 Lokasi : ARGOPANTES
 Waktu loading : SEGERA 04 FEBUARI 2026
 Rute/tujuan : CGK- PDG
 driver  : SUTRISNO
 Nopol  : BM 8364 AU
-No hp  :0853-5388-6066
-Lokasi : ARGOPANTES
-Waktu loading : SEGERA 04 FEBUARI 2026
-Rute/tujuan : CGK- PDG
-driver  : AHMAD
-Nopol  : BM 8364 BB
-No hp  :0853-5388-6077
-Lokasi : ARGOPANTES
-Waktu loading : 05/02/2026
-Rute/tujuan : CGK- PDG
-driver  : wahyudi
-Nopol  : BM 8364 BB
-No hp  :0853-5388-6077</t>
-  </si>
-  <si>
-    <t>085353886077</t>
+No hp  :0853-5388-6066</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: REQUEST ORDER ONCALL 04 FEBRUARI 2026:
+RAFAY
+3 unit Cddl 24 Cbm
+Lokasi : Megahub
+REQUEST ORDER KHUSUS 05/02/2026
+Waktu loading : 07:00
+Rute/tujuan : CGK - JATENG
+driver  : KARYADI
+Nopol  : AD 8517 BA
+No hp  :085865762797</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: REQUEST ORDER ULANG ONCALL 09 MARET 2026
+5 UNIT TWB 50 CBM
+Lokasi : ARGOPANTES 
+Waktu loading : SEGERA 09 MARET 2026
+Rute/tujuan : CGK - SUB
+driver  :
+Nopol  :
+No hp  :
+Waktu loading : 18:00 09 MARET 2026
+Rute/tujuan : CGK - SUB
+driver  : m syaichoni
+Nopol  : N 8872 Rk
+No hp  : +62 812-3189-5971
+Waktu loading : 21:00 09 MARET 2026
+Rute/tujuan : CGK - SUB
+driver  :
+Nopol  :
+No hp  :
+Waktu loading : 00:00 09 MARET 2026
+Rute/tujuan : CGK - SUB
+driver  :
+Nopol  :
+No hp  :
+REQUEST ORDER KHUSUS 05/02/2026
+Waktu loading : 03:00
+Rute/tujuan : CGK -SUB
+driver  : Lailan
+Nopol  : S 9272 UP
+No hp  : +62 878-8686-1780</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: REQUEST TAMBAHAN ORDER ONCALL 04 FEBRUARI 2026:
+RAFAY
+2 UNIT TWB 50 CBM
+Lokasi : CIKOKOL
+Waktu loading : SEGERA 04 FEBRUARI 2026
+Rute/tujuan : CGK - SUB
+driver  : AGUS
+Nopol  : D 9667 AF
+No hp  :08817021866</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: REQUEST ORDER ONCALL 04 FEBRUARI 2026:
+RAFAY
+1 unit Cddl 24 Cbm
+Lokasi : Megahub
+Waktu loading : SEGERA 04 FEBRUARI 2026
+Rute/tujuan : CGK - DPS
+driver 1 : Edi setiawan
+No hp  :0881023544597 
+driver 2 : Jatmiyanta
+No hp  :082118558105
+Nopol : F 9647 FH</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: REQUEST ULANG ORDER ONCALL 05 FEBRUARI 2026:
+2 UNIT TWB 50 CBM
+Lokasi : CIKOKOL
+Waktu loading : SEGERA 05 FEBRUARI 2026
+Rute/tujuan : CGK - TKG
+driver  :
+Nopol  :
+No hp  :</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: REQUEST ULANG ORDER ONCALL 05 FEBRUARI 2026:
+2 UNIT TWB 50 CBM
+Lokasi : CIKOKOL
+Waktu loading : SEGERA 05 FEBRUARI 2026
+Rute/tujuan : CGK - PLM
+driver  :
+Nopol  :
+No hp  :</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: REQUEST ULANG ORDER ONCALL 05 FEBRUARI 2026:
+2 UNIT TWB 50 CBM
+Lokasi : CIKOKOL
+Waktu loading : SEGERA 05 FEBRUARI 2026
+Rute/tujuan : CGK - PKU
+driver  : Siswanto
+Nopol  : B 9120 WXR
+No hp  : 081943564062
+Lokasi : CIKOKOL
+Waktu loading : SEGERA 05 FEBRUARI 2026
+Rute/tujuan : CGK - PKU
+driver  : 
+Nopol  : 
+No hp  :</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: REQUEST ULANG ORDER ONCALL 05 FEBRUARI 2026:
+2 UNIT TWB 50 CBM
+Lokasi : CIKOKOL
+Waktu loading : SEGERA 05 FEBRUARI 2026
+Rute/tujuan : CGK - MES
+driver  : feri irawan
+Nopol  : BK 8516 VV
+No hp  : 085219216210</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: REQUEST ULANG ORDER ONCALL 05 FEBRUARI 2026:
+RAFAY
+2 UNIT TWB 50 CBM
+Lokasi : CIKOKOL
+Waktu loading : SEGERA 05 FEBRUARI 2026
+Rute/tujuan : CGK - MES
+driver  : HADI
+Nopol  :B 9446 MV
+No hp  :+62 831-9621-8655</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: REQUEST ULANG ORDER ONCALL 05 FEBRUARI 2026:
+RAFAY
+2 UNIT TWB 50 CBM
+Lokasi : CIKOKOL
+Waktu loading : SEGERA 05 FEBRUARI 2026
+Rute/tujuan : CGK - MES
+driver  : A. Sukur 
+Nopol  :B 9477 KEU
+No hp  : 083169525183</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: REQUEST ORDER ULANG ONCALL
+5 UNIT TWB 50 CBM
+Lokasi : ARGOPANTES 
+Waktu loading : SEGERA 7/3/2026
+Rute/tujuan : CGK - SUB
+RAFAY
+driver  : AKIYAT
+Nopol  : L 9722 UE
+No hp  :081281122738</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: REQUEST ULANG ORDER ONCALL 05 FEBRUARI 2025
+RAFAY
+2 UNIT TWB 50 CBM
+Lokasi : CIKOKOL
+Waktu loading : SEGERA 05 FEBRUARI 2025
+Rute/tujuan : CGK - PKU
+driver  : RYAN
+Nopol  : B 9084 VEH
+No hp  : 087837496810</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: REQUEST ORDER ULANG ONCALL
+5 UNIT TWB 50 CBM
+Lokasi : ARGOPANTES 
+Waktu loading : SEGERA 7/02/2026
+Rute/tujuan : CGK - SUB
+driver  : HENDRA S.P
+Nopol  : D 9044 AG
+No hp  : +62 877-8667-6177
+Waktu loading : 18:00 7/02/2026
+Rute/tujuan : CGK - SUB
+driver  :
+Nopol  :
+No hp  :
+Waktu loading : 21:00 7/02/2026
+Rute/tujuan : CGK - SUB
+driver  :
+Nopol  :
+No hp  :
+Waktu loading : 00:00 7/02/2026
+Rute/tujuan : CGK - SUB
+driver  :
+Nopol  :
+No hp  :
+REQUEST ORDER KHUSUS 06/02/2026
+Waktu loading : 03:00
+Rute/tujuan : CGK -SUB
+driver  :
+Nopol  :
+No hp  :</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: REQUEST ULANG ORDER ONCALL 05 FEBRUARI 2026:
+2 UNIT TWB 50 CBM
+Lokasi : CIKOKOL
+Waktu loading : SEGERA 05 FEBRUARI 2026
+Rute/tujuan : CGK - PLM
+driver  : SANDRI
+Nopol  : BE 9636 BU
+No hp  :+62 889-0702-0037</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: Request Unit On Call Tgl 05 Feb 26
+2 Unit  Cddl / 24 Cbm
+Lokasi : Cikarang
+Waktu loading : 06:00 06-02-26
+Rute/tujuan : CKR-Jateng Tentative
+driver   : 
+Nopol  : 
+No hp  :</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: Request Unit On Call Tgl 05 Feb 26
+1 Unit  Cddl / 24 Cbm
+Lokasi : Cikarang
+Waktu loading : 03:00 06-02-26
+Rute/tujuan : CKR-Jateng Tentative
+Nama : Apar Rahmat 
+Nopol : E9406HB 
+No hp : 085971812879</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: Request Unit On Call Tgl 06 febuary 2026
+RAFAY
+3 unit twb 50 CBM
+Lokasi : ARGOPANTES 
+Waktu loading : SEGERA 06 febuary 2026
+Rute/tujuan : CGK- SUB
+driver  : M. iBNU
+Nopol  : L 9511 AL
+No hp  :082191633212</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: Request Unit On Call Tgl 06 febuary 2026
+2 unit twb 50 CBM
+Lokasi : JNE SUB
+Waktu loading : SEGERA 06 febuary 2026
+Rute/tujuan : SUB-CGK
+driver  : WAHYUDI
+Nopol  : N 9549 UA
+No hp  :085784422398</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: Request Unit On Call Tgl 06 febuary 2026
+2 unit twb 50 CBM
+Lokasi : JNE SUB
+Waktu loading : SEGERA 06 febuary 2026
+Rute/tujuan : SUB-CGK
+driver  : SOFYAN
+Nopol  : B 9679 WT
+No hp  : 082231837381</t>
+  </si>
+  <si>
+    <t>04 febuari 2026</t>
+  </si>
+  <si>
+    <t>04 februari 2026</t>
+  </si>
+  <si>
+    <t>09 maret 2026</t>
+  </si>
+  <si>
+    <t>05 februari 2026</t>
+  </si>
+  <si>
+    <t>05 februari 2025</t>
+  </si>
+  <si>
+    <t>05 feb 26</t>
+  </si>
+  <si>
+    <t>06 febuary 2026</t>
+  </si>
+  <si>
+    <t>05 / 02 / 2026</t>
+  </si>
+  <si>
+    <t>7 / 3 / 2026</t>
+  </si>
+  <si>
+    <t>7 / 02 / 2026</t>
+  </si>
+  <si>
+    <t>06 2026</t>
+  </si>
+  <si>
+    <t>085353886066</t>
+  </si>
+  <si>
+    <t>085865762797</t>
+  </si>
+  <si>
+    <t>0 81231895971</t>
+  </si>
+  <si>
+    <t>08817021866</t>
+  </si>
+  <si>
+    <t>082118558105</t>
+  </si>
+  <si>
+    <t>081943564062</t>
+  </si>
+  <si>
+    <t>085219216210</t>
+  </si>
+  <si>
+    <t>0 83196218655</t>
+  </si>
+  <si>
+    <t>083169525183</t>
+  </si>
+  <si>
+    <t>081281122738</t>
+  </si>
+  <si>
+    <t>087837496810</t>
+  </si>
+  <si>
+    <t>0 87786676177</t>
+  </si>
+  <si>
+    <t>0 88907020037</t>
+  </si>
+  <si>
+    <t>085971812879</t>
+  </si>
+  <si>
+    <t>082191633212</t>
+  </si>
+  <si>
+    <t>085784422398</t>
+  </si>
+  <si>
+    <t>082231837381</t>
   </si>
 </sst>
 </file>
@@ -451,10 +931,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -485,37 +965,669 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:10">
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F2" t="s">
+        <v>50</v>
+      </c>
+      <c r="G2" t="s">
+        <v>67</v>
+      </c>
+      <c r="H2" t="s">
+        <v>72</v>
+      </c>
+      <c r="I2" t="s">
+        <v>92</v>
+      </c>
+      <c r="J2" t="s">
+        <v>92</v>
+      </c>
+      <c r="K2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F3" t="s">
+        <v>51</v>
+      </c>
+      <c r="G3" t="s">
+        <v>68</v>
+      </c>
+      <c r="H3" t="s">
+        <v>73</v>
+      </c>
+      <c r="I3" t="s">
+        <v>93</v>
+      </c>
+      <c r="J3" t="s">
+        <v>99</v>
+      </c>
+      <c r="K3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F4" t="s">
+        <v>52</v>
+      </c>
+      <c r="G4" t="s">
+        <v>69</v>
+      </c>
+      <c r="H4" t="s">
+        <v>74</v>
+      </c>
+      <c r="I4" t="s">
+        <v>94</v>
+      </c>
+      <c r="J4" t="s">
+        <v>94</v>
+      </c>
+      <c r="K4" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" t="s">
+        <v>36</v>
+      </c>
+      <c r="F5" t="s">
+        <v>53</v>
+      </c>
+      <c r="G5" t="s">
+        <v>67</v>
+      </c>
+      <c r="H5" t="s">
+        <v>75</v>
+      </c>
+      <c r="I5" t="s">
+        <v>93</v>
+      </c>
+      <c r="J5" t="s">
+        <v>93</v>
+      </c>
+      <c r="K5" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" t="s">
         <v>11</v>
       </c>
-      <c r="C2" t="s">
+      <c r="B6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F6" t="s">
+        <v>54</v>
+      </c>
+      <c r="G6" t="s">
+        <v>67</v>
+      </c>
+      <c r="H6" t="s">
+        <v>76</v>
+      </c>
+      <c r="I6" t="s">
+        <v>93</v>
+      </c>
+      <c r="J6" t="s">
+        <v>93</v>
+      </c>
+      <c r="K6" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G7" t="s">
+        <v>67</v>
+      </c>
+      <c r="H7" t="s">
+        <v>77</v>
+      </c>
+      <c r="I7" t="s">
+        <v>95</v>
+      </c>
+      <c r="J7" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" t="s">
+        <v>27</v>
+      </c>
+      <c r="G8" t="s">
+        <v>67</v>
+      </c>
+      <c r="H8" t="s">
+        <v>78</v>
+      </c>
+      <c r="I8" t="s">
+        <v>95</v>
+      </c>
+      <c r="J8" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" t="s">
+        <v>28</v>
+      </c>
+      <c r="E9" t="s">
+        <v>38</v>
+      </c>
+      <c r="F9" t="s">
+        <v>55</v>
+      </c>
+      <c r="G9" t="s">
+        <v>67</v>
+      </c>
+      <c r="H9" t="s">
+        <v>79</v>
+      </c>
+      <c r="I9" t="s">
+        <v>95</v>
+      </c>
+      <c r="J9" t="s">
+        <v>95</v>
+      </c>
+      <c r="K9" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" t="s">
+        <v>29</v>
+      </c>
+      <c r="E10" t="s">
+        <v>39</v>
+      </c>
+      <c r="F10" t="s">
+        <v>56</v>
+      </c>
+      <c r="G10" t="s">
+        <v>67</v>
+      </c>
+      <c r="H10" t="s">
+        <v>80</v>
+      </c>
+      <c r="I10" t="s">
+        <v>95</v>
+      </c>
+      <c r="J10" t="s">
+        <v>95</v>
+      </c>
+      <c r="K10" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" t="s">
+        <v>29</v>
+      </c>
+      <c r="E11" t="s">
+        <v>40</v>
+      </c>
+      <c r="F11" t="s">
+        <v>57</v>
+      </c>
+      <c r="G11" t="s">
+        <v>67</v>
+      </c>
+      <c r="H11" t="s">
+        <v>81</v>
+      </c>
+      <c r="I11" t="s">
+        <v>95</v>
+      </c>
+      <c r="J11" t="s">
+        <v>95</v>
+      </c>
+      <c r="K11" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" t="s">
+        <v>15</v>
+      </c>
+      <c r="C12" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" t="s">
+        <v>29</v>
+      </c>
+      <c r="E12" t="s">
+        <v>41</v>
+      </c>
+      <c r="F12" t="s">
+        <v>58</v>
+      </c>
+      <c r="G12" t="s">
+        <v>67</v>
+      </c>
+      <c r="H12" t="s">
+        <v>82</v>
+      </c>
+      <c r="I12" t="s">
+        <v>95</v>
+      </c>
+      <c r="J12" t="s">
+        <v>95</v>
+      </c>
+      <c r="K12" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" t="s">
+        <v>15</v>
+      </c>
+      <c r="C13" t="s">
+        <v>17</v>
+      </c>
+      <c r="D13" t="s">
+        <v>30</v>
+      </c>
+      <c r="E13" t="s">
+        <v>42</v>
+      </c>
+      <c r="F13" t="s">
+        <v>59</v>
+      </c>
+      <c r="G13" t="s">
+        <v>67</v>
+      </c>
+      <c r="H13" t="s">
+        <v>83</v>
+      </c>
+      <c r="J13" t="s">
+        <v>100</v>
+      </c>
+      <c r="K13" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" t="s">
+        <v>15</v>
+      </c>
+      <c r="C14" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14" t="s">
+        <v>28</v>
+      </c>
+      <c r="E14" t="s">
+        <v>43</v>
+      </c>
+      <c r="F14" t="s">
+        <v>60</v>
+      </c>
+      <c r="G14" t="s">
+        <v>67</v>
+      </c>
+      <c r="H14" t="s">
+        <v>84</v>
+      </c>
+      <c r="I14" t="s">
+        <v>96</v>
+      </c>
+      <c r="J14" t="s">
+        <v>96</v>
+      </c>
+      <c r="K14" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" t="s">
+        <v>15</v>
+      </c>
+      <c r="C15" t="s">
+        <v>17</v>
+      </c>
+      <c r="D15" t="s">
+        <v>24</v>
+      </c>
+      <c r="E15" t="s">
+        <v>44</v>
+      </c>
+      <c r="F15" t="s">
+        <v>61</v>
+      </c>
+      <c r="G15" t="s">
+        <v>69</v>
+      </c>
+      <c r="H15" t="s">
+        <v>85</v>
+      </c>
+      <c r="J15" t="s">
+        <v>101</v>
+      </c>
+      <c r="K15" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" t="s">
+        <v>15</v>
+      </c>
+      <c r="C16" t="s">
+        <v>19</v>
+      </c>
+      <c r="D16" t="s">
+        <v>27</v>
+      </c>
+      <c r="E16" t="s">
+        <v>45</v>
+      </c>
+      <c r="F16" t="s">
+        <v>62</v>
+      </c>
+      <c r="G16" t="s">
+        <v>67</v>
+      </c>
+      <c r="H16" t="s">
+        <v>86</v>
+      </c>
+      <c r="I16" t="s">
+        <v>95</v>
+      </c>
+      <c r="J16" t="s">
+        <v>95</v>
+      </c>
+      <c r="K16" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
+      <c r="A17" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C17" t="s">
+        <v>20</v>
+      </c>
+      <c r="D17" t="s">
+        <v>31</v>
+      </c>
+      <c r="G17" t="s">
+        <v>70</v>
+      </c>
+      <c r="H17" t="s">
+        <v>87</v>
+      </c>
+      <c r="I17" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
+      <c r="A18" t="s">
+        <v>11</v>
+      </c>
+      <c r="B18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18" t="s">
+        <v>20</v>
+      </c>
+      <c r="D18" t="s">
+        <v>31</v>
+      </c>
+      <c r="E18" t="s">
+        <v>46</v>
+      </c>
+      <c r="F18" t="s">
+        <v>63</v>
+      </c>
+      <c r="G18" t="s">
+        <v>71</v>
+      </c>
+      <c r="H18" t="s">
+        <v>88</v>
+      </c>
+      <c r="I18" t="s">
+        <v>97</v>
+      </c>
+      <c r="K18" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
+      <c r="A19" t="s">
         <v>12</v>
       </c>
-      <c r="D2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="B19" t="s">
+        <v>15</v>
+      </c>
+      <c r="C19" t="s">
+        <v>17</v>
+      </c>
+      <c r="D19" t="s">
+        <v>24</v>
+      </c>
+      <c r="E19" t="s">
+        <v>47</v>
+      </c>
+      <c r="F19" t="s">
+        <v>64</v>
+      </c>
+      <c r="G19" t="s">
+        <v>67</v>
+      </c>
+      <c r="H19" t="s">
+        <v>89</v>
+      </c>
+      <c r="I19" t="s">
+        <v>98</v>
+      </c>
+      <c r="J19" t="s">
+        <v>98</v>
+      </c>
+      <c r="K19" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
+      <c r="A20" t="s">
         <v>14</v>
       </c>
-      <c r="F2" t="s">
+      <c r="B20" t="s">
         <v>15</v>
       </c>
-      <c r="G2" t="s">
-        <v>16</v>
-      </c>
-      <c r="H2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I2" t="s">
-        <v>18</v>
-      </c>
-      <c r="J2" t="s">
-        <v>19</v>
+      <c r="C20" t="s">
+        <v>21</v>
+      </c>
+      <c r="D20" t="s">
+        <v>32</v>
+      </c>
+      <c r="E20" t="s">
+        <v>48</v>
+      </c>
+      <c r="F20" t="s">
+        <v>65</v>
+      </c>
+      <c r="G20" t="s">
+        <v>67</v>
+      </c>
+      <c r="H20" t="s">
+        <v>90</v>
+      </c>
+      <c r="I20" t="s">
+        <v>98</v>
+      </c>
+      <c r="J20" t="s">
+        <v>102</v>
+      </c>
+      <c r="K20" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
+      <c r="A21" t="s">
+        <v>14</v>
+      </c>
+      <c r="B21" t="s">
+        <v>15</v>
+      </c>
+      <c r="C21" t="s">
+        <v>21</v>
+      </c>
+      <c r="D21" t="s">
+        <v>32</v>
+      </c>
+      <c r="E21" t="s">
+        <v>49</v>
+      </c>
+      <c r="F21" t="s">
+        <v>66</v>
+      </c>
+      <c r="G21" t="s">
+        <v>67</v>
+      </c>
+      <c r="H21" t="s">
+        <v>91</v>
+      </c>
+      <c r="I21" t="s">
+        <v>98</v>
+      </c>
+      <c r="J21" t="s">
+        <v>102</v>
+      </c>
+      <c r="K21" t="s">
+        <v>119</v>
       </c>
     </row>
   </sheetData>

--- a/output_orderan.xlsx
+++ b/output_orderan.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="131">
   <si>
     <t>UNIT_QTY</t>
   </si>
@@ -43,24 +43,24 @@
     <t>RO_DATE</t>
   </si>
   <si>
+    <t>PHONE</t>
+  </si>
+  <si>
     <t>LOAD_DATE</t>
   </si>
   <si>
-    <t>PHONE</t>
+    <t>5</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>2</t>
   </si>
   <si>
     <t>1</t>
   </si>
   <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
     <t>twb</t>
   </si>
   <si>
@@ -70,510 +70,512 @@
     <t>argopantes</t>
   </si>
   <si>
+    <t>cikokol</t>
+  </si>
+  <si>
     <t>megahub</t>
   </si>
   <si>
-    <t>cikokol</t>
-  </si>
-  <si>
-    <t>cikarang</t>
-  </si>
-  <si>
-    <t>jne sub</t>
-  </si>
-  <si>
-    <t>cgk pdg</t>
+    <t>cikokol + cikarang</t>
+  </si>
+  <si>
+    <t>pku</t>
+  </si>
+  <si>
+    <t>plm</t>
+  </si>
+  <si>
+    <t>mes</t>
+  </si>
+  <si>
+    <t>jne surabaya</t>
+  </si>
+  <si>
+    <t>cgk pku</t>
+  </si>
+  <si>
+    <t>cgk mes</t>
+  </si>
+  <si>
+    <t>twb 50 cbm</t>
+  </si>
+  <si>
+    <t>cgk jatim tentatif</t>
   </si>
   <si>
     <t>cgk jateng</t>
   </si>
   <si>
-    <t>cgk sub</t>
-  </si>
-  <si>
-    <t>cgk dps</t>
-  </si>
-  <si>
-    <t>cgk tkg</t>
-  </si>
-  <si>
-    <t>cgk plm</t>
-  </si>
-  <si>
-    <t>cgk pku</t>
-  </si>
-  <si>
-    <t>cgk mes</t>
-  </si>
-  <si>
-    <t>cgk sub rafay</t>
-  </si>
-  <si>
-    <t>ckrjateng tentative</t>
-  </si>
-  <si>
-    <t>subcgk</t>
-  </si>
-  <si>
-    <t>sutrisno</t>
-  </si>
-  <si>
-    <t>karyadi</t>
-  </si>
-  <si>
-    <t>m syaichoni</t>
-  </si>
-  <si>
-    <t>agus</t>
-  </si>
-  <si>
-    <t>jatmiyanta</t>
+    <t>cgkjbr</t>
+  </si>
+  <si>
+    <t>suxcgk</t>
+  </si>
+  <si>
+    <t>mengri</t>
+  </si>
+  <si>
+    <t>sulis</t>
+  </si>
+  <si>
+    <t>agung</t>
+  </si>
+  <si>
+    <t>manulang</t>
+  </si>
+  <si>
+    <t>samsul</t>
+  </si>
+  <si>
+    <t>akiyat</t>
+  </si>
+  <si>
+    <t>simare</t>
+  </si>
+  <si>
+    <t>fajri</t>
+  </si>
+  <si>
+    <t>manulang noa€¦</t>
+  </si>
+  <si>
+    <t>rajiev fikri</t>
+  </si>
+  <si>
+    <t>alex s</t>
+  </si>
+  <si>
+    <t>arif</t>
   </si>
   <si>
     <t>siswanto</t>
   </si>
   <si>
+    <t>kudir</t>
+  </si>
+  <si>
+    <t>davit</t>
+  </si>
+  <si>
     <t>feri irawan</t>
   </si>
   <si>
-    <t>hadi</t>
-  </si>
-  <si>
-    <t>a . sukur</t>
-  </si>
-  <si>
-    <t>akiyat</t>
-  </si>
-  <si>
-    <t>ryan</t>
-  </si>
-  <si>
-    <t>hendra s . p</t>
-  </si>
-  <si>
     <t>sandri</t>
   </si>
   <si>
-    <t>apar rahmat</t>
-  </si>
-  <si>
-    <t>m . ibnu</t>
-  </si>
-  <si>
-    <t>wahyudi</t>
-  </si>
-  <si>
-    <t>sofyan</t>
-  </si>
-  <si>
-    <t>bm 8364 au</t>
-  </si>
-  <si>
-    <t>ad 8517 ba</t>
-  </si>
-  <si>
-    <t>n 8872 rk</t>
-  </si>
-  <si>
-    <t>d 9667 af</t>
-  </si>
-  <si>
-    <t>f 9647 fh</t>
+    <t>febrianto</t>
+  </si>
+  <si>
+    <t>m doni saputra</t>
+  </si>
+  <si>
+    <t>habib</t>
+  </si>
+  <si>
+    <t>bm 8279 au</t>
+  </si>
+  <si>
+    <t>l 9579 uk</t>
+  </si>
+  <si>
+    <t>bk 8208 vy</t>
+  </si>
+  <si>
+    <t>b 9019 uex</t>
+  </si>
+  <si>
+    <t>b 9771 uew</t>
+  </si>
+  <si>
+    <t>l 9722 ue</t>
+  </si>
+  <si>
+    <t>bk 8639 fj</t>
+  </si>
+  <si>
+    <t>b 9241 fxs</t>
+  </si>
+  <si>
+    <t>b 9591 uxx</t>
+  </si>
+  <si>
+    <t>b 9411 vxr</t>
+  </si>
+  <si>
+    <t>b 9209 nck</t>
   </si>
   <si>
     <t>b 9120 wxr</t>
   </si>
   <si>
-    <t>bk 8516 vv</t>
-  </si>
-  <si>
-    <t>b 9446 mv</t>
-  </si>
-  <si>
-    <t>b 9477 keu</t>
-  </si>
-  <si>
-    <t>l 9722 ue</t>
-  </si>
-  <si>
-    <t>b 9084 veh</t>
-  </si>
-  <si>
-    <t>d 9044 ag</t>
+    <t>b 9380 uex</t>
+  </si>
+  <si>
+    <t>b 9726 sxw</t>
+  </si>
+  <si>
+    <t>bk 8516 w</t>
   </si>
   <si>
     <t>be 9636 bu</t>
   </si>
   <si>
-    <t>e9406hb</t>
-  </si>
-  <si>
-    <t>l 9511 al</t>
-  </si>
-  <si>
-    <t>n 9549 ua</t>
-  </si>
-  <si>
-    <t>b 9679 wt</t>
+    <t>ba 9980 ps</t>
+  </si>
+  <si>
+    <t>bd 8423 b</t>
+  </si>
+  <si>
+    <t>l 8336 uv</t>
+  </si>
+  <si>
+    <t>02 : 00</t>
   </si>
   <si>
     <t>segera</t>
   </si>
   <si>
+    <t>23 : 00</t>
+  </si>
+  <si>
+    <t>03 : 00</t>
+  </si>
+  <si>
+    <t>18 : 00</t>
+  </si>
+  <si>
     <t>07 : 00</t>
   </si>
   <si>
-    <t>21 : 00</t>
-  </si>
-  <si>
-    <t>06 : 00</t>
-  </si>
-  <si>
-    <t>03 : 00</t>
-  </si>
-  <si>
-    <t>[WA_TS] Akbar Rafay: Request Unit On Call 04 FEBUARI 2026
+    <t>[WA_TS] Akbar Rafay: REQUEST ORDER ONCALL 13 FEBRUARI 2026:
+5 UNIT TWB 50 Cbm
+Lokasi : ARGOPANTES
+REQUEST ORDER KHUSUS 14-02-2026
+Waktu loading : 02:00
+Rute/tujuan : CGK - PKU
+driver  : mengri
+Nopol : BM 8279 AU
+No hp : 085364056583</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: REQUEST ORDER ONCALL ULANG 13 FEBRUARI 2026:
+3 UNIT TWB 50 CBM
+Lokasi : CIKOKOL
+Waktu loading : SEGERA 13 FEBRUARI 2026
+Rute/tujuan : CGK - MES
+driver  :Sulis
+Nopol  :L 9579 UK
+No hp  :085225394209</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: REQUEST ORDER ONCALL 13 FEBRUARI 2026:
+5 UNIT TWB 50 Cbm
+Lokasi : ARGOPANTES
+Waktu loading : 23:00 13 FEBRUARI 2026
+Rute/tujuan : CGK - PKU
+driver  : Agung
+Nopol  : BK 8208 VY
+No hp  : 082385989323</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: REQUEST ORDER ONCALL ULANG 13 FEBRUARI 2026:
+3 UNIT TWB 50 CBM
+Lokasi : CIKOKOL
+Waktu loading : SEGERA 13 FEBRUARI 2026
+Rute/tujuan : CGK - MES
+driver  : Manulang
+Nopol  :B 9019 UEX
+No hp  : +62 813-7076-9496</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: REQUEST ORDER ONCALL ULANG 13 FEBRUARI 2026:
+3 UNIT TWB 50 CBM
+Lokasi : CIKOKOL
+Waktu loading : SEGERA 13 FEBRUARI 2026
+Rute/tujuan : CGK - MES
+driver  : SAMSUL
+Nopol  :B 9771 UEW
+No hp  : +62 822-2851-6922</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: REQUEST ORDER ONCALL
+Tanggal : 12 Februari 2026
+Rute/tujuan : CGK - SUB
+Unit/Type : TWB 50 Cbm 
+Nopol : L 9722 UE
+driver : Akiyat
+No hp : 0812-8112-2738
+Lokasi Loading : ARGOPANTES
+Waktu loading : 03:00 7/3/2026</t>
+  </si>
+  <si>
+    <t>REQUEST ORDER ONCALL ULANG
+Tanggal : 13 Februari 2026
+Rute/tujuan : CGK - MES
+Unit/Type : TWB 50 CBM
+Nopol : BK 8639 FJ
+driver : SIMARE
+No hp : +62 812-6934-5748
+Lokasi Loading : CIKOKOL
+Waktu loading : 03:00 7/3/2026</t>
+  </si>
+  <si>
+    <t>REQUEST ORDER ONCALL
+Tanggal : 13 Februari 2026
+Rute/tujuan : CGK - PKU
+Unit/Type : TWB 50 CBM
+Nopol : B 9241 FXS
+driver : FAJRI
+No hp : 081382418508
+Lokasi Loading : ARGOPANTES
+Waktu loading : 18:00 7/3/2026</t>
+  </si>
+  <si>
+    <t>REQUEST ORDER ONCALL
+Tanggal : 13 FEBRUARI 2026
+Rute/tujuan : CGK - MES
+Unit/Type :  TWB 50 CBM
+Nopol : B 9019 UEX
+driver : Manulang
+Noâ€¦</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: REQUEST ORDER ONCALL 15 FEBRUARI 2026:
+2 unit Cddl 24 Cbm
+Lokasi : ARGOPANTES
+Waktu loading : SEGERA 15 FEBRUARI 2026
+Rute/tujuan : CGK - JATIM TENTATIF
+driver  : Rajiev Fikri
+Nopol  : B 9591 UXX
+No hp  : 088290294126
+Waktu loading : SEGERA 15 FEBRUARI 2026</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: REQUEST ORDER ONCALL 15 FEBRUARI 2026
+2 UNIT CDDL 24 Cbm
+Lokasi : MEGAHUB
+Waktu loading : SEGERA 15 FEBRUARI 2026
+Rute/tujuan : CGK - JATENG
+driver  : Alex S
+Nopol  : B 9411 VXR
+No hp  : 088212698834</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: Request Unit On Call Tgl 16 Feb 26
 RAFAY
-1 UNIT TWB 50 Cbm
+1 Unit  Cddl / 24 Cbm
+Lokasi : Cikokol + Cikarang
+Waktu loading : 03:00 17-02-26
+Rute/tujuan : CGK-JBR
+driver   : Arif
+Nopol  :  B 9209 NCK
+No hp :081328851819</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: REQUEST  ORDER  ONCALL  17 FEBRUARI 2026
+2 UNIT TWB 50 CBM
 Lokasi : ARGOPANTES
-Waktu loading : SEGERA 04 FEBUARI 2026
-Rute/tujuan : CGK- PDG
-driver  : SUTRISNO
-Nopol  : BM 8364 AU
-No hp  :0853-5388-6066</t>
-  </si>
-  <si>
-    <t>[WA_TS] Akbar Rafay: REQUEST ORDER ONCALL 04 FEBRUARI 2026:
-RAFAY
-3 unit Cddl 24 Cbm
-Lokasi : Megahub
-REQUEST ORDER KHUSUS 05/02/2026
-Waktu loading : 07:00
-Rute/tujuan : CGK - JATENG
-driver  : KARYADI
-Nopol  : AD 8517 BA
-No hp  :085865762797</t>
-  </si>
-  <si>
-    <t>[WA_TS] Akbar Rafay: REQUEST ORDER ULANG ONCALL 09 MARET 2026
-5 UNIT TWB 50 CBM
-Lokasi : ARGOPANTES 
-Waktu loading : SEGERA 09 MARET 2026
-Rute/tujuan : CGK - SUB
-driver  :
-Nopol  :
-No hp  :
-Waktu loading : 18:00 09 MARET 2026
-Rute/tujuan : CGK - SUB
-driver  : m syaichoni
-Nopol  : N 8872 Rk
-No hp  : +62 812-3189-5971
-Waktu loading : 21:00 09 MARET 2026
-Rute/tujuan : CGK - SUB
-driver  :
-Nopol  :
-No hp  :
-Waktu loading : 00:00 09 MARET 2026
-Rute/tujuan : CGK - SUB
-driver  :
-Nopol  :
-No hp  :
-REQUEST ORDER KHUSUS 05/02/2026
-Waktu loading : 03:00
-Rute/tujuan : CGK -SUB
-driver  : Lailan
-Nopol  : S 9272 UP
-No hp  : +62 878-8686-1780</t>
-  </si>
-  <si>
-    <t>[WA_TS] Akbar Rafay: REQUEST TAMBAHAN ORDER ONCALL 04 FEBRUARI 2026:
-RAFAY
+Rute/tujuan : cgk - PKU
+Waktu loading : SEGERA 17 FEBRUARI 2026
+driver 	: SISWANTO
+Nopol	: B 9120 WXR
+No hp	:081943564062</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: REQUEST  ORDER  ONCALL  17 FEBRUARI 2026
 2 UNIT TWB 50 CBM
-Lokasi : CIKOKOL
-Waktu loading : SEGERA 04 FEBRUARI 2026
-Rute/tujuan : CGK - SUB
-driver  : AGUS
-Nopol  : D 9667 AF
-No hp  :08817021866</t>
-  </si>
-  <si>
-    <t>[WA_TS] Akbar Rafay: REQUEST ORDER ONCALL 04 FEBRUARI 2026:
-RAFAY
-1 unit Cddl 24 Cbm
-Lokasi : Megahub
-Waktu loading : SEGERA 04 FEBRUARI 2026
-Rute/tujuan : CGK - DPS
-driver 1 : Edi setiawan
-No hp  :0881023544597 
-driver 2 : Jatmiyanta
-No hp  :082118558105
-Nopol : F 9647 FH</t>
-  </si>
-  <si>
-    <t>[WA_TS] Akbar Rafay: REQUEST ULANG ORDER ONCALL 05 FEBRUARI 2026:
+Lokasi : ARGOPANTES
+Rute/tujuan : cgk - MES
+Waktu loading : SEGERA 17 FEBRUARI 2026
+driver 	: Anto
+Nopol	: B 9285 UEX
+No hp	:+62 823-7722-5563
+Waktu loading : 07:00 17 FEBRUARI 2026
+driver 	 : Kudir
+Nopol	: B 9380 UEX
+No hp	 :+62 812-6218-9242</t>
+  </si>
+  <si>
+    <t>Request Unit On Call Tgl 26 Feb 26
+1 Unit  Cddl / 24 Cbm
+Lokasi : Cikokol + Cikarang
+Waktu loading : 03:00 27-02-26
+Rute/tujuan : CGK-JBR
+driver   : Davit
+Nopol  : B 9726 SXW
+No hp  :082117275166</t>
+  </si>
+  <si>
+    <t>REQUEST ORDER ULANG ONCALL
 2 UNIT TWB 50 CBM
-Lokasi : CIKOKOL
-Waktu loading : SEGERA 05 FEBRUARI 2026
-Rute/tujuan : CGK - TKG
-driver  :
-Nopol  :
-No hp  :</t>
-  </si>
-  <si>
-    <t>[WA_TS] Akbar Rafay: REQUEST ULANG ORDER ONCALL 05 FEBRUARI 2026:
-2 UNIT TWB 50 CBM
-Lokasi : CIKOKOL
-Waktu loading : SEGERA 05 FEBRUARI 2026
-Rute/tujuan : CGK - PLM
-driver  :
-Nopol  :
-No hp  :</t>
-  </si>
-  <si>
-    <t>[WA_TS] Akbar Rafay: REQUEST ULANG ORDER ONCALL 05 FEBRUARI 2026:
-2 UNIT TWB 50 CBM
-Lokasi : CIKOKOL
-Waktu loading : SEGERA 05 FEBRUARI 2026
-Rute/tujuan : CGK - PKU
-driver  : Siswanto
-Nopol  : B 9120 WXR
-No hp  : 081943564062
-Lokasi : CIKOKOL
-Waktu loading : SEGERA 05 FEBRUARI 2026
-Rute/tujuan : CGK - PKU
-driver  : 
-Nopol  : 
-No hp  :</t>
-  </si>
-  <si>
-    <t>[WA_TS] Akbar Rafay: REQUEST ULANG ORDER ONCALL 05 FEBRUARI 2026:
-2 UNIT TWB 50 CBM
-Lokasi : CIKOKOL
-Waktu loading : SEGERA 05 FEBRUARI 2026
-Rute/tujuan : CGK - MES
-driver  : feri irawan
-Nopol  : BK 8516 VV
-No hp  : 085219216210</t>
-  </si>
-  <si>
-    <t>[WA_TS] Akbar Rafay: REQUEST ULANG ORDER ONCALL 05 FEBRUARI 2026:
-RAFAY
-2 UNIT TWB 50 CBM
-Lokasi : CIKOKOL
-Waktu loading : SEGERA 05 FEBRUARI 2026
-Rute/tujuan : CGK - MES
-driver  : HADI
-Nopol  :B 9446 MV
-No hp  :+62 831-9621-8655</t>
-  </si>
-  <si>
-    <t>[WA_TS] Akbar Rafay: REQUEST ULANG ORDER ONCALL 05 FEBRUARI 2026:
-RAFAY
-2 UNIT TWB 50 CBM
-Lokasi : CIKOKOL
-Waktu loading : SEGERA 05 FEBRUARI 2026
-Rute/tujuan : CGK - MES
-driver  : A. Sukur 
-Nopol  :B 9477 KEU
-No hp  : 083169525183</t>
-  </si>
-  <si>
-    <t>[WA_TS] Akbar Rafay: REQUEST ORDER ULANG ONCALL
-5 UNIT TWB 50 CBM
 Lokasi : ARGOPANTES 
 Waktu loading : SEGERA 7/3/2026
-Rute/tujuan : CGK - SUB
-RAFAY
-driver  : AKIYAT
-Nopol  : L 9722 UE
-No hp  :081281122738</t>
-  </si>
-  <si>
-    <t>[WA_TS] Akbar Rafay: REQUEST ULANG ORDER ONCALL 05 FEBRUARI 2025
-RAFAY
+Rute/tujuan : CGK - MES
+driver  : Kudir
+Nopol  : B 9380 UEX
+No hp  : 0812-6218-9242
+Data yg lain menyusul</t>
+  </si>
+  <si>
+    <t>REQUER ORDER ULANG DAN TAMBAHAN ON CALL
+26 FEBUARI 2026
+2 UNIT TWB 50 CBM 
+Lokasi : ARGOPANTES
+Rute/tujuan : PKU
+Waktu loading : SEGERA 7/3/2026
+driver 	: SISWANTO
+Nopol		: B 9120 WXR
+No hp	:081943564062
+Rute/tujuan : PKU
+Waktu loading : 23:00 7/3/2026
+driver 	: FERI IRAWAN
+Nopol		: BK 8516 W
+No hp	:085219216210</t>
+  </si>
+  <si>
+    <t>REQUER ORDER ULANG DAN TAMBAHAN ON CALL
+26 FEBUARI 2026
+2 UNIT TWB 50 CBM 
+Lokasi : ARGOPANTES
+Rute/tujuan : PLM
+Waktu loading : SEGERA 7/3/2026
+driver 	: SANDRI
+Nopol		:  BE 9636 BU
+No hp	:+62 889-0702-0037</t>
+  </si>
+  <si>
+    <t>REQUEST ORDER ULANG DAN TAMBAHAN ON CALL
+26 FEBUARI 2026
 2 UNIT TWB 50 CBM
-Lokasi : CIKOKOL
-Waktu loading : SEGERA 05 FEBRUARI 2025
-Rute/tujuan : CGK - PKU
-driver  : RYAN
-Nopol  : B 9084 VEH
-No hp  : 087837496810</t>
-  </si>
-  <si>
-    <t>[WA_TS] Akbar Rafay: REQUEST ORDER ULANG ONCALL
-5 UNIT TWB 50 CBM
-Lokasi : ARGOPANTES 
-Waktu loading : SEGERA 7/02/2026
-Rute/tujuan : CGK - SUB
-driver  : HENDRA S.P
-Nopol  : D 9044 AG
-No hp  : +62 877-8667-6177
-Waktu loading : 18:00 7/02/2026
-Rute/tujuan : CGK - SUB
-driver  :
-Nopol  :
-No hp  :
-Waktu loading : 21:00 7/02/2026
-Rute/tujuan : CGK - SUB
-driver  :
-Nopol  :
-No hp  :
-Waktu loading : 00:00 7/02/2026
-Rute/tujuan : CGK - SUB
-driver  :
-Nopol  :
-No hp  :
-REQUEST ORDER KHUSUS 06/02/2026
-Waktu loading : 03:00
-Rute/tujuan : CGK -SUB
-driver  :
-Nopol  :
-No hp  :</t>
-  </si>
-  <si>
-    <t>[WA_TS] Akbar Rafay: REQUEST ULANG ORDER ONCALL 05 FEBRUARI 2026:
+Lokasi : ARGOPANTES
+Rute/tujuan : MES
+Waktu loading : SEGERA 7/3/2026
+driver 	:Hendra setiawan
+Nopol		: BE 8023 WY
+No hp	:081280483919
+Rute/tujuan : MES
+Waktu loading : 23:00 7/3/2026
+driver 	: FEBRIANTO
+Nopol		: BA 9980 PS
+No hp	: 082286523993</t>
+  </si>
+  <si>
+    <t>REQUER ORDER ULANG DAN TAMBAHAN ON CALL
+26 FEBUARI 2026
+Rute/tujuan : PLM
+Waktu loading : 23:00 7/3/2026
+driver 	: M Doni saputra
+Nopol		: BD 8423 B
+No hp	:082164544736</t>
+  </si>
+  <si>
+    <t>Request Order Oncall  27 Febuari 2026
 2 UNIT TWB 50 CBM
-Lokasi : CIKOKOL
-Waktu loading : SEGERA 05 FEBRUARI 2026
-Rute/tujuan : CGK - PLM
-driver  : SANDRI
-Nopol  : BE 9636 BU
-No hp  :+62 889-0702-0037</t>
-  </si>
-  <si>
-    <t>[WA_TS] Akbar Rafay: Request Unit On Call Tgl 05 Feb 26
-2 Unit  Cddl / 24 Cbm
-Lokasi : Cikarang
-Waktu loading : 06:00 06-02-26
-Rute/tujuan : CKR-Jateng Tentative
-driver   : 
-Nopol  : 
-No hp  :</t>
-  </si>
-  <si>
-    <t>[WA_TS] Akbar Rafay: Request Unit On Call Tgl 05 Feb 26
-1 Unit  Cddl / 24 Cbm
-Lokasi : Cikarang
-Waktu loading : 03:00 06-02-26
-Rute/tujuan : CKR-Jateng Tentative
-Nama : Apar Rahmat 
-Nopol : E9406HB 
-No hp : 085971812879</t>
-  </si>
-  <si>
-    <t>[WA_TS] Akbar Rafay: Request Unit On Call Tgl 06 febuary 2026
-RAFAY
-3 unit twb 50 CBM
-Lokasi : ARGOPANTES 
-Waktu loading : SEGERA 06 febuary 2026
-Rute/tujuan : CGK- SUB
-driver  : M. iBNU
-Nopol  : L 9511 AL
-No hp  :082191633212</t>
-  </si>
-  <si>
-    <t>[WA_TS] Akbar Rafay: Request Unit On Call Tgl 06 febuary 2026
-2 unit twb 50 CBM
-Lokasi : JNE SUB
-Waktu loading : SEGERA 06 febuary 2026
-Rute/tujuan : SUB-CGK
-driver  : WAHYUDI
-Nopol  : N 9549 UA
-No hp  :085784422398</t>
-  </si>
-  <si>
-    <t>[WA_TS] Akbar Rafay: Request Unit On Call Tgl 06 febuary 2026
-2 unit twb 50 CBM
-Lokasi : JNE SUB
-Waktu loading : SEGERA 06 febuary 2026
-Rute/tujuan : SUB-CGK
-driver  : SOFYAN
-Nopol  : B 9679 WT
-No hp  : 082231837381</t>
-  </si>
-  <si>
-    <t>04 febuari 2026</t>
-  </si>
-  <si>
-    <t>04 februari 2026</t>
-  </si>
-  <si>
-    <t>09 maret 2026</t>
-  </si>
-  <si>
-    <t>05 februari 2026</t>
-  </si>
-  <si>
-    <t>05 februari 2025</t>
-  </si>
-  <si>
-    <t>05 feb 26</t>
-  </si>
-  <si>
-    <t>06 febuary 2026</t>
-  </si>
-  <si>
-    <t>05 / 02 / 2026</t>
+Lokasi : JNE SURABAYA
+Rute/tujuan   : SUX-CGK
+Waktu loading : SEGERA 27 Febuari 2026
+driver   : HABIB 
+Nopol : L 8336 UV
+No hp  :081231540625</t>
+  </si>
+  <si>
+    <t>13 februari 2026</t>
+  </si>
+  <si>
+    <t>12 februari 2026</t>
+  </si>
+  <si>
+    <t>15 februari 2026</t>
+  </si>
+  <si>
+    <t>16 feb 26</t>
+  </si>
+  <si>
+    <t>17 februari 2026</t>
+  </si>
+  <si>
+    <t>26 feb 26</t>
+  </si>
+  <si>
+    <t>26 febuari 2026</t>
+  </si>
+  <si>
+    <t>27 febuari 2026</t>
+  </si>
+  <si>
+    <t>085364056583</t>
+  </si>
+  <si>
+    <t>085225394209</t>
+  </si>
+  <si>
+    <t>082385989323</t>
+  </si>
+  <si>
+    <t>0 81370769496</t>
+  </si>
+  <si>
+    <t>0 82228516922</t>
+  </si>
+  <si>
+    <t>081281122738</t>
+  </si>
+  <si>
+    <t>0 81269345748</t>
+  </si>
+  <si>
+    <t>081382418508</t>
+  </si>
+  <si>
+    <t>088290294126</t>
+  </si>
+  <si>
+    <t>088212698834</t>
+  </si>
+  <si>
+    <t>081328851819</t>
+  </si>
+  <si>
+    <t>081943564062</t>
+  </si>
+  <si>
+    <t>0 81262189242</t>
+  </si>
+  <si>
+    <t>082117275166</t>
+  </si>
+  <si>
+    <t>081262189242</t>
+  </si>
+  <si>
+    <t>085219216210</t>
+  </si>
+  <si>
+    <t>0 88907020037</t>
+  </si>
+  <si>
+    <t>082286523993</t>
+  </si>
+  <si>
+    <t>082164544736</t>
+  </si>
+  <si>
+    <t>081231540625</t>
+  </si>
+  <si>
+    <t>13</t>
   </si>
   <si>
     <t>7 / 3 / 2026</t>
   </si>
   <si>
-    <t>7 / 02 / 2026</t>
-  </si>
-  <si>
-    <t>06 2026</t>
-  </si>
-  <si>
-    <t>085353886066</t>
-  </si>
-  <si>
-    <t>085865762797</t>
-  </si>
-  <si>
-    <t>0 81231895971</t>
-  </si>
-  <si>
-    <t>08817021866</t>
-  </si>
-  <si>
-    <t>082118558105</t>
-  </si>
-  <si>
-    <t>081943564062</t>
-  </si>
-  <si>
-    <t>085219216210</t>
-  </si>
-  <si>
-    <t>0 83196218655</t>
-  </si>
-  <si>
-    <t>083169525183</t>
-  </si>
-  <si>
-    <t>081281122738</t>
-  </si>
-  <si>
-    <t>087837496810</t>
-  </si>
-  <si>
-    <t>0 87786676177</t>
-  </si>
-  <si>
-    <t>0 88907020037</t>
-  </si>
-  <si>
-    <t>085971812879</t>
-  </si>
-  <si>
-    <t>082191633212</t>
-  </si>
-  <si>
-    <t>085784422398</t>
-  </si>
-  <si>
-    <t>082231837381</t>
+    <t>15</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>27</t>
   </si>
 </sst>
 </file>
@@ -931,7 +933,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:K24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -980,28 +982,25 @@
         <v>17</v>
       </c>
       <c r="D2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G2" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H2" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="I2" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="J2" t="s">
-        <v>92</v>
-      </c>
-      <c r="K2" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1009,39 +1008,36 @@
         <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C3" t="s">
         <v>18</v>
       </c>
       <c r="D3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G3" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="H3" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="I3" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="J3" t="s">
-        <v>99</v>
-      </c>
-      <c r="K3" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
         <v>15</v>
@@ -1050,263 +1046,242 @@
         <v>17</v>
       </c>
       <c r="D4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F4" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G4" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="H4" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="I4" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="J4" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="K4" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
         <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F5" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G5" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="H5" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="I5" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="J5" t="s">
-        <v>93</v>
+        <v>109</v>
       </c>
       <c r="K5" t="s">
-        <v>106</v>
+        <v>126</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s">
         <v>18</v>
       </c>
       <c r="D6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E6" t="s">
+        <v>36</v>
+      </c>
+      <c r="F6" t="s">
+        <v>56</v>
+      </c>
+      <c r="G6" t="s">
+        <v>72</v>
+      </c>
+      <c r="H6" t="s">
+        <v>81</v>
+      </c>
+      <c r="I6" t="s">
+        <v>98</v>
+      </c>
+      <c r="J6" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="C7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" t="s">
+        <v>27</v>
+      </c>
+      <c r="E7" t="s">
         <v>37</v>
       </c>
-      <c r="F6" t="s">
-        <v>54</v>
-      </c>
-      <c r="G6" t="s">
-        <v>67</v>
-      </c>
-      <c r="H6" t="s">
-        <v>76</v>
-      </c>
-      <c r="I6" t="s">
-        <v>93</v>
-      </c>
-      <c r="J6" t="s">
-        <v>93</v>
-      </c>
-      <c r="K6" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11">
-      <c r="A7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D7" t="s">
-        <v>26</v>
+      <c r="F7" t="s">
+        <v>57</v>
       </c>
       <c r="G7" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="H7" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="I7" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="J7" t="s">
-        <v>95</v>
+        <v>111</v>
+      </c>
+      <c r="K7" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="8" spans="1:11">
-      <c r="A8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" t="s">
-        <v>15</v>
-      </c>
       <c r="C8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D8" t="s">
         <v>27</v>
       </c>
+      <c r="E8" t="s">
+        <v>38</v>
+      </c>
+      <c r="F8" t="s">
+        <v>58</v>
+      </c>
       <c r="G8" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="H8" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="I8" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="J8" t="s">
-        <v>95</v>
+        <v>112</v>
+      </c>
+      <c r="K8" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="9" spans="1:11">
-      <c r="A9" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" t="s">
-        <v>15</v>
-      </c>
       <c r="C9" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E9" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F9" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="G9" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="H9" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="I9" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="J9" t="s">
-        <v>95</v>
+        <v>113</v>
       </c>
       <c r="K9" t="s">
-        <v>108</v>
+        <v>127</v>
       </c>
     </row>
     <row r="10" spans="1:11">
-      <c r="A10" t="s">
-        <v>14</v>
-      </c>
       <c r="B10" t="s">
         <v>15</v>
       </c>
-      <c r="C10" t="s">
-        <v>19</v>
-      </c>
       <c r="D10" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F10" t="s">
-        <v>56</v>
-      </c>
-      <c r="G10" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="H10" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="I10" t="s">
-        <v>95</v>
-      </c>
-      <c r="J10" t="s">
-        <v>95</v>
-      </c>
-      <c r="K10" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C11" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F11" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G11" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="H11" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="I11" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="J11" t="s">
-        <v>95</v>
-      </c>
-      <c r="K11" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C12" t="s">
         <v>19</v>
@@ -1315,187 +1290,196 @@
         <v>29</v>
       </c>
       <c r="E12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F12" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G12" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="H12" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="I12" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="J12" t="s">
-        <v>95</v>
+        <v>115</v>
       </c>
       <c r="K12" t="s">
-        <v>111</v>
+        <v>128</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B13" t="s">
         <v>15</v>
       </c>
       <c r="C13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D13" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E13" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="F13" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G13" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="H13" t="s">
-        <v>83</v>
+        <v>80</v>
+      </c>
+      <c r="I13" t="s">
+        <v>98</v>
       </c>
       <c r="J13" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="K13" t="s">
-        <v>112</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B14" t="s">
         <v>15</v>
       </c>
       <c r="C14" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D14" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E14" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="F14" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="G14" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="H14" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="I14" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="J14" t="s">
-        <v>96</v>
-      </c>
-      <c r="K14" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
     <row r="15" spans="1:11">
       <c r="A15" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C15" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D15" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="E15" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F15" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G15" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="H15" t="s">
-        <v>85</v>
+        <v>88</v>
+      </c>
+      <c r="I15" t="s">
+        <v>101</v>
       </c>
       <c r="J15" t="s">
-        <v>101</v>
-      </c>
-      <c r="K15" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="16" spans="1:11">
       <c r="A16" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B16" t="s">
         <v>15</v>
       </c>
       <c r="C16" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D16" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E16" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G16" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="H16" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="I16" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="J16" t="s">
-        <v>95</v>
-      </c>
-      <c r="K16" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="17" spans="1:11">
       <c r="A17" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C17" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D17" t="s">
-        <v>31</v>
+        <v>26</v>
+      </c>
+      <c r="E17" t="s">
+        <v>45</v>
+      </c>
+      <c r="F17" t="s">
+        <v>64</v>
       </c>
       <c r="G17" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="H17" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="I17" t="s">
-        <v>97</v>
+        <v>102</v>
+      </c>
+      <c r="J17" t="s">
+        <v>118</v>
+      </c>
+      <c r="K17" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="18" spans="1:11">
       <c r="A18" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B18" t="s">
         <v>16</v>
@@ -1504,30 +1488,30 @@
         <v>20</v>
       </c>
       <c r="D18" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E18" t="s">
         <v>46</v>
       </c>
       <c r="F18" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G18" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H18" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="I18" t="s">
-        <v>97</v>
-      </c>
-      <c r="K18" t="s">
-        <v>116</v>
+        <v>103</v>
+      </c>
+      <c r="J18" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="19" spans="1:11">
       <c r="A19" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B19" t="s">
         <v>15</v>
@@ -1536,33 +1520,30 @@
         <v>17</v>
       </c>
       <c r="D19" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E19" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F19" t="s">
         <v>64</v>
       </c>
       <c r="G19" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="H19" t="s">
-        <v>89</v>
-      </c>
-      <c r="I19" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="J19" t="s">
-        <v>98</v>
+        <v>120</v>
       </c>
       <c r="K19" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
     </row>
     <row r="20" spans="1:11">
       <c r="A20" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B20" t="s">
         <v>15</v>
@@ -1570,64 +1551,151 @@
       <c r="C20" t="s">
         <v>21</v>
       </c>
-      <c r="D20" t="s">
-        <v>32</v>
-      </c>
       <c r="E20" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F20" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G20" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="H20" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="I20" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="J20" t="s">
-        <v>102</v>
+        <v>121</v>
       </c>
       <c r="K20" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
     </row>
     <row r="21" spans="1:11">
       <c r="A21" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B21" t="s">
         <v>15</v>
       </c>
       <c r="C21" t="s">
-        <v>21</v>
-      </c>
-      <c r="D21" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="E21" t="s">
+        <v>48</v>
+      </c>
+      <c r="F21" t="s">
+        <v>67</v>
+      </c>
+      <c r="G21" t="s">
+        <v>72</v>
+      </c>
+      <c r="H21" t="s">
+        <v>94</v>
+      </c>
+      <c r="I21" t="s">
+        <v>104</v>
+      </c>
+      <c r="J21" t="s">
+        <v>122</v>
+      </c>
+      <c r="K21" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11">
+      <c r="A22" t="s">
+        <v>13</v>
+      </c>
+      <c r="B22" t="s">
+        <v>15</v>
+      </c>
+      <c r="C22" t="s">
+        <v>23</v>
+      </c>
+      <c r="E22" t="s">
         <v>49</v>
       </c>
-      <c r="F21" t="s">
-        <v>66</v>
-      </c>
-      <c r="G21" t="s">
-        <v>67</v>
-      </c>
-      <c r="H21" t="s">
-        <v>91</v>
-      </c>
-      <c r="I21" t="s">
-        <v>98</v>
-      </c>
-      <c r="J21" t="s">
-        <v>102</v>
-      </c>
-      <c r="K21" t="s">
-        <v>119</v>
+      <c r="F22" t="s">
+        <v>68</v>
+      </c>
+      <c r="G22" t="s">
+        <v>73</v>
+      </c>
+      <c r="H22" t="s">
+        <v>95</v>
+      </c>
+      <c r="I22" t="s">
+        <v>104</v>
+      </c>
+      <c r="J22" t="s">
+        <v>123</v>
+      </c>
+      <c r="K22" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11">
+      <c r="C23" t="s">
+        <v>22</v>
+      </c>
+      <c r="E23" t="s">
+        <v>50</v>
+      </c>
+      <c r="F23" t="s">
+        <v>69</v>
+      </c>
+      <c r="G23" t="s">
+        <v>73</v>
+      </c>
+      <c r="H23" t="s">
+        <v>96</v>
+      </c>
+      <c r="I23" t="s">
+        <v>104</v>
+      </c>
+      <c r="J23" t="s">
+        <v>124</v>
+      </c>
+      <c r="K23" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11">
+      <c r="A24" t="s">
+        <v>13</v>
+      </c>
+      <c r="B24" t="s">
+        <v>15</v>
+      </c>
+      <c r="C24" t="s">
+        <v>24</v>
+      </c>
+      <c r="D24" t="s">
+        <v>31</v>
+      </c>
+      <c r="E24" t="s">
+        <v>51</v>
+      </c>
+      <c r="F24" t="s">
+        <v>70</v>
+      </c>
+      <c r="G24" t="s">
+        <v>72</v>
+      </c>
+      <c r="H24" t="s">
+        <v>97</v>
+      </c>
+      <c r="I24" t="s">
+        <v>105</v>
+      </c>
+      <c r="J24" t="s">
+        <v>125</v>
+      </c>
+      <c r="K24" t="s">
+        <v>130</v>
       </c>
     </row>
   </sheetData>

--- a/output_orderan.xlsx
+++ b/output_orderan.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
   <si>
     <t>UNIT_QTY</t>
   </si>
@@ -49,9 +49,6 @@
     <t>RO_DATE</t>
   </si>
   <si>
-    <t>LOAD_DATE</t>
-  </si>
-  <si>
     <t>PHONE</t>
   </si>
   <si>
@@ -67,10 +64,10 @@
     <t>cgk sub</t>
   </si>
   <si>
-    <t>bagus</t>
-  </si>
-  <si>
-    <t>b 9563 taa</t>
+    <t>agung</t>
+  </si>
+  <si>
+    <t>bm 8364 uu</t>
   </si>
   <si>
     <t>segera</t>
@@ -79,35 +76,33 @@
     <t>NEW_ORDER</t>
   </si>
   <si>
-    <t>[WA_TS] Akbar Rafay: REQUEST ORDER ONCALL 12 FEBRUARI 2026:
-3 UNIT TWB 50 Cbm
+    <t>[WA_TS] Akbar Rafay: Request Unit On Call Tgl 12 MARET 2026
+RAFAY
+3 UNIT TWB 50 CBM
 Lokasi : ARGOPANTES
-Waktu loading : SEGERA 12 FEBRUARI 2026
+Waktu loading : SEGERA 12 MARET 2026
 Rute/tujuan : CGK - SUB
-driver  : Rosyit
-Nopol  : B 9563 TEU
-No hp  : 082313572678
+driver  : ADE
+Nopol  : BM 8364 AA
+No hp  : 085353886066
 Lokasi : ARGOPANTES
-Waktu loading : SEGERA 12 FEBRUARI 2026
+Waktu loading : SEGERA 12 MARET 2026
 Rute/tujuan : CGK - SUB
-driver  : BAGUS
-Nopol  : B 9563 TAA
-No hp  : 0823135882147
+driver  : AGUNG
+Nopol  : BM 8364 UU
+No hp  : 085353886066
 Lokasi : ARGOPANTES
-Waktu loading : SEGERA 12 FEBRUARI 2026
+Waktu loading : SEGERA 12 MARET 2026
 Rute/tujuan : CGK - SUB
-driver  : AJENG
-Nopol  : B 9563 TBB
-No hp  : 0823135882147</t>
-  </si>
-  <si>
-    <t>12 februari</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>0823135882147</t>
+driver  : ADRI
+Nopol  : BM 8364 BB
+No hp  : 085353886066</t>
+  </si>
+  <si>
+    <t>12 maret 2026</t>
+  </si>
+  <si>
+    <t>085353886066</t>
   </si>
 </sst>
 </file>
@@ -465,10 +460,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:L2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -505,49 +500,43 @@
       <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" t="s">
+      <c r="B2" t="s">
         <v>13</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>14</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>15</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>16</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>17</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>18</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>19</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2">
+        <v>0.9994</v>
+      </c>
+      <c r="J2" t="s">
         <v>20</v>
       </c>
-      <c r="I2">
-        <v>0.9995000000000001</v>
-      </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>21</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>22</v>
-      </c>
-      <c r="L2" t="s">
-        <v>23</v>
-      </c>
-      <c r="M2" t="s">
-        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/output_orderan.xlsx
+++ b/output_orderan.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="122">
   <si>
     <t>UNIT_QTY</t>
   </si>
@@ -49,60 +49,501 @@
     <t>RO_DATE</t>
   </si>
   <si>
+    <t>LOAD_DATE</t>
+  </si>
+  <si>
     <t>PHONE</t>
   </si>
   <si>
-    <t>3</t>
+    <t>1</t>
   </si>
   <si>
     <t>twb</t>
   </si>
   <si>
+    <t>cddl</t>
+  </si>
+  <si>
     <t>argopantes</t>
   </si>
   <si>
+    <t>cikokol</t>
+  </si>
+  <si>
+    <t>megahub</t>
+  </si>
+  <si>
+    <t>jne sub</t>
+  </si>
+  <si>
+    <t>cikarang</t>
+  </si>
+  <si>
     <t>cgk sub</t>
   </si>
   <si>
-    <t>agung</t>
-  </si>
-  <si>
-    <t>bm 8364 uu</t>
+    <t>cgk pku</t>
+  </si>
+  <si>
+    <t>cgk jateng</t>
+  </si>
+  <si>
+    <t>sub cgk</t>
+  </si>
+  <si>
+    <t>ckr jatim tentative</t>
+  </si>
+  <si>
+    <t>cgk dps</t>
+  </si>
+  <si>
+    <t>cgk plm</t>
+  </si>
+  <si>
+    <t>cgk mes</t>
+  </si>
+  <si>
+    <t>cgk bdg</t>
+  </si>
+  <si>
+    <t>cgk jepara</t>
+  </si>
+  <si>
+    <t>roni</t>
+  </si>
+  <si>
+    <t>dedi</t>
+  </si>
+  <si>
+    <t>sandri</t>
+  </si>
+  <si>
+    <t>hadi</t>
+  </si>
+  <si>
+    <t>apar rahmat</t>
+  </si>
+  <si>
+    <t>edi setiawan</t>
+  </si>
+  <si>
+    <t>sofyan</t>
+  </si>
+  <si>
+    <t>bayu</t>
+  </si>
+  <si>
+    <t>ryan</t>
+  </si>
+  <si>
+    <t>agus</t>
+  </si>
+  <si>
+    <t>lailan</t>
+  </si>
+  <si>
+    <t>akiyat</t>
+  </si>
+  <si>
+    <t>a sukur</t>
+  </si>
+  <si>
+    <t>mujito</t>
+  </si>
+  <si>
+    <t>usman afandi</t>
+  </si>
+  <si>
+    <t>yusni gunawan</t>
+  </si>
+  <si>
+    <t>samsul</t>
+  </si>
+  <si>
+    <t>rajiev fikri</t>
+  </si>
+  <si>
+    <t>dian saputra</t>
+  </si>
+  <si>
+    <t>supriyanto</t>
+  </si>
+  <si>
+    <t>b 9001 aa</t>
+  </si>
+  <si>
+    <t>b 9002 ab</t>
+  </si>
+  <si>
+    <t>be 9636 bu</t>
+  </si>
+  <si>
+    <t>b 9446 mv</t>
+  </si>
+  <si>
+    <t>e 9406 hb</t>
+  </si>
+  <si>
+    <t>f 9647 fh</t>
+  </si>
+  <si>
+    <t>b 9679 wt</t>
+  </si>
+  <si>
+    <t>l 9511 al</t>
+  </si>
+  <si>
+    <t>b 9084 veh</t>
+  </si>
+  <si>
+    <t>d 9667 af</t>
+  </si>
+  <si>
+    <t>s 9272 up</t>
+  </si>
+  <si>
+    <t>l 9722 ue</t>
+  </si>
+  <si>
+    <t>b 9477 keu</t>
+  </si>
+  <si>
+    <t>be 8837 gk</t>
+  </si>
+  <si>
+    <t>be 8456 fn</t>
+  </si>
+  <si>
+    <t>be 8951 by</t>
+  </si>
+  <si>
+    <t>b 9771 uew</t>
+  </si>
+  <si>
+    <t>b 9591 uxx</t>
+  </si>
+  <si>
+    <t>be 8334 gba</t>
+  </si>
+  <si>
+    <t>be 8940 db</t>
   </si>
   <si>
     <t>segera</t>
   </si>
   <si>
+    <t>07 : 00</t>
+  </si>
+  <si>
+    <t>06 : 00</t>
+  </si>
+  <si>
+    <t>21 : 00</t>
+  </si>
+  <si>
+    <t>18 : 00</t>
+  </si>
+  <si>
+    <t>00 : 00</t>
+  </si>
+  <si>
     <t>NEW_ORDER</t>
   </si>
   <si>
-    <t>[WA_TS] Akbar Rafay: Request Unit On Call Tgl 12 MARET 2026
-RAFAY
-3 UNIT TWB 50 CBM
+    <t>[WA_TS] Akbar Rafay: REQUEST ULANG ORDER ONCALL 12 MARET 2026
+RAFAY
+1 UNIT TWB 50 CBM
 Lokasi : ARGOPANTES
 Waktu loading : SEGERA 12 MARET 2026
 Rute/tujuan : CGK - SUB
-driver  : ADE
-Nopol  : BM 8364 AA
-No hp  : 085353886066
+driver  : RONI
+Nopol  : B 9001 AA
+No hp  : 081311110001</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: REQUEST ULANG ORDER ONCALL 12 MARET 2026
+RAFAY
+1 UNIT TWB 50 CBM
 Lokasi : ARGOPANTES
 Waktu loading : SEGERA 12 MARET 2026
 Rute/tujuan : CGK - SUB
-driver  : AGUNG
-Nopol  : BM 8364 UU
-No hp  : 085353886066
+driver  : DEDI
+Nopol  : B 9002 AB
+No hp  : 081311110002</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: REQUEST ULANG ORDER ONCALL 12 MARET 2026
+RAFAY
+1 UNIT TWB 50 CBM
+Lokasi : CIKOKOL
+Waktu loading : SEGERA 12 MARET 2026
+Rute/tujuan : CGK - PKU
+driver  : SANDRI
+Nopol  : BE 9636 BU
+No hp  : 088907020037</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: REQUEST ULANG ORDER ONCALL 12 MARET 2026
+RAFAY
+1 UNIT TWB 50 CBM
+Lokasi : CIKOKOL
+Waktu loading : SEGERA 12 MARET 2026
+Rute/tujuan : CGK - PKU
+driver  : HADI
+Nopol  : B 9446 MV
+No hp  : 083196218655</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: REQUEST ULANG ORDER ONCALL 12 MARET 2026
+RAFAY
+1 UNIT CDDL 24 CBM
+Lokasi : MEGAHUB
+REQUEST ORDER KHUSUS 13/03/2026
+Waktu loading : 07:00
+Rute/tujuan : CGK - JATENG
+driver  : APAR RAHMAT
+Nopol  : E 9406 HB
+No hp  : 085971812879</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: REQUEST ULANG ORDER ONCALL 12 MARET 2026
+RAFAY
+1 UNIT CDDL 24 CBM
+Lokasi : MEGAHUB
+REQUEST ORDER KHUSUS 13/03/2026
+Waktu loading : 07:00
+Rute/tujuan : CGK - JATENG
+driver  : EDI SETIAWAN
+Nopol  : F 9647 FH
+No hp  : 0881023544597</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: REQUEST ULANG ORDER ONCALL 12 MARET 2026
+RAFAY
+1 UNIT TWB 50 CBM
+Lokasi : JNE SUB
+Waktu loading : SEGERA 12 MARET 2026
+Rute/tujuan : SUB - CGK
+driver  : SOFYAN
+Nopol  : B 9679 WT
+No hp  : 082231837381</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: REQUEST ULANG ORDER ONCALL 12 MARET 2026
+RAFAY
+1 UNIT TWB 50 CBM
+Lokasi : JNE SUB
+Waktu loading : SEGERA 12 MARET 2026
+Rute/tujuan : SUB - CGK
+driver  : BAYU
+Nopol  : L 9511 AL
+No hp  : 082191633212</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: REQUEST ULANG ORDER ONCALL 12 MARET 2026
+RAFAY
+1 UNIT CDDL 24 CBM
+Lokasi : CIKARANG
+Waktu loading : 06:00 13-03-26
+Rute/tujuan : CKR - JATIM TENTATIVE
+driver  : RYAN
+Nopol  : B 9084 VEH
+No hp  : 087837496810</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: REQUEST ULANG ORDER ONCALL 12 MARET 2026
+RAFAY
+1 UNIT CDDL 24 CBM
+Lokasi : CIKARANG
+Waktu loading : 06:00 13-03-26
+Rute/tujuan : CKR - JATIM TENTATIVE
+driver  : AGUS
+Nopol  : D 9667 AF
+No hp  : 08817021866</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: REQUEST ULANG ORDER ONCALL 12 MARET 2026
+RAFAY
+1 UNIT TWB 50 CBM
 Lokasi : ARGOPANTES
+Waktu loading : 21:00 12 MARET 2026
+Rute/tujuan : CGK - DPS
+driver  : LAILAN
+Nopol  : S 9272 UP
+No hp  : 087886861780</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: REQUEST ULANG ORDER ONCALL 12 MARET 2026
+RAFAY
+1 UNIT TWB 50 CBM
+Lokasi : ARGOPANTES
+Waktu loading : 21:00 12 MARET 2026
+Rute/tujuan : CGK - DPS
+driver  : AKIYAT
+Nopol  : L 9722 UE
+No hp  : 081281122738</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: REQUEST ULANG ORDER ONCALL 12 MARET 2026
+RAFAY
+1 UNIT TWB 50 CBM
+Lokasi : CIKOKOL
 Waktu loading : SEGERA 12 MARET 2026
-Rute/tujuan : CGK - SUB
-driver  : ADRI
-Nopol  : BM 8364 BB
-No hp  : 085353886066</t>
+Rute/tujuan : CGK - PLM
+driver  : A SUKUR
+Nopol  : B 9477 KEU
+No hp  : 083169525183</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: REQUEST ULANG ORDER ONCALL 12 MARET 2026
+RAFAY
+1 UNIT TWB 50 CBM
+Lokasi : CIKOKOL
+Waktu loading : SEGERA 12 MARET 2026
+Rute/tujuan : CGK - PLM
+driver  : MUJITO
+Nopol  : BE 8837 GK
+No hp  : 082275004149</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: REQUEST ULANG ORDER ONCALL 12 MARET 2026
+RAFAY
+1 UNIT TWB 50 CBM
+Lokasi : CIKOKOL
+Waktu loading : SEGERA 12 MARET 2026
+Rute/tujuan : CGK - MES
+driver  : USMAN AFANDI
+Nopol  : BE 8456 FN
+No hp  : 082382200400</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: REQUEST ULANG ORDER ONCALL 12 MARET 2026
+RAFAY
+1 UNIT TWB 50 CBM
+Lokasi : CIKOKOL
+Waktu loading : SEGERA 12 MARET 2026
+Rute/tujuan : CGK - MES
+driver  : YUSNI GUNAWAN
+Nopol  : BE 8951 BY
+No hp  : 085729113217</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: REQUEST ULANG ORDER ONCALL 12 MARET 2026
+RAFAY
+1 UNIT CDDL 24 CBM
+Lokasi : MEGAHUB
+Waktu loading : 18:00 12 MARET 2026
+Rute/tujuan : CGK - BDG
+driver  : SAMSUL
+Nopol  : B 9771 UEW
+No hp  : 082234567802</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: REQUEST ULANG ORDER ONCALL 12 MARET 2026
+RAFAY
+1 UNIT CDDL 24 CBM
+Lokasi : MEGAHUB
+Waktu loading : 18:00 12 MARET 2026
+Rute/tujuan : CGK - BDG
+driver  : RAJIEV FIKRI
+Nopol  : B 9591 UXX
+No hp  : 082234567803</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: REQUEST ULANG ORDER ONCALL 12 MARET 2026
+RAFAY
+1 UNIT TWB 50 CBM
+Lokasi : ARGOPANTES
+REQUEST ORDER KHUSUS 13/03/2026
+Waktu loading : 00:00
+Rute/tujuan : CGK - JEPARA
+driver  : DIAN SAPUTRA
+Nopol  : BE 8334 GBA
+No hp  : 081262189242</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: REQUEST ULANG ORDER ONCALL 12 MARET 2026
+RAFAY
+1 UNIT TWB 50 CBM
+Lokasi : ARGOPANTES
+REQUEST ORDER KHUSUS 13/03/2026
+Waktu loading : 00:00
+Rute/tujuan : CGK - JEPARA
+driver  : SUPRIYANTO
+Nopol  : BE 8940 DB
+No hp  : 082164544736</t>
   </si>
   <si>
     <t>12 maret 2026</t>
   </si>
   <si>
-    <t>085353886066</t>
+    <t>12</t>
+  </si>
+  <si>
+    <t>13 / 03 / 2026</t>
+  </si>
+  <si>
+    <t>12 2026</t>
+  </si>
+  <si>
+    <t>081311110001</t>
+  </si>
+  <si>
+    <t>081311110002</t>
+  </si>
+  <si>
+    <t>088907020037</t>
+  </si>
+  <si>
+    <t>083196218655</t>
+  </si>
+  <si>
+    <t>085971812879</t>
+  </si>
+  <si>
+    <t>0881023544597</t>
+  </si>
+  <si>
+    <t>082231837381</t>
+  </si>
+  <si>
+    <t>082191633212</t>
+  </si>
+  <si>
+    <t>087837496810</t>
+  </si>
+  <si>
+    <t>08817021866</t>
+  </si>
+  <si>
+    <t>087886861780</t>
+  </si>
+  <si>
+    <t>081281122738</t>
+  </si>
+  <si>
+    <t>083169525183</t>
+  </si>
+  <si>
+    <t>082275004149</t>
+  </si>
+  <si>
+    <t>082382200400</t>
+  </si>
+  <si>
+    <t>085729113217</t>
+  </si>
+  <si>
+    <t>082234567802</t>
+  </si>
+  <si>
+    <t>082234567803</t>
+  </si>
+  <si>
+    <t>081262189242</t>
+  </si>
+  <si>
+    <t>082164544736</t>
   </si>
 </sst>
 </file>
@@ -460,10 +901,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:M21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:13">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -500,43 +941,822 @@
       <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:12">
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D2" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="F2" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="G2" t="s">
-        <v>18</v>
+        <v>71</v>
       </c>
       <c r="H2" t="s">
-        <v>19</v>
+        <v>77</v>
       </c>
       <c r="I2">
         <v>0.9994</v>
       </c>
       <c r="J2" t="s">
+        <v>78</v>
+      </c>
+      <c r="K2" t="s">
+        <v>98</v>
+      </c>
+      <c r="L2" t="s">
+        <v>98</v>
+      </c>
+      <c r="M2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F3" t="s">
+        <v>52</v>
+      </c>
+      <c r="G3" t="s">
+        <v>71</v>
+      </c>
+      <c r="H3" t="s">
+        <v>77</v>
+      </c>
+      <c r="I3">
+        <v>0.9994</v>
+      </c>
+      <c r="J3" t="s">
+        <v>79</v>
+      </c>
+      <c r="K3" t="s">
+        <v>98</v>
+      </c>
+      <c r="L3" t="s">
+        <v>98</v>
+      </c>
+      <c r="M3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F4" t="s">
+        <v>53</v>
+      </c>
+      <c r="G4" t="s">
+        <v>71</v>
+      </c>
+      <c r="H4" t="s">
+        <v>77</v>
+      </c>
+      <c r="I4">
+        <v>0.9994</v>
+      </c>
+      <c r="J4" t="s">
+        <v>80</v>
+      </c>
+      <c r="K4" t="s">
+        <v>98</v>
+      </c>
+      <c r="L4" t="s">
+        <v>99</v>
+      </c>
+      <c r="M4" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" t="s">
+        <v>34</v>
+      </c>
+      <c r="F5" t="s">
+        <v>54</v>
+      </c>
+      <c r="G5" t="s">
+        <v>71</v>
+      </c>
+      <c r="H5" t="s">
+        <v>77</v>
+      </c>
+      <c r="I5">
+        <v>0.9993</v>
+      </c>
+      <c r="J5" t="s">
+        <v>81</v>
+      </c>
+      <c r="K5" t="s">
+        <v>98</v>
+      </c>
+      <c r="L5" t="s">
+        <v>99</v>
+      </c>
+      <c r="M5" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E6" t="s">
+        <v>35</v>
+      </c>
+      <c r="F6" t="s">
+        <v>55</v>
+      </c>
+      <c r="G6" t="s">
+        <v>72</v>
+      </c>
+      <c r="H6" t="s">
+        <v>77</v>
+      </c>
+      <c r="I6">
+        <v>0.9994</v>
+      </c>
+      <c r="J6" t="s">
+        <v>82</v>
+      </c>
+      <c r="K6" t="s">
+        <v>98</v>
+      </c>
+      <c r="L6" t="s">
+        <v>100</v>
+      </c>
+      <c r="M6" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" t="s">
+        <v>36</v>
+      </c>
+      <c r="F7" t="s">
+        <v>56</v>
+      </c>
+      <c r="G7" t="s">
+        <v>72</v>
+      </c>
+      <c r="H7" t="s">
+        <v>77</v>
+      </c>
+      <c r="I7">
+        <v>0.9994</v>
+      </c>
+      <c r="J7" t="s">
+        <v>83</v>
+      </c>
+      <c r="K7" t="s">
+        <v>98</v>
+      </c>
+      <c r="L7" t="s">
+        <v>100</v>
+      </c>
+      <c r="M7" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E8" t="s">
+        <v>37</v>
+      </c>
+      <c r="F8" t="s">
+        <v>57</v>
+      </c>
+      <c r="G8" t="s">
+        <v>71</v>
+      </c>
+      <c r="H8" t="s">
+        <v>77</v>
+      </c>
+      <c r="I8">
+        <v>0.9994</v>
+      </c>
+      <c r="J8" t="s">
+        <v>84</v>
+      </c>
+      <c r="K8" t="s">
+        <v>98</v>
+      </c>
+      <c r="L8" t="s">
+        <v>99</v>
+      </c>
+      <c r="M8" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E9" t="s">
+        <v>38</v>
+      </c>
+      <c r="F9" t="s">
+        <v>58</v>
+      </c>
+      <c r="G9" t="s">
+        <v>71</v>
+      </c>
+      <c r="H9" t="s">
+        <v>77</v>
+      </c>
+      <c r="I9">
+        <v>0.9994</v>
+      </c>
+      <c r="J9" t="s">
+        <v>85</v>
+      </c>
+      <c r="K9" t="s">
+        <v>98</v>
+      </c>
+      <c r="L9" t="s">
+        <v>99</v>
+      </c>
+      <c r="M9" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="A10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" t="s">
         <v>20</v>
       </c>
-      <c r="K2" t="s">
-        <v>21</v>
-      </c>
-      <c r="L2" t="s">
-        <v>22</v>
+      <c r="D10" t="s">
+        <v>25</v>
+      </c>
+      <c r="E10" t="s">
+        <v>39</v>
+      </c>
+      <c r="F10" t="s">
+        <v>59</v>
+      </c>
+      <c r="G10" t="s">
+        <v>73</v>
+      </c>
+      <c r="H10" t="s">
+        <v>77</v>
+      </c>
+      <c r="I10">
+        <v>0.9994</v>
+      </c>
+      <c r="J10" t="s">
+        <v>86</v>
+      </c>
+      <c r="K10" t="s">
+        <v>98</v>
+      </c>
+      <c r="M10" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
+      <c r="A11" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" t="s">
+        <v>20</v>
+      </c>
+      <c r="D11" t="s">
+        <v>25</v>
+      </c>
+      <c r="E11" t="s">
+        <v>40</v>
+      </c>
+      <c r="F11" t="s">
+        <v>60</v>
+      </c>
+      <c r="G11" t="s">
+        <v>73</v>
+      </c>
+      <c r="H11" t="s">
+        <v>77</v>
+      </c>
+      <c r="I11">
+        <v>0.9995000000000001</v>
+      </c>
+      <c r="J11" t="s">
+        <v>87</v>
+      </c>
+      <c r="K11" t="s">
+        <v>98</v>
+      </c>
+      <c r="M11" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
+      <c r="A12" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C12" t="s">
+        <v>16</v>
+      </c>
+      <c r="D12" t="s">
+        <v>26</v>
+      </c>
+      <c r="E12" t="s">
+        <v>41</v>
+      </c>
+      <c r="F12" t="s">
+        <v>61</v>
+      </c>
+      <c r="G12" t="s">
+        <v>74</v>
+      </c>
+      <c r="H12" t="s">
+        <v>77</v>
+      </c>
+      <c r="I12">
+        <v>0.9994</v>
+      </c>
+      <c r="J12" t="s">
+        <v>88</v>
+      </c>
+      <c r="K12" t="s">
+        <v>98</v>
+      </c>
+      <c r="L12" t="s">
+        <v>98</v>
+      </c>
+      <c r="M12" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
+      <c r="A13" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" t="s">
+        <v>16</v>
+      </c>
+      <c r="D13" t="s">
+        <v>26</v>
+      </c>
+      <c r="E13" t="s">
+        <v>42</v>
+      </c>
+      <c r="F13" t="s">
+        <v>62</v>
+      </c>
+      <c r="G13" t="s">
+        <v>74</v>
+      </c>
+      <c r="H13" t="s">
+        <v>77</v>
+      </c>
+      <c r="I13">
+        <v>0.9995000000000001</v>
+      </c>
+      <c r="J13" t="s">
+        <v>89</v>
+      </c>
+      <c r="K13" t="s">
+        <v>98</v>
+      </c>
+      <c r="L13" t="s">
+        <v>98</v>
+      </c>
+      <c r="M13" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13">
+      <c r="A14" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14" t="s">
+        <v>17</v>
+      </c>
+      <c r="D14" t="s">
+        <v>27</v>
+      </c>
+      <c r="E14" t="s">
+        <v>43</v>
+      </c>
+      <c r="F14" t="s">
+        <v>63</v>
+      </c>
+      <c r="G14" t="s">
+        <v>71</v>
+      </c>
+      <c r="H14" t="s">
+        <v>77</v>
+      </c>
+      <c r="I14">
+        <v>0.9994</v>
+      </c>
+      <c r="J14" t="s">
+        <v>90</v>
+      </c>
+      <c r="K14" t="s">
+        <v>98</v>
+      </c>
+      <c r="L14" t="s">
+        <v>99</v>
+      </c>
+      <c r="M14" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13">
+      <c r="A15" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" t="s">
+        <v>14</v>
+      </c>
+      <c r="C15" t="s">
+        <v>17</v>
+      </c>
+      <c r="D15" t="s">
+        <v>27</v>
+      </c>
+      <c r="E15" t="s">
+        <v>44</v>
+      </c>
+      <c r="F15" t="s">
+        <v>64</v>
+      </c>
+      <c r="G15" t="s">
+        <v>71</v>
+      </c>
+      <c r="H15" t="s">
+        <v>77</v>
+      </c>
+      <c r="I15">
+        <v>0.9994</v>
+      </c>
+      <c r="J15" t="s">
+        <v>91</v>
+      </c>
+      <c r="K15" t="s">
+        <v>98</v>
+      </c>
+      <c r="L15" t="s">
+        <v>99</v>
+      </c>
+      <c r="M15" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13">
+      <c r="A16" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16" t="s">
+        <v>14</v>
+      </c>
+      <c r="C16" t="s">
+        <v>17</v>
+      </c>
+      <c r="D16" t="s">
+        <v>28</v>
+      </c>
+      <c r="E16" t="s">
+        <v>45</v>
+      </c>
+      <c r="F16" t="s">
+        <v>65</v>
+      </c>
+      <c r="G16" t="s">
+        <v>71</v>
+      </c>
+      <c r="H16" t="s">
+        <v>77</v>
+      </c>
+      <c r="I16">
+        <v>0.9993</v>
+      </c>
+      <c r="J16" t="s">
+        <v>92</v>
+      </c>
+      <c r="K16" t="s">
+        <v>98</v>
+      </c>
+      <c r="L16" t="s">
+        <v>101</v>
+      </c>
+      <c r="M16" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13">
+      <c r="A17" t="s">
+        <v>13</v>
+      </c>
+      <c r="B17" t="s">
+        <v>14</v>
+      </c>
+      <c r="C17" t="s">
+        <v>17</v>
+      </c>
+      <c r="D17" t="s">
+        <v>28</v>
+      </c>
+      <c r="E17" t="s">
+        <v>46</v>
+      </c>
+      <c r="F17" t="s">
+        <v>66</v>
+      </c>
+      <c r="G17" t="s">
+        <v>71</v>
+      </c>
+      <c r="H17" t="s">
+        <v>77</v>
+      </c>
+      <c r="I17">
+        <v>0.9994</v>
+      </c>
+      <c r="J17" t="s">
+        <v>93</v>
+      </c>
+      <c r="K17" t="s">
+        <v>98</v>
+      </c>
+      <c r="L17" t="s">
+        <v>99</v>
+      </c>
+      <c r="M17" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13">
+      <c r="A18" t="s">
+        <v>13</v>
+      </c>
+      <c r="B18" t="s">
+        <v>15</v>
+      </c>
+      <c r="C18" t="s">
+        <v>18</v>
+      </c>
+      <c r="D18" t="s">
+        <v>29</v>
+      </c>
+      <c r="E18" t="s">
+        <v>47</v>
+      </c>
+      <c r="F18" t="s">
+        <v>67</v>
+      </c>
+      <c r="G18" t="s">
+        <v>75</v>
+      </c>
+      <c r="H18" t="s">
+        <v>77</v>
+      </c>
+      <c r="I18">
+        <v>0.9994</v>
+      </c>
+      <c r="J18" t="s">
+        <v>94</v>
+      </c>
+      <c r="K18" t="s">
+        <v>98</v>
+      </c>
+      <c r="L18" t="s">
+        <v>98</v>
+      </c>
+      <c r="M18" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13">
+      <c r="A19" t="s">
+        <v>13</v>
+      </c>
+      <c r="B19" t="s">
+        <v>15</v>
+      </c>
+      <c r="C19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D19" t="s">
+        <v>29</v>
+      </c>
+      <c r="E19" t="s">
+        <v>48</v>
+      </c>
+      <c r="F19" t="s">
+        <v>68</v>
+      </c>
+      <c r="G19" t="s">
+        <v>75</v>
+      </c>
+      <c r="H19" t="s">
+        <v>77</v>
+      </c>
+      <c r="I19">
+        <v>0.9994</v>
+      </c>
+      <c r="J19" t="s">
+        <v>95</v>
+      </c>
+      <c r="K19" t="s">
+        <v>98</v>
+      </c>
+      <c r="L19" t="s">
+        <v>98</v>
+      </c>
+      <c r="M19" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13">
+      <c r="A20" t="s">
+        <v>13</v>
+      </c>
+      <c r="B20" t="s">
+        <v>14</v>
+      </c>
+      <c r="C20" t="s">
+        <v>16</v>
+      </c>
+      <c r="D20" t="s">
+        <v>30</v>
+      </c>
+      <c r="E20" t="s">
+        <v>49</v>
+      </c>
+      <c r="F20" t="s">
+        <v>69</v>
+      </c>
+      <c r="G20" t="s">
+        <v>76</v>
+      </c>
+      <c r="H20" t="s">
+        <v>77</v>
+      </c>
+      <c r="I20">
+        <v>0.9994</v>
+      </c>
+      <c r="J20" t="s">
+        <v>96</v>
+      </c>
+      <c r="K20" t="s">
+        <v>98</v>
+      </c>
+      <c r="L20" t="s">
+        <v>100</v>
+      </c>
+      <c r="M20" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13">
+      <c r="A21" t="s">
+        <v>13</v>
+      </c>
+      <c r="B21" t="s">
+        <v>14</v>
+      </c>
+      <c r="C21" t="s">
+        <v>16</v>
+      </c>
+      <c r="D21" t="s">
+        <v>30</v>
+      </c>
+      <c r="E21" t="s">
+        <v>50</v>
+      </c>
+      <c r="F21" t="s">
+        <v>70</v>
+      </c>
+      <c r="G21" t="s">
+        <v>76</v>
+      </c>
+      <c r="H21" t="s">
+        <v>77</v>
+      </c>
+      <c r="I21">
+        <v>0.9995000000000001</v>
+      </c>
+      <c r="J21" t="s">
+        <v>97</v>
+      </c>
+      <c r="K21" t="s">
+        <v>98</v>
+      </c>
+      <c r="L21" t="s">
+        <v>100</v>
+      </c>
+      <c r="M21" t="s">
+        <v>121</v>
       </c>
     </row>
   </sheetData>

--- a/output_orderan.xlsx
+++ b/output_orderan.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="176">
   <si>
     <t>UNIT_QTY</t>
   </si>
@@ -46,60 +46,994 @@
     <t>Original_Text</t>
   </si>
   <si>
+    <t>RO_DATE</t>
+  </si>
+  <si>
+    <t>LOAD_DATE</t>
+  </si>
+  <si>
     <t>PHONE</t>
   </si>
   <si>
-    <t>3</t>
+    <t>2</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>twb /</t>
   </si>
   <si>
     <t>cddl</t>
   </si>
   <si>
-    <t>cikokol</t>
-  </si>
-  <si>
-    <t>cgkjateng tentatif</t>
-  </si>
-  <si>
-    <t>dimas</t>
-  </si>
-  <si>
-    <t>h 9263 ov</t>
+    <t>twb</t>
+  </si>
+  <si>
+    <t>cddl twb</t>
+  </si>
+  <si>
+    <t>wb</t>
+  </si>
+  <si>
+    <t>cddl wb</t>
+  </si>
+  <si>
+    <t>argopantes</t>
+  </si>
+  <si>
+    <t>perak</t>
+  </si>
+  <si>
+    <t>jne sub</t>
+  </si>
+  <si>
+    <t>jne srg</t>
+  </si>
+  <si>
+    <t>cikokol + cikarang</t>
+  </si>
+  <si>
+    <t>megahub</t>
+  </si>
+  <si>
+    <t>cgk mes</t>
+  </si>
+  <si>
+    <t>cgk pku</t>
+  </si>
+  <si>
+    <t>cgk pdg</t>
+  </si>
+  <si>
+    <t>cgk upx (</t>
+  </si>
+  <si>
+    <t>cgxcgk</t>
+  </si>
+  <si>
+    <t>cgk upx ( perak )</t>
+  </si>
+  <si>
+    <t>cgk probolinggo</t>
+  </si>
+  <si>
+    <t>srgcgk</t>
+  </si>
+  <si>
+    <t>ckr</t>
+  </si>
+  <si>
+    <t>cgk pk</t>
+  </si>
+  <si>
+    <t>cgkjbr</t>
+  </si>
+  <si>
+    <t>cgk</t>
+  </si>
+  <si>
+    <t>cgk negara , mengwi , tabanan , denpasar ( dps ) , denpasar ( ami )</t>
+  </si>
+  <si>
+    <t>ckrsub</t>
+  </si>
+  <si>
+    <t>cgk sub</t>
+  </si>
+  <si>
+    <t>cgk malang</t>
+  </si>
+  <si>
+    <t>samosir</t>
+  </si>
+  <si>
+    <t>supriadi</t>
+  </si>
+  <si>
+    <t>m . rizki</t>
+  </si>
+  <si>
+    <t>sutrisno</t>
+  </si>
+  <si>
+    <t>ryan</t>
+  </si>
+  <si>
+    <t>sofyan</t>
+  </si>
+  <si>
+    <t>didik</t>
+  </si>
+  <si>
+    <t>sentot</t>
+  </si>
+  <si>
+    <t>arif r</t>
+  </si>
+  <si>
+    <t>sri mardono</t>
+  </si>
+  <si>
+    <t>fajri</t>
+  </si>
+  <si>
+    <t>arif</t>
+  </si>
+  <si>
+    <t>anto</t>
+  </si>
+  <si>
+    <t>syahrial</t>
+  </si>
+  <si>
+    <t>suyoto</t>
+  </si>
+  <si>
+    <t>nanah h</t>
+  </si>
+  <si>
+    <t>manalu</t>
+  </si>
+  <si>
+    <t>bahrul khilmi</t>
+  </si>
+  <si>
+    <t>aris</t>
+  </si>
+  <si>
+    <t>rizky / ariss</t>
+  </si>
+  <si>
+    <t>b 9727 uex</t>
+  </si>
+  <si>
+    <t>bk 8994 xh</t>
+  </si>
+  <si>
+    <t>bm 9156 ru</t>
+  </si>
+  <si>
+    <t>bm 8364 au</t>
+  </si>
+  <si>
+    <t>b 9083 veh</t>
+  </si>
+  <si>
+    <t>b 9679 wt</t>
+  </si>
+  <si>
+    <t>b 9687 jm</t>
+  </si>
+  <si>
+    <t>b 9231 ceu</t>
+  </si>
+  <si>
+    <t>b 9787 xx</t>
+  </si>
+  <si>
+    <t>bk 8678 ve</t>
+  </si>
+  <si>
+    <t>b 9241 fxs</t>
+  </si>
+  <si>
+    <t>b 9209 nck</t>
+  </si>
+  <si>
+    <t>b 9285 uex</t>
+  </si>
+  <si>
+    <t>bk 8215 hb</t>
+  </si>
+  <si>
+    <t>a 8579 zy</t>
+  </si>
+  <si>
+    <t>b 9658 tcp</t>
+  </si>
+  <si>
+    <t>b 9732 uex</t>
+  </si>
+  <si>
+    <t>b 9608 ep</t>
+  </si>
+  <si>
+    <t>l 9722 ue</t>
+  </si>
+  <si>
+    <t>b 9091 scj</t>
   </si>
   <si>
     <t>segera</t>
   </si>
   <si>
+    <t>23 : 00</t>
+  </si>
+  <si>
+    <t>22 : 00</t>
+  </si>
+  <si>
+    <t>02 : 00</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>03 : 00</t>
+  </si>
+  <si>
+    <t>08 : 00</t>
+  </si>
+  <si>
+    <t>18 : 00</t>
+  </si>
+  <si>
+    <t>20 : 00</t>
+  </si>
+  <si>
+    <t>05 : 00 240226</t>
+  </si>
+  <si>
+    <t>19 : 00</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>15 : 00</t>
+  </si>
+  <si>
     <t>NEW_ORDER</t>
   </si>
   <si>
-    <t>UPDATE</t>
-  </si>
-  <si>
-    <t>[WA_TS] Akbar Rafay: 3 UNIT CDDL 24 CBM
-Lokasi  : CIKOKOL</t>
-  </si>
-  <si>
-    <t>Waktu loading : SEGERA
-Rute/tujuan : CGK-JATENG TENTATIF
-driver :
-Nopol :
-No hp :</t>
-  </si>
-  <si>
-    <t>Waktu loading : SEGERA
-driver :
-Nopol :
-No hp :</t>
-  </si>
-  <si>
-    <t>Waktu loading : SEGERA
-driver :Dimas
-Nopol :H 9263 OV
-No hp :082217785226</t>
-  </si>
-  <si>
-    <t>082217785226</t>
+    <t>[WA_TS] Akbar Rafay: Request Unit On Call Tgl 01 Feb 26
+2 Unit TWB / 50 Cbm
+Lokasi : ARGOPANTES
+Waktu loading : SEGERA 01 Feb 26
+Rute/tujuan : CGK - MES
+driver : Samosir
+Nopol : B 9727 UEX
+No hp : 082274296236</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: Request Unit On Call Tgl 02 Feb 26
+5 Unit  CDDL
+Lokasi : ARGOPANTES
+Waktu loading : SEGERA 02 Feb 26
+Rute/tujuan : CGK - MES
+Nama : Supriadi
+Nopol : BK 8994 XH
+No hp : 082391500247</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: Request Unit On Call Tgl 03 Feb 26
+6 Unit TWB 50 Cbm
+Lokasi : ARGOPANTES
+Waktu loading : SEGERA 03 Feb 26
+Rute/tujuan : CGK - MES
+driver : Suhendi
+Nopol : L 8845 UT
+No hp : 082127937145
+Lokasi : ARGOPANTES
+Waktu loading : 23:00 03 Feb 26
+Rute/tujuan : CGK - PKU
+driver : M. Rizki
+Nopol : BM 9156 RU
+No hp : 083894294040</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: Request Unit On Call 04 FEBUARI 2026
+RAFAY
+4 UNIT CDDL/TWB
+Lokasi : ARGOPANTES
+Waktu loading : SEGERA 04 FEBUARI 2026
+Rute/tujuan : CGK - PDG
+driver  : Sutrisno
+Nopol  : BM 8364 AU
+No hp  :085353886066</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: Request Unit On Call Tgl 05 Feb 26
+4 Unit TWB 50 Cbm
+Lokasi : ARGOPANTES
+Waktu loading : SEGERA 05 Feb 26
+Rute/tujuan : CGK - MES
+driver   : Feri Irawan
+Nopol  : BK 8516 VV
+No hp  : 085219216210
+Waktu loading : 20:00 05 Feb 26
+Rute/tujuan : CGK - PKU
+driver   : Ryan
+Nopol  : B 9083 VEH
+No hp  : 087837496810
+Waktu loading : 22:00 05 Feb 26
+Rute/tujuan : CGK - UPX (PERAK)
+driver   : M. Ibnu
+Nopol  : L 9511 AL
+No hp  : 082191633212
+Waktu loading : 23:00 05 Feb 26
+Rute/tujuan : CGK - SUB
+driver   : Akiyat
+Nopol  : L 9722 UE
+No hp  : 081281122738</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: Request Unit On Call Tgl 06 febuary 2026
+2 unit twb 50 CBM
+Lokasi : JNE SUB
+Waktu loading : SEGERA 06 febuary 2026
+Rute/tujuan : SUB-CGK
+driver  : WAHYUDI
+Nopol  : N 9549 UA
+No hp  :085784422398
+REQUEST ORDER KHUSUS 07/02/2026
+Waktu loading : 02:00
+Rute/tujuan : CGX-CGK
+driver  : SOFYAN
+Nopol  : B 9679 WT
+No hp  : 082231837381</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: Request Unit On Call Tgl 06 febuary 2026
+RAFAY
+5 unit TWB 50 CBM
+Lokasi : ARGOPANTES
+REQUEST ORDER KHUSUS 07-02-2026
+Waktu loading : 07:00
+Rute/tujuan : CGK - SUX
+driver  : Chandra
+Nopol  : L 8601 UH
+No hp  : 085231681470
+Waktu loading : SEGERA 07-02-2026
+Rute/tujuan : CGK - UPX (PERAK)
+driver  : Didik
+Nopol  : B 9687 JM
+No hp  :085385220743
+Waktu loading : SEGERA 07-02-2026
+Rute/tujuan : CGK - SUX
+driver  : Hermanto
+Nopol  : S 8635 NJ
+No hp  :085194592825
+Waktu loading : SEGERA 07-02-2026
+Rute/tujuan : CGK - PKU
+driver  :
+Nopol  : 
+No hp  : 
+Waktu loading : SEGERA 07-02-2026
+Rute/tujuan : CGK - UPX (PERAK)
+driver  : 
+Nopol  : 
+No hp  :</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: Request Unit On Call Tgl 08 Feb 26
+4 UNIT TWB 50 CBM
+Lokasi : ARGOPANTES
+Waktu loading : SEGERA 08 Feb 26
+Rute/tujuan : CGK - MES
+driver  : Sentot
+Nopol  : B 9231 CEU
+No hp  :081287147789
+Waktu loading : 17:00 08 Feb 26
+Rute/tujuan : CGK - MES
+driver  : 
+Nopol  : 
+No hp  :
+Lokasi : CGK
+Waktu loading : SEGERA 08 Feb 26
+Rute/tujuan : CGK - PROBOLINGGO
+driver  : 
+Nopol  : 
+No hp  :
+Waktu loading : 23:00 08 Feb 26
+Rute/tujuan : CGK - PKU
+driver  : 
+Nopol  : 
+No hp  :</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: Request Unit On Call Tgl 09 Feb 26
+5 UNIT cddl
+Lokasi : JNE SRG
+Waktu loading : 22:00 09 Feb 26
+Rute/tujuan : SRG-CGK
+driver : Arif R
+Nopol : B 9787 XX
+No hp :089690885555</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: Request Unit On Call Tgl 11 Feb 26
+4 UNIT WB / CDDL
+Lokasi : MEGAHUB
+Waktu loading : SEGERA 11 Feb 26
+Rute/tujuan : CGK - NEGARA, MENGWI, TABANAN, DENPASAR (DPS), DENPASAR (AMI)
+driver  : Nizar
+Nopol  : B 9172 SCP
+No hp  : 082111994263
+Lokasi : ARGOPANTES
+Waktu loading : 23:00 11 Feb 26
+Rute/tujuan : CGK - MES
+driver  : Samosir
+Nopol  : B 9727 UEX
+No hp  : 082274296236
+REQUEST ORDER KHUSUS 12/02/2026
+Waktu loading : 01:00
+Rute/tujuan : CGK - MES
+driver  : Joni
+Nopol  : B 9169 UEX
+No hp  : 082276385077</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: Request Unit On Call Tgl 12 Feb 26
+5 UNIT CDDL
+Lokasi : ARGOPANTES
+Waktu loading : SEGERA 12 Feb 26
+Rute/tujuan : CGK - PKU
+driver  : Nasip K
+Nopol  : BH 8165 QI
+No hp  : 081272463920
+Waktu loading : SEGERA 12 Feb 26
+Rute/tujuan : CGK - MES
+driver  : Sri Mardono
+Nopol  : BK 8678 VE
+No hp  :085218843366
+Lokasi : Cikokol + Cikarang
+Waktu loading : 03:00 13-02-26
+Rute/tujuan : CKR-JBR
+driver   : Jatmiyanta
+Nopol  : F 9647 FH
+No hp  : 082118558105
+Lokasi : Cikokol
+Waktu loading : SEGERA 13-02-26
+Rute/tujuan : CGK - UPX (PERAK)
+driver  : AGENG
+Nopol  : B 9654 YU
+No hp  : +62 857-0738-0584
+Lokasi : ARGOPANTES
+Waktu loading : 22:00 13-02-26
+Rute/tujuan : CGK - SUB
+driver  : Rosyit
+Nopol  : B 9562 TEU
+No hp  : 082313572678</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: Request Unit On Call Tgl 13 Feb 26
+9 UNIT CDDL
+Lokasi : ARGOPANTES
+Waktu loading : 15:00 13 Feb 26
+Rute/tujuan : CGK - PKU
+driver  : HERMAN
+Nopol  : B 9718 TJ
+No hp  :087844510846
+Waktu loading : 18:00 13 Feb 26
+Rute/tujuan : CGK - PKU
+driver  : FAJRI
+Nopol  : B 9241 FXS
+No hp  :081382418508
+Waktu loading : 23:00 13 Feb 26
+Rute/tujuan : CGK - PKU
+driver  : ANDI
+Nopol  : BE 8794 AMB
+No hp  :082183783385
+REQUEST ORDER KHUSUS 14-02-2026
+Waktu loading : 02:00
+Rute/tujuan : CGK - PKU
+driver  : NOPRIANTO
+Nopol  : BE 8251 FOA
+No hp  :085758955627
+REQUEST ORDER KHUSUS 14-02-2026
+Waktu loading : 02:00
+Rute/tujuan : CGK - PKU
+driver  : MENGRI
+Nopol : BM 8279 AU
+No hp : 085364056583
+Waktu loading : 03:00 14-02-2026
+Rute/tujuan : CGK - DEMAK - PURWODADI
+driver  : Dimas
+Nopol : H 9263 OV
+No hp : 082217785226
+Waktu loading : SEGERA 14-02-2026
+Rute/tujuan : CGK - MES
+driver  : SIMARE
+Nopol  : BK 8639 FJ
+No hp  :081269345748
+Waktu loading : 22:00 14-02-2026
+Rute/tujuan : CGK - DENPASAR
+driver  : Nanang
+Nopol  : AB 8053 KA
+No hp  :08889693664
+Waktu loading : 23:30 14-02-2026
+Rute/tujuan : CGK - PDG
+driver  : Agung
+Nopol  : BK 8208 VY
+No hp  : 082385989323</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: Request Unit On Call Tgl 16 Feb 26
+1 Unit  Cddl / 24 Cbm
+Lokasi : Cikokol + Cikarang
+Waktu loading : 03:00 17-02-26
+Rute/tujuan : CGK-JBR
+driver   : Arif
+Nopol  :  B 9209 NCK
+No hp :081328851819</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: Request Unit On Call Tgl 17 Feb 26
+5 UNIT TWB / CDDL
+Lokasi : ARGOPANTES
+Waktu loading : SEGERA 17 Feb 26
+Rute/tujuan : CGK - PKU
+driver : Siswanto
+Nopol : B 9120 WXR
+No hp : 081943564062
+Waktu loading : 07:00 17 Feb 26
+Rute/tujuan : CGK - MES
+driver : Anto
+Nopol : B 9285 UEX
+No hp : 082377225563
+Waktu loading : 08:00 17 Feb 26
+Rute/tujuan : CGK - MES
+driver : Kudir
+Nopol : B 9380 UEX
+No hp : 081262189242
+Waktu loading : 09:00 17 Feb 26
+Rute/tujuan : CGK - PKU
+driver : Amri Suardi
+Nopol : BK 8209 VY
+No hp : 082137700645
+Lokasi : MEGAHUB
+Waktu loading : 10:00 17 Feb 26
+Rute/tujuan : CGK - MALANG
+driver : Sandjiwo
+Nopol : B 9147 SCJ
+No hp : 082119995004</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: Request Unit On Call Tgl 19 Feb 26
+6 UNIT TWB/50 CM
+Lokasi : ARGOPANTES
+Waktu loading : 17:00 19 Feb 26
+Rute/tujuan : CGK - MOJOKERTO
+driver  : Agus
+Nopol  : B 9546 KXX
+No hp  :082128909001
+Waktu loading : SEGERA 19 Feb 26
+Rute/tujuan : CGK - MES
+driver  : Feriandi
+Nopol  : BK 8215 HB
+No hp  :082397112740
+Waktu loading : 18:00 19 Feb 26
+Rute/tujuan : CGK - PKU
+driver  : Syahrial
+Nopol  : BM 8486 AU
+No hp  :081317708658
+Waktu loading : 19:00 19 Feb 26
+Rute/tujuan : CGK - SUX
+driver  : Yuda
+Nopol  : W 8973 UQ
+No hp  :089507296985
+Waktu loading : 20:00 19 Feb 26
+Rute/tujuan : CGK - SUX
+driver  : Wahyudi
+Nopol  : N 9549 UA
+No hp  :085784422398
+Lokasi : CIKARANG
+Waktu loading : 22:00 19 Feb 26
+Rute/tujuan : SUX - PROBOLINGGO
+driver  : Nana Hermawan &amp; Rizky
+Nopol  : B 9658 TCP
+No hp  :082261270165</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: Request Unit On Call Tgl 21 Feb 26
+7 UNIT WB 50 CBM
+Lokasi : ANGKEPOGLAR + ARGOPANTES
+Waktu loading : SEGERA 21 Feb 26
+Rute/tujuan : CGK - PKU
+driver  : Alpinasri
+Nopol  : BM 8743 AU
+No hp  : 082171880402
+Waktu loading : SEGERA 21 Feb 26
+Rute/tujuan : CGK - MES
+driver  : Suyoto
+Nopol  : A 8579 ZY
+No hp  : 081314527908
+Lokasi : ARGOPANTES
+Waktu loading : 20:00 21 Feb 26
+Rute/tujuan : CGK - MES
+driver  : Rio Irvan
+Nopol  : BE 8019 HI
+No hp  :082151440733
+Waktu loading : 21:00 21 Feb 26
+Rute/tujuan : CGK - MES
+driver  : Aritonang
+Nopol  : B 9756 UEU
+No hp  :082285091664
+Waktu loading : 23:00 21 Feb 26
+Rute/tujuan : CGK - MES
+driver  : Manulang
+Nopol  : BK 8965 XJ
+No hp  :081370769496
+REQUEST ORDER KHUSUS 22/02/2026
+Waktu loading : 01:00
+Rute/tujuan : CGK - MES
+driver  : Ambar
+Nopol  : B 9023 UEX
+No hp  :082139009145
+REQUEST ORDER KHUSUS 22/02/2026
+Waktu loading : 03:00
+Rute/tujuan : CGK - MES
+driver  : Didik Permadi
+Nopol  : BE 8235 UQ
+No hp  :082299440556</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: Request Unit On Call Tgl 23 Feb 26
+4 Unit  Cddl / 24 Cbm
+Lokasi : Cikokol + Cikarang
+Waktu loading : 03:00 24-02-26
+Rute/tujuan : CKR-JBR
+driver   : Nana Hermawan
+Nopol  : B 9658 TCP
+No hp  : 082261270165
+Lokasi : MEGAHUB
+Waktu loading : 05:00 24-02-26
+Rute/tujuan : CGK - NEGARA, MENGWI, TABANAN, DENPASAR (DPS), DENPASAR (AMI)
+driver   : Nanah H
+Nopol  : B 9658 TCP
+No hp  : 083180623289
+Lokasi : ARGOPANTES
+Waktu loading : 09:00 24-02-26
+Rute/tujuan : CGK - MALANG
+driver   : Tumilan, Jatmiyanta
+Nopol  : F 9647 FH
+No hp  : 082118558105
+Waktu loading : 11:00 24-02-26
+Rute/tujuan : CGK - MADIUN, JEMBER
+driver   : Agus
+Nopol  : B 9546 KXX
+No hp  : 082128909001</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: Request Unit On Call Tgl 25 Feb 26
+4 UNIT TWB / CDDL
+Lokasi : ARGOPANTES
+Waktu loading : SEGERA 25 Feb 26
+Rute/tujuan : CGK - PKU
+driver : Endra
+Nopol : L 8791 UK
+No hp : 081330790438
+Waktu loading : 17:00 25 Feb 26
+Rute/tujuan : CGK - MES
+driver : Manalu
+Nopol : B 9732 UEX
+No hp : 082228606115
+Lokasi : MEGAHUB
+Waktu loading : 19:00 25 Feb 26
+Rute/tujuan : CGK - NEGARA, MENGWI, TABANAN, DENPASAR (DPS), DENPASAR (AMI)
+driver : Arizal
+Nopol : B 9895 UXX
+No hp : 081229080317
+Lokasi : ARGOPANTES
+Waktu loading : 22:00 25 Feb 26
+Rute/tujuan : CGK - SUB
+driver : Wahyudi
+Nopol : N 9549 UA
+No hp : 085784422398</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: Request Unit On Call Tgl 26 Feb 26
+6 UNIT TWB / CDDL
+Lokasi : CIKARANG
+Waktu loading : 06:00 27-02-26
+Rute/tujuan : CKR-JBR
+driver : Davit
+Nopol : B 9726 SXW
+No hp :082117275166
+Lokasi : CIKARANG
+Waktu loading : SEGERA 27-02-26
+Rute/tujuan : CKR-SUB
+driver : Bahrul Khilmi
+Nopol : B 9608 EP
+No hp :081273004114
+Lokasi : ARGOPANTES
+Waktu loading : 15:00 27-02-26
+Rute/tujuan : CGK - SUX
+driver : Rosyit
+Nopol : B 9562 TEU
+No hp :082313572678
+Lokasi : MEGAHUB
+Waktu loading : 18:00 27-02-26
+Rute/tujuan : CGK - MALANG
+driver : Tumilan, Jatmiyanta
+Nopol : F 9647 FH
+No hp :082118558105
+Lokasi : ARGOPANTES
+Waktu loading : 20:00 27-02-26
+Rute/tujuan : CGK - PKU
+driver : Siswanto
+Nopol : B 9120 WXR
+No hp :081943564062
+Waktu loading : 23:00 27-02-26
+Rute/tujuan : CGK - MES
+driver : Hendra Setiawan
+Nopol : BE 8023 WY
+No hp :081280483919</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: Request Unit On Call Tgl 27 Feb 26
+9 UNIT WB
+Lokasi : SUX
+Waktu loading : SEGERA 27 Feb 26
+Rute/tujuan : CGX + CGK
+NAMA : HABIB
+Nopol : L 8336 UV
+No hp :081231540625
+Waktu loading : SEGERA 27 Feb 26
+Rute/tujuan : CGX, CGK
+NAMA : AKIYAT
+Nopol : L 9722 UE
+No hp :081281122738
+Lokasi : ARGOPANTES
+Waktu loading : 15:00 27 Feb 26
+Rute/tujuan : CGK - SUB
+NAMA : ARIS
+Nopol : B 9139 SYT
+No hp :081936963942
+Waktu loading : 18:00 27 Feb 26
+Rute/tujuan : CGK - SUX
+NAMA : MUATIM
+Nopol : H 9224 MA
+No hp :08121615206
+Waktu loading : 19:00 27 Feb 26
+Rute/tujuan : CGK - SUB
+NAMA : JAMAADI
+Nopol : L 8786 BN
+No hp :082229973792
+Waktu loading : 20:00 27 Feb 26
+Rute/tujuan : CGK - SDA
+NAMA : IBNU
+Nopol : L 9511 AL
+No hp :082191633212
+Lokasi : WANGONGATEWAY
+Waktu loading : 12:00 27 Feb 26
+Rute/tujuan : WGX-MGL-JOG
+Nama : Agung Prasetyo
+Nopol : B 9739 SEU
+No hp : 085726344824
+Lokasi : ARGOPANTES
+Waktu loading : 23:00 27 Feb 26
+Rute/tujuan : CGK - MES
+NAMA : Dian Saputra
+Nopol : BE 8334 GBA
+No hp : 08218218481</t>
+  </si>
+  <si>
+    <t>[WA_TS] Akbar Rafay: Request Unit On Call Tgl 28 Feb 26
+4 UNIT CDDL / WB
+Lokasi : MEGAHUB
+Waktu loading : SEGERA 28 Feb 26
+Rute/tujuan : CGK - PASURUAN, PROBOLINGGO, JEMBER
+driver : Agus Supriatna
+Nopol : B 9546 KXX
+No hp :082128909001
+Lokasi : MEGAHUB
+REQUEST ORDER KHUSUS 01/03/2026
+Waktu loading : 02:00
+Rute/tujuan : CGK - MALANG
+driver : Rizky / Ariss
+Nopol : B 9091 SCJ
+No hp :082229441113
+Lokasi : ARGOPANTES
+REQUEST ORDER KHUSUS 02/03/2026
+Waktu loading : 07:00
+Rute/tujuan : CGK - CGK
+driver : Rosyit
+Nopol : B 9562 TEU
+No hp :082313572678
+Lokasi : ARGOPANTES
+REQUEST ORDER KHUSUS 02/03/2026
+Waktu loading : 08:00
+Rute/tujuan : CGK - PML, PKL
+driver : Dedeng
+Nopol : E 9426 AA
+No hp :0895393659401</t>
+  </si>
+  <si>
+    <t>01 feb 26</t>
+  </si>
+  <si>
+    <t>02 feb 26</t>
+  </si>
+  <si>
+    <t>03 feb 26</t>
+  </si>
+  <si>
+    <t>04 febuari 2026</t>
+  </si>
+  <si>
+    <t>05 feb 26</t>
+  </si>
+  <si>
+    <t>06 febuary 2026</t>
+  </si>
+  <si>
+    <t>09 feb 26</t>
+  </si>
+  <si>
+    <t>11 feb 26</t>
+  </si>
+  <si>
+    <t>12 feb 26</t>
+  </si>
+  <si>
+    <t>13 feb 26</t>
+  </si>
+  <si>
+    <t>16 feb 26</t>
+  </si>
+  <si>
+    <t>17 feb 26</t>
+  </si>
+  <si>
+    <t>19 feb 26</t>
+  </si>
+  <si>
+    <t>21 feb 26</t>
+  </si>
+  <si>
+    <t>23 feb 26</t>
+  </si>
+  <si>
+    <t>25 feb 26</t>
+  </si>
+  <si>
+    <t>26 feb 26</t>
+  </si>
+  <si>
+    <t>27 feb 26</t>
+  </si>
+  <si>
+    <t>28 feb 26</t>
+  </si>
+  <si>
+    <t>01</t>
+  </si>
+  <si>
+    <t>02</t>
+  </si>
+  <si>
+    <t>03</t>
+  </si>
+  <si>
+    <t>05</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>082274296236</t>
+  </si>
+  <si>
+    <t>082391500247</t>
+  </si>
+  <si>
+    <t>083894294040</t>
+  </si>
+  <si>
+    <t>085353886066</t>
+  </si>
+  <si>
+    <t>087837496810</t>
+  </si>
+  <si>
+    <t>082231837381</t>
+  </si>
+  <si>
+    <t>085385220743</t>
+  </si>
+  <si>
+    <t>08</t>
+  </si>
+  <si>
+    <t>089690885555</t>
+  </si>
+  <si>
+    <t>08227429623</t>
+  </si>
+  <si>
+    <t>03 : 00 130226</t>
+  </si>
+  <si>
+    <t>081382418508</t>
+  </si>
+  <si>
+    <t>081328851819</t>
+  </si>
+  <si>
+    <t>082377225563</t>
+  </si>
+  <si>
+    <t>082397112740</t>
+  </si>
+  <si>
+    <t>081314527908</t>
+  </si>
+  <si>
+    <t>082261270165</t>
+  </si>
+  <si>
+    <t>082228606115</t>
+  </si>
+  <si>
+    <t>081273004114</t>
+  </si>
+  <si>
+    <t>081281122738</t>
+  </si>
+  <si>
+    <t>082229441113</t>
   </si>
 </sst>
 </file>
@@ -457,10 +1391,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:13">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -494,79 +1428,851 @@
       <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:13">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E2" t="s">
+        <v>48</v>
+      </c>
+      <c r="F2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G2" t="s">
+        <v>88</v>
+      </c>
+      <c r="H2" t="s">
+        <v>101</v>
+      </c>
+      <c r="I2">
+        <v>0.9996</v>
+      </c>
+      <c r="J2" t="s">
+        <v>102</v>
+      </c>
+      <c r="K2" t="s">
+        <v>123</v>
+      </c>
+      <c r="L2" t="s">
+        <v>142</v>
+      </c>
+      <c r="M2" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F3" t="s">
+        <v>69</v>
+      </c>
+      <c r="G3" t="s">
+        <v>88</v>
+      </c>
+      <c r="H3" t="s">
+        <v>101</v>
+      </c>
+      <c r="I3">
+        <v>0.9996</v>
+      </c>
+      <c r="J3" t="s">
+        <v>103</v>
+      </c>
+      <c r="K3" t="s">
+        <v>124</v>
+      </c>
+      <c r="L3" t="s">
+        <v>143</v>
+      </c>
+      <c r="M3" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E4" t="s">
+        <v>50</v>
+      </c>
+      <c r="F4" t="s">
+        <v>70</v>
+      </c>
+      <c r="G4" t="s">
+        <v>89</v>
+      </c>
+      <c r="H4" t="s">
+        <v>101</v>
+      </c>
+      <c r="I4">
+        <v>0.9997</v>
+      </c>
+      <c r="J4" t="s">
+        <v>104</v>
+      </c>
+      <c r="K4" t="s">
+        <v>125</v>
+      </c>
+      <c r="L4" t="s">
+        <v>144</v>
+      </c>
+      <c r="M4" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F5" t="s">
+        <v>71</v>
+      </c>
+      <c r="G5" t="s">
+        <v>88</v>
+      </c>
+      <c r="H5" t="s">
+        <v>101</v>
+      </c>
+      <c r="I5">
+        <v>0.9994</v>
+      </c>
+      <c r="J5" t="s">
+        <v>105</v>
+      </c>
+      <c r="K5" t="s">
+        <v>126</v>
+      </c>
+      <c r="L5" t="s">
+        <v>126</v>
+      </c>
+      <c r="M5" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E6" t="s">
+        <v>52</v>
+      </c>
+      <c r="F6" t="s">
+        <v>72</v>
+      </c>
+      <c r="G6" t="s">
+        <v>90</v>
+      </c>
+      <c r="H6" t="s">
+        <v>101</v>
+      </c>
+      <c r="I6">
+        <v>0.9993</v>
+      </c>
+      <c r="J6" t="s">
+        <v>106</v>
+      </c>
+      <c r="K6" t="s">
+        <v>127</v>
+      </c>
+      <c r="L6" t="s">
+        <v>145</v>
+      </c>
+      <c r="M6" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" t="s">
         <v>13</v>
       </c>
-      <c r="H2" t="s">
+      <c r="B7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" t="s">
+        <v>36</v>
+      </c>
+      <c r="E7" t="s">
+        <v>53</v>
+      </c>
+      <c r="F7" t="s">
+        <v>73</v>
+      </c>
+      <c r="G7" t="s">
+        <v>91</v>
+      </c>
+      <c r="H7" t="s">
+        <v>101</v>
+      </c>
+      <c r="I7">
+        <v>0.9997</v>
+      </c>
+      <c r="J7" t="s">
+        <v>107</v>
+      </c>
+      <c r="K7" t="s">
+        <v>128</v>
+      </c>
+      <c r="L7" t="s">
+        <v>128</v>
+      </c>
+      <c r="M7" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" t="s">
+        <v>37</v>
+      </c>
+      <c r="E8" t="s">
+        <v>54</v>
+      </c>
+      <c r="F8" t="s">
+        <v>74</v>
+      </c>
+      <c r="G8" t="s">
+        <v>88</v>
+      </c>
+      <c r="H8" t="s">
+        <v>101</v>
+      </c>
+      <c r="I8">
+        <v>0.9932</v>
+      </c>
+      <c r="J8" t="s">
+        <v>108</v>
+      </c>
+      <c r="K8" t="s">
+        <v>128</v>
+      </c>
+      <c r="M8" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" t="s">
+        <v>26</v>
+      </c>
+      <c r="D9" t="s">
+        <v>38</v>
+      </c>
+      <c r="E9" t="s">
+        <v>55</v>
+      </c>
+      <c r="F9" t="s">
+        <v>75</v>
+      </c>
+      <c r="G9" t="s">
+        <v>92</v>
+      </c>
+      <c r="H9" t="s">
+        <v>101</v>
+      </c>
+      <c r="I9">
+        <v>0.9996</v>
+      </c>
+      <c r="J9" t="s">
+        <v>109</v>
+      </c>
+      <c r="M9" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="A10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" t="s">
+        <v>29</v>
+      </c>
+      <c r="D10" t="s">
+        <v>39</v>
+      </c>
+      <c r="E10" t="s">
+        <v>56</v>
+      </c>
+      <c r="F10" t="s">
+        <v>76</v>
+      </c>
+      <c r="G10" t="s">
+        <v>90</v>
+      </c>
+      <c r="H10" t="s">
+        <v>101</v>
+      </c>
+      <c r="I10">
+        <v>0.9996</v>
+      </c>
+      <c r="J10" t="s">
+        <v>110</v>
+      </c>
+      <c r="K10" t="s">
+        <v>129</v>
+      </c>
+      <c r="L10" t="s">
+        <v>129</v>
+      </c>
+      <c r="M10" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
+      <c r="A11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" t="s">
+        <v>26</v>
+      </c>
+      <c r="D11" t="s">
+        <v>32</v>
+      </c>
+      <c r="E11" t="s">
+        <v>48</v>
+      </c>
+      <c r="F11" t="s">
+        <v>68</v>
+      </c>
+      <c r="G11" t="s">
+        <v>89</v>
+      </c>
+      <c r="H11" t="s">
+        <v>101</v>
+      </c>
+      <c r="I11">
+        <v>0.9987</v>
+      </c>
+      <c r="J11" t="s">
+        <v>111</v>
+      </c>
+      <c r="K11" t="s">
+        <v>130</v>
+      </c>
+      <c r="L11" t="s">
+        <v>146</v>
+      </c>
+      <c r="M11" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
+      <c r="A12" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" t="s">
+        <v>21</v>
+      </c>
+      <c r="C12" t="s">
+        <v>30</v>
+      </c>
+      <c r="D12" t="s">
+        <v>40</v>
+      </c>
+      <c r="E12" t="s">
+        <v>57</v>
+      </c>
+      <c r="F12" t="s">
+        <v>77</v>
+      </c>
+      <c r="G12" t="s">
+        <v>88</v>
+      </c>
+      <c r="H12" t="s">
+        <v>101</v>
+      </c>
+      <c r="I12">
+        <v>0.9994</v>
+      </c>
+      <c r="J12" t="s">
+        <v>112</v>
+      </c>
+      <c r="K12" t="s">
+        <v>131</v>
+      </c>
+      <c r="L12" t="s">
+        <v>147</v>
+      </c>
+      <c r="M12" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
+      <c r="A13" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13" t="s">
+        <v>21</v>
+      </c>
+      <c r="C13" t="s">
+        <v>26</v>
+      </c>
+      <c r="D13" t="s">
+        <v>41</v>
+      </c>
+      <c r="E13" t="s">
+        <v>58</v>
+      </c>
+      <c r="F13" t="s">
+        <v>78</v>
+      </c>
+      <c r="G13" t="s">
+        <v>89</v>
+      </c>
+      <c r="H13" t="s">
+        <v>101</v>
+      </c>
+      <c r="I13">
+        <v>0.9988</v>
+      </c>
+      <c r="J13" t="s">
+        <v>113</v>
+      </c>
+      <c r="K13" t="s">
+        <v>132</v>
+      </c>
+      <c r="L13" t="s">
+        <v>148</v>
+      </c>
+      <c r="M13" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13">
+      <c r="A14" t="s">
         <v>18</v>
       </c>
-      <c r="I2">
+      <c r="B14" t="s">
+        <v>21</v>
+      </c>
+      <c r="C14" t="s">
+        <v>30</v>
+      </c>
+      <c r="D14" t="s">
+        <v>42</v>
+      </c>
+      <c r="E14" t="s">
+        <v>59</v>
+      </c>
+      <c r="F14" t="s">
+        <v>79</v>
+      </c>
+      <c r="G14" t="s">
+        <v>93</v>
+      </c>
+      <c r="H14" t="s">
+        <v>101</v>
+      </c>
+      <c r="I14">
+        <v>0.9996</v>
+      </c>
+      <c r="J14" t="s">
+        <v>114</v>
+      </c>
+      <c r="K14" t="s">
+        <v>133</v>
+      </c>
+      <c r="M14" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13">
+      <c r="A15" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>21</v>
+      </c>
+      <c r="C15" t="s">
+        <v>26</v>
+      </c>
+      <c r="D15" t="s">
+        <v>43</v>
+      </c>
+      <c r="E15" t="s">
+        <v>60</v>
+      </c>
+      <c r="F15" t="s">
+        <v>80</v>
+      </c>
+      <c r="G15" t="s">
+        <v>94</v>
+      </c>
+      <c r="H15" t="s">
+        <v>101</v>
+      </c>
+      <c r="I15">
+        <v>0.9994</v>
+      </c>
+      <c r="J15" t="s">
+        <v>115</v>
+      </c>
+      <c r="K15" t="s">
+        <v>134</v>
+      </c>
+      <c r="L15" t="s">
+        <v>149</v>
+      </c>
+      <c r="M15" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13">
+      <c r="A16" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>22</v>
+      </c>
+      <c r="C16" t="s">
+        <v>26</v>
+      </c>
+      <c r="D16" t="s">
+        <v>33</v>
+      </c>
+      <c r="E16" t="s">
+        <v>61</v>
+      </c>
+      <c r="F16" t="s">
+        <v>81</v>
+      </c>
+      <c r="G16" t="s">
+        <v>95</v>
+      </c>
+      <c r="H16" t="s">
+        <v>101</v>
+      </c>
+      <c r="I16">
+        <v>0.9993</v>
+      </c>
+      <c r="J16" t="s">
+        <v>116</v>
+      </c>
+      <c r="K16" t="s">
+        <v>135</v>
+      </c>
+      <c r="L16" t="s">
+        <v>150</v>
+      </c>
+      <c r="M16" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13">
+      <c r="A17" t="s">
+        <v>19</v>
+      </c>
+      <c r="B17" t="s">
+        <v>24</v>
+      </c>
+      <c r="C17" t="s">
+        <v>26</v>
+      </c>
+      <c r="D17" t="s">
+        <v>32</v>
+      </c>
+      <c r="E17" t="s">
+        <v>62</v>
+      </c>
+      <c r="F17" t="s">
+        <v>82</v>
+      </c>
+      <c r="G17" t="s">
+        <v>96</v>
+      </c>
+      <c r="H17" t="s">
+        <v>101</v>
+      </c>
+      <c r="I17">
+        <v>0.9994</v>
+      </c>
+      <c r="J17" t="s">
+        <v>117</v>
+      </c>
+      <c r="K17" t="s">
+        <v>136</v>
+      </c>
+      <c r="L17" t="s">
+        <v>151</v>
+      </c>
+      <c r="M17" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13">
+      <c r="A18" t="s">
+        <v>16</v>
+      </c>
+      <c r="B18" t="s">
+        <v>21</v>
+      </c>
+      <c r="C18" t="s">
+        <v>31</v>
+      </c>
+      <c r="D18" t="s">
+        <v>44</v>
+      </c>
+      <c r="E18" t="s">
+        <v>63</v>
+      </c>
+      <c r="F18" t="s">
+        <v>83</v>
+      </c>
+      <c r="G18" t="s">
+        <v>97</v>
+      </c>
+      <c r="H18" t="s">
+        <v>101</v>
+      </c>
+      <c r="I18">
+        <v>0.9986</v>
+      </c>
+      <c r="J18" t="s">
+        <v>118</v>
+      </c>
+      <c r="K18" t="s">
+        <v>137</v>
+      </c>
+      <c r="M18" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13">
+      <c r="A19" t="s">
+        <v>16</v>
+      </c>
+      <c r="B19" t="s">
+        <v>21</v>
+      </c>
+      <c r="C19" t="s">
+        <v>31</v>
+      </c>
+      <c r="D19" t="s">
+        <v>32</v>
+      </c>
+      <c r="E19" t="s">
+        <v>64</v>
+      </c>
+      <c r="F19" t="s">
+        <v>84</v>
+      </c>
+      <c r="G19" t="s">
+        <v>98</v>
+      </c>
+      <c r="H19" t="s">
+        <v>101</v>
+      </c>
+      <c r="I19">
+        <v>0.9993</v>
+      </c>
+      <c r="J19" t="s">
+        <v>119</v>
+      </c>
+      <c r="K19" t="s">
+        <v>138</v>
+      </c>
+      <c r="L19" t="s">
+        <v>152</v>
+      </c>
+      <c r="M19" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13">
+      <c r="A20" t="s">
+        <v>15</v>
+      </c>
+      <c r="B20" t="s">
+        <v>21</v>
+      </c>
+      <c r="C20" t="s">
+        <v>26</v>
+      </c>
+      <c r="D20" t="s">
+        <v>45</v>
+      </c>
+      <c r="E20" t="s">
+        <v>65</v>
+      </c>
+      <c r="F20" t="s">
+        <v>85</v>
+      </c>
+      <c r="G20" t="s">
+        <v>99</v>
+      </c>
+      <c r="H20" t="s">
+        <v>101</v>
+      </c>
+      <c r="I20">
+        <v>0.9986</v>
+      </c>
+      <c r="J20" t="s">
+        <v>120</v>
+      </c>
+      <c r="K20" t="s">
+        <v>139</v>
+      </c>
+      <c r="M20" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13">
+      <c r="A21" t="s">
+        <v>17</v>
+      </c>
+      <c r="C21" t="s">
+        <v>26</v>
+      </c>
+      <c r="D21" t="s">
+        <v>46</v>
+      </c>
+      <c r="E21" t="s">
+        <v>66</v>
+      </c>
+      <c r="F21" t="s">
+        <v>86</v>
+      </c>
+      <c r="G21" t="s">
+        <v>100</v>
+      </c>
+      <c r="H21" t="s">
+        <v>101</v>
+      </c>
+      <c r="I21">
         <v>0.9995000000000001</v>
       </c>
-      <c r="J2" t="s">
-        <v>20</v>
+      <c r="J21" t="s">
+        <v>121</v>
+      </c>
+      <c r="K21" t="s">
+        <v>140</v>
+      </c>
+      <c r="L21" t="s">
+        <v>153</v>
+      </c>
+      <c r="M21" t="s">
+        <v>174</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
-      <c r="D3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H3" t="s">
-        <v>19</v>
-      </c>
-      <c r="I3">
-        <v>0.9386</v>
-      </c>
-      <c r="J3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
-      <c r="G4" t="s">
-        <v>17</v>
-      </c>
-      <c r="H4" t="s">
-        <v>19</v>
-      </c>
-      <c r="I4">
-        <v>0.9961</v>
-      </c>
-      <c r="J4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
-      <c r="E5" t="s">
-        <v>15</v>
-      </c>
-      <c r="F5" t="s">
+    <row r="22" spans="1:13">
+      <c r="A22" t="s">
         <v>16</v>
       </c>
-      <c r="G5" t="s">
-        <v>17</v>
-      </c>
-      <c r="H5" t="s">
-        <v>19</v>
-      </c>
-      <c r="I5">
-        <v>0.9993</v>
-      </c>
-      <c r="J5" t="s">
-        <v>23</v>
-      </c>
-      <c r="K5" t="s">
-        <v>24</v>
+      <c r="B22" t="s">
+        <v>25</v>
+      </c>
+      <c r="C22" t="s">
+        <v>31</v>
+      </c>
+      <c r="D22" t="s">
+        <v>47</v>
+      </c>
+      <c r="E22" t="s">
+        <v>67</v>
+      </c>
+      <c r="F22" t="s">
+        <v>87</v>
+      </c>
+      <c r="G22" t="s">
+        <v>91</v>
+      </c>
+      <c r="H22" t="s">
+        <v>101</v>
+      </c>
+      <c r="I22">
+        <v>0.9989</v>
+      </c>
+      <c r="J22" t="s">
+        <v>122</v>
+      </c>
+      <c r="K22" t="s">
+        <v>141</v>
+      </c>
+      <c r="L22" t="s">
+        <v>154</v>
+      </c>
+      <c r="M22" t="s">
+        <v>175</v>
       </c>
     </row>
   </sheetData>
